--- a/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
+++ b/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
@@ -13,8 +13,9 @@
     <sheet name="Reguladores" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Banco de capacitor" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Em Execução (Obras)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Discrepâncias" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Observacoes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="VERIFICAR (Obras)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Discrepâncias" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Observacoes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,7 +75,7 @@
       <color rgb="009C6500"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -106,6 +107,16 @@
         <fgColor rgb="00FFE39B"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -133,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -179,6 +190,36 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -188,6 +229,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -557,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -582,7 +629,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Custo para consertar, por projeto. Base: SS pendentes 79/58/59 + equipamentos das OBRAS (em execução). BC sem premissa de preço.</t>
+          <t>Custo para consertar, por projeto. Base: SS pendentes 79/58/59 + equipamentos das OBRAS (em execução). Em dúvida de peça =&gt; equipamento completo.</t>
         </is>
       </c>
     </row>
@@ -656,13 +703,13 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>2166366.05</v>
+        <v>2188151.77</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>592337.78</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>2758703.83</v>
+        <v>2780489.55</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>49</v>
@@ -743,13 +790,13 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3965217.02</v>
+        <v>3987002.739999999</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>1418008.56</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>5383225.58</v>
+        <v>5405011.3</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>64</v>
@@ -802,13 +849,13 @@
         <v>22</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>958253.6799999997</v>
+        <v>980039.3999999998</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>270873.88</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>1229127.56</v>
+        <v>1250913.28</v>
       </c>
     </row>
     <row r="15">
@@ -859,13 +906,13 @@
         <v>49</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>2166366.05</v>
+        <v>2188151.77</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>592337.78</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2758703.83</v>
+        <v>2780489.55</v>
       </c>
     </row>
     <row r="19">
@@ -905,16 +952,16 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>220012.52</v>
+        <v>186195.7</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>74871.24000000001</v>
+        <v>63854.3</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>294883.76</v>
+        <v>250050</v>
       </c>
     </row>
     <row r="22">
@@ -962,16 +1009,16 @@
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1132069.41</v>
+        <v>1187671.95</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>200387.44</v>
+        <v>211404.38</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>1332456.85</v>
+        <v>1399076.33</v>
       </c>
     </row>
     <row r="25">
@@ -1022,13 +1069,13 @@
         <v>49</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>2166366.05</v>
+        <v>2188151.77</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>592337.7799999999</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>2758703.83</v>
+        <v>2780489.549999999</v>
       </c>
     </row>
     <row r="29">
@@ -1351,7 +1398,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
@@ -1381,26 +1428,40 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>• Equipamentos das OBRAS fora da base de pendentes foram INCLUÍDOS no orçamento como em execução.</t>
+          <t>• Modelo e faixa de tensão: SEMPRE da planilha de Ajustes (religadores e reguladores).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>• Reaproveitamentos (7903112004, 7933726256, 5800438116) entram com material R$ 0 ou só controle.</t>
+          <t>• SS duplicadas: adotada a mais recente pelo ano; mesmo ano =&gt; a mais detalhada/mais recente (nº anterior citado na Observação).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>• Banco de capacitor: sem premissa de preço — detalhe na aba própria (49 células identificadas).</t>
+          <t>• Em dúvida sobre a peça (deslocamentos e afins) =&gt; EQUIPAMENTO COMPLETO, com destaque na coluna Observação.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>• Linhas VERMELHAS: discussão com Matheus Alves (status inalterado). Linhas AMARELAS: avaliação — ver aba 'VERIFICAR (Obras)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>• Banco de capacitor: sem premissa de preço — detalhe na aba própria (49 células identificadas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>• MO: religador 11.016,94/13.209,34; regulador 51.402,14/80.318,50 (só controle de RT =&gt; MO 0).</t>
         </is>
@@ -1981,22 +2042,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2006,6 +2068,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vermelho: discussão com Matheus Alves (status inalterado). Amarelo: avaliar — ver aba 'VERIFICAR (Obras)'.</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2024,52 +2093,57 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
+          <t>Modelo (Ajustes)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
           <t>Tensão (kV)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Categoria de Compra</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Item a Comprar</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Custo Material</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Custo Mão de Obra</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Observação</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Custo Total (Mat+MO)</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>OBRA</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Confiança</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>Observações</t>
         </is>
       </c>
     </row>
@@ -2091,46 +2165,51 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>Controle completo + cabo BT</t>
         </is>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="H4" s="18" t="n">
         <v>38094.72</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="I4" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>Obras: 'Controle e ajuste' — aguardando entrega (EMD 510216)</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="n">
         <v>51304.06</v>
       </c>
-      <c r="J4" s="20" t="inlineStr">
+      <c r="L4" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K4" s="16" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>0212600428</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M4" s="17" t="inlineStr">
-        <is>
-          <t>Obras: 'Controle e ajuste' — aguardando entrega (EMD 510216)</t>
         </is>
       </c>
     </row>
@@ -2152,46 +2231,51 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>Tanque + cordão umbilical</t>
         </is>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="H5" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="I5" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>Obras: SS sem número (é esta 00050/2026) e Requisitar=Não — 'João verificar'</t>
+        </is>
+      </c>
+      <c r="K5" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K5" s="16" t="inlineStr">
+      <c r="M5" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="22" t="inlineStr">
+      <c r="N5" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M5" s="17" t="inlineStr">
-        <is>
-          <t>Obras: SS sem número e 'Requisitar: Não' (João verificar)</t>
         </is>
       </c>
     </row>
@@ -2213,46 +2297,51 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Placa =&gt; tratada como Controle completo</t>
         </is>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="H6" s="18" t="n">
         <v>38094.72</v>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="I6" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>Premissa do usuário: placa = controle. COEP avalia placa do estoque (5 un., cód 647641, R$ 1.999)</t>
+        </is>
+      </c>
+      <c r="K6" s="19" t="n">
         <v>51304.06</v>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K6" s="16" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="N6" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M6" s="17" t="inlineStr">
-        <is>
-          <t>Premissa do usuário: placa = controle. COEP avalia placa do estoque (5 un., cód 647641, R$ 1.999)</t>
         </is>
       </c>
     </row>
@@ -2274,46 +2363,51 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="H7" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="I7" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>Selecionado para compra</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="L7" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M7" s="17" t="inlineStr">
-        <is>
-          <t>Selecionado para compra</t>
         </is>
       </c>
     </row>
@@ -2335,46 +2429,51 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="H8" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="I8" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>COEP pediu modelo e faixa de tensão — Ajustes: NOJA RC10 / 34,5</t>
+        </is>
+      </c>
+      <c r="K8" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="L8" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="M8" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L8" s="22" t="inlineStr">
+      <c r="N8" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M8" s="17" t="inlineStr">
-        <is>
-          <t>COEP pediu modelo e faixa de tensão</t>
         </is>
       </c>
     </row>
@@ -2396,46 +2495,51 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="H9" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="I9" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K9" s="16" t="inlineStr">
+      <c r="M9" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -2457,46 +2561,51 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>Tanque + rádio GE</t>
         </is>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="H10" s="18" t="n">
         <v>36397.8</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="I10" s="18" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>Rádio queimado somado (R$ 14.612,08)</t>
+        </is>
+      </c>
+      <c r="K10" s="19" t="n">
         <v>47414.74000000001</v>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="L10" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K10" s="16" t="inlineStr">
+      <c r="M10" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="inlineStr">
-        <is>
-          <t>Rádio queimado somado (R$ 14.612,08)</t>
         </is>
       </c>
     </row>
@@ -2518,46 +2627,51 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Sem compra</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Trafo auxiliar — direto com COCM</t>
         </is>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>COEP: não há compra de equipamento especial</t>
+        </is>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t>Sem compra (COCM/definir)</t>
         </is>
       </c>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="M11" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L11" s="21" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="inlineStr">
-        <is>
-          <t>COEP: não há compra de equipamento especial</t>
         </is>
       </c>
     </row>
@@ -2579,46 +2693,51 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="H12" s="18" t="n">
         <v>38094.72</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="I12" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>Obras: problema no envio (controle NOJA por falta de modelo na SS); SS 00068/2026 (v1.5) é duplicata — adotada a mais recente</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="n">
         <v>51304.06</v>
       </c>
-      <c r="J12" s="20" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K12" s="16" t="inlineStr">
+      <c r="M12" s="16" t="inlineStr">
         <is>
           <t>0612600565</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="inlineStr">
-        <is>
-          <t>Obras: problema no envio (controle NOJA por falta de modelo na SS)</t>
         </is>
       </c>
     </row>
@@ -2640,46 +2759,51 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Religador completo (tanque+módulo+relé)</t>
         </is>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>76246.2</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="I13" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t>SS 00162/2025 (v1.5) é duplicata — adotada a mais recente (00123/2026)</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K13" s="16" t="inlineStr">
+      <c r="M13" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L13" s="22" t="inlineStr">
+      <c r="N13" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="inlineStr">
-        <is>
-          <t>COEP questiona modelo/faixa; v1.5 tratou na SS 00162/2025</t>
         </is>
       </c>
     </row>
@@ -2701,46 +2825,51 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="H14" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="I14" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I14" s="19" t="n">
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>SS 00139/2025 (v1.5) é duplicata — adotada a mais recente</t>
+        </is>
+      </c>
+      <c r="K14" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="L14" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K14" s="16" t="inlineStr">
+      <c r="M14" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -2762,46 +2891,51 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>Tanque + isoladores</t>
         </is>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="H15" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="I15" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>Isoladores/fonte sem premissa</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="L15" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K15" s="16" t="inlineStr">
+      <c r="M15" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="21" t="inlineStr">
+      <c r="N15" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="inlineStr">
-        <is>
-          <t>Isoladores/fonte sem premissa</t>
         </is>
       </c>
     </row>
@@ -2823,46 +2957,51 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
+          <t>TAVRIDA</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>Religador completo (Tavrida s/ sobressalente)</t>
         </is>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="H16" s="18" t="n">
         <v>76246.2</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="I16" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>Confirmar se só placa (=&gt; controle) ou completo</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="L16" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K16" s="16" t="inlineStr">
+      <c r="M16" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L16" s="22" t="inlineStr">
+      <c r="N16" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr">
-        <is>
-          <t>Confirmar se só placa (=&gt; controle) ou completo</t>
         </is>
       </c>
     </row>
@@ -2884,46 +3023,51 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="H17" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H17" s="18" t="n">
+      <c r="I17" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I17" s="19" t="n">
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="L17" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K17" s="16" t="inlineStr">
+      <c r="M17" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L17" s="21" t="inlineStr">
+      <c r="N17" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -2945,46 +3089,51 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>Tanque + trafo (trafo s/ premissa)</t>
         </is>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="H18" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H18" s="18" t="n">
+      <c r="I18" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I18" s="19" t="n">
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="L18" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K18" s="16" t="inlineStr">
+      <c r="M18" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L18" s="21" t="inlineStr">
+      <c r="N18" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M18" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -3006,46 +3155,51 @@
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="H19" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H19" s="18" t="n">
+      <c r="I19" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I19" s="19" t="n">
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>SS 00039/2026 (v1.5) é quase sequencial — adotada a mais detalhada (00078/2026)</t>
+        </is>
+      </c>
+      <c r="K19" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="L19" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K19" s="16" t="inlineStr">
+      <c r="M19" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L19" s="21" t="inlineStr">
+      <c r="N19" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M19" s="17" t="inlineStr">
-        <is>
-          <t>v1.5 tratou na SS 00039/2026 (mesmo ativo)</t>
         </is>
       </c>
     </row>
@@ -3067,46 +3221,51 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="H20" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H20" s="18" t="n">
+      <c r="I20" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I20" s="19" t="n">
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>Aguardando retorno DMSL</t>
+        </is>
+      </c>
+      <c r="K20" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="L20" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K20" s="16" t="inlineStr">
+      <c r="M20" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L20" s="22" t="inlineStr">
+      <c r="N20" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M20" s="17" t="inlineStr">
-        <is>
-          <t>Aguardando retorno DMSL</t>
         </is>
       </c>
     </row>
@@ -3128,46 +3287,51 @@
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>Tanque + cabo umbilical</t>
         </is>
       </c>
-      <c r="G21" s="18" t="n">
+      <c r="H21" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="I21" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I21" s="19" t="n">
+      <c r="J21" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="L21" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K21" s="16" t="inlineStr">
+      <c r="M21" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L21" s="21" t="inlineStr">
+      <c r="N21" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M21" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -3189,46 +3353,51 @@
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G22" s="18" t="n">
+      <c r="H22" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H22" s="18" t="n">
+      <c r="I22" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I22" s="19" t="n">
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="L22" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K22" s="16" t="inlineStr">
+      <c r="M22" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L22" s="21" t="inlineStr">
+      <c r="N22" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M22" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -3250,46 +3419,51 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G23" s="18" t="n">
+      <c r="H23" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H23" s="18" t="n">
+      <c r="I23" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I23" s="19" t="n">
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>Obras: aguardando entrega (EMD 511540, prev. 06/07)</t>
+        </is>
+      </c>
+      <c r="K23" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J23" s="20" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K23" s="16" t="inlineStr">
+      <c r="M23" s="16" t="inlineStr">
         <is>
           <t>0412600392</t>
         </is>
       </c>
-      <c r="L23" s="21" t="inlineStr">
+      <c r="N23" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M23" s="17" t="inlineStr">
-        <is>
-          <t>Obras: aguardando entrega (EMD 511540, prev. 06/07)</t>
         </is>
       </c>
     </row>
@@ -3311,46 +3485,51 @@
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="G24" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G24" s="18" t="n">
+      <c r="H24" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H24" s="18" t="n">
+      <c r="I24" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I24" s="19" t="n">
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>Sem parecer técnico do DMSL</t>
+        </is>
+      </c>
+      <c r="K24" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="L24" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K24" s="16" t="inlineStr">
+      <c r="M24" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L24" s="22" t="inlineStr">
+      <c r="N24" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M24" s="17" t="inlineStr">
-        <is>
-          <t>Sem parecer técnico do DMSL</t>
         </is>
       </c>
     </row>
@@ -3372,46 +3551,51 @@
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
+          <t>ARTECHE P500</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>Relé</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="G25" s="17" t="inlineStr">
         <is>
           <t>Relé prot. 50/51</t>
         </is>
       </c>
-      <c r="G25" s="18" t="n">
+      <c r="H25" s="18" t="n">
         <v>10454.01</v>
       </c>
-      <c r="H25" s="18" t="n">
+      <c r="I25" s="18" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I25" s="19" t="n">
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>Modelo em campo ARTECHE P500 — confirmar compatibilidade; SS 00057/2026 (v1.5) é duplicata — adotada a mais recente</t>
+        </is>
+      </c>
+      <c r="K25" s="19" t="n">
         <v>21470.95</v>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="L25" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K25" s="16" t="inlineStr">
+      <c r="M25" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L25" s="22" t="inlineStr">
+      <c r="N25" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M25" s="17" t="inlineStr">
-        <is>
-          <t>Modelo em campo ARTECHE P500 — confirmar compatibilidade</t>
         </is>
       </c>
     </row>
@@ -3433,46 +3617,51 @@
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
+          <t>SCHNEIDER ADVC</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="G26" s="17" t="inlineStr">
         <is>
           <t>Religador completo (→NOJA) + chave faca fase A</t>
         </is>
       </c>
-      <c r="G26" s="18" t="n">
+      <c r="H26" s="18" t="n">
         <v>76982.62999999999</v>
       </c>
-      <c r="H26" s="18" t="n">
+      <c r="I26" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I26" s="19" t="n">
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="19" t="n">
         <v>90191.96999999999</v>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="L26" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K26" s="16" t="inlineStr">
+      <c r="M26" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L26" s="21" t="inlineStr">
+      <c r="N26" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -3494,46 +3683,51 @@
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>Religador completo (placa+parte ativa)</t>
         </is>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="H27" s="18" t="n">
         <v>76246.2</v>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="I27" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I27" s="19" t="n">
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>Modelo COOPER F6 — completo confirmado</t>
+        </is>
+      </c>
+      <c r="K27" s="19" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="L27" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K27" s="16" t="inlineStr">
+      <c r="M27" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L27" s="21" t="inlineStr">
+      <c r="N27" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M27" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -3555,46 +3749,51 @@
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>Tanque + chave entrada fase B</t>
         </is>
       </c>
-      <c r="G28" s="18" t="n">
+      <c r="H28" s="18" t="n">
         <v>22522.15</v>
       </c>
-      <c r="H28" s="18" t="n">
+      <c r="I28" s="18" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I28" s="19" t="n">
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>Premissa da chave é 36,2kV — validar item 13,8</t>
+        </is>
+      </c>
+      <c r="K28" s="19" t="n">
         <v>33539.09</v>
       </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="L28" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K28" s="16" t="inlineStr">
+      <c r="M28" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L28" s="21" t="inlineStr">
+      <c r="N28" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>Premissa da chave é 36,2kV — validar item 13,8</t>
         </is>
       </c>
     </row>
@@ -3616,46 +3815,51 @@
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="F29" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>Tanque (não substituir controle)</t>
         </is>
       </c>
-      <c r="G29" s="18" t="n">
+      <c r="H29" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H29" s="18" t="n">
+      <c r="I29" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I29" s="19" t="n">
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>Obras cita SS 00174/2024 — adotada a mais recente (00086/2026); EMD 510210, prev. 06/07</t>
+        </is>
+      </c>
+      <c r="K29" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J29" s="20" t="inlineStr">
+      <c r="L29" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K29" s="16" t="inlineStr">
+      <c r="M29" s="16" t="inlineStr">
         <is>
           <t>0212600425</t>
         </is>
       </c>
-      <c r="L29" s="21" t="inlineStr">
+      <c r="N29" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>Obras: SS citada como 00174/2024 — aguardando entrega (EMD 510210)</t>
         </is>
       </c>
     </row>
@@ -3677,46 +3881,51 @@
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>Religador completo (parte ativa+controle)</t>
         </is>
       </c>
-      <c r="G30" s="18" t="n">
+      <c r="H30" s="18" t="n">
         <v>76246.2</v>
       </c>
-      <c r="H30" s="18" t="n">
+      <c r="I30" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I30" s="19" t="n">
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>Rádio e relé retirados serão reaproveitados</t>
+        </is>
+      </c>
+      <c r="K30" s="19" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="L30" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K30" s="16" t="inlineStr">
+      <c r="M30" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L30" s="21" t="inlineStr">
+      <c r="N30" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>Rádio e relé retirados serão reaproveitados</t>
         </is>
       </c>
     </row>
@@ -3738,46 +3947,51 @@
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="F31" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="G31" s="17" t="inlineStr">
         <is>
           <t>Religador completo (tanque+controle)</t>
         </is>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="H31" s="18" t="n">
         <v>55602.54</v>
       </c>
-      <c r="H31" s="18" t="n">
+      <c r="I31" s="18" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I31" s="19" t="n">
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>Cooper remanejado de obra; SS 00168/2025 (v1.5) é duplicata — adotada a mais recente</t>
+        </is>
+      </c>
+      <c r="K31" s="19" t="n">
         <v>66619.48</v>
       </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="L31" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K31" s="16" t="inlineStr">
+      <c r="M31" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L31" s="21" t="inlineStr">
+      <c r="N31" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M31" s="17" t="inlineStr">
-        <is>
-          <t>Cooper remanejado de obra; v1.5 tratou na SS 00168/2025</t>
         </is>
       </c>
     </row>
@@ -3799,46 +4013,51 @@
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>Controle NOJA (tanque cooper reaproveitado do 7900018004)</t>
         </is>
       </c>
-      <c r="G32" s="18" t="n">
+      <c r="H32" s="18" t="n">
         <v>38094.72</v>
       </c>
-      <c r="H32" s="18" t="n">
+      <c r="I32" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I32" s="19" t="n">
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>OBRAS: 'Aproveitar tanque do 7900018004' + 'falta enviar controle NOJA' — custo cai de completo p/ controle</t>
+        </is>
+      </c>
+      <c r="K32" s="19" t="n">
         <v>51304.06</v>
       </c>
-      <c r="J32" s="20" t="inlineStr">
+      <c r="L32" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K32" s="16" t="inlineStr">
+      <c r="M32" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L32" s="22" t="inlineStr">
+      <c r="N32" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M32" s="17" t="inlineStr">
-        <is>
-          <t>OBRAS: 'Aproveitar tanque do 7900018004' + 'falta enviar controle NOJA' — custo cai de completo p/ controle</t>
         </is>
       </c>
     </row>
@@ -3860,46 +4079,51 @@
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G33" s="18" t="n">
+      <c r="H33" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H33" s="18" t="n">
+      <c r="I33" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I33" s="19" t="n">
+      <c r="J33" s="17" t="inlineStr">
+        <is>
+          <t>Levar fonte (removida)</t>
+        </is>
+      </c>
+      <c r="K33" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="L33" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K33" s="16" t="inlineStr">
+      <c r="M33" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L33" s="21" t="inlineStr">
+      <c r="N33" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M33" s="17" t="inlineStr">
-        <is>
-          <t>Levar fonte (removida)</t>
         </is>
       </c>
     </row>
@@ -3921,46 +4145,51 @@
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>Religador completo (nota antiga 210/2025)</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="n">
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>Religador completo (COOPER F6)</t>
+        </is>
+      </c>
+      <c r="H34" s="18" t="n">
         <v>76246.2</v>
       </c>
-      <c r="H34" s="18" t="n">
+      <c r="I34" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I34" s="19" t="n">
+      <c r="J34" s="17" t="inlineStr">
+        <is>
+          <t>EM DÚVIDA (obras: 'Deslocamento COCM', Requisitar=Não) =&gt; mantido EQUIPAMENTO COMPLETO por padrão do gestor</t>
+        </is>
+      </c>
+      <c r="K34" s="19" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="J34" s="20" t="inlineStr">
+      <c r="L34" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K34" s="16" t="inlineStr">
+      <c r="M34" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L34" s="22" t="inlineStr">
+      <c r="N34" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M34" s="17" t="inlineStr">
-        <is>
-          <t>OBRAS: 'Deslocamento COCM', Requisitar=Não — confirmar escopo antes da compra</t>
         </is>
       </c>
     </row>
@@ -3982,46 +4211,51 @@
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="F35" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="G35" s="17" t="inlineStr">
         <is>
           <t>Religador completo (→NOJA RC10)</t>
         </is>
       </c>
-      <c r="G35" s="18" t="n">
+      <c r="H35" s="18" t="n">
         <v>55602.54</v>
       </c>
-      <c r="H35" s="18" t="n">
+      <c r="I35" s="18" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I35" s="19" t="n">
+      <c r="J35" s="17" t="inlineStr">
+        <is>
+          <t>Obras cita SS 00209/2025 — adotada a mais recente (00080/2026); EMD 511539/511541</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="n">
         <v>66619.48</v>
       </c>
-      <c r="J35" s="20" t="inlineStr">
+      <c r="L35" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K35" s="16" t="inlineStr">
+      <c r="M35" s="16" t="inlineStr">
         <is>
           <t>0412600391</t>
         </is>
       </c>
-      <c r="L35" s="21" t="inlineStr">
+      <c r="N35" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>Obras: SS citada como 00209/2025 — aguardando entrega (EMD 511539/511541)</t>
         </is>
       </c>
     </row>
@@ -4043,46 +4277,51 @@
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="F36" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr">
         <is>
           <t>Religador completo (Cooper→NOJA RC10)</t>
         </is>
       </c>
-      <c r="G36" s="18" t="n">
+      <c r="H36" s="18" t="n">
         <v>76246.2</v>
       </c>
-      <c r="H36" s="18" t="n">
+      <c r="I36" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I36" s="19" t="n">
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="19" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="L36" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K36" s="16" t="inlineStr">
+      <c r="M36" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L36" s="21" t="inlineStr">
+      <c r="N36" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -4104,46 +4343,51 @@
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
+          <t>(sem cadastro nos Ajustes)</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="F37" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>Religador completo + rádio GE</t>
         </is>
       </c>
-      <c r="G37" s="18" t="n">
+      <c r="H37" s="18" t="n">
         <v>90858.28</v>
       </c>
-      <c r="H37" s="18" t="n">
+      <c r="I37" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I37" s="19" t="n">
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>Ativo fora da planilha de Ajustes (modelo/tensão a cadastrar) — tensão via ETO 30</t>
+        </is>
+      </c>
+      <c r="K37" s="19" t="n">
         <v>104067.62</v>
       </c>
-      <c r="J37" s="16" t="inlineStr">
+      <c r="L37" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="K37" s="16" t="inlineStr">
+      <c r="M37" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L37" s="22" t="inlineStr">
+      <c r="N37" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>Tensão via ETO 30 (ativo fora das bases de ajustes)</t>
         </is>
       </c>
     </row>
@@ -4165,46 +4409,51 @@
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr">
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>Sem compra</t>
         </is>
       </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Buchas — aguardando definição (COCM?)</t>
         </is>
-      </c>
-      <c r="G38" s="18" t="n">
-        <v>0</v>
       </c>
       <c r="H38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="19" t="n">
+      <c r="I38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="16" t="inlineStr">
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t>Se for só bucha, escopo é COCM</t>
+        </is>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="16" t="inlineStr">
         <is>
           <t>Sem compra (COCM/definir)</t>
         </is>
       </c>
-      <c r="K38" s="16" t="inlineStr">
+      <c r="M38" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L38" s="22" t="inlineStr">
+      <c r="N38" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M38" s="17" t="inlineStr">
-        <is>
-          <t>Se for só bucha, escopo é COCM</t>
         </is>
       </c>
     </row>
@@ -4226,46 +4475,51 @@
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="F39" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F39" s="17" t="inlineStr">
+      <c r="G39" s="17" t="inlineStr">
         <is>
           <t>Religador completo</t>
         </is>
       </c>
-      <c r="G39" s="18" t="n">
+      <c r="H39" s="18" t="n">
         <v>76246.2</v>
       </c>
-      <c r="H39" s="18" t="n">
+      <c r="I39" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I39" s="19" t="n">
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t>OBRAS (SS 00169/2025 — adotada a mais recente 00087/2026): equipamento entregue e REDIRECIONADO p/ 7933726256 — reavaliar custo desta SS</t>
+        </is>
+      </c>
+      <c r="K39" s="19" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="J39" s="20" t="inlineStr">
+      <c r="L39" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K39" s="16" t="inlineStr">
+      <c r="M39" s="16" t="inlineStr">
         <is>
           <t>0312600264</t>
         </is>
       </c>
-      <c r="L39" s="22" t="inlineStr">
+      <c r="N39" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M39" s="17" t="inlineStr">
-        <is>
-          <t>OBRAS (SS 00169/2025): equipamento entregue e REDIRECIONADO p/ 7933726256 — reavaliar custo desta SS</t>
         </is>
       </c>
     </row>
@@ -4287,46 +4541,51 @@
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr">
+      <c r="F40" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F40" s="17" t="inlineStr">
+      <c r="G40" s="17" t="inlineStr">
         <is>
           <t>Religador completo (Cooper F6→NOJA)</t>
         </is>
       </c>
-      <c r="G40" s="18" t="n">
+      <c r="H40" s="18" t="n">
         <v>55602.54</v>
       </c>
-      <c r="H40" s="18" t="n">
+      <c r="I40" s="18" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I40" s="19" t="n">
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t>Obras cita SS 00122/2025 — adotada a mais recente (00084/2026); EMD 510217, prev. 15/07</t>
+        </is>
+      </c>
+      <c r="K40" s="19" t="n">
         <v>66619.48</v>
       </c>
-      <c r="J40" s="20" t="inlineStr">
+      <c r="L40" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K40" s="16" t="inlineStr">
+      <c r="M40" s="16" t="inlineStr">
         <is>
           <t>0212600422</t>
         </is>
       </c>
-      <c r="L40" s="21" t="inlineStr">
+      <c r="N40" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M40" s="17" t="inlineStr">
-        <is>
-          <t>Obras: SS citada como 00122/2025 — aguardando entrega (EMD 510217, prev. 15/07)</t>
         </is>
       </c>
     </row>
@@ -4348,53 +4607,58 @@
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="F41" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F41" s="17" t="inlineStr">
+      <c r="G41" s="17" t="inlineStr">
         <is>
           <t>Religador completo</t>
         </is>
       </c>
-      <c r="G41" s="18" t="n">
+      <c r="H41" s="18" t="n">
         <v>55602.54</v>
       </c>
-      <c r="H41" s="18" t="n">
+      <c r="I41" s="18" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I41" s="19" t="n">
+      <c r="J41" s="17" t="inlineStr">
+        <is>
+          <t>Fora da base de pendentes; EMD 511536, prev. 15/07</t>
+        </is>
+      </c>
+      <c r="K41" s="19" t="n">
         <v>66619.48</v>
       </c>
-      <c r="J41" s="20" t="inlineStr">
+      <c r="L41" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K41" s="16" t="inlineStr">
+      <c r="M41" s="16" t="inlineStr">
         <is>
           <t>0512600135</t>
         </is>
       </c>
-      <c r="L41" s="21" t="inlineStr">
+      <c r="N41" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M41" s="17" t="inlineStr">
-        <is>
-          <t>Fora da base de pendentes; EMD 511536, prev. 15/07</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>ETO-COEP 00211/2025</t>
+          <t>ETO-COEP 00082/2026</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
@@ -4409,114 +4673,124 @@
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr">
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G42" s="18" t="n">
+      <c r="H42" s="18" t="n">
         <v>21785.72</v>
       </c>
-      <c r="H42" s="18" t="n">
+      <c r="I42" s="18" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I42" s="19" t="n">
+      <c r="J42" s="17" t="inlineStr">
+        <is>
+          <t>Obras cita SS 00211/2025 — adotada a mais recente (00082/2026); entrega concluída, substituição pendente</t>
+        </is>
+      </c>
+      <c r="K42" s="19" t="n">
         <v>32802.66</v>
       </c>
-      <c r="J42" s="20" t="inlineStr">
+      <c r="L42" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K42" s="16" t="inlineStr">
+      <c r="M42" s="16" t="inlineStr">
         <is>
           <t>0112600424</t>
         </is>
       </c>
-      <c r="L42" s="22" t="inlineStr">
+      <c r="N42" s="21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00036/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>7927169001</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>Porto Nacional</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>13,8</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>Equipamento completo</t>
+        </is>
+      </c>
+      <c r="G43" s="25" t="inlineStr">
+        <is>
+          <t>Religador completo — EM DÚVIDA (obras=completo x v1.5=tanque)</t>
+        </is>
+      </c>
+      <c r="H43" s="26" t="n">
+        <v>55602.54</v>
+      </c>
+      <c r="I43" s="26" t="n">
+        <v>11016.94</v>
+      </c>
+      <c r="J43" s="25" t="inlineStr">
+        <is>
+          <t>EM DÚVIDA =&gt; assumido EQUIPAMENTO COMPLETO (padrão do gestor). Modelo NOJA RC10 nos Ajustes (há peças) — AVALIAR na aba VERIFICAR</t>
+        </is>
+      </c>
+      <c r="K43" s="27" t="n">
+        <v>66619.48</v>
+      </c>
+      <c r="L43" s="24" t="inlineStr">
+        <is>
+          <t>Em execução (obra)</t>
+        </is>
+      </c>
+      <c r="M43" s="24" t="inlineStr">
+        <is>
+          <t>0112600425</t>
+        </is>
+      </c>
+      <c r="N43" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M42" s="17" t="inlineStr">
-        <is>
-          <t>Fora da base de pendentes; v1.5 tratou como SS 00082/2026 — conferir número</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00036/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>7927169001</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>Palmas</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>13,8</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>Equipamento completo</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>Religador completo (OBRAS) — v1.5 dizia só tanque</t>
-        </is>
-      </c>
-      <c r="G43" s="18" t="n">
-        <v>55602.54</v>
-      </c>
-      <c r="H43" s="18" t="n">
-        <v>11016.94</v>
-      </c>
-      <c r="I43" s="19" t="n">
-        <v>66619.48</v>
-      </c>
-      <c r="J43" s="20" t="inlineStr">
-        <is>
-          <t>Em execução (obra)</t>
-        </is>
-      </c>
-      <c r="K43" s="16" t="inlineStr">
-        <is>
-          <t>0112600425</t>
-        </is>
-      </c>
-      <c r="L43" s="22" t="inlineStr">
-        <is>
-          <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M43" s="17" t="inlineStr">
-        <is>
-          <t>DIVERGÊNCIA de peça: obras=completo, orçamento v1.5=tanque</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>ETO-COEP 00034/2026</t>
+          <t>ETO-COEP 00085/2026</t>
         </is>
       </c>
       <c r="B44" s="16" t="inlineStr">
@@ -4531,46 +4805,51 @@
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
+          <t>SCHNEIDER ADVC</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E44" s="15" t="inlineStr">
+      <c r="F44" s="15" t="inlineStr">
         <is>
           <t>Componentes/Acessórios</t>
         </is>
       </c>
-      <c r="F44" s="17" t="inlineStr">
+      <c r="G44" s="17" t="inlineStr">
         <is>
           <t>Bateria + rádio + trafo/bucha fase A</t>
         </is>
       </c>
-      <c r="G44" s="18" t="n">
+      <c r="H44" s="18" t="n">
         <v>14612.08</v>
       </c>
-      <c r="H44" s="18" t="n">
+      <c r="I44" s="18" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I44" s="19" t="n">
+      <c r="J44" s="17" t="inlineStr">
+        <is>
+          <t>Obras cita SS 00034/2026 — adotada a mais detalhada (00085/2026); rádio será testado/reaproveitado; 'entender sobre bucha da fase A'</t>
+        </is>
+      </c>
+      <c r="K44" s="19" t="n">
         <v>25629.02</v>
       </c>
-      <c r="J44" s="20" t="inlineStr">
+      <c r="L44" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K44" s="16" t="inlineStr">
+      <c r="M44" s="16" t="inlineStr">
         <is>
           <t>0212600423</t>
         </is>
       </c>
-      <c r="L44" s="22" t="inlineStr">
+      <c r="N44" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M44" s="17" t="inlineStr">
-        <is>
-          <t>Fora da base de pendentes; v1.5 tratou como SS 00085/2026; rádio será testado/reaproveitado</t>
         </is>
       </c>
     </row>
@@ -4592,46 +4871,51 @@
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
+          <t>COOPER F6</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="F45" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F45" s="17" t="inlineStr">
+      <c r="G45" s="17" t="inlineStr">
         <is>
           <t>Tanque + controle NOJA enviado 07/07</t>
         </is>
       </c>
-      <c r="G45" s="18" t="n">
+      <c r="H45" s="18" t="n">
         <v>76246.2</v>
       </c>
-      <c r="H45" s="18" t="n">
+      <c r="I45" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I45" s="19" t="n">
+      <c r="J45" s="17" t="inlineStr">
+        <is>
+          <t>v1.5 (SS 00056/2025 — mesmo ano, adotada a mais recente 00106/2025) considerava só tanque; controle NOJA também enviado — custo de completo. Concluída parcialmente</t>
+        </is>
+      </c>
+      <c r="K45" s="19" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="J45" s="20" t="inlineStr">
+      <c r="L45" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K45" s="16" t="inlineStr">
+      <c r="M45" s="16" t="inlineStr">
         <is>
           <t>0712600318</t>
         </is>
       </c>
-      <c r="L45" s="22" t="inlineStr">
+      <c r="N45" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M45" s="17" t="inlineStr">
-        <is>
-          <t>v1.5 (SS 00056/2025) considerava SÓ tanque; obras enviou controle também — custo subiu p/ completo. Concluída parcialmente</t>
         </is>
       </c>
     </row>
@@ -4653,46 +4937,51 @@
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr">
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="G46" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G46" s="18" t="n">
+      <c r="H46" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H46" s="18" t="n">
+      <c r="I46" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I46" s="19" t="n">
+      <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t>CONCLUÍDA 06/06; obras: posto COEP 'Verificar' — confirmar baixa</t>
+        </is>
+      </c>
+      <c r="K46" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J46" s="20" t="inlineStr">
+      <c r="L46" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K46" s="16" t="inlineStr">
+      <c r="M46" s="16" t="inlineStr">
         <is>
           <t>0662600266</t>
         </is>
       </c>
-      <c r="L46" s="21" t="inlineStr">
+      <c r="N46" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M46" s="17" t="inlineStr">
-        <is>
-          <t>CONCLUÍDA 06/06</t>
         </is>
       </c>
     </row>
@@ -4714,53 +5003,58 @@
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="F47" s="15" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="G47" s="17" t="inlineStr">
         <is>
           <t>Religador completo (Cooper→NOJA)</t>
         </is>
       </c>
-      <c r="G47" s="18" t="n">
+      <c r="H47" s="18" t="n">
         <v>76246.2</v>
       </c>
-      <c r="H47" s="18" t="n">
+      <c r="I47" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I47" s="19" t="n">
+      <c r="J47" s="17" t="inlineStr">
+        <is>
+          <t>CONCLUÍDA 27/05; tanque cooper retirado será usado no 7903112004</t>
+        </is>
+      </c>
+      <c r="K47" s="19" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="J47" s="20" t="inlineStr">
+      <c r="L47" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K47" s="16" t="inlineStr">
+      <c r="M47" s="16" t="inlineStr">
         <is>
           <t>0612600439</t>
         </is>
       </c>
-      <c r="L47" s="21" t="inlineStr">
+      <c r="N47" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="M47" s="17" t="inlineStr">
-        <is>
-          <t>CONCLUÍDA 27/05; tanque cooper retirado será usado no 7903112004</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>ETO-COEP 00206/2025</t>
+          <t>ETO-COEP 00083/2026</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
@@ -4775,53 +5069,58 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr">
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="G48" s="17" t="inlineStr">
         <is>
           <t>Tanque + antena</t>
         </is>
       </c>
-      <c r="G48" s="18" t="n">
+      <c r="H48" s="18" t="n">
         <v>21785.72</v>
       </c>
-      <c r="H48" s="18" t="n">
+      <c r="I48" s="18" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I48" s="19" t="n">
+      <c r="J48" s="17" t="inlineStr">
+        <is>
+          <t>Obras cita SS 00206/2025 — adotada a mais recente (00083/2026); substituição prev. 09/07</t>
+        </is>
+      </c>
+      <c r="K48" s="19" t="n">
         <v>32802.66</v>
       </c>
-      <c r="J48" s="20" t="inlineStr">
+      <c r="L48" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K48" s="16" t="inlineStr">
+      <c r="M48" s="16" t="inlineStr">
         <is>
           <t>0112600383</t>
         </is>
       </c>
-      <c r="L48" s="22" t="inlineStr">
-        <is>
-          <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M48" s="17" t="inlineStr">
-        <is>
-          <t>Fora da base de pendentes; v1.5 tratou como SS 00083/2026</t>
+      <c r="N48" s="21" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>ETO-COEP 00104/2025</t>
+          <t>ETO-COEP 00081/2026</t>
         </is>
       </c>
       <c r="B49" s="16" t="inlineStr">
@@ -4836,107 +5135,117 @@
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="F49" s="15" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="F49" s="17" t="inlineStr">
+      <c r="G49" s="17" t="inlineStr">
         <is>
           <t>Rádio + antena + controle</t>
         </is>
       </c>
-      <c r="G49" s="18" t="n">
+      <c r="H49" s="18" t="n">
         <v>33816.82</v>
       </c>
-      <c r="H49" s="18" t="n">
+      <c r="I49" s="18" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I49" s="19" t="n">
+      <c r="J49" s="17" t="inlineStr">
+        <is>
+          <t>Obras cita SS 00104/2025 — adotada a mais recente (00081/2026); CONCLUÍDA (22/05)</t>
+        </is>
+      </c>
+      <c r="K49" s="19" t="n">
         <v>44833.76</v>
       </c>
-      <c r="J49" s="20" t="inlineStr">
+      <c r="L49" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K49" s="16" t="inlineStr">
+      <c r="M49" s="16" t="inlineStr">
         <is>
           <t>0712600316</t>
         </is>
       </c>
-      <c r="L49" s="21" t="inlineStr">
+      <c r="N49" s="21" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="M49" s="17" t="inlineStr">
-        <is>
-          <t>CONCLUÍDA (entrega 22/05); SS repassada</t>
-        </is>
-      </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="23" t="inlineStr">
         <is>
           <t>ETO-COEP 00094/2025</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="24" t="inlineStr">
         <is>
           <t>7934698002</t>
         </is>
       </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C50" s="23" t="inlineStr">
         <is>
           <t>Tocantinópolis</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>Controle completo</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>Controle completo (caixa)</t>
-        </is>
-      </c>
-      <c r="G50" s="18" t="n">
-        <v>33816.82</v>
-      </c>
-      <c r="H50" s="18" t="n">
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>Equipamento completo</t>
+        </is>
+      </c>
+      <c r="G50" s="25" t="inlineStr">
+        <is>
+          <t>Religador completo — EM DÚVIDA (obras=completo x v1.5=controle)</t>
+        </is>
+      </c>
+      <c r="H50" s="26" t="n">
+        <v>55602.54</v>
+      </c>
+      <c r="I50" s="26" t="n">
         <v>11016.94</v>
       </c>
-      <c r="I50" s="19" t="n">
-        <v>44833.76</v>
-      </c>
-      <c r="J50" s="20" t="inlineStr">
+      <c r="J50" s="25" t="inlineStr">
+        <is>
+          <t>EM DÚVIDA =&gt; assumido EQUIPAMENTO COMPLETO (padrão do gestor). CONCLUÍDA 30/05 — confirmar o que foi aplicado; posto COEP 'Verificar'</t>
+        </is>
+      </c>
+      <c r="K50" s="27" t="n">
+        <v>66619.48</v>
+      </c>
+      <c r="L50" s="24" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K50" s="16" t="inlineStr">
+      <c r="M50" s="24" t="inlineStr">
         <is>
           <t>0662600265</t>
         </is>
       </c>
-      <c r="L50" s="22" t="inlineStr">
+      <c r="N50" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="M50" s="17" t="inlineStr">
-        <is>
-          <t>CONCLUÍDA 30/05; obras diz 'Completo' e v1.5 'controle' — conferir</t>
         </is>
       </c>
     </row>
@@ -4958,129 +5267,139 @@
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E51" s="15" t="inlineStr">
+      <c r="F51" s="15" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F51" s="17" t="inlineStr">
+      <c r="G51" s="17" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="G51" s="18" t="n">
+      <c r="H51" s="18" t="n">
         <v>38151.48</v>
       </c>
-      <c r="H51" s="18" t="n">
+      <c r="I51" s="18" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I51" s="19" t="n">
+      <c r="J51" s="17" t="inlineStr">
+        <is>
+          <t>v1.5 cita SS 00149/2025 — adotada a mais recente (00151/2026); Requisitar=Não; EMD/entrega 'João verificar'</t>
+        </is>
+      </c>
+      <c r="K51" s="19" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="J51" s="20" t="inlineStr">
+      <c r="L51" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K51" s="16" t="inlineStr">
+      <c r="M51" s="16" t="inlineStr">
         <is>
           <t>0512600178</t>
         </is>
       </c>
-      <c r="L51" s="22" t="inlineStr">
+      <c r="N51" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="M51" s="17" t="inlineStr">
-        <is>
-          <t>Obras: Requisitar=Não; v1.5 tratava o ativo na SS 00149/2025 — conferir número</t>
-        </is>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>ETO-COEP 00108/2026</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>7933726256</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" s="28" t="inlineStr">
         <is>
           <t>Mateiros</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="29" t="inlineStr">
+        <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E52" s="29" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr">
+      <c r="F52" s="28" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="F52" s="17" t="inlineStr">
+      <c r="G52" s="30" t="inlineStr">
         <is>
           <t>Tanque REAPROVEITADO (redirecionado de Santa Rita/7900453110)</t>
         </is>
       </c>
-      <c r="G52" s="18" t="n">
+      <c r="H52" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="18" t="n">
+      <c r="I52" s="31" t="n">
         <v>13209.34</v>
       </c>
-      <c r="I52" s="19" t="n">
+      <c r="J52" s="30" t="inlineStr">
+        <is>
+          <t>DISCUSSÃO COM MATHEUS ALVES — material R$ 0 (reaproveitamento); obras pede cancelar obra COCM</t>
+        </is>
+      </c>
+      <c r="K52" s="32" t="n">
         <v>13209.34</v>
       </c>
-      <c r="J52" s="20" t="inlineStr">
+      <c r="L52" s="29" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="K52" s="16" t="inlineStr">
+      <c r="M52" s="29" t="inlineStr">
         <is>
           <t>0312600351</t>
         </is>
       </c>
-      <c r="L52" s="22" t="inlineStr">
+      <c r="N52" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="M52" s="17" t="inlineStr">
-        <is>
-          <t>Material R$ 0 (reaproveitamento); obras pede cancelar obra COCM</t>
-        </is>
-      </c>
     </row>
     <row r="53">
-      <c r="F53" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G53" s="23" t="n">
-        <v>2166366.05</v>
-      </c>
-      <c r="H53" s="23" t="n">
+      <c r="H53" s="33" t="n">
+        <v>2188151.77</v>
+      </c>
+      <c r="I53" s="33" t="n">
         <v>592337.78</v>
       </c>
-      <c r="I53" s="23" t="n">
-        <v>2758703.83</v>
+      <c r="K53" s="33" t="n">
+        <v>2780489.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5098,20 +5417,20 @@
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="52" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5121,6 +5440,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vermelho: discussão com Matheus Alves (status inalterado). Amarelo: avaliar — ver aba 'VERIFICAR (Obras)'. Tensão sempre da planilha de Ajustes.</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -5139,7 +5465,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Tensão (kV)</t>
+          <t>Tensão (kV) (Ajustes)</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -5184,102 +5510,102 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
+          <t>Observação</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
           <t>Custo Total</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>OBRA</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>Observações</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>ETO-COEP 00223/2025</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>5862236091</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Almas</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="24" t="n">
         <v>400</v>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Célula de regulador</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="H4" s="16" t="n">
+      <c r="H4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>690241</t>
         </is>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="26" t="n">
         <v>126893.8</v>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="K4" s="26" t="n">
         <v>126893.8</v>
       </c>
-      <c r="L4" s="18" t="n">
+      <c r="L4" s="26" t="n">
         <v>80318.5</v>
       </c>
-      <c r="M4" s="19" t="n">
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t>REVISAR COM MATHEUS ALVES — possível esquema sem cobrança deste material. Ajustes confirmam 34,5kV (v1.5 orçou 13,8). Obras: requisitar 3 peças (2 repõem estoque usado em obra de construção); aqui orçada 1 célula do conserto</t>
+        </is>
+      </c>
+      <c r="N4" s="27" t="n">
         <v>207212.3</v>
       </c>
-      <c r="N4" s="20" t="inlineStr">
+      <c r="O4" s="24" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="O4" s="16" t="inlineStr">
+      <c r="P4" s="24" t="inlineStr">
         <is>
           <t>0512600177</t>
         </is>
       </c>
-      <c r="P4" s="22" t="inlineStr">
+      <c r="Q4" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="Q4" s="17" t="inlineStr">
-        <is>
-          <t>OBRAS: 34,5/400kVA (v1.5 orçou como 13,8!) e manda requisitar 3 peças (2 repõem estoque de obra de construção) — aqui orçada 1 célula do conserto</t>
         </is>
       </c>
     </row>
@@ -5334,27 +5660,27 @@
       <c r="L5" s="18" t="n">
         <v>80318.5</v>
       </c>
-      <c r="M5" s="19" t="n">
+      <c r="M5" s="17" t="inlineStr">
+        <is>
+          <t>Material redirecionado p/ 5854566043 e 5862236091 — nova aquisição será COMPRA (requisição = COCM gera o que está no N1 e manda ao N3)</t>
+        </is>
+      </c>
+      <c r="N5" s="19" t="n">
         <v>460999.9</v>
       </c>
-      <c r="N5" s="20" t="inlineStr">
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="O5" s="16" t="inlineStr">
+      <c r="P5" s="16" t="inlineStr">
         <is>
           <t>0662600361</t>
         </is>
       </c>
-      <c r="P5" s="22" t="inlineStr">
+      <c r="Q5" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="Q5" s="17" t="inlineStr">
-        <is>
-          <t>OBRAS: material redirecionado p/ 5854566043 e 5862236091 — esta SS ficará aguardando novo material</t>
         </is>
       </c>
     </row>
@@ -5409,27 +5735,27 @@
       <c r="L6" s="18" t="n">
         <v>80318.5</v>
       </c>
-      <c r="M6" s="19" t="n">
+      <c r="M6" s="17" t="inlineStr">
+        <is>
+          <t>v1.5 'Em Análise' (SS 00056/2026): equipamento pode já ter sido fornecido — confirmar antes de comprar</t>
+        </is>
+      </c>
+      <c r="N6" s="19" t="n">
         <v>460999.9</v>
       </c>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="O6" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="O6" s="16" t="inlineStr">
+      <c r="P6" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P6" s="22" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="Q6" s="17" t="inlineStr">
-        <is>
-          <t>v1.5 'Em Análise' (SS 00056/2026): equipamento pode já ter sido fornecido — confirmar antes de comprar</t>
         </is>
       </c>
     </row>
@@ -5484,27 +5810,27 @@
       <c r="L7" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="19" t="n">
+      <c r="M7" s="17" t="inlineStr">
+        <is>
+          <t>EMD 514628; MO=0 (padrão ETO 30 p/ só controle)</t>
+        </is>
+      </c>
+      <c r="N7" s="19" t="n">
         <v>29445.39</v>
       </c>
-      <c r="N7" s="20" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="O7" s="16" t="inlineStr">
+      <c r="P7" s="16" t="inlineStr">
         <is>
           <t>0212600536</t>
         </is>
       </c>
-      <c r="P7" s="21" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="Q7" s="17" t="inlineStr">
-        <is>
-          <t>EMD 514628; MO=0 (padrão ETO 30 p/ só controle)</t>
         </is>
       </c>
     </row>
@@ -5559,27 +5885,27 @@
       <c r="L8" s="18" t="n">
         <v>80318.5</v>
       </c>
-      <c r="M8" s="19" t="n">
+      <c r="M8" s="17" t="inlineStr">
+        <is>
+          <t>EMD 513847; divergência fase B (DMSL) x C (solicitante); receberá célula redirecionada do 5858783119</t>
+        </is>
+      </c>
+      <c r="N8" s="19" t="n">
         <v>207212.3</v>
       </c>
-      <c r="N8" s="20" t="inlineStr">
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="O8" s="16" t="inlineStr">
+      <c r="P8" s="16" t="inlineStr">
         <is>
           <t>0312600352</t>
         </is>
       </c>
-      <c r="P8" s="22" t="inlineStr">
+      <c r="Q8" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="Q8" s="17" t="inlineStr">
-        <is>
-          <t>EMD 513847; divergência fase B (DMSL) x C (solicitante); receberá célula redirecionada do 5858783119</t>
         </is>
       </c>
     </row>
@@ -5634,27 +5960,27 @@
       <c r="L9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="19" t="n">
+      <c r="M9" s="17" t="inlineStr">
+        <is>
+          <t>Obras cita SS 00180/2025 — adotada a mais recente (00127/2026); EMD 514635</t>
+        </is>
+      </c>
+      <c r="N9" s="19" t="n">
         <v>29445.39</v>
       </c>
-      <c r="N9" s="20" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="O9" s="16" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr">
         <is>
           <t>0712600418</t>
         </is>
       </c>
-      <c r="P9" s="22" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="Q9" s="17" t="inlineStr">
-        <is>
-          <t>OBRAS/v1.5 tratam o ativo na SS 00180/2025 — duas SS p/ o mesmo defeito (EMD 514635)</t>
         </is>
       </c>
     </row>
@@ -5709,27 +6035,27 @@
       <c r="L10" s="18" t="n">
         <v>51402.14</v>
       </c>
-      <c r="M10" s="19" t="n">
+      <c r="M10" s="17" t="inlineStr">
+        <is>
+          <t>EMD 512848 — requisição aberta, aguardando calendário logístico</t>
+        </is>
+      </c>
+      <c r="N10" s="19" t="n">
         <v>112500.43</v>
       </c>
-      <c r="N10" s="20" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="O10" s="16" t="inlineStr">
+      <c r="P10" s="16" t="inlineStr">
         <is>
           <t>0612600626</t>
         </is>
       </c>
-      <c r="P10" s="21" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="Q10" s="17" t="inlineStr">
-        <is>
-          <t>EMD 512848 — requisição aberta, aguardando calendário logístico</t>
         </is>
       </c>
     </row>
@@ -5786,27 +6112,27 @@
       <c r="L11" s="18" t="n">
         <v>80318.5</v>
       </c>
-      <c r="M11" s="19" t="n">
+      <c r="M11" s="17" t="inlineStr">
+        <is>
+          <t>kVA sem base — assumido 200kVA; analisar com Leandro (categoria compra)</t>
+        </is>
+      </c>
+      <c r="N11" s="19" t="n">
         <v>253479.73</v>
       </c>
-      <c r="N11" s="16" t="inlineStr">
+      <c r="O11" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="O11" s="16" t="inlineStr">
+      <c r="P11" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P11" s="22" t="inlineStr">
+      <c r="Q11" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="Q11" s="17" t="inlineStr">
-        <is>
-          <t>kVA sem base — assumido 200kVA; analisar com Leandro (categoria compra)</t>
         </is>
       </c>
     </row>
@@ -5861,27 +6187,27 @@
       <c r="L12" s="18" t="n">
         <v>51402.14</v>
       </c>
-      <c r="M12" s="19" t="n">
+      <c r="M12" s="17" t="inlineStr">
+        <is>
+          <t>OBRAS confirma 167kVA (cód 690669); EMD 514627</t>
+        </is>
+      </c>
+      <c r="N12" s="19" t="n">
         <v>79018.75999999999</v>
       </c>
-      <c r="N12" s="20" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="O12" s="16" t="inlineStr">
+      <c r="P12" s="16" t="inlineStr">
         <is>
           <t>0212600539</t>
         </is>
       </c>
-      <c r="P12" s="21" t="inlineStr">
+      <c r="Q12" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="Q12" s="17" t="inlineStr">
-        <is>
-          <t>OBRAS confirma 167kVA (cód 690669) — corrigido vs. suposição anterior de 239kVA; EMD 514627</t>
         </is>
       </c>
     </row>
@@ -5938,27 +6264,27 @@
       <c r="L13" s="18" t="n">
         <v>80318.5</v>
       </c>
-      <c r="M13" s="19" t="n">
+      <c r="M13" s="17" t="inlineStr">
+        <is>
+          <t>Ajustes: 34,5kV (v1.5 dizia 13,8 — Ajustes prevalece); kVA sem base (assumido 200) — confirmar antes de requisitar</t>
+        </is>
+      </c>
+      <c r="N13" s="19" t="n">
         <v>253479.73</v>
       </c>
-      <c r="N13" s="16" t="inlineStr">
+      <c r="O13" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="O13" s="16" t="inlineStr">
+      <c r="P13" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P13" s="22" t="inlineStr">
+      <c r="Q13" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="Q13" s="17" t="inlineStr">
-        <is>
-          <t>CONFLITO de tensão: base de ajustes=34,5 x v1.5=13,8; kVA sem base (assumido 200) — confirmar antes de requisitar</t>
         </is>
       </c>
     </row>
@@ -6013,27 +6339,27 @@
       <c r="L14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="19" t="n">
+      <c r="M14" s="17" t="inlineStr">
+        <is>
+          <t>OBRAS: 219kVA; EMD 514632</t>
+        </is>
+      </c>
+      <c r="N14" s="19" t="n">
         <v>29445.39</v>
       </c>
-      <c r="N14" s="20" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="O14" s="16" t="inlineStr">
+      <c r="P14" s="16" t="inlineStr">
         <is>
           <t>0712600419</t>
         </is>
       </c>
-      <c r="P14" s="21" t="inlineStr">
+      <c r="Q14" s="21" t="inlineStr">
         <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="Q14" s="17" t="inlineStr">
-        <is>
-          <t>OBRAS: 219kVA; EMD 514632</t>
         </is>
       </c>
     </row>
@@ -6088,27 +6414,27 @@
       <c r="L15" s="18" t="n">
         <v>80318.5</v>
       </c>
-      <c r="M15" s="19" t="n">
+      <c r="M15" s="17" t="inlineStr">
+        <is>
+          <t>Composição conforme v1.5/Planilha1 (controle 29.445,39 + 3 células 200kVA)</t>
+        </is>
+      </c>
+      <c r="N15" s="19" t="n">
         <v>282925.12</v>
       </c>
-      <c r="N15" s="16" t="inlineStr">
+      <c r="O15" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="O15" s="16" t="inlineStr">
+      <c r="P15" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P15" s="22" t="inlineStr">
+      <c r="Q15" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="Q15" s="17" t="inlineStr">
-        <is>
-          <t>Composição conforme v1.5/Planilha1 (controle 29.445,39 + 3 células 200kVA)</t>
         </is>
       </c>
     </row>
@@ -6165,177 +6491,177 @@
       <c r="L16" s="18" t="n">
         <v>80318.5</v>
       </c>
-      <c r="M16" s="19" t="n">
+      <c r="M16" s="17" t="inlineStr">
+        <is>
+          <t>kVA sem base — assumido 200kVA</t>
+        </is>
+      </c>
+      <c r="N16" s="19" t="n">
         <v>138038.91</v>
       </c>
-      <c r="N16" s="16" t="inlineStr">
+      <c r="O16" s="16" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="O16" s="16" t="inlineStr">
+      <c r="P16" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P16" s="22" t="inlineStr">
+      <c r="Q16" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="Q16" s="17" t="inlineStr">
-        <is>
-          <t>kVA sem base — assumido 200kVA</t>
-        </is>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>ETO-COEP 00216/2025</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>5827102054</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>Pugmil</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="24" t="n">
         <v>200</v>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>Sem compra</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>Repasse COCM — tentar vedação do controle; cancelar obra</t>
         </is>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J17" s="18" t="n">
+      <c r="J17" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="18" t="n">
+      <c r="K17" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="18" t="n">
+      <c r="L17" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="19" t="n">
+      <c r="M17" s="25" t="inlineStr">
+        <is>
+          <t>EM AVALIAÇÃO PELO GESTOR — ver aba 'VERIFICAR (Obras)' e detalhes enviados no chat</t>
+        </is>
+      </c>
+      <c r="N17" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="20" t="inlineStr">
+      <c r="O17" s="24" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="O17" s="16" t="inlineStr">
+      <c r="P17" s="24" t="inlineStr">
         <is>
           <t>0212600537</t>
         </is>
       </c>
-      <c r="P17" s="22" t="inlineStr">
+      <c r="Q17" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="Q17" s="17" t="inlineStr">
-        <is>
-          <t>v1.5 orçava controle 29.445,39; OBRAS manda repassar ao COCM e cancelar a obra — retirado do custo</t>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>ETO-COEP 00171/2025</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>5800438116</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>Chapada da Natividade</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>Célula de regulador</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>Células fases B e C — REAPROVEITAMENTO (eq. retirado de obra)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="n">
+      <c r="H18" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="15" t="inlineStr">
+      <c r="I18" s="28" t="inlineStr">
         <is>
           <t>690240</t>
         </is>
       </c>
-      <c r="J18" s="18" t="n">
+      <c r="J18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="18" t="n">
+      <c r="K18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="18" t="n">
+      <c r="L18" s="31" t="n">
         <v>80318.5</v>
       </c>
-      <c r="M18" s="19" t="n">
+      <c r="M18" s="30" t="inlineStr">
+        <is>
+          <t>DISCUSSÃO COM MATHEUS ALVES — 'não precisa requisitar' (material R$ 0); linha duplicada nas obras (Porto Nacional, sem SS) é engano: Ajustes confirmam alimentador LD04002091 = Chapada da Natividade</t>
+        </is>
+      </c>
+      <c r="N18" s="32" t="n">
         <v>80318.5</v>
       </c>
-      <c r="N18" s="20" t="inlineStr">
+      <c r="O18" s="29" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="O18" s="16" t="inlineStr">
+      <c r="P18" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P18" s="22" t="inlineStr">
+      <c r="Q18" s="22" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="Q18" s="17" t="inlineStr">
-        <is>
-          <t>OBRAS: 'não precisa requisitar' — material R$ 0; linha duplicada nas obras (Porto Nacional, sem SS)</t>
         </is>
       </c>
     </row>
@@ -6345,13 +6671,13 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="K19" s="23" t="n">
+      <c r="K19" s="33" t="n">
         <v>1798850.97</v>
       </c>
-      <c r="L19" s="23" t="n">
+      <c r="L19" s="33" t="n">
         <v>825670.78</v>
       </c>
-      <c r="M19" s="23" t="n">
+      <c r="N19" s="33" t="n">
         <v>2624521.75</v>
       </c>
     </row>
@@ -6432,12 +6758,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00099/2026</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>5961616059</t>
         </is>
@@ -6447,15 +6773,15 @@
           <t>Célula fase A</t>
         </is>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6468,12 +6794,12 @@
       <c r="H4" s="17" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00094/2026</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>5959941122</t>
         </is>
@@ -6483,15 +6809,15 @@
           <t>Células fases B e C</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6504,12 +6830,12 @@
       <c r="H5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00095/2025</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>5955192004</t>
         </is>
@@ -6519,15 +6845,15 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6544,12 +6870,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00091/2026</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>5953586122</t>
         </is>
@@ -6559,15 +6885,15 @@
           <t>Células fases A e C</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="35" t="n">
         <v>300</v>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -6578,12 +6904,12 @@
       <c r="H7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00101/2026</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>5952342122</t>
         </is>
@@ -6593,15 +6919,15 @@
           <t>Células fases A e C</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6614,12 +6940,12 @@
       <c r="H8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00075/2025</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>5952327122</t>
         </is>
@@ -6629,15 +6955,15 @@
           <t>3 células (banco completo)</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6650,12 +6976,12 @@
       <c r="H9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00102/2026</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>5952248122</t>
         </is>
@@ -6665,15 +6991,15 @@
           <t>Células fases B e C</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6686,12 +7012,12 @@
       <c r="H10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00018/2024</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>5952243122</t>
         </is>
@@ -6701,15 +7027,15 @@
           <t>Células fases B e C</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6722,12 +7048,12 @@
       <c r="H11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00074/2025</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>5952202122</t>
         </is>
@@ -6737,15 +7063,15 @@
           <t>Células fases A e B</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="35" t="n">
         <v>300</v>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -6756,12 +7082,12 @@
       <c r="H12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00076/2025</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>5951650122</t>
         </is>
@@ -6771,15 +7097,15 @@
           <t>Células fases B e C</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
+      <c r="F13" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6792,12 +7118,12 @@
       <c r="H13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00047/2026</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>5950106122</t>
         </is>
@@ -6807,17 +7133,17 @@
           <t>A definir (defeito interno)</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6834,12 +7160,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00090/2026</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>5948602003</t>
         </is>
@@ -6849,15 +7175,15 @@
           <t>Células fases A e B</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr">
+      <c r="F15" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6870,12 +7196,12 @@
       <c r="H15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00109/2025</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>5946473071</t>
         </is>
@@ -6885,15 +7211,15 @@
           <t>Células fases B e C</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F16" s="25" t="n">
+      <c r="F16" s="35" t="n">
         <v>300</v>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -6908,12 +7234,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00116/2026</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>5944271122</t>
         </is>
@@ -6923,15 +7249,15 @@
           <t>Célula fase A</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F17" s="25" t="n">
+      <c r="F17" s="35" t="n">
         <v>300</v>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -6942,12 +7268,12 @@
       <c r="H17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00058/2024</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>5924849004</t>
         </is>
@@ -6957,15 +7283,15 @@
           <t>3 células (fases A, B e C)</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="25" t="inlineStr">
+      <c r="F18" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6982,12 +7308,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00093/2026</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>5922361122</t>
         </is>
@@ -6997,15 +7323,15 @@
           <t>Célula fase A</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="F19" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7018,12 +7344,12 @@
       <c r="H19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00060/2024</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>5913313004</t>
         </is>
@@ -7033,17 +7359,17 @@
           <t>A definir</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="25" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7060,12 +7386,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00077/2025</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>5907243122</t>
         </is>
@@ -7075,15 +7401,15 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="D21" s="25" t="n">
+      <c r="D21" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="E21" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="25" t="inlineStr">
+      <c r="F21" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7096,12 +7422,12 @@
       <c r="H21" s="17" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00085/2025</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>5903718004</t>
         </is>
@@ -7111,17 +7437,17 @@
           <t>A definir (manutenção)</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E22" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="F22" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7138,12 +7464,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00082/2025</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>5901886003</t>
         </is>
@@ -7153,17 +7479,17 @@
           <t>A definir (manutenção)</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="E23" s="35" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="F23" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7180,12 +7506,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00118/2026</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>5900600004</t>
         </is>
@@ -7195,15 +7521,15 @@
           <t>Células fases A e C</t>
         </is>
       </c>
-      <c r="D24" s="25" t="n">
+      <c r="D24" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="25" t="inlineStr">
+      <c r="F24" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7216,12 +7542,12 @@
       <c r="H24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00073/2025</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>5900489122</t>
         </is>
@@ -7231,15 +7557,15 @@
           <t>3 células (banco completo)</t>
         </is>
       </c>
-      <c r="D25" s="25" t="n">
+      <c r="D25" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F25" s="25" t="n">
+      <c r="F25" s="35" t="n">
         <v>600</v>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -7254,12 +7580,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00084/2025</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>5900470004</t>
         </is>
@@ -7269,17 +7595,17 @@
           <t>A definir (manutenção)</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E26" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="25" t="inlineStr">
+      <c r="F26" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7296,12 +7622,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00103/2026</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>5900358003</t>
         </is>
@@ -7311,15 +7637,15 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="D27" s="25" t="n">
+      <c r="D27" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="F27" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7332,12 +7658,12 @@
       <c r="H27" s="17" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00064/2025</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>5900293123</t>
         </is>
@@ -7347,15 +7673,15 @@
           <t>Célula fase A</t>
         </is>
       </c>
-      <c r="D28" s="25" t="n">
+      <c r="D28" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F28" s="25" t="inlineStr">
+      <c r="F28" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7368,12 +7694,12 @@
       <c r="H28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00092/2026</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>5900272004</t>
         </is>
@@ -7383,15 +7709,15 @@
           <t>Célula fase C</t>
         </is>
       </c>
-      <c r="D29" s="25" t="n">
+      <c r="D29" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="F29" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7404,12 +7730,12 @@
       <c r="H29" s="17" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00140/2025</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>5900129052</t>
         </is>
@@ -7419,15 +7745,15 @@
           <t>Células fases A e B</t>
         </is>
       </c>
-      <c r="D30" s="25" t="n">
+      <c r="D30" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="35" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F30" s="25" t="inlineStr">
+      <c r="F30" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7440,12 +7766,12 @@
       <c r="H30" s="17" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00100/2026</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>5900109059</t>
         </is>
@@ -7455,15 +7781,15 @@
           <t>Células fases A e C</t>
         </is>
       </c>
-      <c r="D31" s="25" t="n">
+      <c r="D31" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E31" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="F31" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7476,12 +7802,12 @@
       <c r="H31" s="17" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00083/2024</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>5900064029</t>
         </is>
@@ -7491,15 +7817,15 @@
           <t>3 células (fases A, B e C)</t>
         </is>
       </c>
-      <c r="D32" s="25" t="n">
+      <c r="D32" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="25" t="inlineStr">
+      <c r="E32" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="25" t="inlineStr">
+      <c r="F32" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7516,12 +7842,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00002/2026</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>5900038047</t>
         </is>
@@ -7531,15 +7857,15 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="D33" s="25" t="n">
+      <c r="D33" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="E33" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F33" s="25" t="inlineStr">
+      <c r="F33" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7552,12 +7878,12 @@
       <c r="H33" s="17" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00175/2025</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>5900010002</t>
         </is>
@@ -7567,15 +7893,15 @@
           <t>3 células (banco completo)</t>
         </is>
       </c>
-      <c r="D34" s="25" t="n">
+      <c r="D34" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E34" s="25" t="inlineStr">
+      <c r="E34" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F34" s="25" t="n">
+      <c r="F34" s="35" t="n">
         <v>100</v>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -7586,12 +7912,12 @@
       <c r="H34" s="17" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00146/2024</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>5900003013</t>
         </is>
@@ -7601,15 +7927,15 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="D35" s="25" t="n">
+      <c r="D35" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="25" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="25" t="inlineStr">
+      <c r="F35" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7627,7 +7953,7 @@
           <t>TOTAL DE CÉLULAS IDENTIFICADAS</t>
         </is>
       </c>
-      <c r="D36" s="26" t="n">
+      <c r="D36" s="36" t="n">
         <v>49</v>
       </c>
     </row>
@@ -7650,10 +7976,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -7670,7 +7996,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Todos os equipamentos desta aba estão considerados no orçamento com status 'Em execução (obra)'.</t>
+          <t>Todos considerados no orçamento com status 'Em execução (obra)'. Regra de SS duplicada: vale a mais recente (mesmo ano: a mais detalhada).</t>
         </is>
       </c>
     </row>
@@ -7692,7 +8018,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>SS na base de pendentes</t>
+          <t>SS adotada / base de pendentes</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -7727,24 +8053,24 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>7900117013</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00122/2025</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00084/2026</t>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00084/2026 (adotada)</t>
         </is>
       </c>
       <c r="E4" s="17" t="inlineStr">
@@ -7757,7 +8083,7 @@
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>0212600422</t>
         </is>
@@ -7774,27 +8100,27 @@
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t>Número de SS difere entre OBRAS e base de pendentes (mesmo ativo/obra)</t>
+          <t>SS divergente — adotada a mais recente (00084/2026)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>7908705049</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00177/2025</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
@@ -7809,7 +8135,7 @@
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="35" t="inlineStr">
         <is>
           <t>0512600135</t>
         </is>
@@ -7831,24 +8157,24 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>7933766059</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00211/2025</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>(fora da base; v1.5 = SS 00082/2026)</t>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00082/2026 (adotada)</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
@@ -7861,7 +8187,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>0112600424</t>
         </is>
@@ -7878,29 +8204,29 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>Número de SS difere entre OBRAS (00211/2025) e v1.5 (00082/2026)</t>
+          <t>SS divergente — adotada a mais recente (00082/2026)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>7900573047</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00209/2025</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00080/2026</t>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00080/2026 (adotada)</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -7913,7 +8239,7 @@
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>0412600391</t>
         </is>
@@ -7930,27 +8256,27 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>Número de SS difere entre OBRAS e base de pendentes</t>
+          <t>SS divergente — adotada a mais recente (00080/2026)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>7927169001</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00036/2026</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00036/2026</t>
         </is>
@@ -7962,10 +8288,10 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>v1.5 classificou TANQUE</t>
-        </is>
-      </c>
-      <c r="G8" s="25" t="inlineStr">
+          <t>EM DÚVIDA =&gt; Equipamento completo</t>
+        </is>
+      </c>
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>0112600425</t>
         </is>
@@ -7982,29 +8308,29 @@
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>PEÇA divergente: obras=completo x orçamento v1.5=tanque — orçado como completo</t>
+          <t>Obras=completo x v1.5=tanque; modelo NOJA RC10 — AVALIAR (aba VERIFICAR)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>7938137007</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00034/2026</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>(fora da base; v1.5 = SS 00085/2026)</t>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00085/2026 (adotada)</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
@@ -8017,14 +8343,14 @@
           <t>Componentes/Acessórios</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="35" t="inlineStr">
         <is>
           <t>0212600423</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>Rádio indisponível — será testado/reaproveitado</t>
+          <t>Rádio será testado/reaproveitado</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -8034,29 +8360,29 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>Número de SS difere (00034/2026 x 00085/2026); rádio requisitado p/ obra do PN</t>
+          <t>SS divergente (mesmo ano) — adotada a mais detalhada (00085/2026)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>7908686014</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00174/2024</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00086/2026</t>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00086/2026 (adotada)</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
@@ -8069,7 +8395,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="35" t="inlineStr">
         <is>
           <t>0212600425</t>
         </is>
@@ -8086,29 +8412,29 @@
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t>Número de SS difere entre OBRAS e base de pendentes</t>
+          <t>SS divergente — adotada a mais recente (00086/2026)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>7900230155</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00106/2025</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>(fora da base; v1.5 = SS 00056/2025)</t>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00106/2025 (adotada)</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>v1.5: ETO-COEP 00056/2025</t>
         </is>
       </c>
       <c r="E11" s="17" t="inlineStr">
@@ -8121,7 +8447,7 @@
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="35" t="inlineStr">
         <is>
           <t>0712600318</t>
         </is>
@@ -8138,27 +8464,27 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>v1.5 considerava só tanque; controle NOJA também foi enviado (07/07) — custo subiu p/ completo</t>
+          <t>Controle NOJA também enviado (07/07) — custo de completo</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>7943790134</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00181/2025</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
@@ -8173,7 +8499,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="G12" s="35" t="inlineStr">
         <is>
           <t>0662600266</t>
         </is>
@@ -8188,25 +8514,29 @@
           <t>CONSISTENTE</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr"/>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>Posto COEP: 'Verificar' — confirmar baixa</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>7925087021</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00222/2025</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00222/2025</t>
         </is>
@@ -8221,7 +8551,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="35" t="inlineStr">
         <is>
           <t>0412600392</t>
         </is>
@@ -8243,22 +8573,22 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>7900018004</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00178/2025</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="34" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
@@ -8273,7 +8603,7 @@
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G14" s="25" t="inlineStr">
+      <c r="G14" s="35" t="inlineStr">
         <is>
           <t>0612600439</t>
         </is>
@@ -8295,22 +8625,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>7929376022</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2026</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2026</t>
         </is>
@@ -8325,7 +8655,7 @@
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="G15" s="25" t="inlineStr">
+      <c r="G15" s="35" t="inlineStr">
         <is>
           <t>0612600565</t>
         </is>
@@ -8342,27 +8672,27 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>v1.5 também tratava o ativo na SS 00068/2026 (duplicidade)</t>
+          <t>SS 00068/2026 (v1.5) é duplicata</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>5827102054</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00216/2025</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="34" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
@@ -8377,7 +8707,7 @@
           <t>Sem compra</t>
         </is>
       </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="G16" s="35" t="inlineStr">
         <is>
           <t>0212600537</t>
         </is>
@@ -8394,27 +8724,27 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>v1.5 orçava controle R$ 29.445,39; OBRAS manda repassar ao COCM — retirado do custo</t>
+          <t>EM AVALIAÇÃO PELO GESTOR — v1.5 orçava controle R$ 29.445,39</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>5801866013</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00077/2026</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00077/2026</t>
         </is>
@@ -8429,7 +8759,7 @@
           <t>Célula fase C</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G17" s="35" t="inlineStr">
         <is>
           <t>0212600539</t>
         </is>
@@ -8446,27 +8776,27 @@
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>OBRAS confirma 167 kVA — corrigida a suposição anterior de 239 kVA</t>
+          <t>167 kVA confirmado</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>5855411017</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00199/2025</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00199/2025</t>
         </is>
@@ -8481,7 +8811,7 @@
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="G18" s="25" t="inlineStr">
+      <c r="G18" s="35" t="inlineStr">
         <is>
           <t>0212600536</t>
         </is>
@@ -8499,24 +8829,24 @@
       <c r="J18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>7931610122</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00206/2025</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>(fora da base; v1.5 = SS 00083/2026)</t>
+      <c r="D19" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00083/2026 (adotada)</t>
         </is>
       </c>
       <c r="E19" s="17" t="inlineStr">
@@ -8529,14 +8859,14 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G19" s="25" t="inlineStr">
+      <c r="G19" s="35" t="inlineStr">
         <is>
           <t>0112600383</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>Entrega concluída; substituição pendente (prev. 09/07)</t>
+          <t>Substituição pendente (prev. 09/07)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -8546,831 +8876,831 @@
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>Número de SS difere (00206/2025 x 00083/2026)</t>
+          <t>SS divergente — adotada a mais recente (00083/2026)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>7957620015</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00104/2025</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00081/2026 (adotada)</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>Rádio, antena, controle</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>Controle completo</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="inlineStr">
+        <is>
+          <t>0712600316</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>CONCLUÍDA (22/05)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>SS divergente — adotada a mais recente (00081/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>Religador</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>7934698002</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00094/2025</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>Rádio, antena, controle</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>EM DÚVIDA =&gt; Equipamento completo</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="inlineStr">
+        <is>
+          <t>0662600265</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>CONCLUÍDA 30/05</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="J21" s="17" t="inlineStr">
+        <is>
+          <t>Obras=completo x v1.5=controle; posto COEP 'Verificar' — AVALIAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>Religador</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>7900453110</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00169/2025</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00087/2026 (adotada)</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Tanque</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>Equipamento completo (DMSL)</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="inlineStr">
+        <is>
+          <t>0312600264</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>Equipamento entregue e REDIRECIONADO p/ 7933726256</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>SS e peça divergentes; custo desta SS deve ser reavaliado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>Religador</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>7903112004</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00184/2025</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00184/2025</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>Tanque Cooper reaproveitado (do 7900018004)</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="G20" s="25" t="inlineStr">
-        <is>
-          <t>0712600316</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>CONCLUÍDA (22/05)</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="G23" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>Falta enviar controle NOJA</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>Reaproveitamento reduz custo de completo p/ controle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>Religador</t>
+        </is>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>7957126085</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00156/2025</t>
+        </is>
+      </c>
+      <c r="D24" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00156/2025</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Controle e ajuste</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>Controle completo</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="inlineStr">
+        <is>
+          <t>0212600428</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>Pendente entrega (EMD 510216)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>CONSISTENTE</t>
         </is>
       </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>Repassados v1.5 também citam SS 00081/2026 p/ o mesmo ativo</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="J24" s="17" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>Regulador</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>5850308009</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00180/2025</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00127/2026 (adotada)</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>1 controle (651638)</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>Controle</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="inlineStr">
+        <is>
+          <t>0712600418</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
+          <t>Aguardando criação da obra (EMD 514635)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>Duas SS p/ o mesmo defeito — adotada a mais recente (00127/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
+          <t>Regulador</t>
+        </is>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>5800859011</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00115/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00115/2026</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>1 controle (651638)</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>Controle (retrofit RUA)</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="inlineStr">
+        <is>
+          <t>0712600419</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>Aguardando criação da obra (EMD 514632)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>CONSISTENTE</t>
+        </is>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>219 kVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>Regulador</t>
+        </is>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>5844630060</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00167/2025</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00167/2025</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>1 célula fase A (690236)</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>Célula fase A</t>
+        </is>
+      </c>
+      <c r="G27" s="35" t="inlineStr">
+        <is>
+          <t>0612600626</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>Requisição aberta (EMD 512848)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>CONSISTENTE</t>
+        </is>
+      </c>
+      <c r="J27" s="17" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>Regulador</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>5800438116</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00171/2025</t>
+        </is>
+      </c>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>(fora da base de pendentes)</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>Células B e C (690240)</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>Célula de regulador</t>
+        </is>
+      </c>
+      <c r="G28" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>Reaproveitamento de eq. retirado de obra</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>DISCUSSÃO MATHEUS ALVES; linha duplicada (Porto Nacional) é engano — Ajustes: LD04002091 = Chapada da Natividade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>7934698002</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00094/2025</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>7955520116</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00151/2026 (adotada)</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>v1.5: ETO-COEP 00149/2025</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>Tanque (parte ativa)</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>Parte ativa (Tanque)</t>
+        </is>
+      </c>
+      <c r="G29" s="35" t="inlineStr">
+        <is>
+          <t>0512600178</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
+          <t>Requisição; EMD/entrega 'João verificar'</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>Requisitar=Não — confirmar suprimento do material</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>Religador</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>7900594026</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00113/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00113/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>Deslocamento COCM</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>EM DÚVIDA =&gt; Equipamento completo</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>Requisitar=Não</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>Mantido completo por padrão do gestor — confirmar escopo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>Religador</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>7953610256</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP (sem número)</t>
+        </is>
+      </c>
+      <c r="D31" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00050/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>(Parte ativa)</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>Parte ativa (Tanque)</t>
+        </is>
+      </c>
+      <c r="G31" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="inlineStr">
+        <is>
+          <t>Requisitar=Não; 'João verificar'</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>SS sem número nas obras (é a 00050/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t>Regulador</t>
+        </is>
+      </c>
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>5858783119</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00123/2025</t>
+        </is>
+      </c>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00123/2025</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>3 células (690241)</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>3 células</t>
+        </is>
+      </c>
+      <c r="G32" s="35" t="inlineStr">
+        <is>
+          <t>0662600361</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>Material redirecionado p/ 5854566043 e 5862236091</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>Nova aquisição será COMPRA (requisição = COCM gera N1→N3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="34" t="inlineStr">
+        <is>
+          <t>Regulador</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>5862236091</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00223/2025</t>
+        </is>
+      </c>
+      <c r="D33" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00223/2025</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>Célula fase B (690241)</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>Célula fase B</t>
+        </is>
+      </c>
+      <c r="G33" s="35" t="inlineStr">
+        <is>
+          <t>0512600177</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t>Aguardando geração da EMD</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="J33" s="17" t="inlineStr">
+        <is>
+          <t>REVISAR COM MATHEUS ALVES — 34,5/400kVA (Ajustes) x 13,8 (v1.5); requisitar 3 peças (2 repõem estoque)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>Regulador</t>
+        </is>
+      </c>
+      <c r="B34" s="35" t="inlineStr">
+        <is>
+          <t>5854566043</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00160/2025</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00160/2025</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>Célula fase B (690241)</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>Célula fase B</t>
+        </is>
+      </c>
+      <c r="G34" s="35" t="inlineStr">
+        <is>
+          <t>0312600352</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>Pendente (EMD 513847, prev. 10/07)</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>CONSISTENTE</t>
+        </is>
+      </c>
+      <c r="J34" s="17" t="inlineStr">
+        <is>
+          <t>Divergência antiga fase B x C mantida como observação</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>Religador</t>
+        </is>
+      </c>
+      <c r="B35" s="35" t="inlineStr">
+        <is>
+          <t>7933726256</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00108/2026</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>Completo</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>v1.5 classificou CONTROLE (caixa)</t>
-        </is>
-      </c>
-      <c r="G21" s="25" t="inlineStr">
-        <is>
-          <t>0662600265</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>CONCLUÍDA 30/05</t>
-        </is>
-      </c>
-      <c r="I21" s="22" t="inlineStr">
-        <is>
-          <t>DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>PEÇA divergente: obras=completo x v1.5=controle — mantido controle</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>Religador</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>7900453110</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00169/2025</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00087/2026</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>Tanque</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>Equipamento completo (DMSL)</t>
-        </is>
-      </c>
-      <c r="G22" s="25" t="inlineStr">
-        <is>
-          <t>0312600264</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>Equipamento entregue e REDIRECIONADO p/ 7933726256</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
-        <is>
-          <t>DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>SS difere (00169/2025 x 00087/2026) e peça (tanque x completo); custo desta SS deve ser reavaliado</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>Religador</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>7903112004</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00184/2025</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00184/2025</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>Tanque Cooper reaproveitado (do 7900018004)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>Completo (→NOJA) na SS</t>
-        </is>
-      </c>
-      <c r="G23" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>Falta enviar controle NOJA</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
-        <is>
-          <t>DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>Reaproveitamento reduz custo de completo p/ controle — orçado como controle</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>Religador</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>7957126085</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00156/2025</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00156/2025</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>Controle e ajuste</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>Controle completo</t>
-        </is>
-      </c>
-      <c r="G24" s="25" t="inlineStr">
-        <is>
-          <t>0212600428</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>Pendente entrega (EMD 510216)</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>Parte ativa (Tanque)</t>
+        </is>
+      </c>
+      <c r="G35" s="35" t="inlineStr">
+        <is>
+          <t>0312600351</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>Usará equipamento redirecionado de Santa Rita; cancelar obra COCM</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>CONSISTENTE</t>
         </is>
       </c>
-      <c r="J24" s="17" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>Regulador</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>5850308009</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00180/2025</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00127/2026</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>1 controle (651638)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>Controle</t>
-        </is>
-      </c>
-      <c r="G25" s="25" t="inlineStr">
-        <is>
-          <t>0712600418</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>Aguardando criação da obra (EMD 514635)</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
-        <is>
-          <t>DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>DUAS SS para o mesmo ativo/defeito (00180/2025 e 00127/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>Regulador</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>5800859011</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00115/2026</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00115/2026</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>1 controle (651638)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>Controle (retrofit RUA)</t>
-        </is>
-      </c>
-      <c r="G26" s="25" t="inlineStr">
-        <is>
-          <t>0712600419</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>Aguardando criação da obra (EMD 514632)</t>
-        </is>
-      </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>CONSISTENTE</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>219 kVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>Regulador</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>5844630060</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00167/2025</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00167/2025</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>1 célula fase A (690236)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>Célula fase A</t>
-        </is>
-      </c>
-      <c r="G27" s="25" t="inlineStr">
-        <is>
-          <t>0612600626</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>Requisição aberta (EMD 512848)</t>
-        </is>
-      </c>
-      <c r="I27" s="21" t="inlineStr">
-        <is>
-          <t>CONSISTENTE</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="24" t="inlineStr">
-        <is>
-          <t>Regulador</t>
-        </is>
-      </c>
-      <c r="B28" s="25" t="inlineStr">
-        <is>
-          <t>5800438116</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00171/2025</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
-        <is>
-          <t>(fora da base de pendentes)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>Células B e C (690240)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>Célula de regulador</t>
-        </is>
-      </c>
-      <c r="G28" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>Reaproveitamento de eq. retirado de obra</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="inlineStr">
-        <is>
-          <t>DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>'Não precisa requisitar' — material R$ 0; linha DUPLICADA nas obras (Porto Nacional, sem SS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t>Religador</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="inlineStr">
-        <is>
-          <t>7955520116</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00151/2026</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
-        <is>
-          <t>(fora da base; v1.5 = SS 00149/2025)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Tanque (parte ativa)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>Parte ativa (Tanque)</t>
-        </is>
-      </c>
-      <c r="G29" s="25" t="inlineStr">
-        <is>
-          <t>0512600178</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>Requisição; 'João verificar'</t>
-        </is>
-      </c>
-      <c r="I29" s="22" t="inlineStr">
-        <is>
-          <t>DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>Número de SS difere (00151/2026 x 00149/2025); Requisitar=Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>Religador</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>7900594026</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00113/2026</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00113/2026</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Deslocamento COCM</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>Equipamento completo (SS)</t>
-        </is>
-      </c>
-      <c r="G30" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>Requisitar=Não</t>
-        </is>
-      </c>
-      <c r="I30" s="22" t="inlineStr">
-        <is>
-          <t>DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>OBRAS indica só deslocamento COCM; SS pede substituição — confirmar escopo</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="24" t="inlineStr">
-        <is>
-          <t>Religador</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>7953610256</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP (sem número)</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00050/2026</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>(Parte ativa)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>Parte ativa (Tanque)</t>
-        </is>
-      </c>
-      <c r="G31" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>Requisitar=Não; 'João verificar'</t>
-        </is>
-      </c>
-      <c r="I31" s="22" t="inlineStr">
-        <is>
-          <t>DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>SS sem número na planilha de obras (é a 00050/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="24" t="inlineStr">
-        <is>
-          <t>Regulador</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>5858783119</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00123/2025</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00123/2025</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>3 células (690241)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>3 células</t>
-        </is>
-      </c>
-      <c r="G32" s="25" t="inlineStr">
-        <is>
-          <t>0662600361</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>Material redirecionado p/ 5854566043 e 5862236091</t>
-        </is>
-      </c>
-      <c r="I32" s="22" t="inlineStr">
-        <is>
-          <t>DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="J32" s="17" t="inlineStr">
-        <is>
-          <t>A SS de origem fica sem material — precisará de nova requisição</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>Regulador</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>5862236091</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00223/2025</t>
-        </is>
-      </c>
-      <c r="D33" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00223/2025</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>Célula fase B (690241)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>Célula fase B</t>
-        </is>
-      </c>
-      <c r="G33" s="25" t="inlineStr">
-        <is>
-          <t>0512600177</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>Aguardando geração da EMD</t>
-        </is>
-      </c>
-      <c r="I33" s="22" t="inlineStr">
-        <is>
-          <t>DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="J33" s="17" t="inlineStr">
-        <is>
-          <t>OBRAS: 34,5/400 kVA (v1.5 orçou 13,8!) e requisitar 3 peças (2 repõem estoque usado em obra de construção)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="24" t="inlineStr">
-        <is>
-          <t>Regulador</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>5854566043</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00160/2025</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00160/2025</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>Célula fase B (690241)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>Célula fase B</t>
-        </is>
-      </c>
-      <c r="G34" s="25" t="inlineStr">
-        <is>
-          <t>0312600352</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>Pendente (EMD 513847, prev. 10/07)</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
-        <is>
-          <t>CONSISTENTE</t>
-        </is>
-      </c>
-      <c r="J34" s="17" t="inlineStr">
-        <is>
-          <t>Divergência antiga fase B x C mantida como observação</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>Religador</t>
-        </is>
-      </c>
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>7933726256</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00108/2026</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>(fora da base de pendentes)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>Tanque</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>Parte ativa (Tanque)</t>
-        </is>
-      </c>
-      <c r="G35" s="25" t="inlineStr">
-        <is>
-          <t>0312600351</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>Usará equipamento redirecionado de Santa Rita; cancelar obra COCM</t>
-        </is>
-      </c>
-      <c r="I35" s="21" t="inlineStr">
-        <is>
-          <t>CONSISTENTE</t>
-        </is>
-      </c>
       <c r="J35" s="17" t="inlineStr">
         <is>
-          <t>Material R$ 0 (reaproveitamento) — consistente com parecer COEP da SS 00087/2026</t>
+          <t>DISCUSSÃO MATHEUS ALVES — material R$ 0 (reaproveitamento)</t>
         </is>
       </c>
     </row>
@@ -9385,22 +9715,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFFF00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DISCREPÂNCIAS — OBRAS × BASE DE SS PENDENTES × ORÇAMENTO v1.5</t>
+          <t>VERIFICAR (OBRAS) — PONTOS PARA O GESTOR CHECAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Aba amarela: nada aqui altera status do orçamento — são pendências de verificação/decisão.</t>
         </is>
       </c>
     </row>
@@ -9412,265 +9752,417 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Tipo</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>SS (adotada)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Encaminhamento</t>
+          <t>Equipamento / Modelo (Ajustes)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>O que está pendente na planilha de obras</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>O que você precisa verificar / decidir</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>Números de SS divergentes p/ o mesmo ativo</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>7900117013 (00122/2025 x 00084/2026); 7900573047 (00209/2025 x 00080/2026); 7908686014 (00174/2024 x 00086/2026); 7900453110 (00169/2025 x 00087/2026); 5850308009 (00180/2025 x 00127/2026); 7933766059, 7938137007, 7931610122, 7900230155, 7955520116 (obras x v1.5)</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>Padronizar o número de SS de referência em OBRAS (sugestão: usar o da base de pendentes/SGM)</t>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>7953610256</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00050/2026</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Religador NOJA RC10 34,5</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>SS sem número na planilha de obras; Requisitar=Não; EMD e Status de Entrega = 'João Verificar'</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>Confirmar com João se a parte ativa será requisitada e preencher o nº da SS (confirmado pelo print do SGM: 00050/2026)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>SS sem número na planilha de obras</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>7953610256 — campo SS = 'ETO-COEP' (é a SS 00050/2026)</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Preencher o número</t>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>7955520116</t>
+        </is>
+      </c>
+      <c r="C5" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00151/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>Religador NOJA RC10 34,5</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>Requisitar=Não porém a peça é tanque; EMD e entrega = 'João Verificar'; v1.5 usava SS 00149/2025</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>Confirmar com João como o tanque será suprido (estoque? outra obra?) e qual SS vale</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Peça divergente (obras x orçamento)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>7927169001: obras=COMPLETO x v1.5=TANQUE; 7934698002: obras=COMPLETO x v1.5=CONTROLE; 7900453110: obras=TANQUE x DMSL=COMPLETO</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>Confirmar com o técnico responsável; orçado: 7927169001 completo, 7934698002 controle</t>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>7943790134</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00181/2025</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>Religador NOJA RC10 34,5</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>Substituição CONCLUÍDA 06/06, mas coluna Posto COEP = 'Verificar'</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>Confirmar baixa/encerramento da SS e da obra 0662600266</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Tensão/potência divergente</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>5862236091: OBRAS=34,5kV/400kVA x v1.5=13,8kV (base de ajustes confirma 34,5) — diferença de R$ 65.795,51 por célula; 5800961074: base ajustes=34,5 x v1.5=13,8 (não está nas obras)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Orçado a 34,5/400 (5862236091); 5800961074 mantido 34,5 c/ VERIFICAR</t>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>7934698002</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00094/2025</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>Religador NOJA RC10 13,8</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>Obras diz 'Completo' x v1.5 dizia 'Controle (caixa)'; CONCLUÍDA 30/05; Posto COEP = 'Verificar'</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>Confirmar o que foi realmente aplicado (orçado como COMPLETO por padrão do gestor — ajustar após confirmação)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>Qtd a requisitar ≠ qtd do conserto</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>5862236091: obras manda requisitar 3 células porque 2 peças do estoque foram usadas em obra de construção; o conserto usa 1</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Orçada 1 célula no custo do conserto; reposição de estoque tratada à parte</t>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>7927169001</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00036/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Religador NOJA RC10 13,8</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>Obras diz 'Completo' x v1.5 dizia 'Tanque'. Modelo nos Ajustes é NOJA RC10 (há peças de reposição — regra do gestor: só Cooper vira completo automático)</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>AVALIAR: se for só tanque, o custo cai de R$ 55.602,54 p/ R$ 21.785,72 (orçado como COMPLETO por padrão)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Material redirecionado</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>5858783119 (3 células) → redirecionadas p/ 5854566043 e 5862236091; 7900453110 (equipamento) → redirecionado p/ 7933726256</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>As SS de origem ficarão sem material — prever nova requisição</t>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>7938137007</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00085/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>Religador SCHNEIDER ADVC 13,8</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>'Entender sobre bucha da fase A'; rádio foi requisitado p/ obra do PN — 'vamos testar os rádios e tentar mandar o que temos'</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>Definir escopo da bucha fase A e confirmar fornecimento do rádio</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Reaproveitamentos (custo cai)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>7903112004: tanque Cooper do 7900018004 (falta só controle NOJA); 7933726256: recebe eq. de Santa Rita (material R$ 0); 5800438116: usa eq. retirado de obra (material R$ 0)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>Orçamento ajustado: controle p/ 7903112004; material zero p/ os outros dois</t>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>5862236091</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00223/2025</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>Regulador 34,5 / 400 kVA</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>REVISAR COM MATHEUS ALVES: dá para fazer esquema e NÃO cobrar este material. Obras manda requisitar 3 peças (2 repõem estoque usado em obra de construção); aguardando geração da EMD</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>Decidir cobrança do material com Matheus Alves; hoje orçada 1 célula (R$ 126.893,80)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Escopo sem compra</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>5827102054: repassar ao COCM e cancelar obra (v1.5 orçava controle); 7900594026: obras = só deslocamento COCM (SS pede substituição)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>Retirados do custo de material; confirmar escopo do 7900594026</t>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>5800438116</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00171/2025</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>Regulador 34,5 / 200 kVA</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>LINHA DUPLICADA nas obras: 'Chapada da Natividade' (com SS) e 'Porto Nacional' (sem SS) — mesmo ativo. Ajustes: alimentador LD04002091 = Chapada da Natividade =&gt; duplicata de Porto Nacional é engano</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>DISCUSSÃO COM MATHEUS ALVES; excluir a linha duplicada nas obras (status inalterado no orçamento)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Linha duplicada nas obras</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>5800438116 aparece 2x (Chapada da Natividade c/ SS 00171/2025 e Porto Nacional sem SS)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>Excluir a duplicata</t>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>7933726256</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00108/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Religador NOJA RC10 34,5</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>Receberá o equipamento redirecionado de Santa Rita (7900453110); obras pede 'cancelar a obra COCM´s'</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>DISCUSSÃO COM MATHEUS ALVES (status inalterado; material R$ 0 por reaproveitamento)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Duplicidade de SS no mesmo ativo</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>7929376022 tratado nas SS 00068/2026 (v1.5, N3) e 00120/2026 (pendentes); 7957620015 nas SS 00104/2025 e 00081/2026</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>Encerrar a SS duplicada</t>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>5827102054</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00216/2025</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Regulador TOSHIBA 34,5 / 200 kVA</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>EM AVALIAÇÃO PELO GESTOR: ETO30 = relé queimado + cabo rádio-relé danificado + malha de aterramento alta; v1.5 = 'nobreak e relé já substituídos em campo' e orçava controle c/ nobreak R$ 29.445,39; OBRAS = repassar ao COCM, corrigir aterramento, tentar vedar infiltração do controle com cola de trafo e CANCELAR a obra 0212600537</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>Decidir: conserto via COEP (controle R$ 29.445,39) x repasse COCM com vedação (custo zero p/ COEP)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Fora da base de pendentes</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>14 equipamentos das OBRAS não constam na base de SS pendentes enviada (ex.: 7908705049, 7943790134, 7900018004...) — esperado se a base é só 'SS PENDENTE', mas vale conferir</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>Incluídos no orçamento como 'Em execução'</t>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>7903112004</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00184/2025</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>Religador COOPER F6 34,5</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>Requisitar=Não; tanque Cooper reaproveitado do 7900018004; 'FALTA ENVIAR CONTROLE NOJA'</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>Confirmar envio do controle NOJA (orçado só o controle, R$ 38.094,72)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>7900594026</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00113/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Religador COOPER F6 34,5</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>Obras = só 'Deslocamento COCM' (Requisitar=Não) x SS pede substituição do equipamento</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>Confirmar escopo — mantido EQUIPAMENTO COMPLETO no orçamento por padrão do gestor</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9682,7 +10174,301 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DISCREPÂNCIAS — OBRAS × BASE DE SS PENDENTES × ORÇAMENTO v1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Detalhe</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Encaminhamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Números de SS divergentes p/ o mesmo ativo</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>10 casos — ex.: 7900117013 (00122/2025 x 00084/2026); 7908686014 (00174/2024 x 00086/2026); 5850308009 (00180/2025 x 00127/2026)</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>RESOLVIDO pela regra do gestor: vale a SS mais recente pelo ano; mesmo ano =&gt; a mais detalhada/mais recente. Nº antigo citado na Observação de cada linha</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>SS sem número na planilha de obras</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>7953610256 — campo SS = 'ETO-COEP' (print do SGM confirma: 00050/2026)</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Preencher o número nas obras</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Peça divergente (obras x orçamento)</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>7927169001 (completo x tanque, NOJA); 7934698002 (completo x controle, NOJA); 7900594026 (deslocamento x substituição)</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Padrão do gestor aplicado: EM DÚVIDA =&gt; EQUIPAMENTO COMPLETO, com destaque na coluna Observação; avaliação na aba VERIFICAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Tensão/potência divergente</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>5862236091: Ajustes=34,5/400 x v1.5=13,8 (dif. R$ 65.795,51/célula); 5800961074: Ajustes=34,5 x v1.5=13,8</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Regra do gestor: Ajustes SEMPRE prevalece p/ modelo e faixa de tensão — orçados a 34,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Qtd a requisitar ≠ qtd do conserto</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>5862236091: requisitar 3 células (2 repõem estoque usado em obra de construção); conserto usa 1</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>REVISAR COM MATHEUS ALVES — possível esquema sem cobrança do material</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Material redirecionado</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>5858783119 (3 células) → 5854566043 e 5862236091; 7900453110 (equipamento) → 7933726256</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>SS de origem ficará sem material — nova aquisição será COMPRA (requisição = COCM gera N1→N3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Reaproveitamentos (custo cai)</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>7903112004: tanque Cooper do 7900018004 (orçado só controle); 7933726256 e 5800438116: material R$ 0</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>7933726256 e 5800438116 marcados em VERMELHO — discussão com Matheus Alves (status inalterado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Escopo sem compra</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>5827102054 (Pugmil): repasse COCM + vedação x conserto de controle</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>EM AVALIAÇÃO PELO GESTOR — detalhes na aba VERIFICAR e no chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Linha duplicada nas obras</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>5800438116 2x (Chapada da Natividade c/ SS x Porto Nacional sem SS) — Ajustes (LD04002091) confirmam Chapada da Natividade</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>Engano confirmado — excluir a duplicata; discussão com Matheus Alves</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Duplicidade de SS no mesmo ativo</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>7929376022 (00068/2026 e 00120/2026); 7957620015 (00104/2025 e 00081/2026)</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>Adotada a mais recente; encerrar a SS duplicada no SGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Fora da base de pendentes</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>14 equipamentos das OBRAS não constam na base de SS pendentes (esperado p/ concluídas/em execução)</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Incluídos no orçamento como 'Em execução'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -9696,65 +10482,79 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>1. Formato replicado do ORCAMENTO_EQ_ESPECIAIS_revisado_1_5; bloco Orçado/Realizado (8495/8481) preservado na Dinâmica.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>2. Base de cálculo: SS PENDENTES POSTO DO COEP (Localização 79/58/59) — mesmo raciocínio da v2 (leitura de descrição, parecer DMSL prevalece).</t>
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>2. Base de cálculo: SS PENDENTES POSTO DO COEP (Localização 79/58/59) + equipamentos da planilha OBRAS_EQ_ESPECIAL (em execução).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>3. Premissas de célula de regulador e controle (651638) atualizadas conforme a versão revisada 1.5.</t>
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>3. Modelo e faixa de tensão: SEMPRE da planilha de Ajustes (Religadores/Reguladores). Único ativo sem cadastro: 7900532053.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>4. Diferente da v1.5, itens adicionais citados na SS (rádio, chave faca) são SOMADOS ao material da linha.</t>
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>4. SS duplicadas: vale a mais recente pelo ano; mesmo ano =&gt; a mais detalhada/mais recente (nº anterior fica na Observação).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>5. Equipamentos da planilha OBRAS_EQ_ESPECIAL entram com status 'Em execução (obra)' — inclusive os que não estão na base de pendentes.</t>
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>5. Em dúvida sobre a peça (deslocamento e afins) =&gt; EQUIPAMENTO COMPLETO, destacado na coluna Observação (à esquerda do Custo Total).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>6. Reaproveitamentos e repasses ao COCM entram com material R$ 0 (ver aba Discrepâncias).</t>
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>6. Linhas VERMELHAS (7933726256 e 5800438116): discussão com Matheus Alves — status e valores inalterados.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>7. Banco de capacitor: 49 células identificadas; sem premissa de preço/MO — valorar quando houver premissa.</t>
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>7. Linhas AMARELAS (7927169001, 7934698002, 5862236091, 5827102054): avaliação — ver aba amarela 'VERIFICAR (Obras)'.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>8. Placa de religador tratada como CONTROLE COMPLETO (premissa do usuário); alternativa: placa avulsa R$ 1.999 (5 un. em estoque).</t>
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>8. Reguladores: célula por tensão/potência (completo = 3 células); controle 651638 c/ nobreak; só controle =&gt; MO 0 (padrão ETO 30).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>9. ETO_COEP_SS_TODOS_OS_STATUS segue reservada para o próximo raciocínio.</t>
+      <c r="A11" s="39" t="inlineStr">
+        <is>
+          <t>9. Placa de religador tratada como CONTROLE COMPLETO (premissa do usuário); alternativa: placa avulsa R$ 1.999 (5 un. em estoque).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>10. Banco de capacitor: 49 células identificadas; sem premissa de preço/MO — valorar quando houver premissa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="39" t="inlineStr">
+        <is>
+          <t>11. ETO_COEP_SS_TODOS_OS_STATUS segue reservada para o próximo raciocínio.</t>
         </is>
       </c>
     </row>

--- a/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
+++ b/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
@@ -8,15 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="Dinâmica" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Premissas e Preços" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mapeamento Criticidades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Detalhe Religadores" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Reguladores" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Banco de capacitor" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Em Execução (Obras)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="VERIFICAR (Obras)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Discrepâncias" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Observacoes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Visão ETO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Premissas e Preços" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mapeamento Criticidades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Detalhe Religadores" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Reguladores" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Banco de capacitor" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Em Execução (Obras)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="VERIFICAR (Obras)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Discrepâncias" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Observacoes" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -313,6 +314,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1676,6 +1695,300 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DISCREPÂNCIAS — OBRAS × BASE DE SS PENDENTES × ORÇAMENTO v1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Detalhe</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Encaminhamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Números de SS divergentes p/ o mesmo ativo</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>10 casos — ex.: 7900117013 (00122/2025 x 00084/2026); 7908686014 (00174/2024 x 00086/2026); 5850308009 (00180/2025 x 00127/2026)</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>RESOLVIDO pela regra do gestor: vale a SS mais recente pelo ano; mesmo ano =&gt; a mais detalhada/mais recente. Nº antigo citado na Observação de cada linha</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>SS sem número na planilha de obras</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>7953610256 — campo SS = 'ETO-COEP' (print do SGM confirma: 00050/2026)</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>Preencher o número nas obras</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Peça divergente (obras x orçamento)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>7927169001 (completo x tanque, NOJA); 7934698002 (completo x controle, NOJA); 7900594026 (deslocamento x substituição)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Padrão do gestor aplicado: EM DÚVIDA =&gt; EQUIPAMENTO COMPLETO, com destaque na coluna Observação; avaliação na aba VERIFICAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Tensão/potência divergente</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>5862236091: Ajustes=34,5/400 x v1.5=13,8 (dif. R$ 65.795,51/célula); 5800961074: Ajustes=34,5 x v1.5=13,8</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Regra do gestor: Ajustes SEMPRE prevalece p/ modelo e faixa de tensão — orçados a 34,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Qtd a requisitar ≠ qtd do conserto</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>5862236091: requisitar 3 células (2 repõem estoque usado em obra de construção); conserto usa 1</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>REVISAR COM MATHEUS ALVES — possível esquema sem cobrança do material</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Material redirecionado</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>5858783119 (3 células) → 5854566043 e 5862236091; 7900453110 (equipamento) → 7933726256</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>SS de origem ficará sem material — nova aquisição será COMPRA (requisição = COCM gera N1→N3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Reaproveitamentos (custo cai)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>7903112004: tanque Cooper do 7900018004 (orçado só controle); 7933726256 e 5800438116: material R$ 0</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>7933726256 e 5800438116 marcados em VERMELHO — discussão com Matheus Alves (status inalterado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Escopo sem compra</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>5827102054 (Pugmil): repasse COCM + vedação x conserto de controle</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>EM AVALIAÇÃO PELO GESTOR — detalhes na aba VERIFICAR e no chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Linha duplicada nas obras</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>5800438116 2x (Chapada da Natividade c/ SS x Porto Nacional sem SS) — Ajustes (LD04002091) confirmam Chapada da Natividade</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>Engano confirmado — excluir a duplicata; discussão com Matheus Alves</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Duplicidade de SS no mesmo ativo</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>7929376022 (00068/2026 e 00120/2026); 7957620015 (00104/2025 e 00081/2026)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Adotada a mais recente; encerrar a SS duplicada no SGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>Fora da base de pendentes</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>14 equipamentos das OBRAS não constam na base de SS pendentes (esperado p/ concluídas/em execução)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>Incluídos no orçamento como 'Em execução'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1782,6 +2095,3234 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J87"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col hidden="1" width="4" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VISÃO ETO (SIMPLIFICADA) — NA MÃO DE QUEM ESTÁ CADA EQUIPAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fontes: Relação de Equipamentos Indisponíveis ETO 36 (oficial, filtro AREA=DCMD, extração 08/07) e Pendentes da ETO ATUALIZADA v10 (destino da SS). DMSL = destino ETO-TELE ainda fora da fila do DCMD; Proteção = destino ETO-PROT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Na mão de quem (equipamentos indisponíveis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Religadores (79)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Reguladores (58)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>DCMD (oficial ETO 36)</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="n">
+        <v>44</v>
+      </c>
+      <c r="C6" s="55" t="n">
+        <v>21</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>DMSL (destino ETO-TELE)</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="n">
+        <v>22</v>
+      </c>
+      <c r="C7" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Proteção (destino ETO-PROT)</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>67</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Obs.: 7 equipamentos com destino ETO-TELE já entraram na fila do DCMD e estão contados no DCMD. Proteção: 7922995039 (RL) e 5820790038 (RT).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>DCMD — por responsável (oficial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Religadores</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Reguladores</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>COCM-S</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>COCM-N</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>⚠ CONFLITOS (concluídos que aparecem no oficial do DCMD): 5850308009 (Guaraí — dado como concluído via ETO-TELE 00958/2026, mas com 0 dias aguardando DCMD) e 7942572059 (Taquaralto — marcado EXECUTADO no mapeamento, mas com 8 dias aguardando DCMD). Situação NÃO alterada — aguardando sua definição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Lista oficial DCMD (ETO 36) — 65 equipamentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>SS SGM</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Criticidade (oficial)</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Dias aguardando DCMD</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Dias pendente (SS)</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Está no orçamento?</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Situação no mapeamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="56" t="inlineStr">
+        <is>
+          <t>7923927122</t>
+        </is>
+      </c>
+      <c r="B23" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C23" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00079/2025</t>
+        </is>
+      </c>
+      <c r="D23" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E23" s="56" t="n">
+        <v>434</v>
+      </c>
+      <c r="G23" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H23" s="57" t="inlineStr">
+        <is>
+          <t>Palmas</t>
+        </is>
+      </c>
+      <c r="I23" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="56" t="inlineStr">
+        <is>
+          <t>7900532053</t>
+        </is>
+      </c>
+      <c r="B24" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C24" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00102/2025</t>
+        </is>
+      </c>
+      <c r="D24" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E24" s="56" t="n">
+        <v>407</v>
+      </c>
+      <c r="G24" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H24" s="57" t="inlineStr">
+        <is>
+          <t>Piraque</t>
+        </is>
+      </c>
+      <c r="I24" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="56" t="inlineStr">
+        <is>
+          <t>7920024127</t>
+        </is>
+      </c>
+      <c r="B25" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C25" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00120/2025</t>
+        </is>
+      </c>
+      <c r="D25" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E25" s="56" t="n">
+        <v>371</v>
+      </c>
+      <c r="G25" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H25" s="57" t="inlineStr">
+        <is>
+          <t>Palmeiras Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I25" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="56" t="inlineStr">
+        <is>
+          <t>5858783119</t>
+        </is>
+      </c>
+      <c r="B26" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C26" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00123/2025</t>
+        </is>
+      </c>
+      <c r="D26" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="56" t="n">
+        <v>369</v>
+      </c>
+      <c r="G26" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H26" s="57" t="inlineStr">
+        <is>
+          <t>Sao Bento Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I26" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="56" t="inlineStr">
+        <is>
+          <t>7927446001</t>
+        </is>
+      </c>
+      <c r="B27" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C27" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00143/2025</t>
+        </is>
+      </c>
+      <c r="D27" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E27" s="56" t="n">
+        <v>364</v>
+      </c>
+      <c r="G27" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H27" s="57" t="inlineStr">
+        <is>
+          <t>Porto Nacional</t>
+        </is>
+      </c>
+      <c r="I27" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="56" t="inlineStr">
+        <is>
+          <t>7957126085</t>
+        </is>
+      </c>
+      <c r="B28" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C28" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00156/2025</t>
+        </is>
+      </c>
+      <c r="D28" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E28" s="56" t="n">
+        <v>350</v>
+      </c>
+      <c r="G28" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H28" s="57" t="inlineStr">
+        <is>
+          <t>Monte Santo Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I28" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="56" t="inlineStr">
+        <is>
+          <t>7942485096</t>
+        </is>
+      </c>
+      <c r="B29" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C29" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00158/2025</t>
+        </is>
+      </c>
+      <c r="D29" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E29" s="56" t="n">
+        <v>349</v>
+      </c>
+      <c r="G29" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H29" s="57" t="inlineStr">
+        <is>
+          <t>Pindorama Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I29" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="56" t="inlineStr">
+        <is>
+          <t>5854566043</t>
+        </is>
+      </c>
+      <c r="B30" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C30" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00160/2025</t>
+        </is>
+      </c>
+      <c r="D30" s="56" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="E30" s="56" t="n">
+        <v>347</v>
+      </c>
+      <c r="G30" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H30" s="57" t="inlineStr">
+        <is>
+          <t>Silvanopolis</t>
+        </is>
+      </c>
+      <c r="I30" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="56" t="inlineStr">
+        <is>
+          <t>5844630060</t>
+        </is>
+      </c>
+      <c r="B31" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C31" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00167/2025</t>
+        </is>
+      </c>
+      <c r="D31" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E31" s="56" t="n">
+        <v>333</v>
+      </c>
+      <c r="G31" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H31" s="57" t="inlineStr">
+        <is>
+          <t>Nova Olinda</t>
+        </is>
+      </c>
+      <c r="I31" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="56" t="inlineStr">
+        <is>
+          <t>7900535058</t>
+        </is>
+      </c>
+      <c r="B32" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C32" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00173/2025</t>
+        </is>
+      </c>
+      <c r="D32" s="56" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="E32" s="56" t="n">
+        <v>317</v>
+      </c>
+      <c r="G32" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H32" s="57" t="inlineStr">
+        <is>
+          <t>Santa Fe Do Araguaia</t>
+        </is>
+      </c>
+      <c r="I32" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="56" t="inlineStr">
+        <is>
+          <t>7903112004</t>
+        </is>
+      </c>
+      <c r="B33" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C33" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00184/2025</t>
+        </is>
+      </c>
+      <c r="D33" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E33" s="56" t="n">
+        <v>307</v>
+      </c>
+      <c r="G33" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H33" s="57" t="inlineStr">
+        <is>
+          <t>Araguaina</t>
+        </is>
+      </c>
+      <c r="I33" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="56" t="inlineStr">
+        <is>
+          <t>5800371025</t>
+        </is>
+      </c>
+      <c r="B34" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C34" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00187/2025</t>
+        </is>
+      </c>
+      <c r="D34" s="56" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="E34" s="56" t="n">
+        <v>305</v>
+      </c>
+      <c r="G34" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H34" s="57" t="inlineStr">
+        <is>
+          <t>Arapoema</t>
+        </is>
+      </c>
+      <c r="I34" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="56" t="inlineStr">
+        <is>
+          <t>5855411017</t>
+        </is>
+      </c>
+      <c r="B35" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C35" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00199/2025</t>
+        </is>
+      </c>
+      <c r="D35" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E35" s="56" t="n">
+        <v>280</v>
+      </c>
+      <c r="G35" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H35" s="57" t="inlineStr">
+        <is>
+          <t>Barrolandia</t>
+        </is>
+      </c>
+      <c r="I35" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="56" t="inlineStr">
+        <is>
+          <t>5853360007</t>
+        </is>
+      </c>
+      <c r="B36" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C36" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-PS 00323/2025</t>
+        </is>
+      </c>
+      <c r="D36" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E36" s="56" t="n">
+        <v>264</v>
+      </c>
+      <c r="G36" s="56" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="H36" s="57" t="inlineStr">
+        <is>
+          <t>Miracema Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I36" s="58" t="inlineStr">
+        <is>
+          <t>Só no Mapeamento Criticidades</t>
+        </is>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="56" t="inlineStr">
+        <is>
+          <t>5800961074</t>
+        </is>
+      </c>
+      <c r="B37" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C37" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00221/2025</t>
+        </is>
+      </c>
+      <c r="D37" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E37" s="56" t="n">
+        <v>214</v>
+      </c>
+      <c r="G37" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H37" s="57" t="inlineStr">
+        <is>
+          <t>Dianopolis</t>
+        </is>
+      </c>
+      <c r="I37" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="56" t="inlineStr">
+        <is>
+          <t>7925087021</t>
+        </is>
+      </c>
+      <c r="B38" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C38" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00222/2025</t>
+        </is>
+      </c>
+      <c r="D38" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E38" s="56" t="n">
+        <v>211</v>
+      </c>
+      <c r="G38" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H38" s="57" t="inlineStr">
+        <is>
+          <t>Parana</t>
+        </is>
+      </c>
+      <c r="I38" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="56" t="inlineStr">
+        <is>
+          <t>5862236091</t>
+        </is>
+      </c>
+      <c r="B39" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C39" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00223/2025</t>
+        </is>
+      </c>
+      <c r="D39" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="56" t="n">
+        <v>211</v>
+      </c>
+      <c r="G39" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H39" s="57" t="inlineStr">
+        <is>
+          <t>Almas</t>
+        </is>
+      </c>
+      <c r="I39" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="56" t="inlineStr">
+        <is>
+          <t>7933585074</t>
+        </is>
+      </c>
+      <c r="B40" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C40" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00024/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E40" s="56" t="n">
+        <v>161</v>
+      </c>
+      <c r="G40" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H40" s="57" t="inlineStr">
+        <is>
+          <t>Dianopolis</t>
+        </is>
+      </c>
+      <c r="I40" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="56" t="inlineStr">
+        <is>
+          <t>7927646026</t>
+        </is>
+      </c>
+      <c r="B41" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C41" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00029/2026</t>
+        </is>
+      </c>
+      <c r="D41" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E41" s="56" t="n">
+        <v>154</v>
+      </c>
+      <c r="G41" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H41" s="57" t="inlineStr">
+        <is>
+          <t>Ponte Alta Tocantins</t>
+        </is>
+      </c>
+      <c r="I41" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="56" t="inlineStr">
+        <is>
+          <t>7931608059</t>
+        </is>
+      </c>
+      <c r="B42" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C42" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00040/2026</t>
+        </is>
+      </c>
+      <c r="D42" s="56" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="E42" s="56" t="n">
+        <v>133</v>
+      </c>
+      <c r="G42" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H42" s="57" t="inlineStr">
+        <is>
+          <t>Palmas</t>
+        </is>
+      </c>
+      <c r="I42" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="56" t="inlineStr">
+        <is>
+          <t>7908249152</t>
+        </is>
+      </c>
+      <c r="B43" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C43" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00038/2026</t>
+        </is>
+      </c>
+      <c r="D43" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E43" s="56" t="n">
+        <v>133</v>
+      </c>
+      <c r="G43" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H43" s="57" t="inlineStr">
+        <is>
+          <t>Santa Rosa Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I43" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="56" t="inlineStr">
+        <is>
+          <t>7927396052</t>
+        </is>
+      </c>
+      <c r="B44" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C44" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00045/2026</t>
+        </is>
+      </c>
+      <c r="D44" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E44" s="56" t="n">
+        <v>127</v>
+      </c>
+      <c r="G44" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H44" s="57" t="inlineStr">
+        <is>
+          <t>Formoso Do Araguaia</t>
+        </is>
+      </c>
+      <c r="I44" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="56" t="inlineStr">
+        <is>
+          <t>7925871077</t>
+        </is>
+      </c>
+      <c r="B45" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C45" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00048/2026</t>
+        </is>
+      </c>
+      <c r="D45" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E45" s="56" t="n">
+        <v>113</v>
+      </c>
+      <c r="G45" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H45" s="57" t="inlineStr">
+        <is>
+          <t>Goiatins</t>
+        </is>
+      </c>
+      <c r="I45" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="56" t="inlineStr">
+        <is>
+          <t>7953610256</t>
+        </is>
+      </c>
+      <c r="B46" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C46" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00050/2026</t>
+        </is>
+      </c>
+      <c r="D46" s="56" t="inlineStr">
+        <is>
+          <t>Muito Alto</t>
+        </is>
+      </c>
+      <c r="E46" s="56" t="n">
+        <v>111</v>
+      </c>
+      <c r="G46" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H46" s="57" t="inlineStr">
+        <is>
+          <t>Mateiros</t>
+        </is>
+      </c>
+      <c r="I46" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="56" t="inlineStr">
+        <is>
+          <t>7926442035</t>
+        </is>
+      </c>
+      <c r="B47" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C47" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00051/2026</t>
+        </is>
+      </c>
+      <c r="D47" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E47" s="56" t="n">
+        <v>111</v>
+      </c>
+      <c r="G47" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H47" s="57" t="inlineStr">
+        <is>
+          <t>Monte Do Carmo</t>
+        </is>
+      </c>
+      <c r="I47" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="56" t="inlineStr">
+        <is>
+          <t>7925744087</t>
+        </is>
+      </c>
+      <c r="B48" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C48" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00059/2026</t>
+        </is>
+      </c>
+      <c r="D48" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E48" s="56" t="n">
+        <v>99</v>
+      </c>
+      <c r="G48" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H48" s="57" t="inlineStr">
+        <is>
+          <t>Goianorte</t>
+        </is>
+      </c>
+      <c r="I48" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="56" t="inlineStr">
+        <is>
+          <t>7925733015</t>
+        </is>
+      </c>
+      <c r="B49" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C49" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00058/2026</t>
+        </is>
+      </c>
+      <c r="D49" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E49" s="56" t="n">
+        <v>99</v>
+      </c>
+      <c r="G49" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H49" s="57" t="inlineStr">
+        <is>
+          <t>Pedro Afonso</t>
+        </is>
+      </c>
+      <c r="I49" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="56" t="inlineStr">
+        <is>
+          <t>7901110084</t>
+        </is>
+      </c>
+      <c r="B50" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C50" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00061/2026</t>
+        </is>
+      </c>
+      <c r="D50" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E50" s="56" t="n">
+        <v>98</v>
+      </c>
+      <c r="G50" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H50" s="57" t="inlineStr">
+        <is>
+          <t>Divinopolis</t>
+        </is>
+      </c>
+      <c r="I50" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="56" t="inlineStr">
+        <is>
+          <t>7944559149</t>
+        </is>
+      </c>
+      <c r="B51" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C51" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00063/2026</t>
+        </is>
+      </c>
+      <c r="D51" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E51" s="56" t="n">
+        <v>98</v>
+      </c>
+      <c r="G51" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H51" s="57" t="inlineStr">
+        <is>
+          <t>Caseara</t>
+        </is>
+      </c>
+      <c r="I51" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J51" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="56" t="inlineStr">
+        <is>
+          <t>5800291035</t>
+        </is>
+      </c>
+      <c r="B52" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C52" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-PO 00097/2026</t>
+        </is>
+      </c>
+      <c r="D52" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E52" s="56" t="n">
+        <v>98</v>
+      </c>
+      <c r="G52" s="56" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="H52" s="57" t="inlineStr">
+        <is>
+          <t>Monte Do Carmo</t>
+        </is>
+      </c>
+      <c r="I52" s="58" t="inlineStr">
+        <is>
+          <t>Só no Mapeamento Criticidades</t>
+        </is>
+      </c>
+      <c r="J52" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="56" t="inlineStr">
+        <is>
+          <t>7919270014</t>
+        </is>
+      </c>
+      <c r="B53" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C53" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00074/2026</t>
+        </is>
+      </c>
+      <c r="D53" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E53" s="56" t="n">
+        <v>82</v>
+      </c>
+      <c r="G53" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H53" s="57" t="inlineStr">
+        <is>
+          <t>Pium</t>
+        </is>
+      </c>
+      <c r="I53" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J53" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="56" t="inlineStr">
+        <is>
+          <t>5801866013</t>
+        </is>
+      </c>
+      <c r="B54" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C54" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00077/2026</t>
+        </is>
+      </c>
+      <c r="D54" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E54" s="56" t="n">
+        <v>79</v>
+      </c>
+      <c r="G54" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H54" s="57" t="inlineStr">
+        <is>
+          <t>Paraiso Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I54" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J54" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="56" t="inlineStr">
+        <is>
+          <t>7926089013</t>
+        </is>
+      </c>
+      <c r="B55" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C55" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00078/2026</t>
+        </is>
+      </c>
+      <c r="D55" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E55" s="56" t="n">
+        <v>76</v>
+      </c>
+      <c r="G55" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H55" s="57" t="inlineStr">
+        <is>
+          <t>Paraiso Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I55" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J55" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="56" t="inlineStr">
+        <is>
+          <t>7900573047</t>
+        </is>
+      </c>
+      <c r="B56" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C56" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00080/2026</t>
+        </is>
+      </c>
+      <c r="D56" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E56" s="56" t="n">
+        <v>75</v>
+      </c>
+      <c r="G56" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H56" s="57" t="inlineStr">
+        <is>
+          <t>Figueiropolis</t>
+        </is>
+      </c>
+      <c r="I56" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J56" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="56" t="inlineStr">
+        <is>
+          <t>7927413001</t>
+        </is>
+      </c>
+      <c r="B57" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C57" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-PO 00118/2026</t>
+        </is>
+      </c>
+      <c r="D57" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E57" s="56" t="n">
+        <v>75</v>
+      </c>
+      <c r="G57" s="56" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="H57" s="57" t="inlineStr">
+        <is>
+          <t>Porto Nacional</t>
+        </is>
+      </c>
+      <c r="I57" s="58" t="inlineStr">
+        <is>
+          <t>Só no Mapeamento Criticidades</t>
+        </is>
+      </c>
+      <c r="J57" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="56" t="inlineStr">
+        <is>
+          <t>7908686014</t>
+        </is>
+      </c>
+      <c r="B58" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C58" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00086/2026</t>
+        </is>
+      </c>
+      <c r="D58" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E58" s="56" t="n">
+        <v>74</v>
+      </c>
+      <c r="G58" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H58" s="57" t="inlineStr">
+        <is>
+          <t>Pium</t>
+        </is>
+      </c>
+      <c r="I58" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J58" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="56" t="inlineStr">
+        <is>
+          <t>7900117013</t>
+        </is>
+      </c>
+      <c r="B59" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C59" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00084/2026</t>
+        </is>
+      </c>
+      <c r="D59" s="56" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="E59" s="56" t="n">
+        <v>74</v>
+      </c>
+      <c r="G59" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H59" s="57" t="inlineStr">
+        <is>
+          <t>Paraiso Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I59" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J59" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="56" t="inlineStr">
+        <is>
+          <t>7900453110</t>
+        </is>
+      </c>
+      <c r="B60" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C60" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00087/2026</t>
+        </is>
+      </c>
+      <c r="D60" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E60" s="56" t="n">
+        <v>71</v>
+      </c>
+      <c r="G60" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H60" s="57" t="inlineStr">
+        <is>
+          <t>Santa Rita Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I60" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J60" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="56" t="inlineStr">
+        <is>
+          <t>5865120195</t>
+        </is>
+      </c>
+      <c r="B61" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C61" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00538/2026</t>
+        </is>
+      </c>
+      <c r="D61" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="56" t="n">
+        <v>51</v>
+      </c>
+      <c r="G61" s="56" t="inlineStr">
+        <is>
+          <t>COCM-N</t>
+        </is>
+      </c>
+      <c r="H61" s="57" t="inlineStr">
+        <is>
+          <t>Centenario</t>
+        </is>
+      </c>
+      <c r="I61" s="58" t="inlineStr">
+        <is>
+          <t>Só no Mapeamento Criticidades</t>
+        </is>
+      </c>
+      <c r="J61" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="56" t="inlineStr">
+        <is>
+          <t>5836786094</t>
+        </is>
+      </c>
+      <c r="B62" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C62" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00095/2026</t>
+        </is>
+      </c>
+      <c r="D62" s="56" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="E62" s="56" t="n">
+        <v>50</v>
+      </c>
+      <c r="G62" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H62" s="57" t="inlineStr">
+        <is>
+          <t>Peixe</t>
+        </is>
+      </c>
+      <c r="I62" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J62" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="56" t="inlineStr">
+        <is>
+          <t>7900594026</t>
+        </is>
+      </c>
+      <c r="B63" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C63" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00113/2026</t>
+        </is>
+      </c>
+      <c r="D63" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E63" s="56" t="n">
+        <v>27</v>
+      </c>
+      <c r="G63" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H63" s="57" t="inlineStr">
+        <is>
+          <t>Ponte Alta Tocantins</t>
+        </is>
+      </c>
+      <c r="I63" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J63" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="56" t="inlineStr">
+        <is>
+          <t>7913662076</t>
+        </is>
+      </c>
+      <c r="B64" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C64" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00114/2026</t>
+        </is>
+      </c>
+      <c r="D64" s="56" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="E64" s="56" t="n">
+        <v>27</v>
+      </c>
+      <c r="G64" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H64" s="57" t="inlineStr">
+        <is>
+          <t>Duere</t>
+        </is>
+      </c>
+      <c r="I64" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J64" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="56" t="inlineStr">
+        <is>
+          <t>5800859011</t>
+        </is>
+      </c>
+      <c r="B65" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C65" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00115/2026</t>
+        </is>
+      </c>
+      <c r="D65" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E65" s="56" t="n">
+        <v>25</v>
+      </c>
+      <c r="G65" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H65" s="57" t="inlineStr">
+        <is>
+          <t>Tupirama</t>
+        </is>
+      </c>
+      <c r="I65" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J65" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="56" t="inlineStr">
+        <is>
+          <t>5800090147</t>
+        </is>
+      </c>
+      <c r="B66" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C66" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00117/2026</t>
+        </is>
+      </c>
+      <c r="D66" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E66" s="56" t="n">
+        <v>22</v>
+      </c>
+      <c r="G66" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H66" s="57" t="inlineStr">
+        <is>
+          <t>Taipas Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I66" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J66" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="56" t="inlineStr">
+        <is>
+          <t>5856156091</t>
+        </is>
+      </c>
+      <c r="B67" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C67" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-DP 00403/2026</t>
+        </is>
+      </c>
+      <c r="D67" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="G67" s="56" t="inlineStr">
+        <is>
+          <t>COCM-S</t>
+        </is>
+      </c>
+      <c r="H67" s="57" t="inlineStr">
+        <is>
+          <t>Almas</t>
+        </is>
+      </c>
+      <c r="I67" s="58" t="inlineStr">
+        <is>
+          <t>Só no Mapeamento Criticidades</t>
+        </is>
+      </c>
+      <c r="J67" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="56" t="inlineStr">
+        <is>
+          <t>5827102054</t>
+        </is>
+      </c>
+      <c r="B68" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C68" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-PS 00289/2026</t>
+        </is>
+      </c>
+      <c r="D68" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E68" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="G68" s="56" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="H68" s="57" t="inlineStr">
+        <is>
+          <t>Pugmil</t>
+        </is>
+      </c>
+      <c r="I68" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J68" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="56" t="inlineStr">
+        <is>
+          <t>5846328094</t>
+        </is>
+      </c>
+      <c r="B69" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C69" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-GU 00687/2026</t>
+        </is>
+      </c>
+      <c r="D69" s="56" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="E69" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="G69" s="56" t="inlineStr">
+        <is>
+          <t>COCM-S</t>
+        </is>
+      </c>
+      <c r="H69" s="57" t="inlineStr">
+        <is>
+          <t>Peixe</t>
+        </is>
+      </c>
+      <c r="I69" s="58" t="inlineStr">
+        <is>
+          <t>Só no Mapeamento Criticidades</t>
+        </is>
+      </c>
+      <c r="J69" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="59" t="inlineStr">
+        <is>
+          <t>7942572059</t>
+        </is>
+      </c>
+      <c r="B70" s="59" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C70" s="60" t="inlineStr">
+        <is>
+          <t>ETO-RD-PA 00427/2026</t>
+        </is>
+      </c>
+      <c r="D70" s="59" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E70" s="59" t="n">
+        <v>8</v>
+      </c>
+      <c r="G70" s="59" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="H70" s="60" t="inlineStr">
+        <is>
+          <t>Palmas</t>
+        </is>
+      </c>
+      <c r="I70" s="60" t="inlineStr">
+        <is>
+          <t>Só no Mapeamento Criticidades</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>EXECUTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="56" t="inlineStr">
+        <is>
+          <t>7929376022</t>
+        </is>
+      </c>
+      <c r="B71" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C71" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00120/2026</t>
+        </is>
+      </c>
+      <c r="D71" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E71" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="G71" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H71" s="57" t="inlineStr">
+        <is>
+          <t>Babaculandia</t>
+        </is>
+      </c>
+      <c r="I71" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J71" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="56" t="inlineStr">
+        <is>
+          <t>5800438116</t>
+        </is>
+      </c>
+      <c r="B72" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C72" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-DP 00404/2026</t>
+        </is>
+      </c>
+      <c r="D72" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E72" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G72" s="56" t="inlineStr">
+        <is>
+          <t>COCM-S</t>
+        </is>
+      </c>
+      <c r="H72" s="57" t="inlineStr">
+        <is>
+          <t>Chapada Da Natividade</t>
+        </is>
+      </c>
+      <c r="I72" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J72" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="56" t="inlineStr">
+        <is>
+          <t>5803327001</t>
+        </is>
+      </c>
+      <c r="B73" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C73" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-PA 00434/2026</t>
+        </is>
+      </c>
+      <c r="D73" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E73" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G73" s="56" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="H73" s="57" t="inlineStr">
+        <is>
+          <t>Porto Nacional</t>
+        </is>
+      </c>
+      <c r="I73" s="58" t="inlineStr">
+        <is>
+          <t>Só no Mapeamento Criticidades</t>
+        </is>
+      </c>
+      <c r="J73" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="56" t="inlineStr">
+        <is>
+          <t>7933766059</t>
+        </is>
+      </c>
+      <c r="B74" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C74" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-PA 00431/2026</t>
+        </is>
+      </c>
+      <c r="D74" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E74" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G74" s="56" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="H74" s="57" t="inlineStr">
+        <is>
+          <t>Palmas</t>
+        </is>
+      </c>
+      <c r="I74" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J74" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="56" t="inlineStr">
+        <is>
+          <t>7931610122</t>
+        </is>
+      </c>
+      <c r="B75" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C75" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-PA 00433/2026</t>
+        </is>
+      </c>
+      <c r="D75" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E75" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G75" s="56" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="H75" s="57" t="inlineStr">
+        <is>
+          <t>Palmas</t>
+        </is>
+      </c>
+      <c r="I75" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J75" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="56" t="inlineStr">
+        <is>
+          <t>7927169001</t>
+        </is>
+      </c>
+      <c r="B76" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C76" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-PA 00432/2026</t>
+        </is>
+      </c>
+      <c r="D76" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E76" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G76" s="56" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="H76" s="57" t="inlineStr">
+        <is>
+          <t>Porto Nacional</t>
+        </is>
+      </c>
+      <c r="I76" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J76" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="56" t="inlineStr">
+        <is>
+          <t>7933726256</t>
+        </is>
+      </c>
+      <c r="B77" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C77" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-PO 00181/2026</t>
+        </is>
+      </c>
+      <c r="D77" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E77" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G77" s="56" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="H77" s="57" t="inlineStr">
+        <is>
+          <t>Mateiros</t>
+        </is>
+      </c>
+      <c r="I77" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J77" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="56" t="inlineStr">
+        <is>
+          <t>7911120026</t>
+        </is>
+      </c>
+      <c r="B78" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C78" s="57" t="inlineStr">
+        <is>
+          <t>DG-RD-PO 00444/2026</t>
+        </is>
+      </c>
+      <c r="D78" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E78" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G78" s="56" t="inlineStr">
+        <is>
+          <t>COCM-C</t>
+        </is>
+      </c>
+      <c r="H78" s="57" t="inlineStr">
+        <is>
+          <t>Ponte Alta Tocantins</t>
+        </is>
+      </c>
+      <c r="I78" s="58" t="inlineStr">
+        <is>
+          <t>Só no Mapeamento Criticidades</t>
+        </is>
+      </c>
+      <c r="J78" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="56" t="inlineStr">
+        <is>
+          <t>7908705049</t>
+        </is>
+      </c>
+      <c r="B79" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C79" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-DP 00409/2026</t>
+        </is>
+      </c>
+      <c r="D79" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E79" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="56" t="inlineStr">
+        <is>
+          <t>COCM-S</t>
+        </is>
+      </c>
+      <c r="H79" s="57" t="inlineStr">
+        <is>
+          <t>Aurora Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I79" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J79" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="56" t="inlineStr">
+        <is>
+          <t>7900230155</t>
+        </is>
+      </c>
+      <c r="B80" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C80" s="57" t="inlineStr">
+        <is>
+          <t>ETO-RD-GR 00685/2026</t>
+        </is>
+      </c>
+      <c r="D80" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E80" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="56" t="inlineStr">
+        <is>
+          <t>COCM-N</t>
+        </is>
+      </c>
+      <c r="H80" s="57" t="inlineStr">
+        <is>
+          <t>Palmeirante</t>
+        </is>
+      </c>
+      <c r="I80" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J80" s="23" t="inlineStr">
+        <is>
+          <t>Pendente (fora do posto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="56" t="inlineStr">
+        <is>
+          <t>7928564039</t>
+        </is>
+      </c>
+      <c r="B81" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C81" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00123/2026</t>
+        </is>
+      </c>
+      <c r="D81" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E81" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H81" s="57" t="inlineStr">
+        <is>
+          <t>Araguatins</t>
+        </is>
+      </c>
+      <c r="I81" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J81" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="56" t="inlineStr">
+        <is>
+          <t>7928241200</t>
+        </is>
+      </c>
+      <c r="B82" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C82" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00128/2026</t>
+        </is>
+      </c>
+      <c r="D82" s="56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E82" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H82" s="57" t="inlineStr">
+        <is>
+          <t>Sao Salvador Do Tocantins</t>
+        </is>
+      </c>
+      <c r="I82" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J82" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="56" t="inlineStr">
+        <is>
+          <t>5856070091</t>
+        </is>
+      </c>
+      <c r="B83" s="56" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C83" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00130/2026</t>
+        </is>
+      </c>
+      <c r="D83" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H83" s="57" t="inlineStr">
+        <is>
+          <t>Almas</t>
+        </is>
+      </c>
+      <c r="I83" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J83" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="59" t="inlineStr">
+        <is>
+          <t>5850308009</t>
+        </is>
+      </c>
+      <c r="B84" s="59" t="inlineStr">
+        <is>
+          <t>RT (58)</t>
+        </is>
+      </c>
+      <c r="C84" s="60" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00127/2026</t>
+        </is>
+      </c>
+      <c r="D84" s="59" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="E84" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="59" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H84" s="60" t="inlineStr">
+        <is>
+          <t>Guarai</t>
+        </is>
+      </c>
+      <c r="I84" s="60" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J84" s="36" t="inlineStr">
+        <is>
+          <t>CONCLUÍDA MAS AINDA NO POSTO (VERIFICAR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="56" t="inlineStr">
+        <is>
+          <t>7937102148</t>
+        </is>
+      </c>
+      <c r="B85" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C85" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00129/2026</t>
+        </is>
+      </c>
+      <c r="D85" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E85" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H85" s="57" t="inlineStr">
+        <is>
+          <t>Sao Valerio Da Natividade</t>
+        </is>
+      </c>
+      <c r="I85" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J85" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="56" t="inlineStr">
+        <is>
+          <t>7923673004</t>
+        </is>
+      </c>
+      <c r="B86" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C86" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00124/2026</t>
+        </is>
+      </c>
+      <c r="D86" s="56" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="E86" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H86" s="57" t="inlineStr">
+        <is>
+          <t>Araguaina</t>
+        </is>
+      </c>
+      <c r="I86" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J86" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="56" t="inlineStr">
+        <is>
+          <t>7900525015</t>
+        </is>
+      </c>
+      <c r="B87" s="56" t="inlineStr">
+        <is>
+          <t>RL (79)</t>
+        </is>
+      </c>
+      <c r="C87" s="57" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00125/2026</t>
+        </is>
+      </c>
+      <c r="D87" s="56" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E87" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="56" t="inlineStr">
+        <is>
+          <t>COEP</t>
+        </is>
+      </c>
+      <c r="H87" s="57" t="inlineStr">
+        <is>
+          <t>Pedro Afonso</t>
+        </is>
+      </c>
+      <c r="I87" s="57" t="inlineStr">
+        <is>
+          <t>SIM (detalhamento)</t>
+        </is>
+      </c>
+      <c r="J87" s="23" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A19:J19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2342,7 +5883,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9486,7 +13027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9598,32 +13139,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00156/2025</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>7957126085</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>Monte Santo do Tocantins</t>
         </is>
       </c>
-      <c r="D4" s="44" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E4" s="44" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="50" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
@@ -9652,7 +13193,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M4" s="44" t="inlineStr">
+      <c r="M4" s="49" t="inlineStr">
         <is>
           <t>0212600428</t>
         </is>
@@ -9664,32 +13205,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00050/2026</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>7953610256</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="50" t="inlineStr">
         <is>
           <t>Mateiros</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D5" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E5" s="44" t="inlineStr">
+      <c r="E5" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -9718,7 +13259,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M5" s="44" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9730,32 +13271,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00063/2026</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>7944559149</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr">
+      <c r="C6" s="50" t="inlineStr">
         <is>
           <t>Caseara</t>
         </is>
       </c>
-      <c r="D6" s="44" t="inlineStr">
+      <c r="D6" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E6" s="44" t="inlineStr">
+      <c r="E6" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F6" s="43" t="inlineStr">
+      <c r="F6" s="50" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
@@ -9779,12 +13320,12 @@
       <c r="K6" s="25" t="n">
         <v>51304.06</v>
       </c>
-      <c r="L6" s="44" t="inlineStr">
+      <c r="L6" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M6" s="44" t="inlineStr">
+      <c r="M6" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9796,32 +13337,32 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00158/2025</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>7942485096</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="50" t="inlineStr">
         <is>
           <t>Pindorama do Tocantins</t>
         </is>
       </c>
-      <c r="D7" s="44" t="inlineStr">
+      <c r="D7" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E7" s="44" t="inlineStr">
+      <c r="E7" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F7" s="43" t="inlineStr">
+      <c r="F7" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -9845,12 +13386,12 @@
       <c r="K7" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L7" s="44" t="inlineStr">
+      <c r="L7" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M7" s="44" t="inlineStr">
+      <c r="M7" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9862,32 +13403,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00129/2026</t>
         </is>
       </c>
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>7937102148</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>São Valério</t>
         </is>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D8" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E8" s="44" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F8" s="43" t="inlineStr">
+      <c r="F8" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -9911,12 +13452,12 @@
       <c r="K8" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L8" s="44" t="inlineStr">
+      <c r="L8" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M8" s="44" t="inlineStr">
+      <c r="M8" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9928,32 +13469,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00024/2026</t>
         </is>
       </c>
-      <c r="B9" s="44" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>7933585074</t>
         </is>
       </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
         <is>
           <t>Dianópolis</t>
         </is>
       </c>
-      <c r="D9" s="44" t="inlineStr">
+      <c r="D9" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E9" s="44" t="inlineStr">
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F9" s="43" t="inlineStr">
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -9977,12 +13518,12 @@
       <c r="K9" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L9" s="44" t="inlineStr">
+      <c r="L9" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M9" s="44" t="inlineStr">
+      <c r="M9" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9994,32 +13535,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00040/2026</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>7931608059</t>
         </is>
       </c>
-      <c r="C10" s="43" t="inlineStr">
+      <c r="C10" s="50" t="inlineStr">
         <is>
           <t>Taquaralto</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E10" s="44" t="inlineStr">
+      <c r="E10" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F10" s="43" t="inlineStr">
+      <c r="F10" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -10043,12 +13584,12 @@
       <c r="K10" s="25" t="n">
         <v>47414.74000000001</v>
       </c>
-      <c r="L10" s="44" t="inlineStr">
+      <c r="L10" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M10" s="44" t="inlineStr">
+      <c r="M10" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10060,32 +13601,32 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00126/2026</t>
         </is>
       </c>
-      <c r="B11" s="44" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>7931219078</t>
         </is>
       </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="C11" s="50" t="inlineStr">
         <is>
           <t>Pium</t>
         </is>
       </c>
-      <c r="D11" s="44" t="inlineStr">
+      <c r="D11" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E11" s="44" t="inlineStr">
+      <c r="E11" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F11" s="43" t="inlineStr">
+      <c r="F11" s="50" t="inlineStr">
         <is>
           <t>Sem compra</t>
         </is>
@@ -10109,12 +13650,12 @@
       <c r="K11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="44" t="inlineStr">
+      <c r="L11" s="49" t="inlineStr">
         <is>
           <t>Sem compra (COCM/definir)</t>
         </is>
       </c>
-      <c r="M11" s="44" t="inlineStr">
+      <c r="M11" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10126,32 +13667,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2026</t>
         </is>
       </c>
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>7929376022</t>
         </is>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="50" t="inlineStr">
         <is>
           <t>Babaçulândia</t>
         </is>
       </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="D12" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E12" s="44" t="inlineStr">
+      <c r="E12" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F12" s="43" t="inlineStr">
+      <c r="F12" s="50" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
@@ -10180,7 +13721,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M12" s="44" t="inlineStr">
+      <c r="M12" s="49" t="inlineStr">
         <is>
           <t>0612600565</t>
         </is>
@@ -10192,32 +13733,32 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00123/2026</t>
         </is>
       </c>
-      <c r="B13" s="44" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>7928564039</t>
         </is>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>Araguatins</t>
         </is>
       </c>
-      <c r="D13" s="44" t="inlineStr">
+      <c r="D13" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E13" s="44" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F13" s="43" t="inlineStr">
+      <c r="F13" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -10241,12 +13782,12 @@
       <c r="K13" s="25" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="L13" s="44" t="inlineStr">
+      <c r="L13" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M13" s="44" t="inlineStr">
+      <c r="M13" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10258,32 +13799,32 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00128/2026</t>
         </is>
       </c>
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>7928241200</t>
         </is>
       </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="C14" s="50" t="inlineStr">
         <is>
           <t>São Salvador</t>
         </is>
       </c>
-      <c r="D14" s="44" t="inlineStr">
+      <c r="D14" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E14" s="44" t="inlineStr">
+      <c r="E14" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F14" s="43" t="inlineStr">
+      <c r="F14" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -10307,12 +13848,12 @@
       <c r="K14" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L14" s="44" t="inlineStr">
+      <c r="L14" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M14" s="44" t="inlineStr">
+      <c r="M14" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10324,32 +13865,32 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00029/2026</t>
         </is>
       </c>
-      <c r="B15" s="44" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>7927646026</t>
         </is>
       </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>Ponte Alta</t>
         </is>
       </c>
-      <c r="D15" s="44" t="inlineStr">
+      <c r="D15" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E15" s="44" t="inlineStr">
+      <c r="E15" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F15" s="43" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -10373,12 +13914,12 @@
       <c r="K15" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L15" s="44" t="inlineStr">
+      <c r="L15" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M15" s="44" t="inlineStr">
+      <c r="M15" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10390,32 +13931,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00143/2025</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>7927446001</t>
         </is>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C16" s="50" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="D16" s="44" t="inlineStr">
+      <c r="D16" s="49" t="inlineStr">
         <is>
           <t>TAVRIDA</t>
         </is>
       </c>
-      <c r="E16" s="44" t="inlineStr">
+      <c r="E16" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F16" s="43" t="inlineStr">
+      <c r="F16" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -10439,12 +13980,12 @@
       <c r="K16" s="25" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="L16" s="44" t="inlineStr">
+      <c r="L16" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M16" s="44" t="inlineStr">
+      <c r="M16" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10456,32 +13997,32 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00045/2026</t>
         </is>
       </c>
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>7927396052</t>
         </is>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t>Formoso do Araguaia</t>
         </is>
       </c>
-      <c r="D17" s="44" t="inlineStr">
+      <c r="D17" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E17" s="44" t="inlineStr">
+      <c r="E17" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F17" s="43" t="inlineStr">
+      <c r="F17" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -10505,12 +14046,12 @@
       <c r="K17" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L17" s="44" t="inlineStr">
+      <c r="L17" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M17" s="44" t="inlineStr">
+      <c r="M17" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10522,32 +14063,32 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00051/2026</t>
         </is>
       </c>
-      <c r="B18" s="44" t="inlineStr">
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>7926442035</t>
         </is>
       </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="C18" s="50" t="inlineStr">
         <is>
           <t>Monte do Carmo</t>
         </is>
       </c>
-      <c r="D18" s="44" t="inlineStr">
+      <c r="D18" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E18" s="44" t="inlineStr">
+      <c r="E18" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F18" s="43" t="inlineStr">
+      <c r="F18" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -10571,12 +14112,12 @@
       <c r="K18" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L18" s="44" t="inlineStr">
+      <c r="L18" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M18" s="44" t="inlineStr">
+      <c r="M18" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10588,32 +14129,32 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00078/2026</t>
         </is>
       </c>
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>7926089013</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="50" t="inlineStr">
         <is>
           <t>Paraíso do Tocantins</t>
         </is>
       </c>
-      <c r="D19" s="44" t="inlineStr">
+      <c r="D19" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E19" s="44" t="inlineStr">
+      <c r="E19" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F19" s="43" t="inlineStr">
+      <c r="F19" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -10637,12 +14178,12 @@
       <c r="K19" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L19" s="44" t="inlineStr">
+      <c r="L19" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M19" s="44" t="inlineStr">
+      <c r="M19" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10654,32 +14195,32 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00048/2026</t>
         </is>
       </c>
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>7925871077</t>
         </is>
       </c>
-      <c r="C20" s="43" t="inlineStr">
+      <c r="C20" s="50" t="inlineStr">
         <is>
           <t>Goiatins</t>
         </is>
       </c>
-      <c r="D20" s="44" t="inlineStr">
+      <c r="D20" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E20" s="44" t="inlineStr">
+      <c r="E20" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F20" s="43" t="inlineStr">
+      <c r="F20" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -10703,12 +14244,12 @@
       <c r="K20" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L20" s="44" t="inlineStr">
+      <c r="L20" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M20" s="44" t="inlineStr">
+      <c r="M20" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10720,32 +14261,32 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00059/2026</t>
         </is>
       </c>
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>7925744087</t>
         </is>
       </c>
-      <c r="C21" s="43" t="inlineStr">
+      <c r="C21" s="50" t="inlineStr">
         <is>
           <t>Goianorte</t>
         </is>
       </c>
-      <c r="D21" s="44" t="inlineStr">
+      <c r="D21" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E21" s="44" t="inlineStr">
+      <c r="E21" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F21" s="43" t="inlineStr">
+      <c r="F21" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -10769,12 +14310,12 @@
       <c r="K21" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L21" s="44" t="inlineStr">
+      <c r="L21" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M21" s="44" t="inlineStr">
+      <c r="M21" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10786,32 +14327,32 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00058/2026</t>
         </is>
       </c>
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>7925733015</t>
         </is>
       </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="C22" s="50" t="inlineStr">
         <is>
           <t>Pedro Afonso</t>
         </is>
       </c>
-      <c r="D22" s="44" t="inlineStr">
+      <c r="D22" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E22" s="44" t="inlineStr">
+      <c r="E22" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F22" s="43" t="inlineStr">
+      <c r="F22" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -10835,12 +14376,12 @@
       <c r="K22" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L22" s="44" t="inlineStr">
+      <c r="L22" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M22" s="44" t="inlineStr">
+      <c r="M22" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10852,32 +14393,32 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00222/2025</t>
         </is>
       </c>
-      <c r="B23" s="44" t="inlineStr">
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>7925087021</t>
         </is>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C23" s="50" t="inlineStr">
         <is>
           <t>Paranã</t>
         </is>
       </c>
-      <c r="D23" s="44" t="inlineStr">
+      <c r="D23" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E23" s="44" t="inlineStr">
+      <c r="E23" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F23" s="43" t="inlineStr">
+      <c r="F23" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -10906,7 +14447,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M23" s="44" t="inlineStr">
+      <c r="M23" s="49" t="inlineStr">
         <is>
           <t>0412600392</t>
         </is>
@@ -10918,32 +14459,32 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00079/2025</t>
         </is>
       </c>
-      <c r="B24" s="44" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>7923927122</t>
         </is>
       </c>
-      <c r="C24" s="43" t="inlineStr">
+      <c r="C24" s="50" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="D24" s="44" t="inlineStr">
+      <c r="D24" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E24" s="44" t="inlineStr">
+      <c r="E24" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F24" s="43" t="inlineStr">
+      <c r="F24" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -10967,12 +14508,12 @@
       <c r="K24" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L24" s="44" t="inlineStr">
+      <c r="L24" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M24" s="44" t="inlineStr">
+      <c r="M24" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10984,32 +14525,32 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="43" t="inlineStr">
+      <c r="A25" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00124/2026</t>
         </is>
       </c>
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>7923673004</t>
         </is>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C25" s="50" t="inlineStr">
         <is>
           <t>Araguaína</t>
         </is>
       </c>
-      <c r="D25" s="44" t="inlineStr">
+      <c r="D25" s="49" t="inlineStr">
         <is>
           <t>ARTECHE P500</t>
         </is>
       </c>
-      <c r="E25" s="44" t="inlineStr">
+      <c r="E25" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F25" s="43" t="inlineStr">
+      <c r="F25" s="50" t="inlineStr">
         <is>
           <t>Relé</t>
         </is>
@@ -11033,12 +14574,12 @@
       <c r="K25" s="25" t="n">
         <v>21470.95</v>
       </c>
-      <c r="L25" s="44" t="inlineStr">
+      <c r="L25" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M25" s="44" t="inlineStr">
+      <c r="M25" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11050,32 +14591,32 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2025</t>
         </is>
       </c>
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B26" s="49" t="inlineStr">
         <is>
           <t>7920024127</t>
         </is>
       </c>
-      <c r="C26" s="43" t="inlineStr">
+      <c r="C26" s="50" t="inlineStr">
         <is>
           <t>Palmeiras do Tocantins</t>
         </is>
       </c>
-      <c r="D26" s="44" t="inlineStr">
+      <c r="D26" s="49" t="inlineStr">
         <is>
           <t>SCHNEIDER ADVC</t>
         </is>
       </c>
-      <c r="E26" s="44" t="inlineStr">
+      <c r="E26" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F26" s="43" t="inlineStr">
+      <c r="F26" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -11099,12 +14640,12 @@
       <c r="K26" s="25" t="n">
         <v>90191.96999999999</v>
       </c>
-      <c r="L26" s="44" t="inlineStr">
+      <c r="L26" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M26" s="44" t="inlineStr">
+      <c r="M26" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11116,32 +14657,32 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00074/2026</t>
         </is>
       </c>
-      <c r="B27" s="44" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>7919270014</t>
         </is>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C27" s="50" t="inlineStr">
         <is>
           <t>Pium</t>
         </is>
       </c>
-      <c r="D27" s="44" t="inlineStr">
+      <c r="D27" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E27" s="44" t="inlineStr">
+      <c r="E27" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F27" s="43" t="inlineStr">
+      <c r="F27" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -11165,12 +14706,12 @@
       <c r="K27" s="25" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="L27" s="44" t="inlineStr">
+      <c r="L27" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M27" s="44" t="inlineStr">
+      <c r="M27" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11182,32 +14723,32 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="43" t="inlineStr">
+      <c r="A28" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00114/2026</t>
         </is>
       </c>
-      <c r="B28" s="44" t="inlineStr">
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>7913662076</t>
         </is>
       </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="C28" s="50" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="D28" s="44" t="inlineStr">
+      <c r="D28" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E28" s="44" t="inlineStr">
+      <c r="E28" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F28" s="43" t="inlineStr">
+      <c r="F28" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -11231,12 +14772,12 @@
       <c r="K28" s="25" t="n">
         <v>33539.09</v>
       </c>
-      <c r="L28" s="44" t="inlineStr">
+      <c r="L28" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M28" s="44" t="inlineStr">
+      <c r="M28" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11248,32 +14789,32 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="43" t="inlineStr">
+      <c r="A29" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00086/2026</t>
         </is>
       </c>
-      <c r="B29" s="44" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>7908686014</t>
         </is>
       </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="C29" s="50" t="inlineStr">
         <is>
           <t>Pium</t>
         </is>
       </c>
-      <c r="D29" s="44" t="inlineStr">
+      <c r="D29" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E29" s="44" t="inlineStr">
+      <c r="E29" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F29" s="43" t="inlineStr">
+      <c r="F29" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -11302,7 +14843,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M29" s="44" t="inlineStr">
+      <c r="M29" s="49" t="inlineStr">
         <is>
           <t>0212600425</t>
         </is>
@@ -11314,32 +14855,32 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00038/2026</t>
         </is>
       </c>
-      <c r="B30" s="44" t="inlineStr">
+      <c r="B30" s="49" t="inlineStr">
         <is>
           <t>7908249152</t>
         </is>
       </c>
-      <c r="C30" s="43" t="inlineStr">
+      <c r="C30" s="50" t="inlineStr">
         <is>
           <t>Santa Rosa</t>
         </is>
       </c>
-      <c r="D30" s="44" t="inlineStr">
+      <c r="D30" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E30" s="44" t="inlineStr">
+      <c r="E30" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F30" s="43" t="inlineStr">
+      <c r="F30" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -11363,12 +14904,12 @@
       <c r="K30" s="25" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="L30" s="44" t="inlineStr">
+      <c r="L30" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M30" s="44" t="inlineStr">
+      <c r="M30" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11380,32 +14921,32 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="43" t="inlineStr">
+      <c r="A31" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00122/2026</t>
         </is>
       </c>
-      <c r="B31" s="44" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>7908196047</t>
         </is>
       </c>
-      <c r="C31" s="43" t="inlineStr">
+      <c r="C31" s="50" t="inlineStr">
         <is>
           <t>Figueirópolis</t>
         </is>
       </c>
-      <c r="D31" s="44" t="inlineStr">
+      <c r="D31" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E31" s="44" t="inlineStr">
+      <c r="E31" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F31" s="43" t="inlineStr">
+      <c r="F31" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -11429,12 +14970,12 @@
       <c r="K31" s="25" t="n">
         <v>66619.48</v>
       </c>
-      <c r="L31" s="44" t="inlineStr">
+      <c r="L31" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M31" s="44" t="inlineStr">
+      <c r="M31" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11446,32 +14987,32 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="A32" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00184/2025</t>
         </is>
       </c>
-      <c r="B32" s="44" t="inlineStr">
+      <c r="B32" s="49" t="inlineStr">
         <is>
           <t>7903112004</t>
         </is>
       </c>
-      <c r="C32" s="43" t="inlineStr">
+      <c r="C32" s="50" t="inlineStr">
         <is>
           <t>Araguaína</t>
         </is>
       </c>
-      <c r="D32" s="44" t="inlineStr">
+      <c r="D32" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E32" s="44" t="inlineStr">
+      <c r="E32" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F32" s="43" t="inlineStr">
+      <c r="F32" s="50" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
@@ -11500,7 +15041,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M32" s="44" t="inlineStr">
+      <c r="M32" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11512,32 +15053,32 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00061/2026</t>
         </is>
       </c>
-      <c r="B33" s="44" t="inlineStr">
+      <c r="B33" s="49" t="inlineStr">
         <is>
           <t>7901110084</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C33" s="50" t="inlineStr">
         <is>
           <t>Divinópolis</t>
         </is>
       </c>
-      <c r="D33" s="44" t="inlineStr">
+      <c r="D33" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E33" s="44" t="inlineStr">
+      <c r="E33" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F33" s="43" t="inlineStr">
+      <c r="F33" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -11561,12 +15102,12 @@
       <c r="K33" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L33" s="44" t="inlineStr">
+      <c r="L33" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M33" s="44" t="inlineStr">
+      <c r="M33" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11578,32 +15119,32 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="43" t="inlineStr">
+      <c r="A34" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00113/2026</t>
         </is>
       </c>
-      <c r="B34" s="44" t="inlineStr">
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>7900594026</t>
         </is>
       </c>
-      <c r="C34" s="43" t="inlineStr">
+      <c r="C34" s="50" t="inlineStr">
         <is>
           <t>Ponte Alta</t>
         </is>
       </c>
-      <c r="D34" s="44" t="inlineStr">
+      <c r="D34" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E34" s="44" t="inlineStr">
+      <c r="E34" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F34" s="43" t="inlineStr">
+      <c r="F34" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -11632,7 +15173,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M34" s="44" t="inlineStr">
+      <c r="M34" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11644,32 +15185,32 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="A35" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00080/2026</t>
         </is>
       </c>
-      <c r="B35" s="44" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>7900573047</t>
         </is>
       </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="C35" s="50" t="inlineStr">
         <is>
           <t>Figueirópolis</t>
         </is>
       </c>
-      <c r="D35" s="44" t="inlineStr">
+      <c r="D35" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E35" s="44" t="inlineStr">
+      <c r="E35" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F35" s="43" t="inlineStr">
+      <c r="F35" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -11698,7 +15239,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M35" s="44" t="inlineStr">
+      <c r="M35" s="49" t="inlineStr">
         <is>
           <t>0412600391</t>
         </is>
@@ -11710,32 +15251,32 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="43" t="inlineStr">
+      <c r="A36" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00173/2025</t>
         </is>
       </c>
-      <c r="B36" s="44" t="inlineStr">
+      <c r="B36" s="49" t="inlineStr">
         <is>
           <t>7900535058</t>
         </is>
       </c>
-      <c r="C36" s="43" t="inlineStr">
+      <c r="C36" s="50" t="inlineStr">
         <is>
           <t>Santa Fé do Araguaia</t>
         </is>
       </c>
-      <c r="D36" s="44" t="inlineStr">
+      <c r="D36" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E36" s="44" t="inlineStr">
+      <c r="E36" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F36" s="43" t="inlineStr">
+      <c r="F36" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -11759,12 +15300,12 @@
       <c r="K36" s="25" t="n">
         <v>89455.53999999999</v>
       </c>
-      <c r="L36" s="44" t="inlineStr">
+      <c r="L36" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M36" s="44" t="inlineStr">
+      <c r="M36" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11776,32 +15317,32 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="43" t="inlineStr">
+      <c r="A37" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00102/2025</t>
         </is>
       </c>
-      <c r="B37" s="44" t="inlineStr">
+      <c r="B37" s="49" t="inlineStr">
         <is>
           <t>7900532053</t>
         </is>
       </c>
-      <c r="C37" s="43" t="inlineStr">
+      <c r="C37" s="50" t="inlineStr">
         <is>
           <t>Piraquê</t>
         </is>
       </c>
-      <c r="D37" s="44" t="inlineStr">
+      <c r="D37" s="49" t="inlineStr">
         <is>
           <t>(sem cadastro nos Ajustes)</t>
         </is>
       </c>
-      <c r="E37" s="44" t="inlineStr">
+      <c r="E37" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F37" s="43" t="inlineStr">
+      <c r="F37" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -11825,12 +15366,12 @@
       <c r="K37" s="25" t="n">
         <v>104067.62</v>
       </c>
-      <c r="L37" s="44" t="inlineStr">
+      <c r="L37" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="M37" s="44" t="inlineStr">
+      <c r="M37" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11842,32 +15383,32 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="43" t="inlineStr">
+      <c r="A38" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00125/2026</t>
         </is>
       </c>
-      <c r="B38" s="44" t="inlineStr">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>7900525015</t>
         </is>
       </c>
-      <c r="C38" s="43" t="inlineStr">
+      <c r="C38" s="50" t="inlineStr">
         <is>
           <t>Pedro Afonso</t>
         </is>
       </c>
-      <c r="D38" s="44" t="inlineStr">
+      <c r="D38" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E38" s="44" t="inlineStr">
+      <c r="E38" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F38" s="43" t="inlineStr">
+      <c r="F38" s="50" t="inlineStr">
         <is>
           <t>Sem compra</t>
         </is>
@@ -11891,12 +15432,12 @@
       <c r="K38" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="44" t="inlineStr">
+      <c r="L38" s="49" t="inlineStr">
         <is>
           <t>Sem compra (COCM/definir)</t>
         </is>
       </c>
-      <c r="M38" s="44" t="inlineStr">
+      <c r="M38" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11908,32 +15449,32 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="43" t="inlineStr">
+      <c r="A39" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00087/2026</t>
         </is>
       </c>
-      <c r="B39" s="44" t="inlineStr">
+      <c r="B39" s="49" t="inlineStr">
         <is>
           <t>7900453110</t>
         </is>
       </c>
-      <c r="C39" s="43" t="inlineStr">
+      <c r="C39" s="50" t="inlineStr">
         <is>
           <t>Santa Rita do Tocantins</t>
         </is>
       </c>
-      <c r="D39" s="44" t="inlineStr">
+      <c r="D39" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E39" s="44" t="inlineStr">
+      <c r="E39" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F39" s="43" t="inlineStr">
+      <c r="F39" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -11962,7 +15503,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M39" s="44" t="inlineStr">
+      <c r="M39" s="49" t="inlineStr">
         <is>
           <t>0312600264</t>
         </is>
@@ -11974,32 +15515,32 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="43" t="inlineStr">
+      <c r="A40" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00084/2026</t>
         </is>
       </c>
-      <c r="B40" s="44" t="inlineStr">
+      <c r="B40" s="49" t="inlineStr">
         <is>
           <t>7900117013</t>
         </is>
       </c>
-      <c r="C40" s="43" t="inlineStr">
+      <c r="C40" s="50" t="inlineStr">
         <is>
           <t>Paraíso do Tocantins</t>
         </is>
       </c>
-      <c r="D40" s="44" t="inlineStr">
+      <c r="D40" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E40" s="44" t="inlineStr">
+      <c r="E40" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F40" s="43" t="inlineStr">
+      <c r="F40" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -12028,7 +15569,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M40" s="44" t="inlineStr">
+      <c r="M40" s="49" t="inlineStr">
         <is>
           <t>0212600422</t>
         </is>
@@ -12040,32 +15581,32 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="43" t="inlineStr">
+      <c r="A41" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00177/2025</t>
         </is>
       </c>
-      <c r="B41" s="44" t="inlineStr">
+      <c r="B41" s="49" t="inlineStr">
         <is>
           <t>7908705049</t>
         </is>
       </c>
-      <c r="C41" s="43" t="inlineStr">
+      <c r="C41" s="50" t="inlineStr">
         <is>
           <t>Aurora do Tocantins</t>
         </is>
       </c>
-      <c r="D41" s="44" t="inlineStr">
+      <c r="D41" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E41" s="44" t="inlineStr">
+      <c r="E41" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F41" s="43" t="inlineStr">
+      <c r="F41" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -12094,7 +15635,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M41" s="44" t="inlineStr">
+      <c r="M41" s="49" t="inlineStr">
         <is>
           <t>0512600135</t>
         </is>
@@ -12106,32 +15647,32 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="43" t="inlineStr">
+      <c r="A42" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00082/2026</t>
         </is>
       </c>
-      <c r="B42" s="44" t="inlineStr">
+      <c r="B42" s="49" t="inlineStr">
         <is>
           <t>7933766059</t>
         </is>
       </c>
-      <c r="C42" s="43" t="inlineStr">
+      <c r="C42" s="50" t="inlineStr">
         <is>
           <t>Taquaralto</t>
         </is>
       </c>
-      <c r="D42" s="44" t="inlineStr">
+      <c r="D42" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E42" s="44" t="inlineStr">
+      <c r="E42" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F42" s="43" t="inlineStr">
+      <c r="F42" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -12160,7 +15701,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M42" s="44" t="inlineStr">
+      <c r="M42" s="49" t="inlineStr">
         <is>
           <t>0112600424</t>
         </is>
@@ -12238,32 +15779,32 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="43" t="inlineStr">
+      <c r="A44" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00085/2026</t>
         </is>
       </c>
-      <c r="B44" s="44" t="inlineStr">
+      <c r="B44" s="49" t="inlineStr">
         <is>
           <t>7938137007</t>
         </is>
       </c>
-      <c r="C44" s="43" t="inlineStr">
+      <c r="C44" s="50" t="inlineStr">
         <is>
           <t>Miracema do Tocantins</t>
         </is>
       </c>
-      <c r="D44" s="44" t="inlineStr">
+      <c r="D44" s="49" t="inlineStr">
         <is>
           <t>SCHNEIDER ADVC</t>
         </is>
       </c>
-      <c r="E44" s="44" t="inlineStr">
+      <c r="E44" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F44" s="43" t="inlineStr">
+      <c r="F44" s="50" t="inlineStr">
         <is>
           <t>Componentes/Acessórios</t>
         </is>
@@ -12292,7 +15833,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M44" s="44" t="inlineStr">
+      <c r="M44" s="49" t="inlineStr">
         <is>
           <t>0212600423</t>
         </is>
@@ -12304,32 +15845,32 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="43" t="inlineStr">
+      <c r="A45" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00106/2025</t>
         </is>
       </c>
-      <c r="B45" s="44" t="inlineStr">
+      <c r="B45" s="49" t="inlineStr">
         <is>
           <t>7900230155</t>
         </is>
       </c>
-      <c r="C45" s="43" t="inlineStr">
+      <c r="C45" s="50" t="inlineStr">
         <is>
           <t>Palmeirante</t>
         </is>
       </c>
-      <c r="D45" s="44" t="inlineStr">
+      <c r="D45" s="49" t="inlineStr">
         <is>
           <t>COOPER F6</t>
         </is>
       </c>
-      <c r="E45" s="44" t="inlineStr">
+      <c r="E45" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F45" s="43" t="inlineStr">
+      <c r="F45" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -12358,7 +15899,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M45" s="44" t="inlineStr">
+      <c r="M45" s="49" t="inlineStr">
         <is>
           <t>0712600318</t>
         </is>
@@ -12370,32 +15911,32 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="43" t="inlineStr">
+      <c r="A46" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00181/2025</t>
         </is>
       </c>
-      <c r="B46" s="44" t="inlineStr">
+      <c r="B46" s="49" t="inlineStr">
         <is>
           <t>7943790134</t>
         </is>
       </c>
-      <c r="C46" s="43" t="inlineStr">
+      <c r="C46" s="50" t="inlineStr">
         <is>
           <t>Esperantina</t>
         </is>
       </c>
-      <c r="D46" s="44" t="inlineStr">
+      <c r="D46" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E46" s="44" t="inlineStr">
+      <c r="E46" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F46" s="43" t="inlineStr">
+      <c r="F46" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -12424,7 +15965,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M46" s="44" t="inlineStr">
+      <c r="M46" s="49" t="inlineStr">
         <is>
           <t>0662600266</t>
         </is>
@@ -12436,32 +15977,32 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="43" t="inlineStr">
+      <c r="A47" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00178/2025</t>
         </is>
       </c>
-      <c r="B47" s="44" t="inlineStr">
+      <c r="B47" s="49" t="inlineStr">
         <is>
           <t>7900018004</t>
         </is>
       </c>
-      <c r="C47" s="43" t="inlineStr">
+      <c r="C47" s="50" t="inlineStr">
         <is>
           <t>Araguaína</t>
         </is>
       </c>
-      <c r="D47" s="44" t="inlineStr">
+      <c r="D47" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E47" s="44" t="inlineStr">
+      <c r="E47" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F47" s="43" t="inlineStr">
+      <c r="F47" s="50" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
@@ -12490,7 +16031,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M47" s="44" t="inlineStr">
+      <c r="M47" s="49" t="inlineStr">
         <is>
           <t>0612600439</t>
         </is>
@@ -12502,32 +16043,32 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="43" t="inlineStr">
+      <c r="A48" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00083/2026</t>
         </is>
       </c>
-      <c r="B48" s="44" t="inlineStr">
+      <c r="B48" s="49" t="inlineStr">
         <is>
           <t>7931610122</t>
         </is>
       </c>
-      <c r="C48" s="43" t="inlineStr">
+      <c r="C48" s="50" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="D48" s="44" t="inlineStr">
+      <c r="D48" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E48" s="44" t="inlineStr">
+      <c r="E48" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F48" s="43" t="inlineStr">
+      <c r="F48" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -12556,7 +16097,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M48" s="44" t="inlineStr">
+      <c r="M48" s="49" t="inlineStr">
         <is>
           <t>0112600383</t>
         </is>
@@ -12568,32 +16109,32 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="43" t="inlineStr">
+      <c r="A49" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00081/2026</t>
         </is>
       </c>
-      <c r="B49" s="44" t="inlineStr">
+      <c r="B49" s="49" t="inlineStr">
         <is>
           <t>7957620015</t>
         </is>
       </c>
-      <c r="C49" s="43" t="inlineStr">
+      <c r="C49" s="50" t="inlineStr">
         <is>
           <t>Pedro Afonso</t>
         </is>
       </c>
-      <c r="D49" s="44" t="inlineStr">
+      <c r="D49" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E49" s="44" t="inlineStr">
+      <c r="E49" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F49" s="43" t="inlineStr">
+      <c r="F49" s="50" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
@@ -12622,7 +16163,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M49" s="44" t="inlineStr">
+      <c r="M49" s="49" t="inlineStr">
         <is>
           <t>0712600316</t>
         </is>
@@ -12700,32 +16241,32 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="43" t="inlineStr">
+      <c r="A51" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00151/2026</t>
         </is>
       </c>
-      <c r="B51" s="44" t="inlineStr">
+      <c r="B51" s="49" t="inlineStr">
         <is>
           <t>7955520116</t>
         </is>
       </c>
-      <c r="C51" s="43" t="inlineStr">
+      <c r="C51" s="50" t="inlineStr">
         <is>
           <t>Chapada da Natividade</t>
         </is>
       </c>
-      <c r="D51" s="44" t="inlineStr">
+      <c r="D51" s="49" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E51" s="44" t="inlineStr">
+      <c r="E51" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F51" s="43" t="inlineStr">
+      <c r="F51" s="50" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
@@ -12754,7 +16295,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M51" s="44" t="inlineStr">
+      <c r="M51" s="49" t="inlineStr">
         <is>
           <t>0512600178</t>
         </is>
@@ -12855,7 +16396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13060,30 +16601,30 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00123/2025</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>5858783119</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="50" t="inlineStr">
         <is>
           <t>São Bento do Tocantins</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D5" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E5" s="44" t="n">
+      <c r="E5" s="49" t="n">
         <v>400</v>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="50" t="inlineStr">
         <is>
           <t>Célula de regulador</t>
         </is>
@@ -13093,10 +16634,10 @@
           <t>3 células (óleo furtado)</t>
         </is>
       </c>
-      <c r="H5" s="44" t="n">
+      <c r="H5" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="43" t="inlineStr">
+      <c r="I5" s="50" t="inlineStr">
         <is>
           <t>690241</t>
         </is>
@@ -13123,7 +16664,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="P5" s="44" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>0662600361</t>
         </is>
@@ -13135,30 +16676,30 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00130/2026</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>5856070091</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr">
+      <c r="C6" s="50" t="inlineStr">
         <is>
           <t>Almas</t>
         </is>
       </c>
-      <c r="D6" s="44" t="inlineStr">
+      <c r="D6" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="49" t="n">
         <v>400</v>
       </c>
-      <c r="F6" s="43" t="inlineStr">
+      <c r="F6" s="50" t="inlineStr">
         <is>
           <t>Célula de regulador</t>
         </is>
@@ -13168,10 +16709,10 @@
           <t>3 células furtadas</t>
         </is>
       </c>
-      <c r="H6" s="44" t="n">
+      <c r="H6" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="43" t="inlineStr">
+      <c r="I6" s="50" t="inlineStr">
         <is>
           <t>690241</t>
         </is>
@@ -13193,12 +16734,12 @@
       <c r="N6" s="25" t="n">
         <v>460999.9</v>
       </c>
-      <c r="O6" s="44" t="inlineStr">
+      <c r="O6" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="P6" s="44" t="inlineStr">
+      <c r="P6" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13210,30 +16751,30 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00199/2025</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>5855411017</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="50" t="inlineStr">
         <is>
           <t>Barrolândia</t>
         </is>
       </c>
-      <c r="D7" s="44" t="inlineStr">
+      <c r="D7" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="49" t="n">
         <v>239</v>
       </c>
-      <c r="F7" s="43" t="inlineStr">
+      <c r="F7" s="50" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
@@ -13243,10 +16784,10 @@
           <t>Controle c/ nobreak</t>
         </is>
       </c>
-      <c r="H7" s="44" t="n">
+      <c r="H7" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="43" t="inlineStr">
+      <c r="I7" s="50" t="inlineStr">
         <is>
           <t>651638</t>
         </is>
@@ -13273,7 +16814,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="P7" s="44" t="inlineStr">
+      <c r="P7" s="49" t="inlineStr">
         <is>
           <t>0212600536</t>
         </is>
@@ -13285,30 +16826,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00160/2025</t>
         </is>
       </c>
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>5854566043</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>Silvanópolis</t>
         </is>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D8" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="49" t="n">
         <v>400</v>
       </c>
-      <c r="F8" s="43" t="inlineStr">
+      <c r="F8" s="50" t="inlineStr">
         <is>
           <t>Célula de regulador</t>
         </is>
@@ -13318,10 +16859,10 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="H8" s="44" t="n">
+      <c r="H8" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="43" t="inlineStr">
+      <c r="I8" s="50" t="inlineStr">
         <is>
           <t>690241</t>
         </is>
@@ -13348,7 +16889,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="P8" s="44" t="inlineStr">
+      <c r="P8" s="49" t="inlineStr">
         <is>
           <t>0312600352</t>
         </is>
@@ -13360,30 +16901,30 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00127/2026</t>
         </is>
       </c>
-      <c r="B9" s="44" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>5850308009</t>
         </is>
       </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
         <is>
           <t>Guaraí</t>
         </is>
       </c>
-      <c r="D9" s="44" t="inlineStr">
+      <c r="D9" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="49" t="n">
         <v>239</v>
       </c>
-      <c r="F9" s="43" t="inlineStr">
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
@@ -13393,10 +16934,10 @@
           <t>Controle c/ nobreak</t>
         </is>
       </c>
-      <c r="H9" s="44" t="n">
+      <c r="H9" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="43" t="inlineStr">
+      <c r="I9" s="50" t="inlineStr">
         <is>
           <t>651638</t>
         </is>
@@ -13423,7 +16964,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="P9" s="44" t="inlineStr">
+      <c r="P9" s="49" t="inlineStr">
         <is>
           <t>0712600418</t>
         </is>
@@ -13435,30 +16976,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00167/2025</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>5844630060</t>
         </is>
       </c>
-      <c r="C10" s="43" t="inlineStr">
+      <c r="C10" s="50" t="inlineStr">
         <is>
           <t>Nova Olinda</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="49" t="n">
         <v>239</v>
       </c>
-      <c r="F10" s="43" t="inlineStr">
+      <c r="F10" s="50" t="inlineStr">
         <is>
           <t>Célula de regulador</t>
         </is>
@@ -13468,10 +17009,10 @@
           <t>Célula fase A</t>
         </is>
       </c>
-      <c r="H10" s="44" t="n">
+      <c r="H10" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="43" t="inlineStr">
+      <c r="I10" s="50" t="inlineStr">
         <is>
           <t>690236</t>
         </is>
@@ -13498,7 +17039,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="P10" s="44" t="inlineStr">
+      <c r="P10" s="49" t="inlineStr">
         <is>
           <t>0612600626</t>
         </is>
@@ -13510,32 +17051,32 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00095/2026</t>
         </is>
       </c>
-      <c r="B11" s="44" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>5836786094</t>
         </is>
       </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="C11" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="44" t="inlineStr">
+      <c r="D11" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E11" s="44" t="inlineStr">
+      <c r="E11" s="49" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="F11" s="43" t="inlineStr">
+      <c r="F11" s="50" t="inlineStr">
         <is>
           <t>Célula de regulador</t>
         </is>
@@ -13545,10 +17086,10 @@
           <t>3 células (equipamento furtado)</t>
         </is>
       </c>
-      <c r="H11" s="44" t="n">
+      <c r="H11" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="43" t="inlineStr">
+      <c r="I11" s="50" t="inlineStr">
         <is>
           <t>690240</t>
         </is>
@@ -13570,12 +17111,12 @@
       <c r="N11" s="25" t="n">
         <v>253479.73</v>
       </c>
-      <c r="O11" s="44" t="inlineStr">
+      <c r="O11" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="P11" s="44" t="inlineStr">
+      <c r="P11" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13587,30 +17128,30 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00077/2026</t>
         </is>
       </c>
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>5801866013</t>
         </is>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="50" t="inlineStr">
         <is>
           <t>Paraíso do Tocantins</t>
         </is>
       </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="D12" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="49" t="n">
         <v>167</v>
       </c>
-      <c r="F12" s="43" t="inlineStr">
+      <c r="F12" s="50" t="inlineStr">
         <is>
           <t>Célula de regulador</t>
         </is>
@@ -13620,10 +17161,10 @@
           <t>Célula fase C</t>
         </is>
       </c>
-      <c r="H12" s="44" t="n">
+      <c r="H12" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="43" t="inlineStr">
+      <c r="I12" s="50" t="inlineStr">
         <is>
           <t>690669</t>
         </is>
@@ -13650,7 +17191,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="P12" s="44" t="inlineStr">
+      <c r="P12" s="49" t="inlineStr">
         <is>
           <t>0212600539</t>
         </is>
@@ -13662,32 +17203,32 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00221/2025</t>
         </is>
       </c>
-      <c r="B13" s="44" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>5800961074</t>
         </is>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>Dianópolis</t>
         </is>
       </c>
-      <c r="D13" s="44" t="inlineStr">
+      <c r="D13" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E13" s="44" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="F13" s="43" t="inlineStr">
+      <c r="F13" s="50" t="inlineStr">
         <is>
           <t>Célula de regulador</t>
         </is>
@@ -13697,10 +17238,10 @@
           <t>3 células</t>
         </is>
       </c>
-      <c r="H13" s="44" t="n">
+      <c r="H13" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="43" t="inlineStr">
+      <c r="I13" s="50" t="inlineStr">
         <is>
           <t>690240</t>
         </is>
@@ -13722,12 +17263,12 @@
       <c r="N13" s="25" t="n">
         <v>253479.73</v>
       </c>
-      <c r="O13" s="44" t="inlineStr">
+      <c r="O13" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="P13" s="44" t="inlineStr">
+      <c r="P13" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13739,30 +17280,30 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00115/2026</t>
         </is>
       </c>
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>5800859011</t>
         </is>
       </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="C14" s="50" t="inlineStr">
         <is>
           <t>Tupirama</t>
         </is>
       </c>
-      <c r="D14" s="44" t="inlineStr">
+      <c r="D14" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="E14" s="44" t="n">
+      <c r="E14" s="49" t="n">
         <v>219</v>
       </c>
-      <c r="F14" s="43" t="inlineStr">
+      <c r="F14" s="50" t="inlineStr">
         <is>
           <t>Controle completo</t>
         </is>
@@ -13772,10 +17313,10 @@
           <t>Controle c/ nobreak (retrofit RUA)</t>
         </is>
       </c>
-      <c r="H14" s="44" t="n">
+      <c r="H14" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="43" t="inlineStr">
+      <c r="I14" s="50" t="inlineStr">
         <is>
           <t>651638</t>
         </is>
@@ -13802,7 +17343,7 @@
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="P14" s="44" t="inlineStr">
+      <c r="P14" s="49" t="inlineStr">
         <is>
           <t>0712600419</t>
         </is>
@@ -13814,30 +17355,30 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00187/2025</t>
         </is>
       </c>
-      <c r="B15" s="44" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>5800371025</t>
         </is>
       </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>Arapoema</t>
         </is>
       </c>
-      <c r="D15" s="44" t="inlineStr">
+      <c r="D15" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E15" s="44" t="n">
+      <c r="E15" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="F15" s="43" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>Controle + células</t>
         </is>
@@ -13847,10 +17388,10 @@
           <t>Controle RUA + kit comunicação + 3 células</t>
         </is>
       </c>
-      <c r="H15" s="44" t="n">
+      <c r="H15" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="43" t="inlineStr">
+      <c r="I15" s="50" t="inlineStr">
         <is>
           <t>651638 + 3x 690240</t>
         </is>
@@ -13872,12 +17413,12 @@
       <c r="N15" s="25" t="n">
         <v>282925.12</v>
       </c>
-      <c r="O15" s="44" t="inlineStr">
+      <c r="O15" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="P15" s="44" t="inlineStr">
+      <c r="P15" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13889,32 +17430,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00117/2026</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>5800090147</t>
         </is>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C16" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D16" s="44" t="inlineStr">
+      <c r="D16" s="49" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="E16" s="44" t="inlineStr">
+      <c r="E16" s="49" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="F16" s="43" t="inlineStr">
+      <c r="F16" s="50" t="inlineStr">
         <is>
           <t>Célula de regulador</t>
         </is>
@@ -13924,10 +17465,10 @@
           <t>Célula fase C (microswitch)</t>
         </is>
       </c>
-      <c r="H16" s="44" t="n">
+      <c r="H16" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="43" t="inlineStr">
+      <c r="I16" s="50" t="inlineStr">
         <is>
           <t>690240</t>
         </is>
@@ -13949,12 +17490,12 @@
       <c r="N16" s="25" t="n">
         <v>138038.91</v>
       </c>
-      <c r="O16" s="44" t="inlineStr">
+      <c r="O16" s="49" t="inlineStr">
         <is>
           <t>Para avançar (compra)</t>
         </is>
       </c>
-      <c r="P16" s="44" t="inlineStr">
+      <c r="P16" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14139,7 +17680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14227,12 +17768,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ENC-RD-PS 00806/2025</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>5901003014</t>
         </is>
@@ -14242,18 +17783,18 @@
           <t>Aterramento rompido entre células A e B</t>
         </is>
       </c>
-      <c r="D4" s="44" t="n">
+      <c r="D4" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="44" t="n">
+      <c r="E4" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="44" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="44" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14275,12 +17816,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00002/2026</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>5900038047</t>
         </is>
@@ -14290,18 +17831,18 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="D5" s="44" t="n">
+      <c r="D5" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="44" t="n">
+      <c r="E5" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="44" t="inlineStr">
+      <c r="F5" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="44" t="inlineStr">
+      <c r="G5" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14321,12 +17862,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00018/2024</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>5952243122</t>
         </is>
@@ -14336,18 +17877,18 @@
           <t>Células fases B e C</t>
         </is>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="44" t="inlineStr">
+      <c r="F6" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="44" t="inlineStr">
+      <c r="G6" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14367,12 +17908,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00030/2023</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>5900438097</t>
         </is>
@@ -14382,20 +17923,20 @@
           <t>A definir (não aceita fechamento)</t>
         </is>
       </c>
-      <c r="D7" s="44" t="inlineStr">
+      <c r="D7" s="49" t="inlineStr">
         <is>
           <t>não informado</t>
         </is>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="44" t="inlineStr">
+      <c r="F7" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="44" t="inlineStr">
+      <c r="G7" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14415,12 +17956,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00047/2026</t>
         </is>
       </c>
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>5950106122</t>
         </is>
@@ -14430,20 +17971,20 @@
           <t>A definir (defeito interno)</t>
         </is>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D8" s="49" t="inlineStr">
         <is>
           <t>não informado</t>
         </is>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="44" t="inlineStr">
+      <c r="F8" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="44" t="inlineStr">
+      <c r="G8" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14463,12 +18004,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00058/2024</t>
         </is>
       </c>
-      <c r="B9" s="44" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>5924849004</t>
         </is>
@@ -14478,18 +18019,18 @@
           <t>3 células (fases A, B e C)</t>
         </is>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="44" t="inlineStr">
+      <c r="F9" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="44" t="inlineStr">
+      <c r="G9" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14509,12 +18050,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00060/2024</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>5913313004</t>
         </is>
@@ -14524,20 +18065,20 @@
           <t>A definir (não aceitou fechamento)</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="49" t="inlineStr">
         <is>
           <t>não informado</t>
         </is>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="44" t="inlineStr">
+      <c r="F10" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="44" t="inlineStr">
+      <c r="G10" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14557,12 +18098,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00064/2025</t>
         </is>
       </c>
-      <c r="B11" s="44" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>5900293123</t>
         </is>
@@ -14572,18 +18113,18 @@
           <t>Célula fase A</t>
         </is>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="44" t="inlineStr">
+      <c r="F11" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="44" t="inlineStr">
+      <c r="G11" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14603,12 +18144,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00073/2025</t>
         </is>
       </c>
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>5900489122</t>
         </is>
@@ -14618,18 +18159,18 @@
           <t>3 células (banco completo)</t>
         </is>
       </c>
-      <c r="D12" s="44" t="n">
+      <c r="D12" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="44" t="inlineStr">
+      <c r="F12" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="G12" s="44" t="n">
+      <c r="G12" s="49" t="n">
         <v>600</v>
       </c>
       <c r="H12" s="27" t="inlineStr">
@@ -14647,12 +18188,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00074/2025</t>
         </is>
       </c>
-      <c r="B13" s="44" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>5952202122</t>
         </is>
@@ -14662,18 +18203,18 @@
           <t>Células fases A e B</t>
         </is>
       </c>
-      <c r="D13" s="44" t="n">
+      <c r="D13" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="44" t="inlineStr">
+      <c r="F13" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="G13" s="44" t="n">
+      <c r="G13" s="49" t="n">
         <v>300</v>
       </c>
       <c r="H13" s="27" t="inlineStr">
@@ -14691,12 +18232,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00075/2025</t>
         </is>
       </c>
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>5952327122</t>
         </is>
@@ -14706,18 +18247,18 @@
           <t>3 células (banco completo)</t>
         </is>
       </c>
-      <c r="D14" s="44" t="n">
+      <c r="D14" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="44" t="n">
+      <c r="E14" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="44" t="inlineStr">
+      <c r="F14" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="G14" s="44" t="inlineStr">
+      <c r="G14" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14737,12 +18278,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00076/2025</t>
         </is>
       </c>
-      <c r="B15" s="44" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>5951650122</t>
         </is>
@@ -14752,18 +18293,18 @@
           <t>Células fases B e C</t>
         </is>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="44" t="n">
+      <c r="E15" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="44" t="inlineStr">
+      <c r="F15" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="44" t="inlineStr">
+      <c r="G15" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14783,12 +18324,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00077/2025</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>5907243122</t>
         </is>
@@ -14798,18 +18339,18 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="D16" s="44" t="n">
+      <c r="D16" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="44" t="n">
+      <c r="E16" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="44" t="inlineStr">
+      <c r="F16" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="44" t="inlineStr">
+      <c r="G16" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14829,12 +18370,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00082/2025</t>
         </is>
       </c>
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>5901886003</t>
         </is>
@@ -14844,20 +18385,20 @@
           <t>A definir (manutenção)</t>
         </is>
       </c>
-      <c r="D17" s="44" t="inlineStr">
+      <c r="D17" s="49" t="inlineStr">
         <is>
           <t>não informado</t>
         </is>
       </c>
-      <c r="E17" s="44" t="n">
+      <c r="E17" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="44" t="inlineStr">
+      <c r="F17" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="G17" s="44" t="inlineStr">
+      <c r="G17" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14877,12 +18418,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00083/2024</t>
         </is>
       </c>
-      <c r="B18" s="44" t="inlineStr">
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>5900064029</t>
         </is>
@@ -14892,18 +18433,18 @@
           <t>3 células (fases A, B e C)</t>
         </is>
       </c>
-      <c r="D18" s="44" t="n">
+      <c r="D18" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="44" t="n">
+      <c r="E18" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="44" t="inlineStr">
+      <c r="F18" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="44" t="inlineStr">
+      <c r="G18" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14923,12 +18464,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00084/2025</t>
         </is>
       </c>
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>5900470004</t>
         </is>
@@ -14938,20 +18479,20 @@
           <t>A definir (chave aberta)</t>
         </is>
       </c>
-      <c r="D19" s="44" t="inlineStr">
+      <c r="D19" s="49" t="inlineStr">
         <is>
           <t>não informado</t>
         </is>
       </c>
-      <c r="E19" s="44" t="n">
+      <c r="E19" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="44" t="inlineStr">
+      <c r="F19" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="44" t="inlineStr">
+      <c r="G19" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14971,12 +18512,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00085/2025</t>
         </is>
       </c>
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>5903718004</t>
         </is>
@@ -14986,20 +18527,20 @@
           <t>A definir (chave aberta)</t>
         </is>
       </c>
-      <c r="D20" s="44" t="inlineStr">
+      <c r="D20" s="49" t="inlineStr">
         <is>
           <t>não informado</t>
         </is>
       </c>
-      <c r="E20" s="44" t="n">
+      <c r="E20" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="44" t="inlineStr">
+      <c r="F20" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="44" t="inlineStr">
+      <c r="G20" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15019,12 +18560,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00090/2026</t>
         </is>
       </c>
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>5948602003</t>
         </is>
@@ -15034,18 +18575,18 @@
           <t>Células fases A e B</t>
         </is>
       </c>
-      <c r="D21" s="44" t="n">
+      <c r="D21" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="44" t="n">
+      <c r="E21" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="44" t="inlineStr">
+      <c r="F21" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="44" t="inlineStr">
+      <c r="G21" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15065,12 +18606,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00091/2026</t>
         </is>
       </c>
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>5953586122</t>
         </is>
@@ -15080,18 +18621,18 @@
           <t>Células fases A e C</t>
         </is>
       </c>
-      <c r="D22" s="44" t="n">
+      <c r="D22" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="44" t="n">
+      <c r="E22" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="44" t="inlineStr">
+      <c r="F22" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="44" t="n">
+      <c r="G22" s="49" t="n">
         <v>300</v>
       </c>
       <c r="H22" s="27" t="inlineStr">
@@ -15109,12 +18650,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00092/2023</t>
         </is>
       </c>
-      <c r="B23" s="44" t="inlineStr">
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>5902839004</t>
         </is>
@@ -15124,18 +18665,18 @@
           <t>1 célula (vazamento de óleo)</t>
         </is>
       </c>
-      <c r="D23" s="44" t="n">
+      <c r="D23" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="44" t="n">
+      <c r="E23" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="44" t="inlineStr">
+      <c r="F23" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="44" t="inlineStr">
+      <c r="G23" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15155,12 +18696,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00092/2026</t>
         </is>
       </c>
-      <c r="B24" s="44" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>5900272004</t>
         </is>
@@ -15170,18 +18711,18 @@
           <t>Célula fase C</t>
         </is>
       </c>
-      <c r="D24" s="44" t="n">
+      <c r="D24" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="44" t="n">
+      <c r="E24" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="44" t="inlineStr">
+      <c r="F24" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="44" t="inlineStr">
+      <c r="G24" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15201,12 +18742,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="43" t="inlineStr">
+      <c r="A25" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00093/2026</t>
         </is>
       </c>
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>5922361122</t>
         </is>
@@ -15216,18 +18757,18 @@
           <t>Célula fase A</t>
         </is>
       </c>
-      <c r="D25" s="44" t="n">
+      <c r="D25" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="44" t="n">
+      <c r="E25" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="44" t="inlineStr">
+      <c r="F25" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="44" t="inlineStr">
+      <c r="G25" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15247,12 +18788,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00094/2026</t>
         </is>
       </c>
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B26" s="49" t="inlineStr">
         <is>
           <t>5959941122</t>
         </is>
@@ -15262,18 +18803,18 @@
           <t>Células fases B e C</t>
         </is>
       </c>
-      <c r="D26" s="44" t="n">
+      <c r="D26" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E26" s="44" t="n">
+      <c r="E26" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="44" t="inlineStr">
+      <c r="F26" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="44" t="inlineStr">
+      <c r="G26" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15293,12 +18834,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00095/2025</t>
         </is>
       </c>
-      <c r="B27" s="44" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>5955192004</t>
         </is>
@@ -15308,18 +18849,18 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="D27" s="44" t="n">
+      <c r="D27" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="44" t="n">
+      <c r="E27" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="44" t="inlineStr">
+      <c r="F27" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="G27" s="44" t="inlineStr">
+      <c r="G27" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15339,12 +18880,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="43" t="inlineStr">
+      <c r="A28" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00099/2026</t>
         </is>
       </c>
-      <c r="B28" s="44" t="inlineStr">
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>5961616059</t>
         </is>
@@ -15354,18 +18895,18 @@
           <t>Célula fase A</t>
         </is>
       </c>
-      <c r="D28" s="44" t="n">
+      <c r="D28" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="44" t="n">
+      <c r="E28" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="44" t="inlineStr">
+      <c r="F28" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="44" t="inlineStr">
+      <c r="G28" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15385,12 +18926,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="43" t="inlineStr">
+      <c r="A29" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00100/2026</t>
         </is>
       </c>
-      <c r="B29" s="44" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>5900109059</t>
         </is>
@@ -15400,18 +18941,18 @@
           <t>Células fases A e C</t>
         </is>
       </c>
-      <c r="D29" s="44" t="n">
+      <c r="D29" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="44" t="n">
+      <c r="E29" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="44" t="inlineStr">
+      <c r="F29" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="44" t="inlineStr">
+      <c r="G29" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15431,12 +18972,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00101/2026</t>
         </is>
       </c>
-      <c r="B30" s="44" t="inlineStr">
+      <c r="B30" s="49" t="inlineStr">
         <is>
           <t>5952342122</t>
         </is>
@@ -15446,18 +18987,18 @@
           <t>Células fases A e C</t>
         </is>
       </c>
-      <c r="D30" s="44" t="n">
+      <c r="D30" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="44" t="n">
+      <c r="E30" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="44" t="inlineStr">
+      <c r="F30" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="44" t="inlineStr">
+      <c r="G30" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15477,12 +19018,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="43" t="inlineStr">
+      <c r="A31" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00102/2026</t>
         </is>
       </c>
-      <c r="B31" s="44" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>5952248122</t>
         </is>
@@ -15492,18 +19033,18 @@
           <t>Células fases B e C</t>
         </is>
       </c>
-      <c r="D31" s="44" t="n">
+      <c r="D31" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="44" t="n">
+      <c r="E31" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="44" t="inlineStr">
+      <c r="F31" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="44" t="inlineStr">
+      <c r="G31" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15523,12 +19064,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="A32" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00103/2026</t>
         </is>
       </c>
-      <c r="B32" s="44" t="inlineStr">
+      <c r="B32" s="49" t="inlineStr">
         <is>
           <t>5900358003</t>
         </is>
@@ -15538,18 +19079,18 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="D32" s="44" t="n">
+      <c r="D32" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="44" t="n">
+      <c r="E32" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="44" t="inlineStr">
+      <c r="F32" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="44" t="inlineStr">
+      <c r="G32" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15569,12 +19110,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00108/2025</t>
         </is>
       </c>
-      <c r="B33" s="44" t="inlineStr">
+      <c r="B33" s="49" t="inlineStr">
         <is>
           <t>5946472071</t>
         </is>
@@ -15584,18 +19125,18 @@
           <t>Célula fase C</t>
         </is>
       </c>
-      <c r="D33" s="44" t="n">
+      <c r="D33" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="44" t="n">
+      <c r="E33" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="44" t="inlineStr">
+      <c r="F33" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="G33" s="44" t="n">
+      <c r="G33" s="49" t="n">
         <v>300</v>
       </c>
       <c r="H33" s="27" t="inlineStr">
@@ -15613,12 +19154,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="43" t="inlineStr">
+      <c r="A34" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00109/2025</t>
         </is>
       </c>
-      <c r="B34" s="44" t="inlineStr">
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>5946473071</t>
         </is>
@@ -15628,18 +19169,18 @@
           <t>Células fases B e C</t>
         </is>
       </c>
-      <c r="D34" s="44" t="n">
+      <c r="D34" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="44" t="n">
+      <c r="E34" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="44" t="inlineStr">
+      <c r="F34" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="G34" s="44" t="n">
+      <c r="G34" s="49" t="n">
         <v>300</v>
       </c>
       <c r="H34" s="27" t="inlineStr">
@@ -15657,12 +19198,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="A35" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00140/2025</t>
         </is>
       </c>
-      <c r="B35" s="44" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>5900129052</t>
         </is>
@@ -15672,18 +19213,18 @@
           <t>Células fases A e B</t>
         </is>
       </c>
-      <c r="D35" s="44" t="n">
+      <c r="D35" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E35" s="44" t="n">
+      <c r="E35" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F35" s="44" t="inlineStr">
+      <c r="F35" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="G35" s="44" t="inlineStr">
+      <c r="G35" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15703,12 +19244,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="43" t="inlineStr">
+      <c r="A36" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00146/2024</t>
         </is>
       </c>
-      <c r="B36" s="44" t="inlineStr">
+      <c r="B36" s="49" t="inlineStr">
         <is>
           <t>5900003013</t>
         </is>
@@ -15718,18 +19259,18 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="D36" s="44" t="n">
+      <c r="D36" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E36" s="44" t="n">
+      <c r="E36" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="44" t="inlineStr">
+      <c r="F36" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="44" t="inlineStr">
+      <c r="G36" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15749,12 +19290,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="43" t="inlineStr">
+      <c r="A37" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00175/2025</t>
         </is>
       </c>
-      <c r="B37" s="44" t="inlineStr">
+      <c r="B37" s="49" t="inlineStr">
         <is>
           <t>5900010002</t>
         </is>
@@ -15764,18 +19305,18 @@
           <t>3 células (banco completo)</t>
         </is>
       </c>
-      <c r="D37" s="44" t="n">
+      <c r="D37" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="E37" s="44" t="n">
+      <c r="E37" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="44" t="inlineStr">
+      <c r="F37" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="44" t="n">
+      <c r="G37" s="49" t="n">
         <v>100</v>
       </c>
       <c r="H37" s="27" t="inlineStr">
@@ -15793,12 +19334,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="43" t="inlineStr">
+      <c r="A38" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00116/2026</t>
         </is>
       </c>
-      <c r="B38" s="44" t="inlineStr">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>5944271122</t>
         </is>
@@ -15808,18 +19349,18 @@
           <t>Célula fase A</t>
         </is>
       </c>
-      <c r="D38" s="44" t="n">
+      <c r="D38" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="44" t="n">
+      <c r="E38" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="44" t="inlineStr">
+      <c r="F38" s="49" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="G38" s="44" t="n">
+      <c r="G38" s="49" t="n">
         <v>300</v>
       </c>
       <c r="H38" s="28" t="inlineStr">
@@ -15837,12 +19378,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="43" t="inlineStr">
+      <c r="A39" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00118/2026</t>
         </is>
       </c>
-      <c r="B39" s="44" t="inlineStr">
+      <c r="B39" s="49" t="inlineStr">
         <is>
           <t>5900600004</t>
         </is>
@@ -15852,18 +19393,18 @@
           <t>Células fases A e C</t>
         </is>
       </c>
-      <c r="D39" s="44" t="n">
+      <c r="D39" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="44" t="n">
+      <c r="E39" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="F39" s="44" t="inlineStr">
+      <c r="F39" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="44" t="inlineStr">
+      <c r="G39" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15913,7 +19454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16001,22 +19542,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>7900117013</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00122/2025</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00084/2026 (adotada)</t>
         </is>
@@ -16031,7 +19572,7 @@
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G4" s="44" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>0212600422</t>
         </is>
@@ -16053,22 +19594,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>7908705049</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00177/2025</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="50" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
@@ -16083,7 +19624,7 @@
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G5" s="44" t="inlineStr">
+      <c r="G5" s="49" t="inlineStr">
         <is>
           <t>0512600135</t>
         </is>
@@ -16105,22 +19646,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>7933766059</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr">
+      <c r="C6" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00211/2025</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
+      <c r="D6" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00082/2026 (adotada)</t>
         </is>
@@ -16135,7 +19676,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G6" s="44" t="inlineStr">
+      <c r="G6" s="49" t="inlineStr">
         <is>
           <t>0112600424</t>
         </is>
@@ -16157,22 +19698,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>7900573047</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00209/2025</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00080/2026 (adotada)</t>
         </is>
@@ -16187,7 +19728,7 @@
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G7" s="44" t="inlineStr">
+      <c r="G7" s="49" t="inlineStr">
         <is>
           <t>0412600391</t>
         </is>
@@ -16209,22 +19750,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>7927169001</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00036/2026</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00036/2026</t>
         </is>
@@ -16239,7 +19780,7 @@
           <t>EM DÚVIDA =&gt; Equipamento completo</t>
         </is>
       </c>
-      <c r="G8" s="44" t="inlineStr">
+      <c r="G8" s="49" t="inlineStr">
         <is>
           <t>0112600425</t>
         </is>
@@ -16261,22 +19802,22 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B9" s="44" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>7938137007</t>
         </is>
       </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00034/2026</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr">
+      <c r="D9" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00085/2026 (adotada)</t>
         </is>
@@ -16291,7 +19832,7 @@
           <t>Componentes/Acessórios</t>
         </is>
       </c>
-      <c r="G9" s="44" t="inlineStr">
+      <c r="G9" s="49" t="inlineStr">
         <is>
           <t>0212600423</t>
         </is>
@@ -16313,22 +19854,22 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>7908686014</t>
         </is>
       </c>
-      <c r="C10" s="43" t="inlineStr">
+      <c r="C10" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00174/2024</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr">
+      <c r="D10" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00086/2026 (adotada)</t>
         </is>
@@ -16343,7 +19884,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G10" s="44" t="inlineStr">
+      <c r="G10" s="49" t="inlineStr">
         <is>
           <t>0212600425</t>
         </is>
@@ -16365,22 +19906,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B11" s="44" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>7900230155</t>
         </is>
       </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="C11" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00106/2025 (adotada)</t>
         </is>
       </c>
-      <c r="D11" s="43" t="inlineStr">
+      <c r="D11" s="50" t="inlineStr">
         <is>
           <t>v1.5: ETO-COEP 00056/2025</t>
         </is>
@@ -16395,7 +19936,7 @@
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G11" s="44" t="inlineStr">
+      <c r="G11" s="49" t="inlineStr">
         <is>
           <t>0712600318</t>
         </is>
@@ -16417,22 +19958,22 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>7943790134</t>
         </is>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00181/2025</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
+      <c r="D12" s="50" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
@@ -16447,7 +19988,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G12" s="44" t="inlineStr">
+      <c r="G12" s="49" t="inlineStr">
         <is>
           <t>0662600266</t>
         </is>
@@ -16469,22 +20010,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B13" s="44" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>7925087021</t>
         </is>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00222/2025</t>
         </is>
       </c>
-      <c r="D13" s="43" t="inlineStr">
+      <c r="D13" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00222/2025</t>
         </is>
@@ -16499,7 +20040,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G13" s="44" t="inlineStr">
+      <c r="G13" s="49" t="inlineStr">
         <is>
           <t>0412600392</t>
         </is>
@@ -16521,22 +20062,22 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>7900018004</t>
         </is>
       </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="C14" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00178/2025</t>
         </is>
       </c>
-      <c r="D14" s="43" t="inlineStr">
+      <c r="D14" s="50" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
@@ -16551,7 +20092,7 @@
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G14" s="44" t="inlineStr">
+      <c r="G14" s="49" t="inlineStr">
         <is>
           <t>0612600439</t>
         </is>
@@ -16573,22 +20114,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B15" s="44" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>7929376022</t>
         </is>
       </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2026</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr">
+      <c r="D15" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2026</t>
         </is>
@@ -16603,7 +20144,7 @@
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="G15" s="44" t="inlineStr">
+      <c r="G15" s="49" t="inlineStr">
         <is>
           <t>0612600565</t>
         </is>
@@ -16625,22 +20166,22 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>5827102054</t>
         </is>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C16" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00216/2025</t>
         </is>
       </c>
-      <c r="D16" s="43" t="inlineStr">
+      <c r="D16" s="50" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
@@ -16655,7 +20196,7 @@
           <t>Sem compra</t>
         </is>
       </c>
-      <c r="G16" s="44" t="inlineStr">
+      <c r="G16" s="49" t="inlineStr">
         <is>
           <t>0212600537</t>
         </is>
@@ -16677,22 +20218,22 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>5801866013</t>
         </is>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00077/2026</t>
         </is>
       </c>
-      <c r="D17" s="43" t="inlineStr">
+      <c r="D17" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00077/2026</t>
         </is>
@@ -16707,7 +20248,7 @@
           <t>Célula fase C</t>
         </is>
       </c>
-      <c r="G17" s="44" t="inlineStr">
+      <c r="G17" s="49" t="inlineStr">
         <is>
           <t>0212600539</t>
         </is>
@@ -16729,22 +20270,22 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B18" s="44" t="inlineStr">
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>5855411017</t>
         </is>
       </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="C18" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00199/2025</t>
         </is>
       </c>
-      <c r="D18" s="43" t="inlineStr">
+      <c r="D18" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00199/2025</t>
         </is>
@@ -16759,7 +20300,7 @@
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="G18" s="44" t="inlineStr">
+      <c r="G18" s="49" t="inlineStr">
         <is>
           <t>0212600536</t>
         </is>
@@ -16777,22 +20318,22 @@
       <c r="J18" s="23" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>7931610122</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00206/2025</t>
         </is>
       </c>
-      <c r="D19" s="43" t="inlineStr">
+      <c r="D19" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00083/2026 (adotada)</t>
         </is>
@@ -16807,7 +20348,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G19" s="44" t="inlineStr">
+      <c r="G19" s="49" t="inlineStr">
         <is>
           <t>0112600383</t>
         </is>
@@ -16829,22 +20370,22 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>7957620015</t>
         </is>
       </c>
-      <c r="C20" s="43" t="inlineStr">
+      <c r="C20" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00104/2025</t>
         </is>
       </c>
-      <c r="D20" s="43" t="inlineStr">
+      <c r="D20" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00081/2026 (adotada)</t>
         </is>
@@ -16859,7 +20400,7 @@
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="G20" s="44" t="inlineStr">
+      <c r="G20" s="49" t="inlineStr">
         <is>
           <t>0712600316</t>
         </is>
@@ -16881,22 +20422,22 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>7934698002</t>
         </is>
       </c>
-      <c r="C21" s="43" t="inlineStr">
+      <c r="C21" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00094/2025</t>
         </is>
       </c>
-      <c r="D21" s="43" t="inlineStr">
+      <c r="D21" s="50" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
@@ -16911,7 +20452,7 @@
           <t>EM DÚVIDA =&gt; Equipamento completo</t>
         </is>
       </c>
-      <c r="G21" s="44" t="inlineStr">
+      <c r="G21" s="49" t="inlineStr">
         <is>
           <t>0662600265</t>
         </is>
@@ -16933,22 +20474,22 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>7900453110</t>
         </is>
       </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="C22" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00169/2025</t>
         </is>
       </c>
-      <c r="D22" s="43" t="inlineStr">
+      <c r="D22" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00087/2026 (adotada)</t>
         </is>
@@ -16963,7 +20504,7 @@
           <t>Equipamento completo (DMSL)</t>
         </is>
       </c>
-      <c r="G22" s="44" t="inlineStr">
+      <c r="G22" s="49" t="inlineStr">
         <is>
           <t>0312600264</t>
         </is>
@@ -16985,22 +20526,22 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B23" s="44" t="inlineStr">
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>7903112004</t>
         </is>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C23" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00184/2025</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr">
+      <c r="D23" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00184/2025</t>
         </is>
@@ -17015,7 +20556,7 @@
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="G23" s="44" t="inlineStr">
+      <c r="G23" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -17037,22 +20578,22 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B24" s="44" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>7957126085</t>
         </is>
       </c>
-      <c r="C24" s="43" t="inlineStr">
+      <c r="C24" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00156/2025</t>
         </is>
       </c>
-      <c r="D24" s="43" t="inlineStr">
+      <c r="D24" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00156/2025</t>
         </is>
@@ -17067,7 +20608,7 @@
           <t>Controle completo</t>
         </is>
       </c>
-      <c r="G24" s="44" t="inlineStr">
+      <c r="G24" s="49" t="inlineStr">
         <is>
           <t>0212600428</t>
         </is>
@@ -17085,22 +20626,22 @@
       <c r="J24" s="23" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="43" t="inlineStr">
+      <c r="A25" s="50" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>5850308009</t>
         </is>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C25" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00180/2025</t>
         </is>
       </c>
-      <c r="D25" s="43" t="inlineStr">
+      <c r="D25" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00127/2026 (adotada)</t>
         </is>
@@ -17115,7 +20656,7 @@
           <t>Controle</t>
         </is>
       </c>
-      <c r="G25" s="44" t="inlineStr">
+      <c r="G25" s="49" t="inlineStr">
         <is>
           <t>0712600418</t>
         </is>
@@ -17137,22 +20678,22 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="50" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B26" s="49" t="inlineStr">
         <is>
           <t>5800859011</t>
         </is>
       </c>
-      <c r="C26" s="43" t="inlineStr">
+      <c r="C26" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00115/2026</t>
         </is>
       </c>
-      <c r="D26" s="43" t="inlineStr">
+      <c r="D26" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00115/2026</t>
         </is>
@@ -17167,7 +20708,7 @@
           <t>Controle (retrofit RUA)</t>
         </is>
       </c>
-      <c r="G26" s="44" t="inlineStr">
+      <c r="G26" s="49" t="inlineStr">
         <is>
           <t>0712600419</t>
         </is>
@@ -17189,22 +20730,22 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="50" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B27" s="44" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>5844630060</t>
         </is>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C27" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00167/2025</t>
         </is>
       </c>
-      <c r="D27" s="43" t="inlineStr">
+      <c r="D27" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00167/2025</t>
         </is>
@@ -17219,7 +20760,7 @@
           <t>Célula fase A</t>
         </is>
       </c>
-      <c r="G27" s="44" t="inlineStr">
+      <c r="G27" s="49" t="inlineStr">
         <is>
           <t>0612600626</t>
         </is>
@@ -17237,22 +20778,22 @@
       <c r="J27" s="23" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="43" t="inlineStr">
+      <c r="A28" s="50" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B28" s="44" t="inlineStr">
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>5800438116</t>
         </is>
       </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="C28" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00171/2025</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
+      <c r="D28" s="50" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
@@ -17267,7 +20808,7 @@
           <t>Célula de regulador</t>
         </is>
       </c>
-      <c r="G28" s="44" t="inlineStr">
+      <c r="G28" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -17289,22 +20830,22 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="43" t="inlineStr">
+      <c r="A29" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B29" s="44" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>7955520116</t>
         </is>
       </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="C29" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00151/2026 (adotada)</t>
         </is>
       </c>
-      <c r="D29" s="43" t="inlineStr">
+      <c r="D29" s="50" t="inlineStr">
         <is>
           <t>v1.5: ETO-COEP 00149/2025</t>
         </is>
@@ -17319,7 +20860,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G29" s="44" t="inlineStr">
+      <c r="G29" s="49" t="inlineStr">
         <is>
           <t>0512600178</t>
         </is>
@@ -17341,22 +20882,22 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B30" s="44" t="inlineStr">
+      <c r="B30" s="49" t="inlineStr">
         <is>
           <t>7900594026</t>
         </is>
       </c>
-      <c r="C30" s="43" t="inlineStr">
+      <c r="C30" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00113/2026</t>
         </is>
       </c>
-      <c r="D30" s="43" t="inlineStr">
+      <c r="D30" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00113/2026</t>
         </is>
@@ -17371,7 +20912,7 @@
           <t>EM DÚVIDA =&gt; Equipamento completo</t>
         </is>
       </c>
-      <c r="G30" s="44" t="inlineStr">
+      <c r="G30" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -17393,22 +20934,22 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="43" t="inlineStr">
+      <c r="A31" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B31" s="44" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>7953610256</t>
         </is>
       </c>
-      <c r="C31" s="43" t="inlineStr">
+      <c r="C31" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP (sem número)</t>
         </is>
       </c>
-      <c r="D31" s="43" t="inlineStr">
+      <c r="D31" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00050/2026</t>
         </is>
@@ -17423,7 +20964,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G31" s="44" t="inlineStr">
+      <c r="G31" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -17445,22 +20986,22 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="A32" s="50" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B32" s="44" t="inlineStr">
+      <c r="B32" s="49" t="inlineStr">
         <is>
           <t>5858783119</t>
         </is>
       </c>
-      <c r="C32" s="43" t="inlineStr">
+      <c r="C32" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00123/2025</t>
         </is>
       </c>
-      <c r="D32" s="43" t="inlineStr">
+      <c r="D32" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00123/2025</t>
         </is>
@@ -17475,7 +21016,7 @@
           <t>3 células</t>
         </is>
       </c>
-      <c r="G32" s="44" t="inlineStr">
+      <c r="G32" s="49" t="inlineStr">
         <is>
           <t>0662600361</t>
         </is>
@@ -17497,22 +21038,22 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="50" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B33" s="44" t="inlineStr">
+      <c r="B33" s="49" t="inlineStr">
         <is>
           <t>5862236091</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C33" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00223/2025</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
+      <c r="D33" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00223/2025</t>
         </is>
@@ -17527,7 +21068,7 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="G33" s="44" t="inlineStr">
+      <c r="G33" s="49" t="inlineStr">
         <is>
           <t>0512600177</t>
         </is>
@@ -17549,22 +21090,22 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="43" t="inlineStr">
+      <c r="A34" s="50" t="inlineStr">
         <is>
           <t>Regulador</t>
         </is>
       </c>
-      <c r="B34" s="44" t="inlineStr">
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>5854566043</t>
         </is>
       </c>
-      <c r="C34" s="43" t="inlineStr">
+      <c r="C34" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00160/2025</t>
         </is>
       </c>
-      <c r="D34" s="43" t="inlineStr">
+      <c r="D34" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00160/2025</t>
         </is>
@@ -17579,7 +21120,7 @@
           <t>Célula fase B</t>
         </is>
       </c>
-      <c r="G34" s="44" t="inlineStr">
+      <c r="G34" s="49" t="inlineStr">
         <is>
           <t>0312600352</t>
         </is>
@@ -17601,22 +21142,22 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="A35" s="50" t="inlineStr">
         <is>
           <t>Religador</t>
         </is>
       </c>
-      <c r="B35" s="44" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>7933726256</t>
         </is>
       </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="C35" s="50" t="inlineStr">
         <is>
           <t>ETO-COEP 00108/2026</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr">
+      <c r="D35" s="50" t="inlineStr">
         <is>
           <t>(fora da base de pendentes)</t>
         </is>
@@ -17631,7 +21172,7 @@
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G35" s="44" t="inlineStr">
+      <c r="G35" s="49" t="inlineStr">
         <is>
           <t>0312600351</t>
         </is>
@@ -17660,7 +21201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FFFF00"/>
@@ -18114,298 +21655,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DISCREPÂNCIAS — OBRAS × BASE DE SS PENDENTES × ORÇAMENTO v1.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Detalhe</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Encaminhamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>Números de SS divergentes p/ o mesmo ativo</t>
-        </is>
-      </c>
-      <c r="C4" s="23" t="inlineStr">
-        <is>
-          <t>10 casos — ex.: 7900117013 (00122/2025 x 00084/2026); 7908686014 (00174/2024 x 00086/2026); 5850308009 (00180/2025 x 00127/2026)</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t>RESOLVIDO pela regra do gestor: vale a SS mais recente pelo ano; mesmo ano =&gt; a mais detalhada/mais recente. Nº antigo citado na Observação de cada linha</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>SS sem número na planilha de obras</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>7953610256 — campo SS = 'ETO-COEP' (print do SGM confirma: 00050/2026)</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>Preencher o número nas obras</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>Peça divergente (obras x orçamento)</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>7927169001 (completo x tanque, NOJA); 7934698002 (completo x controle, NOJA); 7900594026 (deslocamento x substituição)</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>Padrão do gestor aplicado: EM DÚVIDA =&gt; EQUIPAMENTO COMPLETO, com destaque na coluna Observação; avaliação na aba VERIFICAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>Tensão/potência divergente</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>5862236091: Ajustes=34,5/400 x v1.5=13,8 (dif. R$ 65.795,51/célula); 5800961074: Ajustes=34,5 x v1.5=13,8</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>Regra do gestor: Ajustes SEMPRE prevalece p/ modelo e faixa de tensão — orçados a 34,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>Qtd a requisitar ≠ qtd do conserto</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>5862236091: requisitar 3 células (2 repõem estoque usado em obra de construção); conserto usa 1</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>REVISAR COM MATHEUS ALVES — possível esquema sem cobrança do material</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>Material redirecionado</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>5858783119 (3 células) → 5854566043 e 5862236091; 7900453110 (equipamento) → 7933726256</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>SS de origem ficará sem material — nova aquisição será COMPRA (requisição = COCM gera N1→N3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>Reaproveitamentos (custo cai)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>7903112004: tanque Cooper do 7900018004 (orçado só controle); 7933726256 e 5800438116: material R$ 0</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>7933726256 e 5800438116 marcados em VERMELHO — discussão com Matheus Alves (status inalterado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Escopo sem compra</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>5827102054 (Pugmil): repasse COCM + vedação x conserto de controle</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>EM AVALIAÇÃO PELO GESTOR — detalhes na aba VERIFICAR e no chat</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>Linha duplicada nas obras</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>5800438116 2x (Chapada da Natividade c/ SS x Porto Nacional sem SS) — Ajustes (LD04002091) confirmam Chapada da Natividade</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>Engano confirmado — excluir a duplicata; discussão com Matheus Alves</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>Duplicidade de SS no mesmo ativo</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>7929376022 (00068/2026 e 00120/2026); 7957620015 (00104/2025 e 00081/2026)</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>Adotada a mais recente; encerrar a SS duplicada no SGM</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="44" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>Fora da base de pendentes</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>14 equipamentos das OBRAS não constam na base de SS pendentes (esperado p/ concluídas/em execução)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>Incluídos no orçamento como 'Em execução'</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
+++ b/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,6 +88,11 @@
     <font>
       <b val="1"/>
       <color rgb="00006100"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="10">
@@ -309,6 +314,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -318,6 +326,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -325,12 +334,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1000,7 +1003,7 @@
         <v>22</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -2164,10 +2167,10 @@
           <t>DCMD (oficial ETO 36)</t>
         </is>
       </c>
-      <c r="B6" s="55" t="n">
+      <c r="B6" s="56" t="n">
         <v>44</v>
       </c>
-      <c r="C6" s="55" t="n">
+      <c r="C6" s="56" t="n">
         <v>21</v>
       </c>
       <c r="D6" s="19" t="n">
@@ -2180,10 +2183,10 @@
           <t>DMSL (destino ETO-TELE)</t>
         </is>
       </c>
-      <c r="B7" s="55" t="n">
+      <c r="B7" s="56" t="n">
         <v>22</v>
       </c>
-      <c r="C7" s="55" t="n">
+      <c r="C7" s="56" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="19" t="n">
@@ -2196,10 +2199,10 @@
           <t>Proteção (destino ETO-PROT)</t>
         </is>
       </c>
-      <c r="B8" s="55" t="n">
+      <c r="B8" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="55" t="n">
+      <c r="C8" s="56" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="19" t="n">
@@ -2323,9 +2326,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>⚠ CONFLITOS (concluídos que aparecem no oficial do DCMD): 5850308009 (Guaraí — dado como concluído via ETO-TELE 00958/2026, mas com 0 dias aguardando DCMD) e 7942572059 (Taquaralto — marcado EXECUTADO no mapeamento, mas com 8 dias aguardando DCMD). Situação NÃO alterada — aguardando sua definição.</t>
+      <c r="A19" s="57" t="inlineStr">
+        <is>
+          <t>Definições do gestor (08/07): 5850308009 (Guaraí) = NÃO concluído — segue no posto do COEP/fila DCMD; 7942572059 (Taquaralto) = melhoria de aterramento SEM CUSTO, considerado EM EXECUÇÃO via ETO-RD-PA 00427/2026 (SS ainda aberta).</t>
         </is>
       </c>
     </row>
@@ -2389,40 +2392,40 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="56" t="inlineStr">
+      <c r="A23" s="58" t="inlineStr">
         <is>
           <t>7923927122</t>
         </is>
       </c>
-      <c r="B23" s="56" t="inlineStr">
+      <c r="B23" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C23" s="57" t="inlineStr">
+      <c r="C23" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00079/2025</t>
         </is>
       </c>
-      <c r="D23" s="56" t="inlineStr">
+      <c r="D23" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E23" s="56" t="n">
+      <c r="E23" s="58" t="n">
         <v>434</v>
       </c>
-      <c r="G23" s="56" t="inlineStr">
+      <c r="G23" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H23" s="57" t="inlineStr">
+      <c r="H23" s="59" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I23" s="57" t="inlineStr">
+      <c r="I23" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2434,40 +2437,40 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="56" t="inlineStr">
+      <c r="A24" s="58" t="inlineStr">
         <is>
           <t>7900532053</t>
         </is>
       </c>
-      <c r="B24" s="56" t="inlineStr">
+      <c r="B24" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C24" s="57" t="inlineStr">
+      <c r="C24" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00102/2025</t>
         </is>
       </c>
-      <c r="D24" s="56" t="inlineStr">
+      <c r="D24" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E24" s="56" t="n">
+      <c r="E24" s="58" t="n">
         <v>407</v>
       </c>
-      <c r="G24" s="56" t="inlineStr">
+      <c r="G24" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H24" s="57" t="inlineStr">
+      <c r="H24" s="59" t="inlineStr">
         <is>
           <t>Piraque</t>
         </is>
       </c>
-      <c r="I24" s="57" t="inlineStr">
+      <c r="I24" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2479,40 +2482,40 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="56" t="inlineStr">
+      <c r="A25" s="58" t="inlineStr">
         <is>
           <t>7920024127</t>
         </is>
       </c>
-      <c r="B25" s="56" t="inlineStr">
+      <c r="B25" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C25" s="57" t="inlineStr">
+      <c r="C25" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2025</t>
         </is>
       </c>
-      <c r="D25" s="56" t="inlineStr">
+      <c r="D25" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E25" s="56" t="n">
+      <c r="E25" s="58" t="n">
         <v>371</v>
       </c>
-      <c r="G25" s="56" t="inlineStr">
+      <c r="G25" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H25" s="57" t="inlineStr">
+      <c r="H25" s="59" t="inlineStr">
         <is>
           <t>Palmeiras Do Tocantins</t>
         </is>
       </c>
-      <c r="I25" s="57" t="inlineStr">
+      <c r="I25" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2524,40 +2527,40 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="56" t="inlineStr">
+      <c r="A26" s="58" t="inlineStr">
         <is>
           <t>5858783119</t>
         </is>
       </c>
-      <c r="B26" s="56" t="inlineStr">
+      <c r="B26" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C26" s="57" t="inlineStr">
+      <c r="C26" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00123/2025</t>
         </is>
       </c>
-      <c r="D26" s="56" t="inlineStr">
+      <c r="D26" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E26" s="56" t="n">
+      <c r="E26" s="58" t="n">
         <v>369</v>
       </c>
-      <c r="G26" s="56" t="inlineStr">
+      <c r="G26" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H26" s="57" t="inlineStr">
+      <c r="H26" s="59" t="inlineStr">
         <is>
           <t>Sao Bento Do Tocantins</t>
         </is>
       </c>
-      <c r="I26" s="57" t="inlineStr">
+      <c r="I26" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2569,40 +2572,40 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="56" t="inlineStr">
+      <c r="A27" s="58" t="inlineStr">
         <is>
           <t>7927446001</t>
         </is>
       </c>
-      <c r="B27" s="56" t="inlineStr">
+      <c r="B27" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C27" s="57" t="inlineStr">
+      <c r="C27" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00143/2025</t>
         </is>
       </c>
-      <c r="D27" s="56" t="inlineStr">
+      <c r="D27" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E27" s="56" t="n">
+      <c r="E27" s="58" t="n">
         <v>364</v>
       </c>
-      <c r="G27" s="56" t="inlineStr">
+      <c r="G27" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H27" s="57" t="inlineStr">
+      <c r="H27" s="59" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I27" s="57" t="inlineStr">
+      <c r="I27" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2614,40 +2617,40 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="56" t="inlineStr">
+      <c r="A28" s="58" t="inlineStr">
         <is>
           <t>7957126085</t>
         </is>
       </c>
-      <c r="B28" s="56" t="inlineStr">
+      <c r="B28" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C28" s="57" t="inlineStr">
+      <c r="C28" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00156/2025</t>
         </is>
       </c>
-      <c r="D28" s="56" t="inlineStr">
+      <c r="D28" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E28" s="56" t="n">
+      <c r="E28" s="58" t="n">
         <v>350</v>
       </c>
-      <c r="G28" s="56" t="inlineStr">
+      <c r="G28" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H28" s="57" t="inlineStr">
+      <c r="H28" s="59" t="inlineStr">
         <is>
           <t>Monte Santo Do Tocantins</t>
         </is>
       </c>
-      <c r="I28" s="57" t="inlineStr">
+      <c r="I28" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2659,40 +2662,40 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="56" t="inlineStr">
+      <c r="A29" s="58" t="inlineStr">
         <is>
           <t>7942485096</t>
         </is>
       </c>
-      <c r="B29" s="56" t="inlineStr">
+      <c r="B29" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C29" s="57" t="inlineStr">
+      <c r="C29" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00158/2025</t>
         </is>
       </c>
-      <c r="D29" s="56" t="inlineStr">
+      <c r="D29" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E29" s="56" t="n">
+      <c r="E29" s="58" t="n">
         <v>349</v>
       </c>
-      <c r="G29" s="56" t="inlineStr">
+      <c r="G29" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H29" s="57" t="inlineStr">
+      <c r="H29" s="59" t="inlineStr">
         <is>
           <t>Pindorama Do Tocantins</t>
         </is>
       </c>
-      <c r="I29" s="57" t="inlineStr">
+      <c r="I29" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2704,40 +2707,40 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="56" t="inlineStr">
+      <c r="A30" s="58" t="inlineStr">
         <is>
           <t>5854566043</t>
         </is>
       </c>
-      <c r="B30" s="56" t="inlineStr">
+      <c r="B30" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C30" s="57" t="inlineStr">
+      <c r="C30" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00160/2025</t>
         </is>
       </c>
-      <c r="D30" s="56" t="inlineStr">
+      <c r="D30" s="58" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E30" s="56" t="n">
+      <c r="E30" s="58" t="n">
         <v>347</v>
       </c>
-      <c r="G30" s="56" t="inlineStr">
+      <c r="G30" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H30" s="57" t="inlineStr">
+      <c r="H30" s="59" t="inlineStr">
         <is>
           <t>Silvanopolis</t>
         </is>
       </c>
-      <c r="I30" s="57" t="inlineStr">
+      <c r="I30" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2749,40 +2752,40 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="56" t="inlineStr">
+      <c r="A31" s="58" t="inlineStr">
         <is>
           <t>5844630060</t>
         </is>
       </c>
-      <c r="B31" s="56" t="inlineStr">
+      <c r="B31" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C31" s="57" t="inlineStr">
+      <c r="C31" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00167/2025</t>
         </is>
       </c>
-      <c r="D31" s="56" t="inlineStr">
+      <c r="D31" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E31" s="56" t="n">
+      <c r="E31" s="58" t="n">
         <v>333</v>
       </c>
-      <c r="G31" s="56" t="inlineStr">
+      <c r="G31" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H31" s="57" t="inlineStr">
+      <c r="H31" s="59" t="inlineStr">
         <is>
           <t>Nova Olinda</t>
         </is>
       </c>
-      <c r="I31" s="57" t="inlineStr">
+      <c r="I31" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2794,40 +2797,40 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="56" t="inlineStr">
+      <c r="A32" s="58" t="inlineStr">
         <is>
           <t>7900535058</t>
         </is>
       </c>
-      <c r="B32" s="56" t="inlineStr">
+      <c r="B32" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C32" s="57" t="inlineStr">
+      <c r="C32" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00173/2025</t>
         </is>
       </c>
-      <c r="D32" s="56" t="inlineStr">
+      <c r="D32" s="58" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E32" s="56" t="n">
+      <c r="E32" s="58" t="n">
         <v>317</v>
       </c>
-      <c r="G32" s="56" t="inlineStr">
+      <c r="G32" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H32" s="57" t="inlineStr">
+      <c r="H32" s="59" t="inlineStr">
         <is>
           <t>Santa Fe Do Araguaia</t>
         </is>
       </c>
-      <c r="I32" s="57" t="inlineStr">
+      <c r="I32" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2839,40 +2842,40 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="56" t="inlineStr">
+      <c r="A33" s="58" t="inlineStr">
         <is>
           <t>7903112004</t>
         </is>
       </c>
-      <c r="B33" s="56" t="inlineStr">
+      <c r="B33" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C33" s="57" t="inlineStr">
+      <c r="C33" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00184/2025</t>
         </is>
       </c>
-      <c r="D33" s="56" t="inlineStr">
+      <c r="D33" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E33" s="56" t="n">
+      <c r="E33" s="58" t="n">
         <v>307</v>
       </c>
-      <c r="G33" s="56" t="inlineStr">
+      <c r="G33" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H33" s="57" t="inlineStr">
+      <c r="H33" s="59" t="inlineStr">
         <is>
           <t>Araguaina</t>
         </is>
       </c>
-      <c r="I33" s="57" t="inlineStr">
+      <c r="I33" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2884,40 +2887,40 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="56" t="inlineStr">
+      <c r="A34" s="58" t="inlineStr">
         <is>
           <t>5800371025</t>
         </is>
       </c>
-      <c r="B34" s="56" t="inlineStr">
+      <c r="B34" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C34" s="57" t="inlineStr">
+      <c r="C34" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00187/2025</t>
         </is>
       </c>
-      <c r="D34" s="56" t="inlineStr">
+      <c r="D34" s="58" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E34" s="56" t="n">
+      <c r="E34" s="58" t="n">
         <v>305</v>
       </c>
-      <c r="G34" s="56" t="inlineStr">
+      <c r="G34" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H34" s="57" t="inlineStr">
+      <c r="H34" s="59" t="inlineStr">
         <is>
           <t>Arapoema</t>
         </is>
       </c>
-      <c r="I34" s="57" t="inlineStr">
+      <c r="I34" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2929,40 +2932,40 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="56" t="inlineStr">
+      <c r="A35" s="58" t="inlineStr">
         <is>
           <t>5855411017</t>
         </is>
       </c>
-      <c r="B35" s="56" t="inlineStr">
+      <c r="B35" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C35" s="57" t="inlineStr">
+      <c r="C35" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00199/2025</t>
         </is>
       </c>
-      <c r="D35" s="56" t="inlineStr">
+      <c r="D35" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E35" s="56" t="n">
+      <c r="E35" s="58" t="n">
         <v>280</v>
       </c>
-      <c r="G35" s="56" t="inlineStr">
+      <c r="G35" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H35" s="57" t="inlineStr">
+      <c r="H35" s="59" t="inlineStr">
         <is>
           <t>Barrolandia</t>
         </is>
       </c>
-      <c r="I35" s="57" t="inlineStr">
+      <c r="I35" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2974,40 +2977,40 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="56" t="inlineStr">
+      <c r="A36" s="58" t="inlineStr">
         <is>
           <t>5853360007</t>
         </is>
       </c>
-      <c r="B36" s="56" t="inlineStr">
+      <c r="B36" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C36" s="57" t="inlineStr">
+      <c r="C36" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-PS 00323/2025</t>
         </is>
       </c>
-      <c r="D36" s="56" t="inlineStr">
+      <c r="D36" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E36" s="56" t="n">
+      <c r="E36" s="58" t="n">
         <v>264</v>
       </c>
-      <c r="G36" s="56" t="inlineStr">
+      <c r="G36" s="58" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H36" s="57" t="inlineStr">
+      <c r="H36" s="59" t="inlineStr">
         <is>
           <t>Miracema Do Tocantins</t>
         </is>
       </c>
-      <c r="I36" s="58" t="inlineStr">
+      <c r="I36" s="60" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -3019,40 +3022,40 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="56" t="inlineStr">
+      <c r="A37" s="58" t="inlineStr">
         <is>
           <t>5800961074</t>
         </is>
       </c>
-      <c r="B37" s="56" t="inlineStr">
+      <c r="B37" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C37" s="57" t="inlineStr">
+      <c r="C37" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00221/2025</t>
         </is>
       </c>
-      <c r="D37" s="56" t="inlineStr">
+      <c r="D37" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E37" s="56" t="n">
+      <c r="E37" s="58" t="n">
         <v>214</v>
       </c>
-      <c r="G37" s="56" t="inlineStr">
+      <c r="G37" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H37" s="57" t="inlineStr">
+      <c r="H37" s="59" t="inlineStr">
         <is>
           <t>Dianopolis</t>
         </is>
       </c>
-      <c r="I37" s="57" t="inlineStr">
+      <c r="I37" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3064,40 +3067,40 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="56" t="inlineStr">
+      <c r="A38" s="58" t="inlineStr">
         <is>
           <t>7925087021</t>
         </is>
       </c>
-      <c r="B38" s="56" t="inlineStr">
+      <c r="B38" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C38" s="57" t="inlineStr">
+      <c r="C38" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00222/2025</t>
         </is>
       </c>
-      <c r="D38" s="56" t="inlineStr">
+      <c r="D38" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E38" s="56" t="n">
+      <c r="E38" s="58" t="n">
         <v>211</v>
       </c>
-      <c r="G38" s="56" t="inlineStr">
+      <c r="G38" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H38" s="57" t="inlineStr">
+      <c r="H38" s="59" t="inlineStr">
         <is>
           <t>Parana</t>
         </is>
       </c>
-      <c r="I38" s="57" t="inlineStr">
+      <c r="I38" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3109,40 +3112,40 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="56" t="inlineStr">
+      <c r="A39" s="58" t="inlineStr">
         <is>
           <t>5862236091</t>
         </is>
       </c>
-      <c r="B39" s="56" t="inlineStr">
+      <c r="B39" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C39" s="57" t="inlineStr">
+      <c r="C39" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00223/2025</t>
         </is>
       </c>
-      <c r="D39" s="56" t="inlineStr">
+      <c r="D39" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E39" s="56" t="n">
+      <c r="E39" s="58" t="n">
         <v>211</v>
       </c>
-      <c r="G39" s="56" t="inlineStr">
+      <c r="G39" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H39" s="57" t="inlineStr">
+      <c r="H39" s="59" t="inlineStr">
         <is>
           <t>Almas</t>
         </is>
       </c>
-      <c r="I39" s="57" t="inlineStr">
+      <c r="I39" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3154,40 +3157,40 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="56" t="inlineStr">
+      <c r="A40" s="58" t="inlineStr">
         <is>
           <t>7933585074</t>
         </is>
       </c>
-      <c r="B40" s="56" t="inlineStr">
+      <c r="B40" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C40" s="57" t="inlineStr">
+      <c r="C40" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00024/2026</t>
         </is>
       </c>
-      <c r="D40" s="56" t="inlineStr">
+      <c r="D40" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E40" s="56" t="n">
+      <c r="E40" s="58" t="n">
         <v>161</v>
       </c>
-      <c r="G40" s="56" t="inlineStr">
+      <c r="G40" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H40" s="57" t="inlineStr">
+      <c r="H40" s="59" t="inlineStr">
         <is>
           <t>Dianopolis</t>
         </is>
       </c>
-      <c r="I40" s="57" t="inlineStr">
+      <c r="I40" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3199,40 +3202,40 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="56" t="inlineStr">
+      <c r="A41" s="58" t="inlineStr">
         <is>
           <t>7927646026</t>
         </is>
       </c>
-      <c r="B41" s="56" t="inlineStr">
+      <c r="B41" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C41" s="57" t="inlineStr">
+      <c r="C41" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00029/2026</t>
         </is>
       </c>
-      <c r="D41" s="56" t="inlineStr">
+      <c r="D41" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E41" s="56" t="n">
+      <c r="E41" s="58" t="n">
         <v>154</v>
       </c>
-      <c r="G41" s="56" t="inlineStr">
+      <c r="G41" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H41" s="57" t="inlineStr">
+      <c r="H41" s="59" t="inlineStr">
         <is>
           <t>Ponte Alta Tocantins</t>
         </is>
       </c>
-      <c r="I41" s="57" t="inlineStr">
+      <c r="I41" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3244,40 +3247,40 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="56" t="inlineStr">
+      <c r="A42" s="58" t="inlineStr">
         <is>
           <t>7931608059</t>
         </is>
       </c>
-      <c r="B42" s="56" t="inlineStr">
+      <c r="B42" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C42" s="57" t="inlineStr">
+      <c r="C42" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00040/2026</t>
         </is>
       </c>
-      <c r="D42" s="56" t="inlineStr">
+      <c r="D42" s="58" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E42" s="56" t="n">
+      <c r="E42" s="58" t="n">
         <v>133</v>
       </c>
-      <c r="G42" s="56" t="inlineStr">
+      <c r="G42" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H42" s="57" t="inlineStr">
+      <c r="H42" s="59" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I42" s="57" t="inlineStr">
+      <c r="I42" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3289,40 +3292,40 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="56" t="inlineStr">
+      <c r="A43" s="58" t="inlineStr">
         <is>
           <t>7908249152</t>
         </is>
       </c>
-      <c r="B43" s="56" t="inlineStr">
+      <c r="B43" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C43" s="57" t="inlineStr">
+      <c r="C43" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00038/2026</t>
         </is>
       </c>
-      <c r="D43" s="56" t="inlineStr">
+      <c r="D43" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E43" s="56" t="n">
+      <c r="E43" s="58" t="n">
         <v>133</v>
       </c>
-      <c r="G43" s="56" t="inlineStr">
+      <c r="G43" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H43" s="57" t="inlineStr">
+      <c r="H43" s="59" t="inlineStr">
         <is>
           <t>Santa Rosa Do Tocantins</t>
         </is>
       </c>
-      <c r="I43" s="57" t="inlineStr">
+      <c r="I43" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3334,40 +3337,40 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="56" t="inlineStr">
+      <c r="A44" s="58" t="inlineStr">
         <is>
           <t>7927396052</t>
         </is>
       </c>
-      <c r="B44" s="56" t="inlineStr">
+      <c r="B44" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C44" s="57" t="inlineStr">
+      <c r="C44" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00045/2026</t>
         </is>
       </c>
-      <c r="D44" s="56" t="inlineStr">
+      <c r="D44" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E44" s="56" t="n">
+      <c r="E44" s="58" t="n">
         <v>127</v>
       </c>
-      <c r="G44" s="56" t="inlineStr">
+      <c r="G44" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H44" s="57" t="inlineStr">
+      <c r="H44" s="59" t="inlineStr">
         <is>
           <t>Formoso Do Araguaia</t>
         </is>
       </c>
-      <c r="I44" s="57" t="inlineStr">
+      <c r="I44" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3379,40 +3382,40 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="56" t="inlineStr">
+      <c r="A45" s="58" t="inlineStr">
         <is>
           <t>7925871077</t>
         </is>
       </c>
-      <c r="B45" s="56" t="inlineStr">
+      <c r="B45" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C45" s="57" t="inlineStr">
+      <c r="C45" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00048/2026</t>
         </is>
       </c>
-      <c r="D45" s="56" t="inlineStr">
+      <c r="D45" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E45" s="56" t="n">
+      <c r="E45" s="58" t="n">
         <v>113</v>
       </c>
-      <c r="G45" s="56" t="inlineStr">
+      <c r="G45" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H45" s="57" t="inlineStr">
+      <c r="H45" s="59" t="inlineStr">
         <is>
           <t>Goiatins</t>
         </is>
       </c>
-      <c r="I45" s="57" t="inlineStr">
+      <c r="I45" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3424,40 +3427,40 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="56" t="inlineStr">
+      <c r="A46" s="58" t="inlineStr">
         <is>
           <t>7953610256</t>
         </is>
       </c>
-      <c r="B46" s="56" t="inlineStr">
+      <c r="B46" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C46" s="57" t="inlineStr">
+      <c r="C46" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00050/2026</t>
         </is>
       </c>
-      <c r="D46" s="56" t="inlineStr">
+      <c r="D46" s="58" t="inlineStr">
         <is>
           <t>Muito Alto</t>
         </is>
       </c>
-      <c r="E46" s="56" t="n">
+      <c r="E46" s="58" t="n">
         <v>111</v>
       </c>
-      <c r="G46" s="56" t="inlineStr">
+      <c r="G46" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H46" s="57" t="inlineStr">
+      <c r="H46" s="59" t="inlineStr">
         <is>
           <t>Mateiros</t>
         </is>
       </c>
-      <c r="I46" s="57" t="inlineStr">
+      <c r="I46" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3469,40 +3472,40 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="56" t="inlineStr">
+      <c r="A47" s="58" t="inlineStr">
         <is>
           <t>7926442035</t>
         </is>
       </c>
-      <c r="B47" s="56" t="inlineStr">
+      <c r="B47" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C47" s="57" t="inlineStr">
+      <c r="C47" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00051/2026</t>
         </is>
       </c>
-      <c r="D47" s="56" t="inlineStr">
+      <c r="D47" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E47" s="56" t="n">
+      <c r="E47" s="58" t="n">
         <v>111</v>
       </c>
-      <c r="G47" s="56" t="inlineStr">
+      <c r="G47" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H47" s="57" t="inlineStr">
+      <c r="H47" s="59" t="inlineStr">
         <is>
           <t>Monte Do Carmo</t>
         </is>
       </c>
-      <c r="I47" s="57" t="inlineStr">
+      <c r="I47" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3514,40 +3517,40 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="56" t="inlineStr">
+      <c r="A48" s="58" t="inlineStr">
         <is>
           <t>7925744087</t>
         </is>
       </c>
-      <c r="B48" s="56" t="inlineStr">
+      <c r="B48" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C48" s="57" t="inlineStr">
+      <c r="C48" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00059/2026</t>
         </is>
       </c>
-      <c r="D48" s="56" t="inlineStr">
+      <c r="D48" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E48" s="56" t="n">
+      <c r="E48" s="58" t="n">
         <v>99</v>
       </c>
-      <c r="G48" s="56" t="inlineStr">
+      <c r="G48" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H48" s="57" t="inlineStr">
+      <c r="H48" s="59" t="inlineStr">
         <is>
           <t>Goianorte</t>
         </is>
       </c>
-      <c r="I48" s="57" t="inlineStr">
+      <c r="I48" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3559,40 +3562,40 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="56" t="inlineStr">
+      <c r="A49" s="58" t="inlineStr">
         <is>
           <t>7925733015</t>
         </is>
       </c>
-      <c r="B49" s="56" t="inlineStr">
+      <c r="B49" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C49" s="57" t="inlineStr">
+      <c r="C49" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00058/2026</t>
         </is>
       </c>
-      <c r="D49" s="56" t="inlineStr">
+      <c r="D49" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E49" s="56" t="n">
+      <c r="E49" s="58" t="n">
         <v>99</v>
       </c>
-      <c r="G49" s="56" t="inlineStr">
+      <c r="G49" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H49" s="57" t="inlineStr">
+      <c r="H49" s="59" t="inlineStr">
         <is>
           <t>Pedro Afonso</t>
         </is>
       </c>
-      <c r="I49" s="57" t="inlineStr">
+      <c r="I49" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3604,40 +3607,40 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="56" t="inlineStr">
+      <c r="A50" s="58" t="inlineStr">
         <is>
           <t>7901110084</t>
         </is>
       </c>
-      <c r="B50" s="56" t="inlineStr">
+      <c r="B50" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C50" s="57" t="inlineStr">
+      <c r="C50" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00061/2026</t>
         </is>
       </c>
-      <c r="D50" s="56" t="inlineStr">
+      <c r="D50" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E50" s="56" t="n">
+      <c r="E50" s="58" t="n">
         <v>98</v>
       </c>
-      <c r="G50" s="56" t="inlineStr">
+      <c r="G50" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H50" s="57" t="inlineStr">
+      <c r="H50" s="59" t="inlineStr">
         <is>
           <t>Divinopolis</t>
         </is>
       </c>
-      <c r="I50" s="57" t="inlineStr">
+      <c r="I50" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3649,40 +3652,40 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="56" t="inlineStr">
+      <c r="A51" s="58" t="inlineStr">
         <is>
           <t>7944559149</t>
         </is>
       </c>
-      <c r="B51" s="56" t="inlineStr">
+      <c r="B51" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C51" s="57" t="inlineStr">
+      <c r="C51" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00063/2026</t>
         </is>
       </c>
-      <c r="D51" s="56" t="inlineStr">
+      <c r="D51" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E51" s="56" t="n">
+      <c r="E51" s="58" t="n">
         <v>98</v>
       </c>
-      <c r="G51" s="56" t="inlineStr">
+      <c r="G51" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H51" s="57" t="inlineStr">
+      <c r="H51" s="59" t="inlineStr">
         <is>
           <t>Caseara</t>
         </is>
       </c>
-      <c r="I51" s="57" t="inlineStr">
+      <c r="I51" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3694,40 +3697,40 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="56" t="inlineStr">
+      <c r="A52" s="58" t="inlineStr">
         <is>
           <t>5800291035</t>
         </is>
       </c>
-      <c r="B52" s="56" t="inlineStr">
+      <c r="B52" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C52" s="57" t="inlineStr">
+      <c r="C52" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-PO 00097/2026</t>
         </is>
       </c>
-      <c r="D52" s="56" t="inlineStr">
+      <c r="D52" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E52" s="56" t="n">
+      <c r="E52" s="58" t="n">
         <v>98</v>
       </c>
-      <c r="G52" s="56" t="inlineStr">
+      <c r="G52" s="58" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H52" s="57" t="inlineStr">
+      <c r="H52" s="59" t="inlineStr">
         <is>
           <t>Monte Do Carmo</t>
         </is>
       </c>
-      <c r="I52" s="58" t="inlineStr">
+      <c r="I52" s="60" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -3739,40 +3742,40 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="56" t="inlineStr">
+      <c r="A53" s="58" t="inlineStr">
         <is>
           <t>7919270014</t>
         </is>
       </c>
-      <c r="B53" s="56" t="inlineStr">
+      <c r="B53" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C53" s="57" t="inlineStr">
+      <c r="C53" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00074/2026</t>
         </is>
       </c>
-      <c r="D53" s="56" t="inlineStr">
+      <c r="D53" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E53" s="56" t="n">
+      <c r="E53" s="58" t="n">
         <v>82</v>
       </c>
-      <c r="G53" s="56" t="inlineStr">
+      <c r="G53" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H53" s="57" t="inlineStr">
+      <c r="H53" s="59" t="inlineStr">
         <is>
           <t>Pium</t>
         </is>
       </c>
-      <c r="I53" s="57" t="inlineStr">
+      <c r="I53" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3784,40 +3787,40 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="56" t="inlineStr">
+      <c r="A54" s="58" t="inlineStr">
         <is>
           <t>5801866013</t>
         </is>
       </c>
-      <c r="B54" s="56" t="inlineStr">
+      <c r="B54" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C54" s="57" t="inlineStr">
+      <c r="C54" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00077/2026</t>
         </is>
       </c>
-      <c r="D54" s="56" t="inlineStr">
+      <c r="D54" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E54" s="56" t="n">
+      <c r="E54" s="58" t="n">
         <v>79</v>
       </c>
-      <c r="G54" s="56" t="inlineStr">
+      <c r="G54" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H54" s="57" t="inlineStr">
+      <c r="H54" s="59" t="inlineStr">
         <is>
           <t>Paraiso Do Tocantins</t>
         </is>
       </c>
-      <c r="I54" s="57" t="inlineStr">
+      <c r="I54" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3829,40 +3832,40 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="56" t="inlineStr">
+      <c r="A55" s="58" t="inlineStr">
         <is>
           <t>7926089013</t>
         </is>
       </c>
-      <c r="B55" s="56" t="inlineStr">
+      <c r="B55" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C55" s="57" t="inlineStr">
+      <c r="C55" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00078/2026</t>
         </is>
       </c>
-      <c r="D55" s="56" t="inlineStr">
+      <c r="D55" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E55" s="56" t="n">
+      <c r="E55" s="58" t="n">
         <v>76</v>
       </c>
-      <c r="G55" s="56" t="inlineStr">
+      <c r="G55" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H55" s="57" t="inlineStr">
+      <c r="H55" s="59" t="inlineStr">
         <is>
           <t>Paraiso Do Tocantins</t>
         </is>
       </c>
-      <c r="I55" s="57" t="inlineStr">
+      <c r="I55" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3874,40 +3877,40 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="56" t="inlineStr">
+      <c r="A56" s="58" t="inlineStr">
         <is>
           <t>7900573047</t>
         </is>
       </c>
-      <c r="B56" s="56" t="inlineStr">
+      <c r="B56" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C56" s="57" t="inlineStr">
+      <c r="C56" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00080/2026</t>
         </is>
       </c>
-      <c r="D56" s="56" t="inlineStr">
+      <c r="D56" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E56" s="56" t="n">
+      <c r="E56" s="58" t="n">
         <v>75</v>
       </c>
-      <c r="G56" s="56" t="inlineStr">
+      <c r="G56" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H56" s="57" t="inlineStr">
+      <c r="H56" s="59" t="inlineStr">
         <is>
           <t>Figueiropolis</t>
         </is>
       </c>
-      <c r="I56" s="57" t="inlineStr">
+      <c r="I56" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3919,40 +3922,40 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="56" t="inlineStr">
+      <c r="A57" s="58" t="inlineStr">
         <is>
           <t>7927413001</t>
         </is>
       </c>
-      <c r="B57" s="56" t="inlineStr">
+      <c r="B57" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C57" s="57" t="inlineStr">
+      <c r="C57" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-PO 00118/2026</t>
         </is>
       </c>
-      <c r="D57" s="56" t="inlineStr">
+      <c r="D57" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E57" s="56" t="n">
+      <c r="E57" s="58" t="n">
         <v>75</v>
       </c>
-      <c r="G57" s="56" t="inlineStr">
+      <c r="G57" s="58" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H57" s="57" t="inlineStr">
+      <c r="H57" s="59" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I57" s="58" t="inlineStr">
+      <c r="I57" s="60" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -3964,40 +3967,40 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="56" t="inlineStr">
+      <c r="A58" s="58" t="inlineStr">
         <is>
           <t>7908686014</t>
         </is>
       </c>
-      <c r="B58" s="56" t="inlineStr">
+      <c r="B58" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C58" s="57" t="inlineStr">
+      <c r="C58" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00086/2026</t>
         </is>
       </c>
-      <c r="D58" s="56" t="inlineStr">
+      <c r="D58" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E58" s="56" t="n">
+      <c r="E58" s="58" t="n">
         <v>74</v>
       </c>
-      <c r="G58" s="56" t="inlineStr">
+      <c r="G58" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H58" s="57" t="inlineStr">
+      <c r="H58" s="59" t="inlineStr">
         <is>
           <t>Pium</t>
         </is>
       </c>
-      <c r="I58" s="57" t="inlineStr">
+      <c r="I58" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4009,40 +4012,40 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="56" t="inlineStr">
+      <c r="A59" s="58" t="inlineStr">
         <is>
           <t>7900117013</t>
         </is>
       </c>
-      <c r="B59" s="56" t="inlineStr">
+      <c r="B59" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C59" s="57" t="inlineStr">
+      <c r="C59" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00084/2026</t>
         </is>
       </c>
-      <c r="D59" s="56" t="inlineStr">
+      <c r="D59" s="58" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E59" s="56" t="n">
+      <c r="E59" s="58" t="n">
         <v>74</v>
       </c>
-      <c r="G59" s="56" t="inlineStr">
+      <c r="G59" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H59" s="57" t="inlineStr">
+      <c r="H59" s="59" t="inlineStr">
         <is>
           <t>Paraiso Do Tocantins</t>
         </is>
       </c>
-      <c r="I59" s="57" t="inlineStr">
+      <c r="I59" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4054,40 +4057,40 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="56" t="inlineStr">
+      <c r="A60" s="58" t="inlineStr">
         <is>
           <t>7900453110</t>
         </is>
       </c>
-      <c r="B60" s="56" t="inlineStr">
+      <c r="B60" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C60" s="57" t="inlineStr">
+      <c r="C60" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00087/2026</t>
         </is>
       </c>
-      <c r="D60" s="56" t="inlineStr">
+      <c r="D60" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E60" s="56" t="n">
+      <c r="E60" s="58" t="n">
         <v>71</v>
       </c>
-      <c r="G60" s="56" t="inlineStr">
+      <c r="G60" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H60" s="57" t="inlineStr">
+      <c r="H60" s="59" t="inlineStr">
         <is>
           <t>Santa Rita Do Tocantins</t>
         </is>
       </c>
-      <c r="I60" s="57" t="inlineStr">
+      <c r="I60" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4099,40 +4102,40 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="56" t="inlineStr">
+      <c r="A61" s="58" t="inlineStr">
         <is>
           <t>5865120195</t>
         </is>
       </c>
-      <c r="B61" s="56" t="inlineStr">
+      <c r="B61" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C61" s="57" t="inlineStr">
+      <c r="C61" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-GR 00538/2026</t>
         </is>
       </c>
-      <c r="D61" s="56" t="inlineStr">
+      <c r="D61" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E61" s="56" t="n">
+      <c r="E61" s="58" t="n">
         <v>51</v>
       </c>
-      <c r="G61" s="56" t="inlineStr">
+      <c r="G61" s="58" t="inlineStr">
         <is>
           <t>COCM-N</t>
         </is>
       </c>
-      <c r="H61" s="57" t="inlineStr">
+      <c r="H61" s="59" t="inlineStr">
         <is>
           <t>Centenario</t>
         </is>
       </c>
-      <c r="I61" s="58" t="inlineStr">
+      <c r="I61" s="60" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -4144,40 +4147,40 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="56" t="inlineStr">
+      <c r="A62" s="58" t="inlineStr">
         <is>
           <t>5836786094</t>
         </is>
       </c>
-      <c r="B62" s="56" t="inlineStr">
+      <c r="B62" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C62" s="57" t="inlineStr">
+      <c r="C62" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00095/2026</t>
         </is>
       </c>
-      <c r="D62" s="56" t="inlineStr">
+      <c r="D62" s="58" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E62" s="56" t="n">
+      <c r="E62" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="G62" s="56" t="inlineStr">
+      <c r="G62" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H62" s="57" t="inlineStr">
+      <c r="H62" s="59" t="inlineStr">
         <is>
           <t>Peixe</t>
         </is>
       </c>
-      <c r="I62" s="57" t="inlineStr">
+      <c r="I62" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4189,40 +4192,40 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="56" t="inlineStr">
+      <c r="A63" s="58" t="inlineStr">
         <is>
           <t>7900594026</t>
         </is>
       </c>
-      <c r="B63" s="56" t="inlineStr">
+      <c r="B63" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C63" s="57" t="inlineStr">
+      <c r="C63" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00113/2026</t>
         </is>
       </c>
-      <c r="D63" s="56" t="inlineStr">
+      <c r="D63" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E63" s="56" t="n">
+      <c r="E63" s="58" t="n">
         <v>27</v>
       </c>
-      <c r="G63" s="56" t="inlineStr">
+      <c r="G63" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H63" s="57" t="inlineStr">
+      <c r="H63" s="59" t="inlineStr">
         <is>
           <t>Ponte Alta Tocantins</t>
         </is>
       </c>
-      <c r="I63" s="57" t="inlineStr">
+      <c r="I63" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4234,40 +4237,40 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="56" t="inlineStr">
+      <c r="A64" s="58" t="inlineStr">
         <is>
           <t>7913662076</t>
         </is>
       </c>
-      <c r="B64" s="56" t="inlineStr">
+      <c r="B64" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C64" s="57" t="inlineStr">
+      <c r="C64" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00114/2026</t>
         </is>
       </c>
-      <c r="D64" s="56" t="inlineStr">
+      <c r="D64" s="58" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E64" s="56" t="n">
+      <c r="E64" s="58" t="n">
         <v>27</v>
       </c>
-      <c r="G64" s="56" t="inlineStr">
+      <c r="G64" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H64" s="57" t="inlineStr">
+      <c r="H64" s="59" t="inlineStr">
         <is>
           <t>Duere</t>
         </is>
       </c>
-      <c r="I64" s="57" t="inlineStr">
+      <c r="I64" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4279,40 +4282,40 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="56" t="inlineStr">
+      <c r="A65" s="58" t="inlineStr">
         <is>
           <t>5800859011</t>
         </is>
       </c>
-      <c r="B65" s="56" t="inlineStr">
+      <c r="B65" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C65" s="57" t="inlineStr">
+      <c r="C65" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00115/2026</t>
         </is>
       </c>
-      <c r="D65" s="56" t="inlineStr">
+      <c r="D65" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E65" s="56" t="n">
+      <c r="E65" s="58" t="n">
         <v>25</v>
       </c>
-      <c r="G65" s="56" t="inlineStr">
+      <c r="G65" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H65" s="57" t="inlineStr">
+      <c r="H65" s="59" t="inlineStr">
         <is>
           <t>Tupirama</t>
         </is>
       </c>
-      <c r="I65" s="57" t="inlineStr">
+      <c r="I65" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4324,40 +4327,40 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="56" t="inlineStr">
+      <c r="A66" s="58" t="inlineStr">
         <is>
           <t>5800090147</t>
         </is>
       </c>
-      <c r="B66" s="56" t="inlineStr">
+      <c r="B66" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C66" s="57" t="inlineStr">
+      <c r="C66" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00117/2026</t>
         </is>
       </c>
-      <c r="D66" s="56" t="inlineStr">
+      <c r="D66" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E66" s="56" t="n">
+      <c r="E66" s="58" t="n">
         <v>22</v>
       </c>
-      <c r="G66" s="56" t="inlineStr">
+      <c r="G66" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H66" s="57" t="inlineStr">
+      <c r="H66" s="59" t="inlineStr">
         <is>
           <t>Taipas Do Tocantins</t>
         </is>
       </c>
-      <c r="I66" s="57" t="inlineStr">
+      <c r="I66" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4369,40 +4372,40 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="56" t="inlineStr">
+      <c r="A67" s="58" t="inlineStr">
         <is>
           <t>5856156091</t>
         </is>
       </c>
-      <c r="B67" s="56" t="inlineStr">
+      <c r="B67" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C67" s="57" t="inlineStr">
+      <c r="C67" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-DP 00403/2026</t>
         </is>
       </c>
-      <c r="D67" s="56" t="inlineStr">
+      <c r="D67" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E67" s="56" t="n">
+      <c r="E67" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="G67" s="56" t="inlineStr">
+      <c r="G67" s="58" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H67" s="57" t="inlineStr">
+      <c r="H67" s="59" t="inlineStr">
         <is>
           <t>Almas</t>
         </is>
       </c>
-      <c r="I67" s="58" t="inlineStr">
+      <c r="I67" s="60" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -4414,40 +4417,40 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="56" t="inlineStr">
+      <c r="A68" s="58" t="inlineStr">
         <is>
           <t>5827102054</t>
         </is>
       </c>
-      <c r="B68" s="56" t="inlineStr">
+      <c r="B68" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C68" s="57" t="inlineStr">
+      <c r="C68" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-PS 00289/2026</t>
         </is>
       </c>
-      <c r="D68" s="56" t="inlineStr">
+      <c r="D68" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E68" s="56" t="n">
+      <c r="E68" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="G68" s="56" t="inlineStr">
+      <c r="G68" s="58" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H68" s="57" t="inlineStr">
+      <c r="H68" s="59" t="inlineStr">
         <is>
           <t>Pugmil</t>
         </is>
       </c>
-      <c r="I68" s="57" t="inlineStr">
+      <c r="I68" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4459,40 +4462,40 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="56" t="inlineStr">
+      <c r="A69" s="58" t="inlineStr">
         <is>
           <t>5846328094</t>
         </is>
       </c>
-      <c r="B69" s="56" t="inlineStr">
+      <c r="B69" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C69" s="57" t="inlineStr">
+      <c r="C69" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-GU 00687/2026</t>
         </is>
       </c>
-      <c r="D69" s="56" t="inlineStr">
+      <c r="D69" s="58" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E69" s="56" t="n">
+      <c r="E69" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="G69" s="56" t="inlineStr">
+      <c r="G69" s="58" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H69" s="57" t="inlineStr">
+      <c r="H69" s="59" t="inlineStr">
         <is>
           <t>Peixe</t>
         </is>
       </c>
-      <c r="I69" s="58" t="inlineStr">
+      <c r="I69" s="60" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -4504,35 +4507,35 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="59" t="inlineStr">
+      <c r="A70" s="58" t="inlineStr">
         <is>
           <t>7942572059</t>
         </is>
       </c>
-      <c r="B70" s="59" t="inlineStr">
+      <c r="B70" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C70" s="60" t="inlineStr">
+      <c r="C70" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00427/2026</t>
         </is>
       </c>
-      <c r="D70" s="59" t="inlineStr">
+      <c r="D70" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E70" s="59" t="n">
+      <c r="E70" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="G70" s="59" t="inlineStr">
+      <c r="G70" s="58" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H70" s="60" t="inlineStr">
+      <c r="H70" s="59" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
@@ -4542,47 +4545,47 @@
           <t>Só no Mapeamento Criticidades</t>
         </is>
       </c>
-      <c r="J70" s="36" t="inlineStr">
+      <c r="J70" s="23" t="inlineStr">
         <is>
           <t>EXECUTADO</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="56" t="inlineStr">
+      <c r="A71" s="58" t="inlineStr">
         <is>
           <t>7929376022</t>
         </is>
       </c>
-      <c r="B71" s="56" t="inlineStr">
+      <c r="B71" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C71" s="57" t="inlineStr">
+      <c r="C71" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2026</t>
         </is>
       </c>
-      <c r="D71" s="56" t="inlineStr">
+      <c r="D71" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E71" s="56" t="n">
+      <c r="E71" s="58" t="n">
         <v>7</v>
       </c>
-      <c r="G71" s="56" t="inlineStr">
+      <c r="G71" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H71" s="57" t="inlineStr">
+      <c r="H71" s="59" t="inlineStr">
         <is>
           <t>Babaculandia</t>
         </is>
       </c>
-      <c r="I71" s="57" t="inlineStr">
+      <c r="I71" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4594,40 +4597,40 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="56" t="inlineStr">
+      <c r="A72" s="58" t="inlineStr">
         <is>
           <t>5800438116</t>
         </is>
       </c>
-      <c r="B72" s="56" t="inlineStr">
+      <c r="B72" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C72" s="57" t="inlineStr">
+      <c r="C72" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-DP 00404/2026</t>
         </is>
       </c>
-      <c r="D72" s="56" t="inlineStr">
+      <c r="D72" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E72" s="56" t="n">
+      <c r="E72" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="G72" s="56" t="inlineStr">
+      <c r="G72" s="58" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H72" s="57" t="inlineStr">
+      <c r="H72" s="59" t="inlineStr">
         <is>
           <t>Chapada Da Natividade</t>
         </is>
       </c>
-      <c r="I72" s="57" t="inlineStr">
+      <c r="I72" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4639,40 +4642,40 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="56" t="inlineStr">
+      <c r="A73" s="58" t="inlineStr">
         <is>
           <t>5803327001</t>
         </is>
       </c>
-      <c r="B73" s="56" t="inlineStr">
+      <c r="B73" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C73" s="57" t="inlineStr">
+      <c r="C73" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00434/2026</t>
         </is>
       </c>
-      <c r="D73" s="56" t="inlineStr">
+      <c r="D73" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E73" s="56" t="n">
+      <c r="E73" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="G73" s="56" t="inlineStr">
+      <c r="G73" s="58" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H73" s="57" t="inlineStr">
+      <c r="H73" s="59" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I73" s="58" t="inlineStr">
+      <c r="I73" s="60" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -4684,40 +4687,40 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="56" t="inlineStr">
+      <c r="A74" s="58" t="inlineStr">
         <is>
           <t>7933766059</t>
         </is>
       </c>
-      <c r="B74" s="56" t="inlineStr">
+      <c r="B74" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C74" s="57" t="inlineStr">
+      <c r="C74" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00431/2026</t>
         </is>
       </c>
-      <c r="D74" s="56" t="inlineStr">
+      <c r="D74" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E74" s="56" t="n">
+      <c r="E74" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="G74" s="56" t="inlineStr">
+      <c r="G74" s="58" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H74" s="57" t="inlineStr">
+      <c r="H74" s="59" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I74" s="57" t="inlineStr">
+      <c r="I74" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4729,40 +4732,40 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="56" t="inlineStr">
+      <c r="A75" s="58" t="inlineStr">
         <is>
           <t>7931610122</t>
         </is>
       </c>
-      <c r="B75" s="56" t="inlineStr">
+      <c r="B75" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C75" s="57" t="inlineStr">
+      <c r="C75" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00433/2026</t>
         </is>
       </c>
-      <c r="D75" s="56" t="inlineStr">
+      <c r="D75" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E75" s="56" t="n">
+      <c r="E75" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="G75" s="56" t="inlineStr">
+      <c r="G75" s="58" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H75" s="57" t="inlineStr">
+      <c r="H75" s="59" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I75" s="57" t="inlineStr">
+      <c r="I75" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4774,40 +4777,40 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="56" t="inlineStr">
+      <c r="A76" s="58" t="inlineStr">
         <is>
           <t>7927169001</t>
         </is>
       </c>
-      <c r="B76" s="56" t="inlineStr">
+      <c r="B76" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C76" s="57" t="inlineStr">
+      <c r="C76" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00432/2026</t>
         </is>
       </c>
-      <c r="D76" s="56" t="inlineStr">
+      <c r="D76" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E76" s="56" t="n">
+      <c r="E76" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="G76" s="56" t="inlineStr">
+      <c r="G76" s="58" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H76" s="57" t="inlineStr">
+      <c r="H76" s="59" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I76" s="57" t="inlineStr">
+      <c r="I76" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4819,40 +4822,40 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="56" t="inlineStr">
+      <c r="A77" s="58" t="inlineStr">
         <is>
           <t>7933726256</t>
         </is>
       </c>
-      <c r="B77" s="56" t="inlineStr">
+      <c r="B77" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C77" s="57" t="inlineStr">
+      <c r="C77" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-PO 00181/2026</t>
         </is>
       </c>
-      <c r="D77" s="56" t="inlineStr">
+      <c r="D77" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E77" s="56" t="n">
+      <c r="E77" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="G77" s="56" t="inlineStr">
+      <c r="G77" s="58" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H77" s="57" t="inlineStr">
+      <c r="H77" s="59" t="inlineStr">
         <is>
           <t>Mateiros</t>
         </is>
       </c>
-      <c r="I77" s="57" t="inlineStr">
+      <c r="I77" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4864,40 +4867,40 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="56" t="inlineStr">
+      <c r="A78" s="58" t="inlineStr">
         <is>
           <t>7911120026</t>
         </is>
       </c>
-      <c r="B78" s="56" t="inlineStr">
+      <c r="B78" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C78" s="57" t="inlineStr">
+      <c r="C78" s="59" t="inlineStr">
         <is>
           <t>DG-RD-PO 00444/2026</t>
         </is>
       </c>
-      <c r="D78" s="56" t="inlineStr">
+      <c r="D78" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E78" s="56" t="n">
+      <c r="E78" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="G78" s="56" t="inlineStr">
+      <c r="G78" s="58" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H78" s="57" t="inlineStr">
+      <c r="H78" s="59" t="inlineStr">
         <is>
           <t>Ponte Alta Tocantins</t>
         </is>
       </c>
-      <c r="I78" s="58" t="inlineStr">
+      <c r="I78" s="60" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -4909,40 +4912,40 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="56" t="inlineStr">
+      <c r="A79" s="58" t="inlineStr">
         <is>
           <t>7908705049</t>
         </is>
       </c>
-      <c r="B79" s="56" t="inlineStr">
+      <c r="B79" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C79" s="57" t="inlineStr">
+      <c r="C79" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-DP 00409/2026</t>
         </is>
       </c>
-      <c r="D79" s="56" t="inlineStr">
+      <c r="D79" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E79" s="56" t="n">
+      <c r="E79" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G79" s="56" t="inlineStr">
+      <c r="G79" s="58" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H79" s="57" t="inlineStr">
+      <c r="H79" s="59" t="inlineStr">
         <is>
           <t>Aurora Do Tocantins</t>
         </is>
       </c>
-      <c r="I79" s="57" t="inlineStr">
+      <c r="I79" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4954,40 +4957,40 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="56" t="inlineStr">
+      <c r="A80" s="58" t="inlineStr">
         <is>
           <t>7900230155</t>
         </is>
       </c>
-      <c r="B80" s="56" t="inlineStr">
+      <c r="B80" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C80" s="57" t="inlineStr">
+      <c r="C80" s="59" t="inlineStr">
         <is>
           <t>ETO-RD-GR 00685/2026</t>
         </is>
       </c>
-      <c r="D80" s="56" t="inlineStr">
+      <c r="D80" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E80" s="56" t="n">
+      <c r="E80" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="G80" s="56" t="inlineStr">
+      <c r="G80" s="58" t="inlineStr">
         <is>
           <t>COCM-N</t>
         </is>
       </c>
-      <c r="H80" s="57" t="inlineStr">
+      <c r="H80" s="59" t="inlineStr">
         <is>
           <t>Palmeirante</t>
         </is>
       </c>
-      <c r="I80" s="57" t="inlineStr">
+      <c r="I80" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4999,40 +5002,40 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="56" t="inlineStr">
+      <c r="A81" s="58" t="inlineStr">
         <is>
           <t>7928564039</t>
         </is>
       </c>
-      <c r="B81" s="56" t="inlineStr">
+      <c r="B81" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C81" s="57" t="inlineStr">
+      <c r="C81" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00123/2026</t>
         </is>
       </c>
-      <c r="D81" s="56" t="inlineStr">
+      <c r="D81" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E81" s="56" t="n">
+      <c r="E81" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="G81" s="56" t="inlineStr">
+      <c r="G81" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H81" s="57" t="inlineStr">
+      <c r="H81" s="59" t="inlineStr">
         <is>
           <t>Araguatins</t>
         </is>
       </c>
-      <c r="I81" s="57" t="inlineStr">
+      <c r="I81" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5044,40 +5047,40 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="56" t="inlineStr">
+      <c r="A82" s="58" t="inlineStr">
         <is>
           <t>7928241200</t>
         </is>
       </c>
-      <c r="B82" s="56" t="inlineStr">
+      <c r="B82" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C82" s="57" t="inlineStr">
+      <c r="C82" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00128/2026</t>
         </is>
       </c>
-      <c r="D82" s="56" t="inlineStr">
+      <c r="D82" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E82" s="56" t="n">
+      <c r="E82" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="56" t="inlineStr">
+      <c r="G82" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H82" s="57" t="inlineStr">
+      <c r="H82" s="59" t="inlineStr">
         <is>
           <t>Sao Salvador Do Tocantins</t>
         </is>
       </c>
-      <c r="I82" s="57" t="inlineStr">
+      <c r="I82" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5089,40 +5092,40 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="56" t="inlineStr">
+      <c r="A83" s="58" t="inlineStr">
         <is>
           <t>5856070091</t>
         </is>
       </c>
-      <c r="B83" s="56" t="inlineStr">
+      <c r="B83" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C83" s="57" t="inlineStr">
+      <c r="C83" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00130/2026</t>
         </is>
       </c>
-      <c r="D83" s="56" t="inlineStr">
+      <c r="D83" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E83" s="56" t="n">
+      <c r="E83" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="G83" s="56" t="inlineStr">
+      <c r="G83" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H83" s="57" t="inlineStr">
+      <c r="H83" s="59" t="inlineStr">
         <is>
           <t>Almas</t>
         </is>
       </c>
-      <c r="I83" s="57" t="inlineStr">
+      <c r="I83" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5134,85 +5137,85 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="59" t="inlineStr">
+      <c r="A84" s="58" t="inlineStr">
         <is>
           <t>5850308009</t>
         </is>
       </c>
-      <c r="B84" s="59" t="inlineStr">
+      <c r="B84" s="58" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C84" s="60" t="inlineStr">
+      <c r="C84" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00127/2026</t>
         </is>
       </c>
-      <c r="D84" s="59" t="inlineStr">
+      <c r="D84" s="58" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E84" s="59" t="n">
+      <c r="E84" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="G84" s="59" t="inlineStr">
+      <c r="G84" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H84" s="60" t="inlineStr">
+      <c r="H84" s="59" t="inlineStr">
         <is>
           <t>Guarai</t>
         </is>
       </c>
-      <c r="I84" s="60" t="inlineStr">
+      <c r="I84" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J84" s="36" t="inlineStr">
+      <c r="J84" s="23" t="inlineStr">
         <is>
           <t>CONCLUÍDA MAS AINDA NO POSTO (VERIFICAR)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="56" t="inlineStr">
+      <c r="A85" s="58" t="inlineStr">
         <is>
           <t>7937102148</t>
         </is>
       </c>
-      <c r="B85" s="56" t="inlineStr">
+      <c r="B85" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C85" s="57" t="inlineStr">
+      <c r="C85" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00129/2026</t>
         </is>
       </c>
-      <c r="D85" s="56" t="inlineStr">
+      <c r="D85" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E85" s="56" t="n">
+      <c r="E85" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="G85" s="56" t="inlineStr">
+      <c r="G85" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H85" s="57" t="inlineStr">
+      <c r="H85" s="59" t="inlineStr">
         <is>
           <t>Sao Valerio Da Natividade</t>
         </is>
       </c>
-      <c r="I85" s="57" t="inlineStr">
+      <c r="I85" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5224,40 +5227,40 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="56" t="inlineStr">
+      <c r="A86" s="58" t="inlineStr">
         <is>
           <t>7923673004</t>
         </is>
       </c>
-      <c r="B86" s="56" t="inlineStr">
+      <c r="B86" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C86" s="57" t="inlineStr">
+      <c r="C86" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00124/2026</t>
         </is>
       </c>
-      <c r="D86" s="56" t="inlineStr">
+      <c r="D86" s="58" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E86" s="56" t="n">
+      <c r="E86" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="56" t="inlineStr">
+      <c r="G86" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H86" s="57" t="inlineStr">
+      <c r="H86" s="59" t="inlineStr">
         <is>
           <t>Araguaina</t>
         </is>
       </c>
-      <c r="I86" s="57" t="inlineStr">
+      <c r="I86" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5269,40 +5272,40 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="56" t="inlineStr">
+      <c r="A87" s="58" t="inlineStr">
         <is>
           <t>7900525015</t>
         </is>
       </c>
-      <c r="B87" s="56" t="inlineStr">
+      <c r="B87" s="58" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C87" s="57" t="inlineStr">
+      <c r="C87" s="59" t="inlineStr">
         <is>
           <t>ETO-COEP 00125/2026</t>
         </is>
       </c>
-      <c r="D87" s="56" t="inlineStr">
+      <c r="D87" s="58" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E87" s="56" t="n">
+      <c r="E87" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="G87" s="56" t="inlineStr">
+      <c r="G87" s="58" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H87" s="57" t="inlineStr">
+      <c r="H87" s="59" t="inlineStr">
         <is>
           <t>Pedro Afonso</t>
         </is>
       </c>
-      <c r="I87" s="57" t="inlineStr">
+      <c r="I87" s="59" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5945,15 +5948,20 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
+          <t>Em execução (COCM)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
           <t>No posto COEP</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Pendente fora do posto</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -5972,12 +5980,15 @@
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="F6" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="G6" s="19" t="n">
         <v>30</v>
       </c>
     </row>
@@ -5994,12 +6005,15 @@
         <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="F7" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="G7" s="19" t="n">
         <v>21</v>
       </c>
     </row>
@@ -6010,18 +6024,21 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>12</v>
-      </c>
       <c r="E8" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F8" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="G8" s="19" t="n">
         <v>25</v>
       </c>
     </row>
@@ -6038,12 +6055,15 @@
         <v>1</v>
       </c>
       <c r="D9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="F9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="G9" s="19" t="n">
         <v>26</v>
       </c>
     </row>
@@ -6063,9 +6083,12 @@
         <v>0</v>
       </c>
       <c r="E10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="G10" s="19" t="n">
         <v>13</v>
       </c>
     </row>
@@ -6082,12 +6105,15 @@
         <v>0</v>
       </c>
       <c r="D11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="F11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="G11" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6098,18 +6124,21 @@
         </is>
       </c>
       <c r="B12" s="19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="E12" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="G12" s="19" t="n">
         <v>116</v>
       </c>
     </row>
@@ -7138,7 +7167,7 @@
     <row r="31">
       <c r="A31" s="49" t="inlineStr">
         <is>
-          <t>7942572059</t>
+          <t>7944319149</t>
         </is>
       </c>
       <c r="B31" s="49" t="inlineStr">
@@ -7148,12 +7177,12 @@
       </c>
       <c r="C31" s="50" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Caseara</t>
         </is>
       </c>
       <c r="D31" s="50" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Divinopolis</t>
         </is>
       </c>
       <c r="E31" s="50" t="inlineStr">
@@ -7163,12 +7192,12 @@
       </c>
       <c r="F31" s="50" t="inlineStr">
         <is>
-          <t>ETO-RD-PA 00427/2026</t>
+          <t>CONCLUÍDA</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>Comunicação/rádio + Aterramento (da descrição da SS)</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H31" s="49" t="inlineStr">
@@ -7184,21 +7213,21 @@
           <t>EXECUTADO</t>
         </is>
       </c>
-      <c r="K31" s="31" t="inlineStr">
-        <is>
-          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>— (executado)</t>
         </is>
       </c>
       <c r="L31" s="23" t="inlineStr">
         <is>
-          <t>Atendimento do Ramal do Marasca e GAs (108 UCs)</t>
+          <t>Atendimento do Grupo A - Matosul (TF 1500 kVA)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="49" t="inlineStr">
         <is>
-          <t>7944319149</t>
+          <t>7955986084</t>
         </is>
       </c>
       <c r="B32" s="49" t="inlineStr">
@@ -7208,7 +7237,7 @@
       </c>
       <c r="C32" s="50" t="inlineStr">
         <is>
-          <t>Caseara</t>
+          <t>Divinopolis</t>
         </is>
       </c>
       <c r="D32" s="50" t="inlineStr">
@@ -7228,7 +7257,7 @@
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>— (concluída, sem descrição na base)</t>
         </is>
       </c>
       <c r="H32" s="49" t="inlineStr">
@@ -7251,14 +7280,14 @@
       </c>
       <c r="L32" s="23" t="inlineStr">
         <is>
-          <t>Atendimento do Grupo A - Matosul (TF 1500 kVA)</t>
+          <t>Transferência de cargas do 444R da SE Paraíso I</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="49" t="inlineStr">
         <is>
-          <t>7955986084</t>
+          <t>7967181127</t>
         </is>
       </c>
       <c r="B33" s="49" t="inlineStr">
@@ -7268,17 +7297,17 @@
       </c>
       <c r="C33" s="50" t="inlineStr">
         <is>
-          <t>Divinopolis</t>
+          <t>Palmeiras Do Tocantins</t>
         </is>
       </c>
       <c r="D33" s="50" t="inlineStr">
         <is>
-          <t>Divinopolis</t>
+          <t>Tocantinopolis</t>
         </is>
       </c>
       <c r="E33" s="50" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F33" s="50" t="inlineStr">
@@ -7311,34 +7340,34 @@
       </c>
       <c r="L33" s="23" t="inlineStr">
         <is>
-          <t>Transferência de cargas do 444R da SE Paraíso I</t>
+          <t>Transferência de Palmeiras, 3 RLs sendo 2 operando</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="49" t="inlineStr">
         <is>
-          <t>7967181127</t>
+          <t>5841308190</t>
         </is>
       </c>
       <c r="B34" s="49" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C34" s="50" t="inlineStr">
         <is>
-          <t>Palmeiras Do Tocantins</t>
+          <t>Novo Jardim</t>
         </is>
       </c>
       <c r="D34" s="50" t="inlineStr">
         <is>
-          <t>Tocantinopolis</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E34" s="50" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F34" s="50" t="inlineStr">
@@ -7348,16 +7377,16 @@
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>— (concluída, sem descrição na base)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="49" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I34" s="49" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J34" s="51" t="inlineStr">
         <is>
@@ -7371,34 +7400,34 @@
       </c>
       <c r="L34" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Palmeiras, 3 RLs sendo 2 operando</t>
+          <t>Equipamento obsoleto com a entrada da SE Serras Gerais</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="49" t="inlineStr">
         <is>
-          <t>5841308190</t>
+          <t>7900505026</t>
         </is>
       </c>
       <c r="B35" s="49" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C35" s="50" t="inlineStr">
         <is>
-          <t>Novo Jardim</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="D35" s="50" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="E35" s="50" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F35" s="50" t="inlineStr">
@@ -7408,7 +7437,7 @@
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="H35" s="49" t="inlineStr">
@@ -7417,7 +7446,7 @@
         </is>
       </c>
       <c r="I35" s="49" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J35" s="51" t="inlineStr">
         <is>
@@ -7431,14 +7460,14 @@
       </c>
       <c r="L35" s="23" t="inlineStr">
         <is>
-          <t>Equipamento obsoleto com a entrada da SE Serras Gerais</t>
+          <t>Atendimento do Ramal do Gato (288 UCs) e UFV Videira, no desarme a jusante penaliza a cidade de Pindorama</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="49" t="inlineStr">
         <is>
-          <t>7900505026</t>
+          <t>7908206074</t>
         </is>
       </c>
       <c r="B36" s="49" t="inlineStr">
@@ -7448,17 +7477,17 @@
       </c>
       <c r="C36" s="50" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="D36" s="50" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E36" s="50" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F36" s="50" t="inlineStr">
@@ -7468,7 +7497,7 @@
       </c>
       <c r="G36" s="23" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H36" s="49" t="inlineStr">
@@ -7477,7 +7506,7 @@
         </is>
       </c>
       <c r="I36" s="49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J36" s="51" t="inlineStr">
         <is>
@@ -7491,14 +7520,14 @@
       </c>
       <c r="L36" s="23" t="inlineStr">
         <is>
-          <t>Atendimento do Ramal do Gato (288 UCs) e UFV Videira, no desarme a jusante penaliza a cidade de Pindorama</t>
+          <t>Atendimento do PA Novo Plano (102 UCs)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="49" t="inlineStr">
         <is>
-          <t>7908206074</t>
+          <t>7910027196</t>
         </is>
       </c>
       <c r="B37" s="49" t="inlineStr">
@@ -7508,17 +7537,17 @@
       </c>
       <c r="C37" s="50" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Lagoa Do Tocantins</t>
         </is>
       </c>
       <c r="D37" s="50" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="E37" s="50" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F37" s="50" t="inlineStr">
@@ -7528,7 +7557,7 @@
       </c>
       <c r="G37" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Completo sem o radio</t>
         </is>
       </c>
       <c r="H37" s="49" t="inlineStr">
@@ -7551,14 +7580,14 @@
       </c>
       <c r="L37" s="23" t="inlineStr">
         <is>
-          <t>Atendimento do PA Novo Plano (102 UCs)</t>
+          <t>Concluída em 2026-06-17 via ETO-TELE 00973/2026 | Atendimento do Ramal do Rio Preto (197 UCs)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="49" t="inlineStr">
         <is>
-          <t>7910027196</t>
+          <t>7955430075</t>
         </is>
       </c>
       <c r="B38" s="49" t="inlineStr">
@@ -7568,12 +7597,12 @@
       </c>
       <c r="C38" s="50" t="inlineStr">
         <is>
-          <t>Lagoa Do Tocantins</t>
+          <t>Dois Irmaos Do Tocantins</t>
         </is>
       </c>
       <c r="D38" s="50" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Divinopolis</t>
         </is>
       </c>
       <c r="E38" s="50" t="inlineStr">
@@ -7588,7 +7617,7 @@
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>Completo sem o radio</t>
+          <t>tanque</t>
         </is>
       </c>
       <c r="H38" s="49" t="inlineStr">
@@ -7597,7 +7626,7 @@
         </is>
       </c>
       <c r="I38" s="49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J38" s="51" t="inlineStr">
         <is>
@@ -7611,14 +7640,14 @@
       </c>
       <c r="L38" s="23" t="inlineStr">
         <is>
-          <t>Concluída em 2026-06-17 via ETO-TELE 00973/2026 | Atendimento do Ramal do Rio Preto (197 UCs)</t>
+          <t>Atendimento do Ramal do Boleu (13 UCs), no desarme a jusante penaliza parte 303 UCs rurais</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="49" t="inlineStr">
         <is>
-          <t>7955430075</t>
+          <t>7955686076</t>
         </is>
       </c>
       <c r="B39" s="49" t="inlineStr">
@@ -7628,17 +7657,17 @@
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
-          <t>Dois Irmaos Do Tocantins</t>
+          <t>Duere</t>
         </is>
       </c>
       <c r="D39" s="50" t="inlineStr">
         <is>
-          <t>Divinopolis</t>
+          <t>Gurupi</t>
         </is>
       </c>
       <c r="E39" s="50" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F39" s="50" t="inlineStr">
@@ -7648,7 +7677,7 @@
       </c>
       <c r="G39" s="23" t="inlineStr">
         <is>
-          <t>tanque</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="49" t="inlineStr">
@@ -7671,14 +7700,14 @@
       </c>
       <c r="L39" s="23" t="inlineStr">
         <is>
-          <t>Atendimento do Ramal do Boleu (13 UCs), no desarme a jusante penaliza parte 303 UCs rurais</t>
+          <t>Fonte alternativa de atendimento do Ramal Bacuri (217 UCs)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="49" t="inlineStr">
         <is>
-          <t>7955686076</t>
+          <t>7955946007</t>
         </is>
       </c>
       <c r="B40" s="49" t="inlineStr">
@@ -7688,17 +7717,17 @@
       </c>
       <c r="C40" s="50" t="inlineStr">
         <is>
-          <t>Duere</t>
+          <t>Miracema Do Tocantins</t>
         </is>
       </c>
       <c r="D40" s="50" t="inlineStr">
         <is>
-          <t>Gurupi</t>
+          <t>Miracema Do Tocantins</t>
         </is>
       </c>
       <c r="E40" s="50" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F40" s="50" t="inlineStr">
@@ -7708,7 +7737,7 @@
       </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>— (concluída, sem descrição na base)</t>
         </is>
       </c>
       <c r="H40" s="49" t="inlineStr">
@@ -7731,14 +7760,14 @@
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
-          <t>Fonte alternativa de atendimento do Ramal Bacuri (217 UCs)</t>
+          <t>Alimentação do serviço auxiliar da Investco e clientes rurais (260 UCs)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="49" t="inlineStr">
         <is>
-          <t>7955946007</t>
+          <t>7908196047</t>
         </is>
       </c>
       <c r="B41" s="49" t="inlineStr">
@@ -7748,17 +7777,17 @@
       </c>
       <c r="C41" s="50" t="inlineStr">
         <is>
-          <t>Miracema Do Tocantins</t>
+          <t>Figueiropolis</t>
         </is>
       </c>
       <c r="D41" s="50" t="inlineStr">
         <is>
-          <t>Miracema Do Tocantins</t>
+          <t>Alvorada</t>
         </is>
       </c>
       <c r="E41" s="50" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F41" s="50" t="inlineStr">
@@ -7768,7 +7797,7 @@
       </c>
       <c r="G41" s="23" t="inlineStr">
         <is>
-          <t>— (concluída, sem descrição na base)</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="H41" s="49" t="inlineStr">
@@ -7779,56 +7808,54 @@
       <c r="I41" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="J41" s="51" t="inlineStr">
-        <is>
-          <t>EXECUTADO</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="inlineStr">
-        <is>
-          <t>— (executado)</t>
-        </is>
+      <c r="J41" s="52" t="inlineStr">
+        <is>
+          <t>CONCLUÍDA MAS AINDA NO POSTO (VERIFICAR)</t>
+        </is>
+      </c>
+      <c r="K41" s="24" t="n">
+        <v>66619.48</v>
       </c>
       <c r="L41" s="23" t="inlineStr">
         <is>
-          <t>Alimentação do serviço auxiliar da Investco e clientes rurais (260 UCs)</t>
+          <t>Seccionamento do Rural e energização do 224R</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="49" t="inlineStr">
         <is>
-          <t>5850308009</t>
+          <t>7942572059</t>
         </is>
       </c>
       <c r="B42" s="49" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>Guarai</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="D42" s="50" t="inlineStr">
         <is>
-          <t>Guarai</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="E42" s="50" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F42" s="50" t="inlineStr">
         <is>
-          <t>ETO-TELE 00958/2026</t>
+          <t>ETO-RD-PA 00427/2026</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>Controle</t>
+          <t>Comunicação/rádio + Aterramento (da descrição da SS)</t>
         </is>
       </c>
       <c r="H42" s="49" t="inlineStr">
@@ -7837,84 +7864,86 @@
         </is>
       </c>
       <c r="I42" s="49" t="n">
-        <v>50</v>
-      </c>
-      <c r="J42" s="52" t="inlineStr">
-        <is>
-          <t>CONCLUÍDA MAS AINDA NO POSTO (VERIFICAR)</t>
-        </is>
-      </c>
-      <c r="K42" s="24" t="n">
-        <v>29445.39</v>
+        <v>35</v>
+      </c>
+      <c r="J42" s="53" t="inlineStr">
+        <is>
+          <t>Em execução (ETO-RD-PA)</t>
+        </is>
+      </c>
+      <c r="K42" s="31" t="inlineStr">
+        <is>
+          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
+        </is>
       </c>
       <c r="L42" s="23" t="inlineStr">
         <is>
-          <t>Atendimento de parte da RDU de Guaraí e ramal da PRF/Repetidora</t>
+          <t>Atendimento do Ramal do Marasca e GAs (108 UCs) | Definição do gestor 08/07: melhoria de aterramento SEM CUSTO; SS ETO-RD-PA 00427/2026 ainda aberta (8 dias aguardando DCMD) =&gt; em execução</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="49" t="inlineStr">
         <is>
-          <t>7908196047</t>
+          <t>5800859011</t>
         </is>
       </c>
       <c r="B43" s="49" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C43" s="50" t="inlineStr">
         <is>
-          <t>Figueiropolis</t>
+          <t>Tupirama</t>
         </is>
       </c>
       <c r="D43" s="50" t="inlineStr">
         <is>
-          <t>Alvorada</t>
+          <t>Guarai</t>
         </is>
       </c>
       <c r="E43" s="50" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F43" s="50" t="inlineStr">
         <is>
-          <t>CONCLUÍDA</t>
+          <t>ETO-COEP 00115/2026</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t xml:space="preserve">Controle </t>
         </is>
       </c>
       <c r="H43" s="49" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Muito Alta</t>
         </is>
       </c>
       <c r="I43" s="49" t="n">
-        <v>25</v>
-      </c>
-      <c r="J43" s="52" t="inlineStr">
-        <is>
-          <t>CONCLUÍDA MAS AINDA NO POSTO (VERIFICAR)</t>
+        <v>110</v>
+      </c>
+      <c r="J43" s="54" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K43" s="24" t="n">
-        <v>66619.48</v>
+        <v>29445.39</v>
       </c>
       <c r="L43" s="23" t="inlineStr">
         <is>
-          <t>Seccionamento do Rural e energização do 224R</t>
+          <t>Atendimento de parte da RDU Guaraí por fonte alternativa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="49" t="inlineStr">
         <is>
-          <t>5800859011</t>
+          <t>5854566043</t>
         </is>
       </c>
       <c r="B44" s="49" t="inlineStr">
@@ -7924,27 +7953,27 @@
       </c>
       <c r="C44" s="50" t="inlineStr">
         <is>
-          <t>Tupirama</t>
+          <t>Silvanopolis</t>
         </is>
       </c>
       <c r="D44" s="50" t="inlineStr">
         <is>
-          <t>Guarai</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="E44" s="50" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F44" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00115/2026</t>
+          <t>ETO-COEP 00160/2025</t>
         </is>
       </c>
       <c r="G44" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Controle </t>
+          <t>1 célula</t>
         </is>
       </c>
       <c r="H44" s="49" t="inlineStr">
@@ -7955,24 +7984,24 @@
       <c r="I44" s="49" t="n">
         <v>110</v>
       </c>
-      <c r="J44" s="53" t="inlineStr">
+      <c r="J44" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K44" s="24" t="n">
-        <v>29445.39</v>
+        <v>207212.3</v>
       </c>
       <c r="L44" s="23" t="inlineStr">
         <is>
-          <t>Atendimento de parte da RDU Guaraí por fonte alternativa</t>
+          <t>Aumento de reclamações no atendimento de Silvanópolis por Porto Nacional no período seco (Outra fonte com defeito também)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="49" t="inlineStr">
         <is>
-          <t>5854566043</t>
+          <t>5856070091</t>
         </is>
       </c>
       <c r="B45" s="49" t="inlineStr">
@@ -7982,27 +8011,27 @@
       </c>
       <c r="C45" s="50" t="inlineStr">
         <is>
-          <t>Silvanopolis</t>
+          <t>Almas</t>
         </is>
       </c>
       <c r="D45" s="50" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E45" s="50" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F45" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00160/2025</t>
+          <t>ETO-TELE 00955/2026</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>1 célula</t>
+          <t>Conexão invertida</t>
         </is>
       </c>
       <c r="H45" s="49" t="inlineStr">
@@ -8011,56 +8040,56 @@
         </is>
       </c>
       <c r="I45" s="49" t="n">
-        <v>110</v>
-      </c>
-      <c r="J45" s="53" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="J45" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K45" s="24" t="n">
-        <v>207212.3</v>
+        <v>460999.9</v>
       </c>
       <c r="L45" s="23" t="inlineStr">
         <is>
-          <t>Aumento de reclamações no atendimento de Silvanópolis por Porto Nacional no período seco (Outra fonte com defeito também)</t>
+          <t>Atendimento da região da Engegold, Nativa, cidade Natividade e Chapada da Natividade</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="49" t="inlineStr">
         <is>
-          <t>5856070091</t>
+          <t>7900117013</t>
         </is>
       </c>
       <c r="B46" s="49" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C46" s="50" t="inlineStr">
         <is>
-          <t>Almas</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="D46" s="50" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E46" s="50" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F46" s="50" t="inlineStr">
         <is>
-          <t>ETO-TELE 00955/2026</t>
+          <t>ETO-COEP 00084/2026</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
-          <t>Conexão invertida</t>
+          <t>Relé Cooper</t>
         </is>
       </c>
       <c r="H46" s="49" t="inlineStr">
@@ -8069,26 +8098,26 @@
         </is>
       </c>
       <c r="I46" s="49" t="n">
-        <v>100</v>
-      </c>
-      <c r="J46" s="53" t="inlineStr">
+        <v>95</v>
+      </c>
+      <c r="J46" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K46" s="24" t="n">
-        <v>460999.9</v>
+        <v>66619.48</v>
       </c>
       <c r="L46" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da região da Engegold, Nativa, cidade Natividade e Chapada da Natividade</t>
+          <t>Transferência do 214R de Paraíso I, Centro Comercial de Paraíso</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="49" t="inlineStr">
         <is>
-          <t>7900117013</t>
+          <t>7900453110</t>
         </is>
       </c>
       <c r="B47" s="49" t="inlineStr">
@@ -8098,12 +8127,12 @@
       </c>
       <c r="C47" s="50" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Santa Rita Do Tocantins</t>
         </is>
       </c>
       <c r="D47" s="50" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="E47" s="50" t="inlineStr">
@@ -8113,12 +8142,12 @@
       </c>
       <c r="F47" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00084/2026</t>
+          <t>ETO-COEP 00087/2026</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>Relé Cooper</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H47" s="49" t="inlineStr">
@@ -8127,26 +8156,26 @@
         </is>
       </c>
       <c r="I47" s="49" t="n">
-        <v>95</v>
-      </c>
-      <c r="J47" s="53" t="inlineStr">
+        <v>85</v>
+      </c>
+      <c r="J47" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K47" s="24" t="n">
-        <v>66619.48</v>
+        <v>89455.53999999999</v>
       </c>
       <c r="L47" s="23" t="inlineStr">
         <is>
-          <t>Transferência do 214R de Paraíso I, Centro Comercial de Paraíso</t>
+          <t>Transferência de Santa Rita, fonte principal operando</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="49" t="inlineStr">
         <is>
-          <t>7900453110</t>
+          <t>7900594026</t>
         </is>
       </c>
       <c r="B48" s="49" t="inlineStr">
@@ -8156,12 +8185,12 @@
       </c>
       <c r="C48" s="50" t="inlineStr">
         <is>
-          <t>Santa Rita Do Tocantins</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="D48" s="50" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="E48" s="50" t="inlineStr">
@@ -8171,12 +8200,12 @@
       </c>
       <c r="F48" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00087/2026</t>
+          <t>ETO-COEP 00113/2026</t>
         </is>
       </c>
       <c r="G48" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Comunicação/rádio (da descrição da SS)</t>
         </is>
       </c>
       <c r="H48" s="49" t="inlineStr">
@@ -8185,9 +8214,9 @@
         </is>
       </c>
       <c r="I48" s="49" t="n">
-        <v>85</v>
-      </c>
-      <c r="J48" s="53" t="inlineStr">
+        <v>95</v>
+      </c>
+      <c r="J48" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -8197,14 +8226,14 @@
       </c>
       <c r="L48" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Santa Rita, fonte principal operando</t>
+          <t>Religador responsável pela proteção da barra da SE Ponte Alta (2381 UCs)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="49" t="inlineStr">
         <is>
-          <t>7900594026</t>
+          <t>7908686014</t>
         </is>
       </c>
       <c r="B49" s="49" t="inlineStr">
@@ -8214,12 +8243,12 @@
       </c>
       <c r="C49" s="50" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Pium</t>
         </is>
       </c>
       <c r="D49" s="50" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E49" s="50" t="inlineStr">
@@ -8229,12 +8258,12 @@
       </c>
       <c r="F49" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00113/2026</t>
+          <t>ETO-COEP 00086/2026</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
         <is>
-          <t>Comunicação/rádio (da descrição da SS)</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H49" s="49" t="inlineStr">
@@ -8243,26 +8272,26 @@
         </is>
       </c>
       <c r="I49" s="49" t="n">
-        <v>95</v>
-      </c>
-      <c r="J49" s="53" t="inlineStr">
+        <v>90</v>
+      </c>
+      <c r="J49" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K49" s="24" t="n">
-        <v>89455.53999999999</v>
+        <v>51360.82000000001</v>
       </c>
       <c r="L49" s="23" t="inlineStr">
         <is>
-          <t>Religador responsável pela proteção da barra da SE Ponte Alta (2381 UCs)</t>
+          <t>Fonte principal de Pium, RL de transferência operando</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="49" t="inlineStr">
         <is>
-          <t>7908686014</t>
+          <t>7923673004</t>
         </is>
       </c>
       <c r="B50" s="49" t="inlineStr">
@@ -8272,27 +8301,27 @@
       </c>
       <c r="C50" s="50" t="inlineStr">
         <is>
-          <t>Pium</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="D50" s="50" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="E50" s="50" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F50" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00086/2026</t>
+          <t>ETO-TELE 00967/2026</t>
         </is>
       </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Relé (da descrição da SS)</t>
         </is>
       </c>
       <c r="H50" s="49" t="inlineStr">
@@ -8301,26 +8330,26 @@
         </is>
       </c>
       <c r="I50" s="49" t="n">
-        <v>90</v>
-      </c>
-      <c r="J50" s="53" t="inlineStr">
+        <v>105</v>
+      </c>
+      <c r="J50" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K50" s="24" t="n">
-        <v>51360.82000000001</v>
+        <v>21470.95</v>
       </c>
       <c r="L50" s="23" t="inlineStr">
         <is>
-          <t>Fonte principal de Pium, RL de transferência operando</t>
+          <t>Transferência de cargas na RDU de Araguaína (2797 UCs)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="49" t="inlineStr">
         <is>
-          <t>7923673004</t>
+          <t>7925744087</t>
         </is>
       </c>
       <c r="B51" s="49" t="inlineStr">
@@ -8330,12 +8359,12 @@
       </c>
       <c r="C51" s="50" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Goianorte</t>
         </is>
       </c>
       <c r="D51" s="50" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Guarai</t>
         </is>
       </c>
       <c r="E51" s="50" t="inlineStr">
@@ -8345,12 +8374,12 @@
       </c>
       <c r="F51" s="50" t="inlineStr">
         <is>
-          <t>ETO-TELE 00967/2026</t>
+          <t>ETO-COEP 00059/2026</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr">
         <is>
-          <t>Relé (da descrição da SS)</t>
+          <t>Tanque/parte ativa + Comunicação/rádio + Bateria (da descrição da SS)</t>
         </is>
       </c>
       <c r="H51" s="49" t="inlineStr">
@@ -8359,26 +8388,26 @@
         </is>
       </c>
       <c r="I51" s="49" t="n">
-        <v>105</v>
-      </c>
-      <c r="J51" s="53" t="inlineStr">
+        <v>95</v>
+      </c>
+      <c r="J51" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K51" s="24" t="n">
-        <v>21470.95</v>
+        <v>51360.82000000001</v>
       </c>
       <c r="L51" s="23" t="inlineStr">
         <is>
-          <t>Transferência de cargas na RDU de Araguaína (2797 UCs)</t>
+          <t>Transferência de Goianorte, fonte principal operando</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="49" t="inlineStr">
         <is>
-          <t>7925744087</t>
+          <t>7925871077</t>
         </is>
       </c>
       <c r="B52" s="49" t="inlineStr">
@@ -8388,12 +8417,12 @@
       </c>
       <c r="C52" s="50" t="inlineStr">
         <is>
-          <t>Goianorte</t>
+          <t>Goiatins</t>
         </is>
       </c>
       <c r="D52" s="50" t="inlineStr">
         <is>
-          <t>Guarai</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="E52" s="50" t="inlineStr">
@@ -8403,12 +8432,12 @@
       </c>
       <c r="F52" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00059/2026</t>
+          <t>ETO-COEP 00048/2026</t>
         </is>
       </c>
       <c r="G52" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa + Comunicação/rádio + Bateria (da descrição da SS)</t>
+          <t>Tanque/parte ativa (da descrição da SS)</t>
         </is>
       </c>
       <c r="H52" s="49" t="inlineStr">
@@ -8417,9 +8446,9 @@
         </is>
       </c>
       <c r="I52" s="49" t="n">
-        <v>95</v>
-      </c>
-      <c r="J52" s="53" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="J52" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -8429,14 +8458,14 @@
       </c>
       <c r="L52" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Goianorte, fonte principal operando</t>
+          <t>Transferência de Goiatins e GAs (2492 UCs)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="49" t="inlineStr">
         <is>
-          <t>7925871077</t>
+          <t>7929376022</t>
         </is>
       </c>
       <c r="B53" s="49" t="inlineStr">
@@ -8446,7 +8475,7 @@
       </c>
       <c r="C53" s="50" t="inlineStr">
         <is>
-          <t>Goiatins</t>
+          <t>Babaculandia</t>
         </is>
       </c>
       <c r="D53" s="50" t="inlineStr">
@@ -8461,12 +8490,12 @@
       </c>
       <c r="F53" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00048/2026</t>
+          <t>ETO-COEP 00120/2026</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa (da descrição da SS)</t>
+          <t>Controle + Relé + Bateria (da descrição da SS)</t>
         </is>
       </c>
       <c r="H53" s="49" t="inlineStr">
@@ -8475,26 +8504,26 @@
         </is>
       </c>
       <c r="I53" s="49" t="n">
-        <v>80</v>
-      </c>
-      <c r="J53" s="53" t="inlineStr">
+        <v>95</v>
+      </c>
+      <c r="J53" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K53" s="24" t="n">
-        <v>51360.82000000001</v>
+        <v>51304.06</v>
       </c>
       <c r="L53" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Goiatins e GAs (2492 UCs)</t>
+          <t>Transferência de Babaçulândia, fonte principal operando</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="49" t="inlineStr">
         <is>
-          <t>7929376022</t>
+          <t>7931608059</t>
         </is>
       </c>
       <c r="B54" s="49" t="inlineStr">
@@ -8504,27 +8533,27 @@
       </c>
       <c r="C54" s="50" t="inlineStr">
         <is>
-          <t>Babaculandia</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="D54" s="50" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="E54" s="50" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F54" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00120/2026</t>
+          <t>ETO-COEP 00040/2026</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
         <is>
-          <t>Controle + Relé + Bateria (da descrição da SS)</t>
+          <t>Tanque e rádio</t>
         </is>
       </c>
       <c r="H54" s="49" t="inlineStr">
@@ -8533,84 +8562,84 @@
         </is>
       </c>
       <c r="I54" s="49" t="n">
-        <v>95</v>
-      </c>
-      <c r="J54" s="53" t="inlineStr">
+        <v>105</v>
+      </c>
+      <c r="J54" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K54" s="24" t="n">
-        <v>51304.06</v>
+        <v>47414.74000000001</v>
       </c>
       <c r="L54" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Babaçulândia, fonte principal operando</t>
+          <t>Transferência dos bairros Morada do Sol, Vale do Sol, Morada do Sol II, Nova Esperança, Sõa João, Araras I e II e Jardim Laila em Taquaralto (6033 UCs)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="49" t="inlineStr">
         <is>
-          <t>7931608059</t>
+          <t>5800371025</t>
         </is>
       </c>
       <c r="B55" s="49" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C55" s="50" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Arapoema</t>
         </is>
       </c>
       <c r="D55" s="50" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Colinas Do Tocantins</t>
         </is>
       </c>
       <c r="E55" s="50" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F55" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00040/2026</t>
+          <t>ETO-COEP 00187/2025</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
         <is>
-          <t>Tanque e rádio</t>
+          <t>Relé e fiquei em duvida sobre kit</t>
         </is>
       </c>
       <c r="H55" s="49" t="inlineStr">
         <is>
-          <t>Muito Alta</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I55" s="49" t="n">
-        <v>105</v>
-      </c>
-      <c r="J55" s="53" t="inlineStr">
+        <v>70</v>
+      </c>
+      <c r="J55" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K55" s="24" t="n">
-        <v>47414.74000000001</v>
+        <v>282925.12</v>
       </c>
       <c r="L55" s="23" t="inlineStr">
         <is>
-          <t>Transferência dos bairros Morada do Sol, Vale do Sol, Morada do Sol II, Nova Esperança, Sõa João, Araras I e II e Jardim Laila em Taquaralto (6033 UCs)</t>
+          <t>Aumento de reclamações no atendimento de Arapoema no período seco</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="49" t="inlineStr">
         <is>
-          <t>5800371025</t>
+          <t>5801866013</t>
         </is>
       </c>
       <c r="B56" s="49" t="inlineStr">
@@ -8620,27 +8649,27 @@
       </c>
       <c r="C56" s="50" t="inlineStr">
         <is>
-          <t>Arapoema</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="D56" s="50" t="inlineStr">
         <is>
-          <t>Colinas Do Tocantins</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E56" s="50" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F56" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00187/2025</t>
+          <t>ETO-COEP 00077/2026</t>
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr">
         <is>
-          <t>Relé e fiquei em duvida sobre kit</t>
+          <t>1 célula</t>
         </is>
       </c>
       <c r="H56" s="49" t="inlineStr">
@@ -8651,54 +8680,54 @@
       <c r="I56" s="49" t="n">
         <v>70</v>
       </c>
-      <c r="J56" s="53" t="inlineStr">
+      <c r="J56" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K56" s="24" t="n">
-        <v>282925.12</v>
+        <v>79018.75999999999</v>
       </c>
       <c r="L56" s="23" t="inlineStr">
         <is>
-          <t>Aumento de reclamações no atendimento de Arapoema no período seco</t>
+          <t>Atendimento da RDU Luzimangues Industrial por fonte alternativa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="49" t="inlineStr">
         <is>
-          <t>5801866013</t>
+          <t>7900573047</t>
         </is>
       </c>
       <c r="B57" s="49" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C57" s="50" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Figueiropolis</t>
         </is>
       </c>
       <c r="D57" s="50" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Alvorada</t>
         </is>
       </c>
       <c r="E57" s="50" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F57" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00077/2026</t>
+          <t>ETO-COEP 00080/2026</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
         <is>
-          <t>1 célula</t>
+          <t>Tanque e relé</t>
         </is>
       </c>
       <c r="H57" s="49" t="inlineStr">
@@ -8707,26 +8736,26 @@
         </is>
       </c>
       <c r="I57" s="49" t="n">
-        <v>70</v>
-      </c>
-      <c r="J57" s="53" t="inlineStr">
+        <v>65</v>
+      </c>
+      <c r="J57" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K57" s="24" t="n">
-        <v>79018.75999999999</v>
+        <v>66619.48</v>
       </c>
       <c r="L57" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da RDU Luzimangues Industrial por fonte alternativa</t>
+          <t>Transferência da Bunge, Saneatins e secadora</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="49" t="inlineStr">
         <is>
-          <t>7900573047</t>
+          <t>7903112004</t>
         </is>
       </c>
       <c r="B58" s="49" t="inlineStr">
@@ -8736,27 +8765,27 @@
       </c>
       <c r="C58" s="50" t="inlineStr">
         <is>
-          <t>Figueiropolis</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="D58" s="50" t="inlineStr">
         <is>
-          <t>Alvorada</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="E58" s="50" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F58" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00080/2026</t>
+          <t>ETO-COEP 00184/2025</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
-          <t>Tanque e relé</t>
+          <t>Tanque cooper</t>
         </is>
       </c>
       <c r="H58" s="49" t="inlineStr">
@@ -8765,26 +8794,26 @@
         </is>
       </c>
       <c r="I58" s="49" t="n">
-        <v>65</v>
-      </c>
-      <c r="J58" s="53" t="inlineStr">
+        <v>55</v>
+      </c>
+      <c r="J58" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K58" s="24" t="n">
-        <v>66619.48</v>
+        <v>51304.06</v>
       </c>
       <c r="L58" s="23" t="inlineStr">
         <is>
-          <t>Transferência da Bunge, Saneatins e secadora</t>
+          <t>Transferência de Babaçulândia, 4 RLs sendo 2 operando</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="49" t="inlineStr">
         <is>
-          <t>7903112004</t>
+          <t>7920024127</t>
         </is>
       </c>
       <c r="B59" s="49" t="inlineStr">
@@ -8794,12 +8823,12 @@
       </c>
       <c r="C59" s="50" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Palmeiras Do Tocantins</t>
         </is>
       </c>
       <c r="D59" s="50" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Tocantinopolis</t>
         </is>
       </c>
       <c r="E59" s="50" t="inlineStr">
@@ -8809,12 +8838,12 @@
       </c>
       <c r="F59" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00184/2025</t>
+          <t>ETO-COEP 00120/2025</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr">
         <is>
-          <t>Tanque cooper</t>
+          <t>Tanque, relé e chave</t>
         </is>
       </c>
       <c r="H59" s="49" t="inlineStr">
@@ -8825,24 +8854,24 @@
       <c r="I59" s="49" t="n">
         <v>55</v>
       </c>
-      <c r="J59" s="53" t="inlineStr">
+      <c r="J59" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K59" s="24" t="n">
-        <v>51304.06</v>
+        <v>90191.96999999999</v>
       </c>
       <c r="L59" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Babaçulândia, 4 RLs sendo 2 operando</t>
+          <t>Transferência de Palmeiras, 3 fontes operando</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="49" t="inlineStr">
         <is>
-          <t>7920024127</t>
+          <t>7925087021</t>
         </is>
       </c>
       <c r="B60" s="49" t="inlineStr">
@@ -8852,27 +8881,27 @@
       </c>
       <c r="C60" s="50" t="inlineStr">
         <is>
-          <t>Palmeiras Do Tocantins</t>
+          <t>Parana</t>
         </is>
       </c>
       <c r="D60" s="50" t="inlineStr">
         <is>
-          <t>Tocantinopolis</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="E60" s="50" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F60" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00120/2025</t>
+          <t>ETO-COEP 00222/2025</t>
         </is>
       </c>
       <c r="G60" s="23" t="inlineStr">
         <is>
-          <t>Tanque, relé e chave</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H60" s="49" t="inlineStr">
@@ -8881,26 +8910,26 @@
         </is>
       </c>
       <c r="I60" s="49" t="n">
-        <v>55</v>
-      </c>
-      <c r="J60" s="53" t="inlineStr">
+        <v>70</v>
+      </c>
+      <c r="J60" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K60" s="24" t="n">
-        <v>90191.96999999999</v>
+        <v>51360.82000000001</v>
       </c>
       <c r="L60" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Palmeiras, 3 fontes operando</t>
+          <t>Primeiro RL do 414R de Paranã, RL a jusante na LD também está bay-passado (630 UCs)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="49" t="inlineStr">
         <is>
-          <t>7925087021</t>
+          <t>7926089013</t>
         </is>
       </c>
       <c r="B61" s="49" t="inlineStr">
@@ -8910,22 +8939,22 @@
       </c>
       <c r="C61" s="50" t="inlineStr">
         <is>
-          <t>Parana</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="D61" s="50" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E61" s="50" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F61" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00222/2025</t>
+          <t>ETO-COEP 00078/2026</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -8941,7 +8970,7 @@
       <c r="I61" s="49" t="n">
         <v>70</v>
       </c>
-      <c r="J61" s="53" t="inlineStr">
+      <c r="J61" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -8951,14 +8980,14 @@
       </c>
       <c r="L61" s="23" t="inlineStr">
         <is>
-          <t>Primeiro RL do 414R de Paranã, RL a jusante na LD também está bay-passado (630 UCs)</t>
+          <t>Transferência da RDU de Chapada de Areia (937 UCs) para fonte alternativa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="49" t="inlineStr">
         <is>
-          <t>7926089013</t>
+          <t>7927646026</t>
         </is>
       </c>
       <c r="B62" s="49" t="inlineStr">
@@ -8968,12 +8997,12 @@
       </c>
       <c r="C62" s="50" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="D62" s="50" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="E62" s="50" t="inlineStr">
@@ -8983,7 +9012,7 @@
       </c>
       <c r="F62" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00078/2026</t>
+          <t>ETO-COEP 00029/2026</t>
         </is>
       </c>
       <c r="G62" s="23" t="inlineStr">
@@ -8997,9 +9026,9 @@
         </is>
       </c>
       <c r="I62" s="49" t="n">
-        <v>70</v>
-      </c>
-      <c r="J62" s="53" t="inlineStr">
+        <v>55</v>
+      </c>
+      <c r="J62" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9009,14 +9038,14 @@
       </c>
       <c r="L62" s="23" t="inlineStr">
         <is>
-          <t>Transferência da RDU de Chapada de Areia (937 UCs) para fonte alternativa</t>
+          <t>Opção de isolação de São Félix e Mateiros para alimentação por gerador</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="49" t="inlineStr">
         <is>
-          <t>7927646026</t>
+          <t>7953610256</t>
         </is>
       </c>
       <c r="B63" s="49" t="inlineStr">
@@ -9026,14 +9055,14 @@
       </c>
       <c r="C63" s="50" t="inlineStr">
         <is>
+          <t>Mateiros</t>
+        </is>
+      </c>
+      <c r="D63" s="50" t="inlineStr">
+        <is>
           <t>Ponte Alta Tocantins</t>
         </is>
       </c>
-      <c r="D63" s="50" t="inlineStr">
-        <is>
-          <t>Ponte Alta Tocantins</t>
-        </is>
-      </c>
       <c r="E63" s="50" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -9041,12 +9070,12 @@
       </c>
       <c r="F63" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00029/2026</t>
+          <t>ETO-COEP 00050/2026</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Tanque/parte ativa + Relé + Curto interno (da descrição da SS)</t>
         </is>
       </c>
       <c r="H63" s="49" t="inlineStr">
@@ -9055,9 +9084,9 @@
         </is>
       </c>
       <c r="I63" s="49" t="n">
-        <v>55</v>
-      </c>
-      <c r="J63" s="53" t="inlineStr">
+        <v>65</v>
+      </c>
+      <c r="J63" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9067,72 +9096,72 @@
       </c>
       <c r="L63" s="23" t="inlineStr">
         <is>
-          <t>Opção de isolação de São Félix e Mateiros para alimentação por gerador</t>
+          <t>Atenidmento da COELBA (Alto potencial de compensação)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="49" t="inlineStr">
         <is>
-          <t>7953610256</t>
+          <t>5800090147</t>
         </is>
       </c>
       <c r="B64" s="49" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C64" s="50" t="inlineStr">
         <is>
-          <t>Mateiros</t>
+          <t>Taipas Do Tocantins</t>
         </is>
       </c>
       <c r="D64" s="50" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E64" s="50" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F64" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00050/2026</t>
+          <t>ETO-COEP 00117/2026</t>
         </is>
       </c>
       <c r="G64" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa + Relé + Curto interno (da descrição da SS)</t>
+          <t>Célula + Comunicação/rádio (da descrição da SS)</t>
         </is>
       </c>
       <c r="H64" s="49" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I64" s="49" t="n">
-        <v>65</v>
-      </c>
-      <c r="J64" s="53" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="J64" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K64" s="24" t="n">
-        <v>51360.82000000001</v>
+        <v>138038.91</v>
       </c>
       <c r="L64" s="23" t="inlineStr">
         <is>
-          <t>Atenidmento da COELBA (Alto potencial de compensação)</t>
+          <t>Atendimento de Taipas</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="49" t="inlineStr">
         <is>
-          <t>5800090147</t>
+          <t>5800961074</t>
         </is>
       </c>
       <c r="B65" s="49" t="inlineStr">
@@ -9142,7 +9171,7 @@
       </c>
       <c r="C65" s="50" t="inlineStr">
         <is>
-          <t>Taipas Do Tocantins</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="D65" s="50" t="inlineStr">
@@ -9157,12 +9186,12 @@
       </c>
       <c r="F65" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00117/2026</t>
+          <t>ETO-COEP 00221/2025</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
         <is>
-          <t>Célula + Comunicação/rádio (da descrição da SS)</t>
+          <t>3 células e conectores</t>
         </is>
       </c>
       <c r="H65" s="49" t="inlineStr">
@@ -9171,26 +9200,26 @@
         </is>
       </c>
       <c r="I65" s="49" t="n">
-        <v>60</v>
-      </c>
-      <c r="J65" s="53" t="inlineStr">
+        <v>40</v>
+      </c>
+      <c r="J65" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K65" s="24" t="n">
-        <v>138038.91</v>
+        <v>253479.73</v>
       </c>
       <c r="L65" s="23" t="inlineStr">
         <is>
-          <t>Atendimento de Taipas</t>
+          <t>Atendimento da COELBA e GA Alessandro Maurício (1600 kVA)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="49" t="inlineStr">
         <is>
-          <t>5800961074</t>
+          <t>5850308009</t>
         </is>
       </c>
       <c r="B66" s="49" t="inlineStr">
@@ -9200,27 +9229,27 @@
       </c>
       <c r="C66" s="50" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Guarai</t>
         </is>
       </c>
       <c r="D66" s="50" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Guarai</t>
         </is>
       </c>
       <c r="E66" s="50" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F66" s="50" t="inlineStr">
         <is>
-          <t>ETO-COEP 00221/2025</t>
+          <t>ETO-TELE 00958/2026</t>
         </is>
       </c>
       <c r="G66" s="23" t="inlineStr">
         <is>
-          <t>3 células e conectores</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="H66" s="49" t="inlineStr">
@@ -9229,19 +9258,19 @@
         </is>
       </c>
       <c r="I66" s="49" t="n">
-        <v>40</v>
-      </c>
-      <c r="J66" s="53" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="J66" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K66" s="24" t="n">
-        <v>253479.73</v>
+        <v>29445.39</v>
       </c>
       <c r="L66" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da COELBA e GA Alessandro Maurício (1600 kVA)</t>
+          <t>Atendimento de parte da RDU de Guaraí e ramal da PRF/Repetidora | Definição do gestor 08/07: NÃO concluído — oficial ETO 36 mostra 0 dias aguardando DCMD</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9318,7 @@
       <c r="I67" s="49" t="n">
         <v>35</v>
       </c>
-      <c r="J67" s="53" t="inlineStr">
+      <c r="J67" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9347,7 +9376,7 @@
       <c r="I68" s="49" t="n">
         <v>45</v>
       </c>
-      <c r="J68" s="53" t="inlineStr">
+      <c r="J68" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9405,7 +9434,7 @@
       <c r="I69" s="49" t="n">
         <v>35</v>
       </c>
-      <c r="J69" s="53" t="inlineStr">
+      <c r="J69" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9463,7 +9492,7 @@
       <c r="I70" s="49" t="n">
         <v>35</v>
       </c>
-      <c r="J70" s="53" t="inlineStr">
+      <c r="J70" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9521,7 +9550,7 @@
       <c r="I71" s="49" t="n">
         <v>35</v>
       </c>
-      <c r="J71" s="53" t="inlineStr">
+      <c r="J71" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9579,7 +9608,7 @@
       <c r="I72" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="J72" s="53" t="inlineStr">
+      <c r="J72" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9637,7 +9666,7 @@
       <c r="I73" s="49" t="n">
         <v>35</v>
       </c>
-      <c r="J73" s="53" t="inlineStr">
+      <c r="J73" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9695,7 +9724,7 @@
       <c r="I74" s="49" t="n">
         <v>40</v>
       </c>
-      <c r="J74" s="53" t="inlineStr">
+      <c r="J74" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9753,7 +9782,7 @@
       <c r="I75" s="49" t="n">
         <v>40</v>
       </c>
-      <c r="J75" s="53" t="inlineStr">
+      <c r="J75" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9811,7 +9840,7 @@
       <c r="I76" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="J76" s="53" t="inlineStr">
+      <c r="J76" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9869,7 +9898,7 @@
       <c r="I77" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="J77" s="53" t="inlineStr">
+      <c r="J77" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9927,7 +9956,7 @@
       <c r="I78" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="J78" s="53" t="inlineStr">
+      <c r="J78" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -9985,7 +10014,7 @@
       <c r="I79" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="J79" s="53" t="inlineStr">
+      <c r="J79" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10043,7 +10072,7 @@
       <c r="I80" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="53" t="inlineStr">
+      <c r="J80" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10101,7 +10130,7 @@
       <c r="I81" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="J81" s="53" t="inlineStr">
+      <c r="J81" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10159,7 +10188,7 @@
       <c r="I82" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="J82" s="53" t="inlineStr">
+      <c r="J82" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10217,7 +10246,7 @@
       <c r="I83" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="J83" s="53" t="inlineStr">
+      <c r="J83" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10275,7 +10304,7 @@
       <c r="I84" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="J84" s="53" t="inlineStr">
+      <c r="J84" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10333,7 +10362,7 @@
       <c r="I85" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="J85" s="53" t="inlineStr">
+      <c r="J85" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10391,7 +10420,7 @@
       <c r="I86" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="J86" s="53" t="inlineStr">
+      <c r="J86" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10449,7 +10478,7 @@
       <c r="I87" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="J87" s="53" t="inlineStr">
+      <c r="J87" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10507,7 +10536,7 @@
       <c r="I88" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="J88" s="53" t="inlineStr">
+      <c r="J88" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10565,7 +10594,7 @@
       <c r="I89" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="J89" s="53" t="inlineStr">
+      <c r="J89" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10623,7 +10652,7 @@
       <c r="I90" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="53" t="inlineStr">
+      <c r="J90" s="54" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
@@ -10681,7 +10710,7 @@
       <c r="I91" s="49" t="n">
         <v>80</v>
       </c>
-      <c r="J91" s="54" t="inlineStr">
+      <c r="J91" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -10739,7 +10768,7 @@
       <c r="I92" s="49" t="n">
         <v>95</v>
       </c>
-      <c r="J92" s="54" t="inlineStr">
+      <c r="J92" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -10799,7 +10828,7 @@
       <c r="I93" s="49" t="n">
         <v>95</v>
       </c>
-      <c r="J93" s="54" t="inlineStr">
+      <c r="J93" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -10857,7 +10886,7 @@
       <c r="I94" s="49" t="n">
         <v>90</v>
       </c>
-      <c r="J94" s="54" t="inlineStr">
+      <c r="J94" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -10917,7 +10946,7 @@
       <c r="I95" s="49" t="n">
         <v>105</v>
       </c>
-      <c r="J95" s="54" t="inlineStr">
+      <c r="J95" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -10975,7 +11004,7 @@
       <c r="I96" s="49" t="n">
         <v>95</v>
       </c>
-      <c r="J96" s="54" t="inlineStr">
+      <c r="J96" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11033,7 +11062,7 @@
       <c r="I97" s="49" t="n">
         <v>95</v>
       </c>
-      <c r="J97" s="54" t="inlineStr">
+      <c r="J97" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11091,7 +11120,7 @@
       <c r="I98" s="49" t="n">
         <v>100</v>
       </c>
-      <c r="J98" s="54" t="inlineStr">
+      <c r="J98" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11151,7 +11180,7 @@
       <c r="I99" s="49" t="n">
         <v>80</v>
       </c>
-      <c r="J99" s="54" t="inlineStr">
+      <c r="J99" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11211,7 +11240,7 @@
       <c r="I100" s="49" t="n">
         <v>70</v>
       </c>
-      <c r="J100" s="54" t="inlineStr">
+      <c r="J100" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11271,7 +11300,7 @@
       <c r="I101" s="49" t="n">
         <v>70</v>
       </c>
-      <c r="J101" s="54" t="inlineStr">
+      <c r="J101" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11331,7 +11360,7 @@
       <c r="I102" s="49" t="n">
         <v>55</v>
       </c>
-      <c r="J102" s="54" t="inlineStr">
+      <c r="J102" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11389,7 +11418,7 @@
       <c r="I103" s="49" t="n">
         <v>50</v>
       </c>
-      <c r="J103" s="54" t="inlineStr">
+      <c r="J103" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11449,7 +11478,7 @@
       <c r="I104" s="49" t="n">
         <v>50</v>
       </c>
-      <c r="J104" s="54" t="inlineStr">
+      <c r="J104" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11509,7 +11538,7 @@
       <c r="I105" s="49" t="n">
         <v>50</v>
       </c>
-      <c r="J105" s="54" t="inlineStr">
+      <c r="J105" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11567,7 +11596,7 @@
       <c r="I106" s="49" t="n">
         <v>50</v>
       </c>
-      <c r="J106" s="54" t="inlineStr">
+      <c r="J106" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11627,7 +11656,7 @@
       <c r="I107" s="49" t="n">
         <v>60</v>
       </c>
-      <c r="J107" s="54" t="inlineStr">
+      <c r="J107" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11685,7 +11714,7 @@
       <c r="I108" s="49" t="n">
         <v>50</v>
       </c>
-      <c r="J108" s="54" t="inlineStr">
+      <c r="J108" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11745,7 +11774,7 @@
       <c r="I109" s="49" t="n">
         <v>60</v>
       </c>
-      <c r="J109" s="54" t="inlineStr">
+      <c r="J109" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11805,7 +11834,7 @@
       <c r="I110" s="49" t="n">
         <v>60</v>
       </c>
-      <c r="J110" s="54" t="inlineStr">
+      <c r="J110" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11865,7 +11894,7 @@
       <c r="I111" s="49" t="n">
         <v>60</v>
       </c>
-      <c r="J111" s="54" t="inlineStr">
+      <c r="J111" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11925,7 +11954,7 @@
       <c r="I112" s="49" t="n">
         <v>40</v>
       </c>
-      <c r="J112" s="54" t="inlineStr">
+      <c r="J112" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -11985,7 +12014,7 @@
       <c r="I113" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J113" s="54" t="inlineStr">
+      <c r="J113" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12045,7 +12074,7 @@
       <c r="I114" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="J114" s="54" t="inlineStr">
+      <c r="J114" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12105,7 +12134,7 @@
       <c r="I115" s="49" t="n">
         <v>25</v>
       </c>
-      <c r="J115" s="54" t="inlineStr">
+      <c r="J115" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12165,7 +12194,7 @@
       <c r="I116" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="J116" s="54" t="inlineStr">
+      <c r="J116" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12223,7 +12252,7 @@
       <c r="I117" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="J117" s="54" t="inlineStr">
+      <c r="J117" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12283,7 +12312,7 @@
       <c r="I118" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J118" s="54" t="inlineStr">
+      <c r="J118" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12343,7 +12372,7 @@
       <c r="I119" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J119" s="54" t="inlineStr">
+      <c r="J119" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12403,7 +12432,7 @@
       <c r="I120" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J120" s="54" t="inlineStr">
+      <c r="J120" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12463,7 +12492,7 @@
       <c r="I121" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J121" s="54" t="inlineStr">
+      <c r="J121" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12523,7 +12552,7 @@
       <c r="I122" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J122" s="54" t="inlineStr">
+      <c r="J122" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12583,7 +12612,7 @@
       <c r="I123" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J123" s="54" t="inlineStr">
+      <c r="J123" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12643,7 +12672,7 @@
       <c r="I124" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J124" s="54" t="inlineStr">
+      <c r="J124" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12703,7 +12732,7 @@
       <c r="I125" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J125" s="54" t="inlineStr">
+      <c r="J125" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12763,7 +12792,7 @@
       <c r="I126" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J126" s="54" t="inlineStr">
+      <c r="J126" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12823,7 +12852,7 @@
       <c r="I127" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J127" s="54" t="inlineStr">
+      <c r="J127" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12883,7 +12912,7 @@
       <c r="I128" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J128" s="54" t="inlineStr">
+      <c r="J128" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -12943,7 +12972,7 @@
       <c r="I129" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J129" s="54" t="inlineStr">
+      <c r="J129" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
@@ -13003,7 +13032,7 @@
       <c r="I130" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J130" s="54" t="inlineStr">
+      <c r="J130" s="55" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>

--- a/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
+++ b/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
@@ -170,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -315,6 +315,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2619,7 +2628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2841,2992 +2850,3008 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="56" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>Definições do gestor (08/07): 5850308009 (Guaraí) = NÃO concluído — segue no posto do COEP/fila DCMD; 7942572059 (Taquaralto) = melhoria de aterramento SEM CUSTO, considerado EM EXECUÇÃO via ETO-RD-PA 00427/2026 (SS ainda aberta).</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Lista oficial DCMD (ETO 36) — 65 equipamentos</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Ativo</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>SS SGM</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Criticidade (oficial)</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Dias aguardando DCMD</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Dias pendente (SS)</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Responsável</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>Município</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>Está no orçamento?</t>
         </is>
       </c>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>Situação no mapeamento</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="57" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="62" t="inlineStr">
         <is>
           <t>7923927122</t>
         </is>
       </c>
-      <c r="B23" s="57" t="inlineStr">
+      <c r="B24" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C23" s="58" t="inlineStr">
+      <c r="C24" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00079/2025</t>
         </is>
       </c>
-      <c r="D23" s="57" t="inlineStr">
+      <c r="D24" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E23" s="57" t="n">
+      <c r="E24" s="62" t="n">
         <v>434</v>
       </c>
-      <c r="G23" s="57" t="inlineStr">
+      <c r="G24" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H23" s="58" t="inlineStr">
+      <c r="H24" s="63" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I23" s="58" t="inlineStr">
+      <c r="I24" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J23" s="23" t="inlineStr">
+      <c r="J24" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="57" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="62" t="inlineStr">
         <is>
           <t>7900532053</t>
         </is>
       </c>
-      <c r="B24" s="57" t="inlineStr">
+      <c r="B25" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C24" s="58" t="inlineStr">
+      <c r="C25" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00102/2025</t>
         </is>
       </c>
-      <c r="D24" s="57" t="inlineStr">
+      <c r="D25" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E24" s="57" t="n">
+      <c r="E25" s="62" t="n">
         <v>407</v>
       </c>
-      <c r="G24" s="57" t="inlineStr">
+      <c r="G25" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H24" s="58" t="inlineStr">
+      <c r="H25" s="63" t="inlineStr">
         <is>
           <t>Piraque</t>
         </is>
       </c>
-      <c r="I24" s="58" t="inlineStr">
+      <c r="I25" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J24" s="23" t="inlineStr">
+      <c r="J25" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="57" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="62" t="inlineStr">
         <is>
           <t>7920024127</t>
         </is>
       </c>
-      <c r="B25" s="57" t="inlineStr">
+      <c r="B26" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C25" s="58" t="inlineStr">
+      <c r="C26" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2025</t>
         </is>
       </c>
-      <c r="D25" s="57" t="inlineStr">
+      <c r="D26" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E25" s="57" t="n">
+      <c r="E26" s="62" t="n">
         <v>371</v>
       </c>
-      <c r="G25" s="57" t="inlineStr">
+      <c r="G26" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H25" s="58" t="inlineStr">
+      <c r="H26" s="63" t="inlineStr">
         <is>
           <t>Palmeiras Do Tocantins</t>
         </is>
       </c>
-      <c r="I25" s="58" t="inlineStr">
+      <c r="I26" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J25" s="23" t="inlineStr">
+      <c r="J26" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="57" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="62" t="inlineStr">
         <is>
           <t>5858783119</t>
         </is>
       </c>
-      <c r="B26" s="57" t="inlineStr">
+      <c r="B27" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C26" s="58" t="inlineStr">
+      <c r="C27" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00123/2025</t>
         </is>
       </c>
-      <c r="D26" s="57" t="inlineStr">
+      <c r="D27" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E26" s="57" t="n">
+      <c r="E27" s="62" t="n">
         <v>369</v>
       </c>
-      <c r="G26" s="57" t="inlineStr">
+      <c r="G27" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H26" s="58" t="inlineStr">
+      <c r="H27" s="63" t="inlineStr">
         <is>
           <t>Sao Bento Do Tocantins</t>
         </is>
       </c>
-      <c r="I26" s="58" t="inlineStr">
+      <c r="I27" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J26" s="23" t="inlineStr">
+      <c r="J27" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="57" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="62" t="inlineStr">
         <is>
           <t>7927446001</t>
         </is>
       </c>
-      <c r="B27" s="57" t="inlineStr">
+      <c r="B28" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C27" s="58" t="inlineStr">
+      <c r="C28" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00143/2025</t>
         </is>
       </c>
-      <c r="D27" s="57" t="inlineStr">
+      <c r="D28" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E27" s="57" t="n">
+      <c r="E28" s="62" t="n">
         <v>364</v>
       </c>
-      <c r="G27" s="57" t="inlineStr">
+      <c r="G28" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H27" s="58" t="inlineStr">
+      <c r="H28" s="63" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I27" s="58" t="inlineStr">
+      <c r="I28" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J27" s="23" t="inlineStr">
+      <c r="J28" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="57" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="62" t="inlineStr">
         <is>
           <t>7957126085</t>
         </is>
       </c>
-      <c r="B28" s="57" t="inlineStr">
+      <c r="B29" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C28" s="58" t="inlineStr">
+      <c r="C29" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00156/2025</t>
         </is>
       </c>
-      <c r="D28" s="57" t="inlineStr">
+      <c r="D29" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E28" s="57" t="n">
+      <c r="E29" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="G28" s="57" t="inlineStr">
+      <c r="G29" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H28" s="58" t="inlineStr">
+      <c r="H29" s="63" t="inlineStr">
         <is>
           <t>Monte Santo Do Tocantins</t>
         </is>
       </c>
-      <c r="I28" s="58" t="inlineStr">
+      <c r="I29" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J28" s="23" t="inlineStr">
+      <c r="J29" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="57" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="62" t="inlineStr">
         <is>
           <t>7942485096</t>
         </is>
       </c>
-      <c r="B29" s="57" t="inlineStr">
+      <c r="B30" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C29" s="58" t="inlineStr">
+      <c r="C30" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00158/2025</t>
         </is>
       </c>
-      <c r="D29" s="57" t="inlineStr">
+      <c r="D30" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E29" s="57" t="n">
+      <c r="E30" s="62" t="n">
         <v>349</v>
       </c>
-      <c r="G29" s="57" t="inlineStr">
+      <c r="G30" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H29" s="58" t="inlineStr">
+      <c r="H30" s="63" t="inlineStr">
         <is>
           <t>Pindorama Do Tocantins</t>
         </is>
       </c>
-      <c r="I29" s="58" t="inlineStr">
+      <c r="I30" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J29" s="23" t="inlineStr">
+      <c r="J30" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="57" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="62" t="inlineStr">
         <is>
           <t>5854566043</t>
         </is>
       </c>
-      <c r="B30" s="57" t="inlineStr">
+      <c r="B31" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C30" s="58" t="inlineStr">
+      <c r="C31" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00160/2025</t>
         </is>
       </c>
-      <c r="D30" s="57" t="inlineStr">
+      <c r="D31" s="62" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E30" s="57" t="n">
+      <c r="E31" s="62" t="n">
         <v>347</v>
       </c>
-      <c r="G30" s="57" t="inlineStr">
+      <c r="G31" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H30" s="58" t="inlineStr">
+      <c r="H31" s="63" t="inlineStr">
         <is>
           <t>Silvanopolis</t>
         </is>
       </c>
-      <c r="I30" s="58" t="inlineStr">
+      <c r="I31" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J30" s="23" t="inlineStr">
+      <c r="J31" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="57" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="62" t="inlineStr">
         <is>
           <t>5844630060</t>
         </is>
       </c>
-      <c r="B31" s="57" t="inlineStr">
+      <c r="B32" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C31" s="58" t="inlineStr">
+      <c r="C32" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00167/2025</t>
         </is>
       </c>
-      <c r="D31" s="57" t="inlineStr">
+      <c r="D32" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E31" s="57" t="n">
+      <c r="E32" s="62" t="n">
         <v>333</v>
       </c>
-      <c r="G31" s="57" t="inlineStr">
+      <c r="G32" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H31" s="58" t="inlineStr">
+      <c r="H32" s="63" t="inlineStr">
         <is>
           <t>Nova Olinda</t>
         </is>
       </c>
-      <c r="I31" s="58" t="inlineStr">
+      <c r="I32" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J31" s="23" t="inlineStr">
+      <c r="J32" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="57" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="62" t="inlineStr">
         <is>
           <t>7900535058</t>
         </is>
       </c>
-      <c r="B32" s="57" t="inlineStr">
+      <c r="B33" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C32" s="58" t="inlineStr">
+      <c r="C33" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00173/2025</t>
         </is>
       </c>
-      <c r="D32" s="57" t="inlineStr">
+      <c r="D33" s="62" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E32" s="57" t="n">
+      <c r="E33" s="62" t="n">
         <v>317</v>
       </c>
-      <c r="G32" s="57" t="inlineStr">
+      <c r="G33" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H32" s="58" t="inlineStr">
+      <c r="H33" s="63" t="inlineStr">
         <is>
           <t>Santa Fe Do Araguaia</t>
         </is>
       </c>
-      <c r="I32" s="58" t="inlineStr">
+      <c r="I33" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J32" s="23" t="inlineStr">
+      <c r="J33" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="57" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="62" t="inlineStr">
         <is>
           <t>7903112004</t>
         </is>
       </c>
-      <c r="B33" s="57" t="inlineStr">
+      <c r="B34" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C33" s="58" t="inlineStr">
+      <c r="C34" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00184/2025</t>
         </is>
       </c>
-      <c r="D33" s="57" t="inlineStr">
+      <c r="D34" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E33" s="57" t="n">
+      <c r="E34" s="62" t="n">
         <v>307</v>
       </c>
-      <c r="G33" s="57" t="inlineStr">
+      <c r="G34" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H33" s="58" t="inlineStr">
+      <c r="H34" s="63" t="inlineStr">
         <is>
           <t>Araguaina</t>
         </is>
       </c>
-      <c r="I33" s="58" t="inlineStr">
+      <c r="I34" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J33" s="23" t="inlineStr">
+      <c r="J34" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="57" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="62" t="inlineStr">
         <is>
           <t>5800371025</t>
         </is>
       </c>
-      <c r="B34" s="57" t="inlineStr">
+      <c r="B35" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C34" s="58" t="inlineStr">
+      <c r="C35" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00187/2025</t>
         </is>
       </c>
-      <c r="D34" s="57" t="inlineStr">
+      <c r="D35" s="62" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E34" s="57" t="n">
+      <c r="E35" s="62" t="n">
         <v>305</v>
       </c>
-      <c r="G34" s="57" t="inlineStr">
+      <c r="G35" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H34" s="58" t="inlineStr">
+      <c r="H35" s="63" t="inlineStr">
         <is>
           <t>Arapoema</t>
         </is>
       </c>
-      <c r="I34" s="58" t="inlineStr">
+      <c r="I35" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J34" s="23" t="inlineStr">
+      <c r="J35" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="57" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="62" t="inlineStr">
         <is>
           <t>5855411017</t>
         </is>
       </c>
-      <c r="B35" s="57" t="inlineStr">
+      <c r="B36" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C35" s="58" t="inlineStr">
+      <c r="C36" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00199/2025</t>
         </is>
       </c>
-      <c r="D35" s="57" t="inlineStr">
+      <c r="D36" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E35" s="57" t="n">
+      <c r="E36" s="62" t="n">
         <v>280</v>
       </c>
-      <c r="G35" s="57" t="inlineStr">
+      <c r="G36" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H35" s="58" t="inlineStr">
+      <c r="H36" s="63" t="inlineStr">
         <is>
           <t>Barrolandia</t>
         </is>
       </c>
-      <c r="I35" s="58" t="inlineStr">
+      <c r="I36" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J35" s="23" t="inlineStr">
+      <c r="J36" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="57" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="62" t="inlineStr">
         <is>
           <t>5853360007</t>
         </is>
       </c>
-      <c r="B36" s="57" t="inlineStr">
+      <c r="B37" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C36" s="58" t="inlineStr">
+      <c r="C37" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-PS 00323/2025</t>
         </is>
       </c>
-      <c r="D36" s="57" t="inlineStr">
+      <c r="D37" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E36" s="57" t="n">
+      <c r="E37" s="62" t="n">
         <v>264</v>
       </c>
-      <c r="G36" s="57" t="inlineStr">
+      <c r="G37" s="62" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H36" s="58" t="inlineStr">
+      <c r="H37" s="63" t="inlineStr">
         <is>
           <t>Miracema Do Tocantins</t>
         </is>
       </c>
-      <c r="I36" s="59" t="inlineStr">
+      <c r="I37" s="64" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
       </c>
-      <c r="J36" s="23" t="inlineStr">
+      <c r="J37" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="57" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="62" t="inlineStr">
         <is>
           <t>5800961074</t>
         </is>
       </c>
-      <c r="B37" s="57" t="inlineStr">
+      <c r="B38" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C37" s="58" t="inlineStr">
+      <c r="C38" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00221/2025</t>
         </is>
       </c>
-      <c r="D37" s="57" t="inlineStr">
+      <c r="D38" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E37" s="57" t="n">
+      <c r="E38" s="62" t="n">
         <v>214</v>
       </c>
-      <c r="G37" s="57" t="inlineStr">
+      <c r="G38" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H37" s="58" t="inlineStr">
+      <c r="H38" s="63" t="inlineStr">
         <is>
           <t>Dianopolis</t>
         </is>
       </c>
-      <c r="I37" s="58" t="inlineStr">
+      <c r="I38" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J37" s="23" t="inlineStr">
+      <c r="J38" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="57" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="62" t="inlineStr">
         <is>
           <t>7925087021</t>
         </is>
       </c>
-      <c r="B38" s="57" t="inlineStr">
+      <c r="B39" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C38" s="58" t="inlineStr">
+      <c r="C39" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00222/2025</t>
         </is>
       </c>
-      <c r="D38" s="57" t="inlineStr">
+      <c r="D39" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E38" s="57" t="n">
+      <c r="E39" s="62" t="n">
         <v>211</v>
       </c>
-      <c r="G38" s="57" t="inlineStr">
+      <c r="G39" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H38" s="58" t="inlineStr">
+      <c r="H39" s="63" t="inlineStr">
         <is>
           <t>Parana</t>
         </is>
       </c>
-      <c r="I38" s="58" t="inlineStr">
+      <c r="I39" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J38" s="23" t="inlineStr">
+      <c r="J39" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="57" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="62" t="inlineStr">
         <is>
           <t>5862236091</t>
         </is>
       </c>
-      <c r="B39" s="57" t="inlineStr">
+      <c r="B40" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C39" s="58" t="inlineStr">
+      <c r="C40" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00223/2025</t>
         </is>
       </c>
-      <c r="D39" s="57" t="inlineStr">
+      <c r="D40" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E39" s="57" t="n">
+      <c r="E40" s="62" t="n">
         <v>211</v>
       </c>
-      <c r="G39" s="57" t="inlineStr">
+      <c r="G40" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H39" s="58" t="inlineStr">
+      <c r="H40" s="63" t="inlineStr">
         <is>
           <t>Almas</t>
         </is>
       </c>
-      <c r="I39" s="58" t="inlineStr">
+      <c r="I40" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J39" s="23" t="inlineStr">
+      <c r="J40" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="57" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="62" t="inlineStr">
         <is>
           <t>7933585074</t>
         </is>
       </c>
-      <c r="B40" s="57" t="inlineStr">
+      <c r="B41" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C40" s="58" t="inlineStr">
+      <c r="C41" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00024/2026</t>
         </is>
       </c>
-      <c r="D40" s="57" t="inlineStr">
+      <c r="D41" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E40" s="57" t="n">
+      <c r="E41" s="62" t="n">
         <v>161</v>
       </c>
-      <c r="G40" s="57" t="inlineStr">
+      <c r="G41" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H40" s="58" t="inlineStr">
+      <c r="H41" s="63" t="inlineStr">
         <is>
           <t>Dianopolis</t>
         </is>
       </c>
-      <c r="I40" s="58" t="inlineStr">
+      <c r="I41" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J40" s="23" t="inlineStr">
+      <c r="J41" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="57" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="62" t="inlineStr">
         <is>
           <t>7927646026</t>
         </is>
       </c>
-      <c r="B41" s="57" t="inlineStr">
+      <c r="B42" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C41" s="58" t="inlineStr">
+      <c r="C42" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00029/2026</t>
         </is>
       </c>
-      <c r="D41" s="57" t="inlineStr">
+      <c r="D42" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E41" s="57" t="n">
+      <c r="E42" s="62" t="n">
         <v>154</v>
       </c>
-      <c r="G41" s="57" t="inlineStr">
+      <c r="G42" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H41" s="58" t="inlineStr">
+      <c r="H42" s="63" t="inlineStr">
         <is>
           <t>Ponte Alta Tocantins</t>
         </is>
       </c>
-      <c r="I41" s="58" t="inlineStr">
+      <c r="I42" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J41" s="23" t="inlineStr">
+      <c r="J42" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="57" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="62" t="inlineStr">
         <is>
           <t>7931608059</t>
         </is>
       </c>
-      <c r="B42" s="57" t="inlineStr">
+      <c r="B43" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C42" s="58" t="inlineStr">
+      <c r="C43" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00040/2026</t>
         </is>
       </c>
-      <c r="D42" s="57" t="inlineStr">
+      <c r="D43" s="62" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E42" s="57" t="n">
+      <c r="E43" s="62" t="n">
         <v>133</v>
       </c>
-      <c r="G42" s="57" t="inlineStr">
+      <c r="G43" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H42" s="58" t="inlineStr">
+      <c r="H43" s="63" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I42" s="58" t="inlineStr">
+      <c r="I43" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J42" s="23" t="inlineStr">
+      <c r="J43" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="57" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="62" t="inlineStr">
         <is>
           <t>7908249152</t>
         </is>
       </c>
-      <c r="B43" s="57" t="inlineStr">
+      <c r="B44" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C43" s="58" t="inlineStr">
+      <c r="C44" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00038/2026</t>
         </is>
       </c>
-      <c r="D43" s="57" t="inlineStr">
+      <c r="D44" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E43" s="57" t="n">
+      <c r="E44" s="62" t="n">
         <v>133</v>
       </c>
-      <c r="G43" s="57" t="inlineStr">
+      <c r="G44" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H43" s="58" t="inlineStr">
+      <c r="H44" s="63" t="inlineStr">
         <is>
           <t>Santa Rosa Do Tocantins</t>
         </is>
       </c>
-      <c r="I43" s="58" t="inlineStr">
+      <c r="I44" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J43" s="23" t="inlineStr">
+      <c r="J44" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="57" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="62" t="inlineStr">
         <is>
           <t>7927396052</t>
         </is>
       </c>
-      <c r="B44" s="57" t="inlineStr">
+      <c r="B45" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C44" s="58" t="inlineStr">
+      <c r="C45" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00045/2026</t>
         </is>
       </c>
-      <c r="D44" s="57" t="inlineStr">
+      <c r="D45" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E44" s="57" t="n">
+      <c r="E45" s="62" t="n">
         <v>127</v>
       </c>
-      <c r="G44" s="57" t="inlineStr">
+      <c r="G45" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H44" s="58" t="inlineStr">
+      <c r="H45" s="63" t="inlineStr">
         <is>
           <t>Formoso Do Araguaia</t>
         </is>
       </c>
-      <c r="I44" s="58" t="inlineStr">
+      <c r="I45" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J44" s="23" t="inlineStr">
+      <c r="J45" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="57" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="62" t="inlineStr">
         <is>
           <t>7925871077</t>
         </is>
       </c>
-      <c r="B45" s="57" t="inlineStr">
+      <c r="B46" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C45" s="58" t="inlineStr">
+      <c r="C46" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00048/2026</t>
         </is>
       </c>
-      <c r="D45" s="57" t="inlineStr">
+      <c r="D46" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E45" s="57" t="n">
+      <c r="E46" s="62" t="n">
         <v>113</v>
       </c>
-      <c r="G45" s="57" t="inlineStr">
+      <c r="G46" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H45" s="58" t="inlineStr">
+      <c r="H46" s="63" t="inlineStr">
         <is>
           <t>Goiatins</t>
         </is>
       </c>
-      <c r="I45" s="58" t="inlineStr">
+      <c r="I46" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J45" s="23" t="inlineStr">
+      <c r="J46" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="57" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="62" t="inlineStr">
         <is>
           <t>7953610256</t>
         </is>
       </c>
-      <c r="B46" s="57" t="inlineStr">
+      <c r="B47" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C46" s="58" t="inlineStr">
+      <c r="C47" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00050/2026</t>
         </is>
       </c>
-      <c r="D46" s="57" t="inlineStr">
+      <c r="D47" s="62" t="inlineStr">
         <is>
           <t>Muito Alto</t>
         </is>
       </c>
-      <c r="E46" s="57" t="n">
+      <c r="E47" s="62" t="n">
         <v>111</v>
       </c>
-      <c r="G46" s="57" t="inlineStr">
+      <c r="G47" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H46" s="58" t="inlineStr">
+      <c r="H47" s="63" t="inlineStr">
         <is>
           <t>Mateiros</t>
         </is>
       </c>
-      <c r="I46" s="58" t="inlineStr">
+      <c r="I47" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J46" s="23" t="inlineStr">
+      <c r="J47" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="57" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="62" t="inlineStr">
         <is>
           <t>7926442035</t>
         </is>
       </c>
-      <c r="B47" s="57" t="inlineStr">
+      <c r="B48" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C47" s="58" t="inlineStr">
+      <c r="C48" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00051/2026</t>
         </is>
       </c>
-      <c r="D47" s="57" t="inlineStr">
+      <c r="D48" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E47" s="57" t="n">
+      <c r="E48" s="62" t="n">
         <v>111</v>
       </c>
-      <c r="G47" s="57" t="inlineStr">
+      <c r="G48" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H47" s="58" t="inlineStr">
+      <c r="H48" s="63" t="inlineStr">
         <is>
           <t>Monte Do Carmo</t>
         </is>
       </c>
-      <c r="I47" s="58" t="inlineStr">
+      <c r="I48" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J47" s="23" t="inlineStr">
+      <c r="J48" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="57" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="62" t="inlineStr">
         <is>
           <t>7925744087</t>
         </is>
       </c>
-      <c r="B48" s="57" t="inlineStr">
+      <c r="B49" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C48" s="58" t="inlineStr">
+      <c r="C49" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00059/2026</t>
         </is>
       </c>
-      <c r="D48" s="57" t="inlineStr">
+      <c r="D49" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E48" s="57" t="n">
+      <c r="E49" s="62" t="n">
         <v>99</v>
       </c>
-      <c r="G48" s="57" t="inlineStr">
+      <c r="G49" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H48" s="58" t="inlineStr">
+      <c r="H49" s="63" t="inlineStr">
         <is>
           <t>Goianorte</t>
         </is>
       </c>
-      <c r="I48" s="58" t="inlineStr">
+      <c r="I49" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J48" s="23" t="inlineStr">
+      <c r="J49" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="57" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="62" t="inlineStr">
         <is>
           <t>7925733015</t>
         </is>
       </c>
-      <c r="B49" s="57" t="inlineStr">
+      <c r="B50" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C49" s="58" t="inlineStr">
+      <c r="C50" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00058/2026</t>
         </is>
       </c>
-      <c r="D49" s="57" t="inlineStr">
+      <c r="D50" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E49" s="57" t="n">
+      <c r="E50" s="62" t="n">
         <v>99</v>
       </c>
-      <c r="G49" s="57" t="inlineStr">
+      <c r="G50" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H49" s="58" t="inlineStr">
+      <c r="H50" s="63" t="inlineStr">
         <is>
           <t>Pedro Afonso</t>
         </is>
       </c>
-      <c r="I49" s="58" t="inlineStr">
+      <c r="I50" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J49" s="23" t="inlineStr">
+      <c r="J50" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="57" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="62" t="inlineStr">
         <is>
           <t>7901110084</t>
         </is>
       </c>
-      <c r="B50" s="57" t="inlineStr">
+      <c r="B51" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C50" s="58" t="inlineStr">
+      <c r="C51" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00061/2026</t>
         </is>
       </c>
-      <c r="D50" s="57" t="inlineStr">
+      <c r="D51" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E50" s="57" t="n">
+      <c r="E51" s="62" t="n">
         <v>98</v>
       </c>
-      <c r="G50" s="57" t="inlineStr">
+      <c r="G51" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H50" s="58" t="inlineStr">
+      <c r="H51" s="63" t="inlineStr">
         <is>
           <t>Divinopolis</t>
         </is>
       </c>
-      <c r="I50" s="58" t="inlineStr">
+      <c r="I51" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J50" s="23" t="inlineStr">
+      <c r="J51" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="57" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="62" t="inlineStr">
         <is>
           <t>7944559149</t>
         </is>
       </c>
-      <c r="B51" s="57" t="inlineStr">
+      <c r="B52" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C51" s="58" t="inlineStr">
+      <c r="C52" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00063/2026</t>
         </is>
       </c>
-      <c r="D51" s="57" t="inlineStr">
+      <c r="D52" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E51" s="57" t="n">
+      <c r="E52" s="62" t="n">
         <v>98</v>
       </c>
-      <c r="G51" s="57" t="inlineStr">
+      <c r="G52" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H51" s="58" t="inlineStr">
+      <c r="H52" s="63" t="inlineStr">
         <is>
           <t>Caseara</t>
         </is>
       </c>
-      <c r="I51" s="58" t="inlineStr">
+      <c r="I52" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J51" s="23" t="inlineStr">
+      <c r="J52" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="57" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="62" t="inlineStr">
         <is>
           <t>5800291035</t>
         </is>
       </c>
-      <c r="B52" s="57" t="inlineStr">
+      <c r="B53" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C52" s="58" t="inlineStr">
+      <c r="C53" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-PO 00097/2026</t>
         </is>
       </c>
-      <c r="D52" s="57" t="inlineStr">
+      <c r="D53" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E52" s="57" t="n">
+      <c r="E53" s="62" t="n">
         <v>98</v>
       </c>
-      <c r="G52" s="57" t="inlineStr">
+      <c r="G53" s="62" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H52" s="58" t="inlineStr">
+      <c r="H53" s="63" t="inlineStr">
         <is>
           <t>Monte Do Carmo</t>
         </is>
       </c>
-      <c r="I52" s="59" t="inlineStr">
+      <c r="I53" s="64" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
       </c>
-      <c r="J52" s="23" t="inlineStr">
+      <c r="J53" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="57" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="62" t="inlineStr">
         <is>
           <t>7919270014</t>
         </is>
       </c>
-      <c r="B53" s="57" t="inlineStr">
+      <c r="B54" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C53" s="58" t="inlineStr">
+      <c r="C54" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00074/2026</t>
         </is>
       </c>
-      <c r="D53" s="57" t="inlineStr">
+      <c r="D54" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E53" s="57" t="n">
+      <c r="E54" s="62" t="n">
         <v>82</v>
       </c>
-      <c r="G53" s="57" t="inlineStr">
+      <c r="G54" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H53" s="58" t="inlineStr">
+      <c r="H54" s="63" t="inlineStr">
         <is>
           <t>Pium</t>
         </is>
       </c>
-      <c r="I53" s="58" t="inlineStr">
+      <c r="I54" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J53" s="23" t="inlineStr">
+      <c r="J54" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="57" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="62" t="inlineStr">
         <is>
           <t>5801866013</t>
         </is>
       </c>
-      <c r="B54" s="57" t="inlineStr">
+      <c r="B55" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C54" s="58" t="inlineStr">
+      <c r="C55" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00077/2026</t>
         </is>
       </c>
-      <c r="D54" s="57" t="inlineStr">
+      <c r="D55" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E54" s="57" t="n">
+      <c r="E55" s="62" t="n">
         <v>79</v>
       </c>
-      <c r="G54" s="57" t="inlineStr">
+      <c r="G55" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H54" s="58" t="inlineStr">
+      <c r="H55" s="63" t="inlineStr">
         <is>
           <t>Paraiso Do Tocantins</t>
         </is>
       </c>
-      <c r="I54" s="58" t="inlineStr">
+      <c r="I55" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J54" s="23" t="inlineStr">
+      <c r="J55" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="57" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="62" t="inlineStr">
         <is>
           <t>7926089013</t>
         </is>
       </c>
-      <c r="B55" s="57" t="inlineStr">
+      <c r="B56" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C55" s="58" t="inlineStr">
+      <c r="C56" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00078/2026</t>
         </is>
       </c>
-      <c r="D55" s="57" t="inlineStr">
+      <c r="D56" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E55" s="57" t="n">
+      <c r="E56" s="62" t="n">
         <v>76</v>
       </c>
-      <c r="G55" s="57" t="inlineStr">
+      <c r="G56" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H55" s="58" t="inlineStr">
+      <c r="H56" s="63" t="inlineStr">
         <is>
           <t>Paraiso Do Tocantins</t>
         </is>
       </c>
-      <c r="I55" s="58" t="inlineStr">
+      <c r="I56" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J55" s="23" t="inlineStr">
+      <c r="J56" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="57" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="62" t="inlineStr">
         <is>
           <t>7900573047</t>
         </is>
       </c>
-      <c r="B56" s="57" t="inlineStr">
+      <c r="B57" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C56" s="58" t="inlineStr">
+      <c r="C57" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00080/2026</t>
         </is>
       </c>
-      <c r="D56" s="57" t="inlineStr">
+      <c r="D57" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E56" s="57" t="n">
+      <c r="E57" s="62" t="n">
         <v>75</v>
       </c>
-      <c r="G56" s="57" t="inlineStr">
+      <c r="G57" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H56" s="58" t="inlineStr">
+      <c r="H57" s="63" t="inlineStr">
         <is>
           <t>Figueiropolis</t>
         </is>
       </c>
-      <c r="I56" s="58" t="inlineStr">
+      <c r="I57" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J56" s="23" t="inlineStr">
+      <c r="J57" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="57" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="62" t="inlineStr">
         <is>
           <t>7927413001</t>
         </is>
       </c>
-      <c r="B57" s="57" t="inlineStr">
+      <c r="B58" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C57" s="58" t="inlineStr">
+      <c r="C58" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-PO 00118/2026</t>
         </is>
       </c>
-      <c r="D57" s="57" t="inlineStr">
+      <c r="D58" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E57" s="57" t="n">
+      <c r="E58" s="62" t="n">
         <v>75</v>
       </c>
-      <c r="G57" s="57" t="inlineStr">
+      <c r="G58" s="62" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H57" s="58" t="inlineStr">
+      <c r="H58" s="63" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I57" s="59" t="inlineStr">
+      <c r="I58" s="64" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
       </c>
-      <c r="J57" s="23" t="inlineStr">
+      <c r="J58" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="57" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="62" t="inlineStr">
         <is>
           <t>7908686014</t>
         </is>
       </c>
-      <c r="B58" s="57" t="inlineStr">
+      <c r="B59" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C58" s="58" t="inlineStr">
+      <c r="C59" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00086/2026</t>
         </is>
       </c>
-      <c r="D58" s="57" t="inlineStr">
+      <c r="D59" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E58" s="57" t="n">
+      <c r="E59" s="62" t="n">
         <v>74</v>
       </c>
-      <c r="G58" s="57" t="inlineStr">
+      <c r="G59" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H58" s="58" t="inlineStr">
+      <c r="H59" s="63" t="inlineStr">
         <is>
           <t>Pium</t>
         </is>
       </c>
-      <c r="I58" s="58" t="inlineStr">
+      <c r="I59" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J58" s="23" t="inlineStr">
+      <c r="J59" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="57" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="62" t="inlineStr">
         <is>
           <t>7900117013</t>
         </is>
       </c>
-      <c r="B59" s="57" t="inlineStr">
+      <c r="B60" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C59" s="58" t="inlineStr">
+      <c r="C60" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00084/2026</t>
         </is>
       </c>
-      <c r="D59" s="57" t="inlineStr">
+      <c r="D60" s="62" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E59" s="57" t="n">
+      <c r="E60" s="62" t="n">
         <v>74</v>
       </c>
-      <c r="G59" s="57" t="inlineStr">
+      <c r="G60" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H59" s="58" t="inlineStr">
+      <c r="H60" s="63" t="inlineStr">
         <is>
           <t>Paraiso Do Tocantins</t>
         </is>
       </c>
-      <c r="I59" s="58" t="inlineStr">
+      <c r="I60" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J59" s="23" t="inlineStr">
+      <c r="J60" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="57" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="62" t="inlineStr">
         <is>
           <t>7900453110</t>
         </is>
       </c>
-      <c r="B60" s="57" t="inlineStr">
+      <c r="B61" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C60" s="58" t="inlineStr">
+      <c r="C61" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00087/2026</t>
         </is>
       </c>
-      <c r="D60" s="57" t="inlineStr">
+      <c r="D61" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E60" s="57" t="n">
+      <c r="E61" s="62" t="n">
         <v>71</v>
       </c>
-      <c r="G60" s="57" t="inlineStr">
+      <c r="G61" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H60" s="58" t="inlineStr">
+      <c r="H61" s="63" t="inlineStr">
         <is>
           <t>Santa Rita Do Tocantins</t>
         </is>
       </c>
-      <c r="I60" s="58" t="inlineStr">
+      <c r="I61" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J60" s="23" t="inlineStr">
+      <c r="J61" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="57" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="62" t="inlineStr">
         <is>
           <t>5865120195</t>
         </is>
       </c>
-      <c r="B61" s="57" t="inlineStr">
+      <c r="B62" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C61" s="58" t="inlineStr">
+      <c r="C62" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-GR 00538/2026</t>
         </is>
       </c>
-      <c r="D61" s="57" t="inlineStr">
+      <c r="D62" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E61" s="57" t="n">
+      <c r="E62" s="62" t="n">
         <v>51</v>
       </c>
-      <c r="G61" s="57" t="inlineStr">
+      <c r="G62" s="62" t="inlineStr">
         <is>
           <t>COCM-N</t>
         </is>
       </c>
-      <c r="H61" s="58" t="inlineStr">
+      <c r="H62" s="63" t="inlineStr">
         <is>
           <t>Centenario</t>
         </is>
       </c>
-      <c r="I61" s="59" t="inlineStr">
+      <c r="I62" s="64" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
       </c>
-      <c r="J61" s="23" t="inlineStr">
+      <c r="J62" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="57" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="62" t="inlineStr">
         <is>
           <t>5836786094</t>
         </is>
       </c>
-      <c r="B62" s="57" t="inlineStr">
+      <c r="B63" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C62" s="58" t="inlineStr">
+      <c r="C63" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00095/2026</t>
         </is>
       </c>
-      <c r="D62" s="57" t="inlineStr">
+      <c r="D63" s="62" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E62" s="57" t="n">
+      <c r="E63" s="62" t="n">
         <v>50</v>
       </c>
-      <c r="G62" s="57" t="inlineStr">
+      <c r="G63" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H62" s="58" t="inlineStr">
+      <c r="H63" s="63" t="inlineStr">
         <is>
           <t>Peixe</t>
         </is>
       </c>
-      <c r="I62" s="58" t="inlineStr">
+      <c r="I63" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J62" s="23" t="inlineStr">
+      <c r="J63" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="57" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="62" t="inlineStr">
         <is>
           <t>7900594026</t>
         </is>
       </c>
-      <c r="B63" s="57" t="inlineStr">
+      <c r="B64" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C63" s="58" t="inlineStr">
+      <c r="C64" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00113/2026</t>
         </is>
       </c>
-      <c r="D63" s="57" t="inlineStr">
+      <c r="D64" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E63" s="57" t="n">
+      <c r="E64" s="62" t="n">
         <v>27</v>
       </c>
-      <c r="G63" s="57" t="inlineStr">
+      <c r="G64" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H63" s="58" t="inlineStr">
+      <c r="H64" s="63" t="inlineStr">
         <is>
           <t>Ponte Alta Tocantins</t>
         </is>
       </c>
-      <c r="I63" s="58" t="inlineStr">
+      <c r="I64" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J63" s="23" t="inlineStr">
+      <c r="J64" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="57" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="62" t="inlineStr">
         <is>
           <t>7913662076</t>
         </is>
       </c>
-      <c r="B64" s="57" t="inlineStr">
+      <c r="B65" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C64" s="58" t="inlineStr">
+      <c r="C65" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00114/2026</t>
         </is>
       </c>
-      <c r="D64" s="57" t="inlineStr">
+      <c r="D65" s="62" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E64" s="57" t="n">
+      <c r="E65" s="62" t="n">
         <v>27</v>
       </c>
-      <c r="G64" s="57" t="inlineStr">
+      <c r="G65" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H64" s="58" t="inlineStr">
+      <c r="H65" s="63" t="inlineStr">
         <is>
           <t>Duere</t>
         </is>
       </c>
-      <c r="I64" s="58" t="inlineStr">
+      <c r="I65" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J64" s="23" t="inlineStr">
+      <c r="J65" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="57" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="62" t="inlineStr">
         <is>
           <t>5800859011</t>
         </is>
       </c>
-      <c r="B65" s="57" t="inlineStr">
+      <c r="B66" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C65" s="58" t="inlineStr">
+      <c r="C66" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00115/2026</t>
         </is>
       </c>
-      <c r="D65" s="57" t="inlineStr">
+      <c r="D66" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E65" s="57" t="n">
+      <c r="E66" s="62" t="n">
         <v>25</v>
       </c>
-      <c r="G65" s="57" t="inlineStr">
+      <c r="G66" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H65" s="58" t="inlineStr">
+      <c r="H66" s="63" t="inlineStr">
         <is>
           <t>Tupirama</t>
         </is>
       </c>
-      <c r="I65" s="58" t="inlineStr">
+      <c r="I66" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J65" s="23" t="inlineStr">
+      <c r="J66" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="57" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="62" t="inlineStr">
         <is>
           <t>5800090147</t>
         </is>
       </c>
-      <c r="B66" s="57" t="inlineStr">
+      <c r="B67" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C66" s="58" t="inlineStr">
+      <c r="C67" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00117/2026</t>
         </is>
       </c>
-      <c r="D66" s="57" t="inlineStr">
+      <c r="D67" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E66" s="57" t="n">
+      <c r="E67" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="G66" s="57" t="inlineStr">
+      <c r="G67" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H66" s="58" t="inlineStr">
+      <c r="H67" s="63" t="inlineStr">
         <is>
           <t>Taipas Do Tocantins</t>
         </is>
       </c>
-      <c r="I66" s="58" t="inlineStr">
+      <c r="I67" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J66" s="23" t="inlineStr">
+      <c r="J67" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="57" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="62" t="inlineStr">
         <is>
           <t>5856156091</t>
         </is>
       </c>
-      <c r="B67" s="57" t="inlineStr">
+      <c r="B68" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C67" s="58" t="inlineStr">
+      <c r="C68" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-DP 00403/2026</t>
         </is>
       </c>
-      <c r="D67" s="57" t="inlineStr">
+      <c r="D68" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E67" s="57" t="n">
+      <c r="E68" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="G67" s="57" t="inlineStr">
+      <c r="G68" s="62" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H67" s="58" t="inlineStr">
+      <c r="H68" s="63" t="inlineStr">
         <is>
           <t>Almas</t>
         </is>
       </c>
-      <c r="I67" s="59" t="inlineStr">
+      <c r="I68" s="64" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
       </c>
-      <c r="J67" s="23" t="inlineStr">
+      <c r="J68" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="57" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="62" t="inlineStr">
         <is>
           <t>5827102054</t>
         </is>
       </c>
-      <c r="B68" s="57" t="inlineStr">
+      <c r="B69" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C68" s="58" t="inlineStr">
+      <c r="C69" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-PS 00289/2026</t>
         </is>
       </c>
-      <c r="D68" s="57" t="inlineStr">
+      <c r="D69" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E68" s="57" t="n">
+      <c r="E69" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="G68" s="57" t="inlineStr">
+      <c r="G69" s="62" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H68" s="58" t="inlineStr">
+      <c r="H69" s="63" t="inlineStr">
         <is>
           <t>Pugmil</t>
         </is>
       </c>
-      <c r="I68" s="58" t="inlineStr">
+      <c r="I69" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J68" s="23" t="inlineStr">
+      <c r="J69" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="57" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="62" t="inlineStr">
         <is>
           <t>5846328094</t>
         </is>
       </c>
-      <c r="B69" s="57" t="inlineStr">
+      <c r="B70" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C69" s="58" t="inlineStr">
+      <c r="C70" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-GU 00687/2026</t>
         </is>
       </c>
-      <c r="D69" s="57" t="inlineStr">
+      <c r="D70" s="62" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E69" s="57" t="n">
+      <c r="E70" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="G69" s="57" t="inlineStr">
+      <c r="G70" s="62" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H69" s="58" t="inlineStr">
+      <c r="H70" s="63" t="inlineStr">
         <is>
           <t>Peixe</t>
         </is>
       </c>
-      <c r="I69" s="59" t="inlineStr">
+      <c r="I70" s="64" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
       </c>
-      <c r="J69" s="23" t="inlineStr">
+      <c r="J70" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="57" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="62" t="inlineStr">
         <is>
           <t>7942572059</t>
         </is>
       </c>
-      <c r="B70" s="57" t="inlineStr">
+      <c r="B71" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C70" s="58" t="inlineStr">
+      <c r="C71" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00427/2026</t>
         </is>
       </c>
-      <c r="D70" s="57" t="inlineStr">
+      <c r="D71" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E70" s="57" t="n">
+      <c r="E71" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="G70" s="57" t="inlineStr">
+      <c r="G71" s="62" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H70" s="58" t="inlineStr">
+      <c r="H71" s="63" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I70" s="59" t="inlineStr">
+      <c r="I71" s="64" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
       </c>
-      <c r="J70" s="23" t="inlineStr">
+      <c r="J71" s="23" t="inlineStr">
         <is>
           <t>EXECUTADO</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="57" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="62" t="inlineStr">
         <is>
           <t>7929376022</t>
         </is>
       </c>
-      <c r="B71" s="57" t="inlineStr">
+      <c r="B72" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C71" s="58" t="inlineStr">
+      <c r="C72" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2026</t>
         </is>
       </c>
-      <c r="D71" s="57" t="inlineStr">
+      <c r="D72" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E71" s="57" t="n">
+      <c r="E72" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="G71" s="57" t="inlineStr">
+      <c r="G72" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H71" s="58" t="inlineStr">
+      <c r="H72" s="63" t="inlineStr">
         <is>
           <t>Babaculandia</t>
         </is>
       </c>
-      <c r="I71" s="58" t="inlineStr">
+      <c r="I72" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J71" s="23" t="inlineStr">
+      <c r="J72" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="57" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="62" t="inlineStr">
         <is>
           <t>5800438116</t>
         </is>
       </c>
-      <c r="B72" s="57" t="inlineStr">
+      <c r="B73" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C72" s="58" t="inlineStr">
+      <c r="C73" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-DP 00404/2026</t>
         </is>
       </c>
-      <c r="D72" s="57" t="inlineStr">
+      <c r="D73" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E72" s="57" t="n">
+      <c r="E73" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="G72" s="57" t="inlineStr">
+      <c r="G73" s="62" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H72" s="58" t="inlineStr">
+      <c r="H73" s="63" t="inlineStr">
         <is>
           <t>Chapada Da Natividade</t>
         </is>
       </c>
-      <c r="I72" s="58" t="inlineStr">
+      <c r="I73" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J72" s="23" t="inlineStr">
+      <c r="J73" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="57" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="62" t="inlineStr">
         <is>
           <t>5803327001</t>
         </is>
       </c>
-      <c r="B73" s="57" t="inlineStr">
+      <c r="B74" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C73" s="58" t="inlineStr">
+      <c r="C74" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00434/2026</t>
         </is>
       </c>
-      <c r="D73" s="57" t="inlineStr">
+      <c r="D74" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E73" s="57" t="n">
+      <c r="E74" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="G73" s="57" t="inlineStr">
+      <c r="G74" s="62" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H73" s="58" t="inlineStr">
+      <c r="H74" s="63" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I73" s="59" t="inlineStr">
+      <c r="I74" s="64" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
       </c>
-      <c r="J73" s="23" t="inlineStr">
+      <c r="J74" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="57" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="62" t="inlineStr">
         <is>
           <t>7933766059</t>
         </is>
       </c>
-      <c r="B74" s="57" t="inlineStr">
+      <c r="B75" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C74" s="58" t="inlineStr">
+      <c r="C75" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00431/2026</t>
         </is>
       </c>
-      <c r="D74" s="57" t="inlineStr">
+      <c r="D75" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E74" s="57" t="n">
+      <c r="E75" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="G74" s="57" t="inlineStr">
+      <c r="G75" s="62" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H74" s="58" t="inlineStr">
+      <c r="H75" s="63" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I74" s="58" t="inlineStr">
+      <c r="I75" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J74" s="23" t="inlineStr">
+      <c r="J75" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="57" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="62" t="inlineStr">
         <is>
           <t>7931610122</t>
         </is>
       </c>
-      <c r="B75" s="57" t="inlineStr">
+      <c r="B76" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C75" s="58" t="inlineStr">
+      <c r="C76" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00433/2026</t>
         </is>
       </c>
-      <c r="D75" s="57" t="inlineStr">
+      <c r="D76" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E75" s="57" t="n">
+      <c r="E76" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="G75" s="57" t="inlineStr">
+      <c r="G76" s="62" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H75" s="58" t="inlineStr">
+      <c r="H76" s="63" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I75" s="58" t="inlineStr">
+      <c r="I76" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J75" s="23" t="inlineStr">
+      <c r="J76" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="57" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="62" t="inlineStr">
         <is>
           <t>7927169001</t>
         </is>
       </c>
-      <c r="B76" s="57" t="inlineStr">
+      <c r="B77" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C76" s="58" t="inlineStr">
+      <c r="C77" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00432/2026</t>
         </is>
       </c>
-      <c r="D76" s="57" t="inlineStr">
+      <c r="D77" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E76" s="57" t="n">
+      <c r="E77" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="G76" s="57" t="inlineStr">
+      <c r="G77" s="62" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H76" s="58" t="inlineStr">
+      <c r="H77" s="63" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I76" s="58" t="inlineStr">
+      <c r="I77" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J76" s="23" t="inlineStr">
+      <c r="J77" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="57" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="62" t="inlineStr">
         <is>
           <t>7933726256</t>
         </is>
       </c>
-      <c r="B77" s="57" t="inlineStr">
+      <c r="B78" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C77" s="58" t="inlineStr">
+      <c r="C78" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-PO 00181/2026</t>
         </is>
       </c>
-      <c r="D77" s="57" t="inlineStr">
+      <c r="D78" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E77" s="57" t="n">
+      <c r="E78" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="G77" s="57" t="inlineStr">
+      <c r="G78" s="62" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H77" s="58" t="inlineStr">
+      <c r="H78" s="63" t="inlineStr">
         <is>
           <t>Mateiros</t>
         </is>
       </c>
-      <c r="I77" s="58" t="inlineStr">
+      <c r="I78" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J77" s="23" t="inlineStr">
+      <c r="J78" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="57" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="62" t="inlineStr">
         <is>
           <t>7911120026</t>
         </is>
       </c>
-      <c r="B78" s="57" t="inlineStr">
+      <c r="B79" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C78" s="58" t="inlineStr">
+      <c r="C79" s="63" t="inlineStr">
         <is>
           <t>DG-RD-PO 00444/2026</t>
         </is>
       </c>
-      <c r="D78" s="57" t="inlineStr">
+      <c r="D79" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E78" s="57" t="n">
+      <c r="E79" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="G78" s="57" t="inlineStr">
+      <c r="G79" s="62" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H78" s="58" t="inlineStr">
+      <c r="H79" s="63" t="inlineStr">
         <is>
           <t>Ponte Alta Tocantins</t>
         </is>
       </c>
-      <c r="I78" s="59" t="inlineStr">
+      <c r="I79" s="64" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
       </c>
-      <c r="J78" s="23" t="inlineStr">
+      <c r="J79" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="57" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="62" t="inlineStr">
         <is>
           <t>7908705049</t>
         </is>
       </c>
-      <c r="B79" s="57" t="inlineStr">
+      <c r="B80" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C79" s="58" t="inlineStr">
+      <c r="C80" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-DP 00409/2026</t>
         </is>
       </c>
-      <c r="D79" s="57" t="inlineStr">
+      <c r="D80" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E79" s="57" t="n">
+      <c r="E80" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="G79" s="57" t="inlineStr">
+      <c r="G80" s="62" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H79" s="58" t="inlineStr">
+      <c r="H80" s="63" t="inlineStr">
         <is>
           <t>Aurora Do Tocantins</t>
         </is>
       </c>
-      <c r="I79" s="58" t="inlineStr">
+      <c r="I80" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J79" s="23" t="inlineStr">
+      <c r="J80" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="57" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="62" t="inlineStr">
         <is>
           <t>7900230155</t>
         </is>
       </c>
-      <c r="B80" s="57" t="inlineStr">
+      <c r="B81" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C80" s="58" t="inlineStr">
+      <c r="C81" s="63" t="inlineStr">
         <is>
           <t>ETO-RD-GR 00685/2026</t>
         </is>
       </c>
-      <c r="D80" s="57" t="inlineStr">
+      <c r="D81" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E80" s="57" t="n">
+      <c r="E81" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G80" s="57" t="inlineStr">
+      <c r="G81" s="62" t="inlineStr">
         <is>
           <t>COCM-N</t>
         </is>
       </c>
-      <c r="H80" s="58" t="inlineStr">
+      <c r="H81" s="63" t="inlineStr">
         <is>
           <t>Palmeirante</t>
         </is>
       </c>
-      <c r="I80" s="58" t="inlineStr">
+      <c r="I81" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J80" s="23" t="inlineStr">
+      <c r="J81" s="23" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="57" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="62" t="inlineStr">
         <is>
           <t>7928564039</t>
         </is>
       </c>
-      <c r="B81" s="57" t="inlineStr">
+      <c r="B82" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C81" s="58" t="inlineStr">
+      <c r="C82" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00123/2026</t>
         </is>
       </c>
-      <c r="D81" s="57" t="inlineStr">
+      <c r="D82" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E81" s="57" t="n">
+      <c r="E82" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G81" s="57" t="inlineStr">
+      <c r="G82" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H81" s="58" t="inlineStr">
+      <c r="H82" s="63" t="inlineStr">
         <is>
           <t>Araguatins</t>
         </is>
       </c>
-      <c r="I81" s="58" t="inlineStr">
+      <c r="I82" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J81" s="23" t="inlineStr">
+      <c r="J82" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="57" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="62" t="inlineStr">
         <is>
           <t>7928241200</t>
         </is>
       </c>
-      <c r="B82" s="57" t="inlineStr">
+      <c r="B83" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C82" s="58" t="inlineStr">
+      <c r="C83" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00128/2026</t>
         </is>
       </c>
-      <c r="D82" s="57" t="inlineStr">
+      <c r="D83" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E82" s="57" t="n">
+      <c r="E83" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="57" t="inlineStr">
+      <c r="G83" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H82" s="58" t="inlineStr">
+      <c r="H83" s="63" t="inlineStr">
         <is>
           <t>Sao Salvador Do Tocantins</t>
         </is>
       </c>
-      <c r="I82" s="58" t="inlineStr">
+      <c r="I83" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J82" s="23" t="inlineStr">
+      <c r="J83" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="57" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="62" t="inlineStr">
         <is>
           <t>5856070091</t>
         </is>
       </c>
-      <c r="B83" s="57" t="inlineStr">
+      <c r="B84" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C83" s="58" t="inlineStr">
+      <c r="C84" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00130/2026</t>
         </is>
       </c>
-      <c r="D83" s="57" t="inlineStr">
+      <c r="D84" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E83" s="57" t="n">
+      <c r="E84" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G83" s="57" t="inlineStr">
+      <c r="G84" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H83" s="58" t="inlineStr">
+      <c r="H84" s="63" t="inlineStr">
         <is>
           <t>Almas</t>
         </is>
       </c>
-      <c r="I83" s="58" t="inlineStr">
+      <c r="I84" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J83" s="23" t="inlineStr">
+      <c r="J84" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="57" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="62" t="inlineStr">
         <is>
           <t>5850308009</t>
         </is>
       </c>
-      <c r="B84" s="57" t="inlineStr">
+      <c r="B85" s="62" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C84" s="58" t="inlineStr">
+      <c r="C85" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00127/2026</t>
         </is>
       </c>
-      <c r="D84" s="57" t="inlineStr">
+      <c r="D85" s="62" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E84" s="57" t="n">
+      <c r="E85" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G84" s="57" t="inlineStr">
+      <c r="G85" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H84" s="58" t="inlineStr">
+      <c r="H85" s="63" t="inlineStr">
         <is>
           <t>Guarai</t>
         </is>
       </c>
-      <c r="I84" s="58" t="inlineStr">
+      <c r="I85" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J84" s="23" t="inlineStr">
+      <c r="J85" s="23" t="inlineStr">
         <is>
           <t>CONCLUÍDA MAS AINDA NO POSTO (VERIFICAR)</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="57" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="62" t="inlineStr">
         <is>
           <t>7937102148</t>
         </is>
       </c>
-      <c r="B85" s="57" t="inlineStr">
+      <c r="B86" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C85" s="58" t="inlineStr">
+      <c r="C86" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00129/2026</t>
         </is>
       </c>
-      <c r="D85" s="57" t="inlineStr">
+      <c r="D86" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E85" s="57" t="n">
+      <c r="E86" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G85" s="57" t="inlineStr">
+      <c r="G86" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H85" s="58" t="inlineStr">
+      <c r="H86" s="63" t="inlineStr">
         <is>
           <t>Sao Valerio Da Natividade</t>
         </is>
       </c>
-      <c r="I85" s="58" t="inlineStr">
+      <c r="I86" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J85" s="23" t="inlineStr">
+      <c r="J86" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="57" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="62" t="inlineStr">
         <is>
           <t>7923673004</t>
         </is>
       </c>
-      <c r="B86" s="57" t="inlineStr">
+      <c r="B87" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C86" s="58" t="inlineStr">
+      <c r="C87" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00124/2026</t>
         </is>
       </c>
-      <c r="D86" s="57" t="inlineStr">
+      <c r="D87" s="62" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E86" s="57" t="n">
+      <c r="E87" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="57" t="inlineStr">
+      <c r="G87" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H86" s="58" t="inlineStr">
+      <c r="H87" s="63" t="inlineStr">
         <is>
           <t>Araguaina</t>
         </is>
       </c>
-      <c r="I86" s="58" t="inlineStr">
+      <c r="I87" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J86" s="23" t="inlineStr">
+      <c r="J87" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="57" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="62" t="inlineStr">
         <is>
           <t>7900525015</t>
         </is>
       </c>
-      <c r="B87" s="57" t="inlineStr">
+      <c r="B88" s="62" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C87" s="58" t="inlineStr">
+      <c r="C88" s="63" t="inlineStr">
         <is>
           <t>ETO-COEP 00125/2026</t>
         </is>
       </c>
-      <c r="D87" s="57" t="inlineStr">
+      <c r="D88" s="62" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E87" s="57" t="n">
+      <c r="E88" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="G87" s="57" t="inlineStr">
+      <c r="G88" s="62" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H87" s="58" t="inlineStr">
+      <c r="H88" s="63" t="inlineStr">
         <is>
           <t>Pedro Afonso</t>
         </is>
       </c>
-      <c r="I87" s="58" t="inlineStr">
+      <c r="I88" s="63" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
       </c>
-      <c r="J87" s="23" t="inlineStr">
+      <c r="J88" s="23" t="inlineStr">
         <is>
           <t>No posto do COEP (pendente)</t>
         </is>

--- a/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
+++ b/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
@@ -170,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -315,15 +315,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2933,40 +2924,40 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="62" t="inlineStr">
+      <c r="A24" s="57" t="inlineStr">
         <is>
           <t>7923927122</t>
         </is>
       </c>
-      <c r="B24" s="62" t="inlineStr">
+      <c r="B24" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C24" s="63" t="inlineStr">
+      <c r="C24" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00079/2025</t>
         </is>
       </c>
-      <c r="D24" s="62" t="inlineStr">
+      <c r="D24" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E24" s="62" t="n">
+      <c r="E24" s="57" t="n">
         <v>434</v>
       </c>
-      <c r="G24" s="62" t="inlineStr">
+      <c r="G24" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H24" s="63" t="inlineStr">
+      <c r="H24" s="58" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I24" s="63" t="inlineStr">
+      <c r="I24" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -2978,40 +2969,40 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="62" t="inlineStr">
+      <c r="A25" s="57" t="inlineStr">
         <is>
           <t>7900532053</t>
         </is>
       </c>
-      <c r="B25" s="62" t="inlineStr">
+      <c r="B25" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C25" s="63" t="inlineStr">
+      <c r="C25" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00102/2025</t>
         </is>
       </c>
-      <c r="D25" s="62" t="inlineStr">
+      <c r="D25" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E25" s="62" t="n">
+      <c r="E25" s="57" t="n">
         <v>407</v>
       </c>
-      <c r="G25" s="62" t="inlineStr">
+      <c r="G25" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H25" s="63" t="inlineStr">
+      <c r="H25" s="58" t="inlineStr">
         <is>
           <t>Piraque</t>
         </is>
       </c>
-      <c r="I25" s="63" t="inlineStr">
+      <c r="I25" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3023,40 +3014,40 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="62" t="inlineStr">
+      <c r="A26" s="57" t="inlineStr">
         <is>
           <t>7920024127</t>
         </is>
       </c>
-      <c r="B26" s="62" t="inlineStr">
+      <c r="B26" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C26" s="63" t="inlineStr">
+      <c r="C26" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2025</t>
         </is>
       </c>
-      <c r="D26" s="62" t="inlineStr">
+      <c r="D26" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E26" s="62" t="n">
+      <c r="E26" s="57" t="n">
         <v>371</v>
       </c>
-      <c r="G26" s="62" t="inlineStr">
+      <c r="G26" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H26" s="63" t="inlineStr">
+      <c r="H26" s="58" t="inlineStr">
         <is>
           <t>Palmeiras Do Tocantins</t>
         </is>
       </c>
-      <c r="I26" s="63" t="inlineStr">
+      <c r="I26" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3068,40 +3059,40 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="62" t="inlineStr">
+      <c r="A27" s="57" t="inlineStr">
         <is>
           <t>5858783119</t>
         </is>
       </c>
-      <c r="B27" s="62" t="inlineStr">
+      <c r="B27" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C27" s="63" t="inlineStr">
+      <c r="C27" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00123/2025</t>
         </is>
       </c>
-      <c r="D27" s="62" t="inlineStr">
+      <c r="D27" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E27" s="62" t="n">
+      <c r="E27" s="57" t="n">
         <v>369</v>
       </c>
-      <c r="G27" s="62" t="inlineStr">
+      <c r="G27" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H27" s="63" t="inlineStr">
+      <c r="H27" s="58" t="inlineStr">
         <is>
           <t>Sao Bento Do Tocantins</t>
         </is>
       </c>
-      <c r="I27" s="63" t="inlineStr">
+      <c r="I27" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3113,40 +3104,40 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="62" t="inlineStr">
+      <c r="A28" s="57" t="inlineStr">
         <is>
           <t>7927446001</t>
         </is>
       </c>
-      <c r="B28" s="62" t="inlineStr">
+      <c r="B28" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C28" s="63" t="inlineStr">
+      <c r="C28" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00143/2025</t>
         </is>
       </c>
-      <c r="D28" s="62" t="inlineStr">
+      <c r="D28" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E28" s="62" t="n">
+      <c r="E28" s="57" t="n">
         <v>364</v>
       </c>
-      <c r="G28" s="62" t="inlineStr">
+      <c r="G28" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H28" s="63" t="inlineStr">
+      <c r="H28" s="58" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I28" s="63" t="inlineStr">
+      <c r="I28" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3158,40 +3149,40 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="62" t="inlineStr">
+      <c r="A29" s="57" t="inlineStr">
         <is>
           <t>7957126085</t>
         </is>
       </c>
-      <c r="B29" s="62" t="inlineStr">
+      <c r="B29" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C29" s="63" t="inlineStr">
+      <c r="C29" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00156/2025</t>
         </is>
       </c>
-      <c r="D29" s="62" t="inlineStr">
+      <c r="D29" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E29" s="62" t="n">
+      <c r="E29" s="57" t="n">
         <v>350</v>
       </c>
-      <c r="G29" s="62" t="inlineStr">
+      <c r="G29" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H29" s="63" t="inlineStr">
+      <c r="H29" s="58" t="inlineStr">
         <is>
           <t>Monte Santo Do Tocantins</t>
         </is>
       </c>
-      <c r="I29" s="63" t="inlineStr">
+      <c r="I29" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3203,40 +3194,40 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="62" t="inlineStr">
+      <c r="A30" s="57" t="inlineStr">
         <is>
           <t>7942485096</t>
         </is>
       </c>
-      <c r="B30" s="62" t="inlineStr">
+      <c r="B30" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C30" s="63" t="inlineStr">
+      <c r="C30" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00158/2025</t>
         </is>
       </c>
-      <c r="D30" s="62" t="inlineStr">
+      <c r="D30" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E30" s="62" t="n">
+      <c r="E30" s="57" t="n">
         <v>349</v>
       </c>
-      <c r="G30" s="62" t="inlineStr">
+      <c r="G30" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H30" s="63" t="inlineStr">
+      <c r="H30" s="58" t="inlineStr">
         <is>
           <t>Pindorama Do Tocantins</t>
         </is>
       </c>
-      <c r="I30" s="63" t="inlineStr">
+      <c r="I30" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3248,40 +3239,40 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="62" t="inlineStr">
+      <c r="A31" s="57" t="inlineStr">
         <is>
           <t>5854566043</t>
         </is>
       </c>
-      <c r="B31" s="62" t="inlineStr">
+      <c r="B31" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C31" s="63" t="inlineStr">
+      <c r="C31" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00160/2025</t>
         </is>
       </c>
-      <c r="D31" s="62" t="inlineStr">
+      <c r="D31" s="57" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E31" s="62" t="n">
+      <c r="E31" s="57" t="n">
         <v>347</v>
       </c>
-      <c r="G31" s="62" t="inlineStr">
+      <c r="G31" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H31" s="63" t="inlineStr">
+      <c r="H31" s="58" t="inlineStr">
         <is>
           <t>Silvanopolis</t>
         </is>
       </c>
-      <c r="I31" s="63" t="inlineStr">
+      <c r="I31" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3293,40 +3284,40 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="62" t="inlineStr">
+      <c r="A32" s="57" t="inlineStr">
         <is>
           <t>5844630060</t>
         </is>
       </c>
-      <c r="B32" s="62" t="inlineStr">
+      <c r="B32" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C32" s="63" t="inlineStr">
+      <c r="C32" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00167/2025</t>
         </is>
       </c>
-      <c r="D32" s="62" t="inlineStr">
+      <c r="D32" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E32" s="62" t="n">
+      <c r="E32" s="57" t="n">
         <v>333</v>
       </c>
-      <c r="G32" s="62" t="inlineStr">
+      <c r="G32" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H32" s="63" t="inlineStr">
+      <c r="H32" s="58" t="inlineStr">
         <is>
           <t>Nova Olinda</t>
         </is>
       </c>
-      <c r="I32" s="63" t="inlineStr">
+      <c r="I32" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3338,40 +3329,40 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="62" t="inlineStr">
+      <c r="A33" s="57" t="inlineStr">
         <is>
           <t>7900535058</t>
         </is>
       </c>
-      <c r="B33" s="62" t="inlineStr">
+      <c r="B33" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C33" s="63" t="inlineStr">
+      <c r="C33" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00173/2025</t>
         </is>
       </c>
-      <c r="D33" s="62" t="inlineStr">
+      <c r="D33" s="57" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E33" s="62" t="n">
+      <c r="E33" s="57" t="n">
         <v>317</v>
       </c>
-      <c r="G33" s="62" t="inlineStr">
+      <c r="G33" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H33" s="63" t="inlineStr">
+      <c r="H33" s="58" t="inlineStr">
         <is>
           <t>Santa Fe Do Araguaia</t>
         </is>
       </c>
-      <c r="I33" s="63" t="inlineStr">
+      <c r="I33" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3383,40 +3374,40 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="62" t="inlineStr">
+      <c r="A34" s="57" t="inlineStr">
         <is>
           <t>7903112004</t>
         </is>
       </c>
-      <c r="B34" s="62" t="inlineStr">
+      <c r="B34" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C34" s="63" t="inlineStr">
+      <c r="C34" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00184/2025</t>
         </is>
       </c>
-      <c r="D34" s="62" t="inlineStr">
+      <c r="D34" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E34" s="62" t="n">
+      <c r="E34" s="57" t="n">
         <v>307</v>
       </c>
-      <c r="G34" s="62" t="inlineStr">
+      <c r="G34" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H34" s="63" t="inlineStr">
+      <c r="H34" s="58" t="inlineStr">
         <is>
           <t>Araguaina</t>
         </is>
       </c>
-      <c r="I34" s="63" t="inlineStr">
+      <c r="I34" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3428,40 +3419,40 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="62" t="inlineStr">
+      <c r="A35" s="57" t="inlineStr">
         <is>
           <t>5800371025</t>
         </is>
       </c>
-      <c r="B35" s="62" t="inlineStr">
+      <c r="B35" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C35" s="63" t="inlineStr">
+      <c r="C35" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00187/2025</t>
         </is>
       </c>
-      <c r="D35" s="62" t="inlineStr">
+      <c r="D35" s="57" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E35" s="62" t="n">
+      <c r="E35" s="57" t="n">
         <v>305</v>
       </c>
-      <c r="G35" s="62" t="inlineStr">
+      <c r="G35" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H35" s="63" t="inlineStr">
+      <c r="H35" s="58" t="inlineStr">
         <is>
           <t>Arapoema</t>
         </is>
       </c>
-      <c r="I35" s="63" t="inlineStr">
+      <c r="I35" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3473,40 +3464,40 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="62" t="inlineStr">
+      <c r="A36" s="57" t="inlineStr">
         <is>
           <t>5855411017</t>
         </is>
       </c>
-      <c r="B36" s="62" t="inlineStr">
+      <c r="B36" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C36" s="63" t="inlineStr">
+      <c r="C36" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00199/2025</t>
         </is>
       </c>
-      <c r="D36" s="62" t="inlineStr">
+      <c r="D36" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E36" s="62" t="n">
+      <c r="E36" s="57" t="n">
         <v>280</v>
       </c>
-      <c r="G36" s="62" t="inlineStr">
+      <c r="G36" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H36" s="63" t="inlineStr">
+      <c r="H36" s="58" t="inlineStr">
         <is>
           <t>Barrolandia</t>
         </is>
       </c>
-      <c r="I36" s="63" t="inlineStr">
+      <c r="I36" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3518,40 +3509,40 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="62" t="inlineStr">
+      <c r="A37" s="57" t="inlineStr">
         <is>
           <t>5853360007</t>
         </is>
       </c>
-      <c r="B37" s="62" t="inlineStr">
+      <c r="B37" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C37" s="63" t="inlineStr">
+      <c r="C37" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-PS 00323/2025</t>
         </is>
       </c>
-      <c r="D37" s="62" t="inlineStr">
+      <c r="D37" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E37" s="62" t="n">
+      <c r="E37" s="57" t="n">
         <v>264</v>
       </c>
-      <c r="G37" s="62" t="inlineStr">
+      <c r="G37" s="57" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H37" s="63" t="inlineStr">
+      <c r="H37" s="58" t="inlineStr">
         <is>
           <t>Miracema Do Tocantins</t>
         </is>
       </c>
-      <c r="I37" s="64" t="inlineStr">
+      <c r="I37" s="59" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -3563,40 +3554,40 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="62" t="inlineStr">
+      <c r="A38" s="57" t="inlineStr">
         <is>
           <t>5800961074</t>
         </is>
       </c>
-      <c r="B38" s="62" t="inlineStr">
+      <c r="B38" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C38" s="63" t="inlineStr">
+      <c r="C38" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00221/2025</t>
         </is>
       </c>
-      <c r="D38" s="62" t="inlineStr">
+      <c r="D38" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E38" s="62" t="n">
+      <c r="E38" s="57" t="n">
         <v>214</v>
       </c>
-      <c r="G38" s="62" t="inlineStr">
+      <c r="G38" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H38" s="63" t="inlineStr">
+      <c r="H38" s="58" t="inlineStr">
         <is>
           <t>Dianopolis</t>
         </is>
       </c>
-      <c r="I38" s="63" t="inlineStr">
+      <c r="I38" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3608,40 +3599,40 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="62" t="inlineStr">
+      <c r="A39" s="57" t="inlineStr">
         <is>
           <t>7925087021</t>
         </is>
       </c>
-      <c r="B39" s="62" t="inlineStr">
+      <c r="B39" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C39" s="63" t="inlineStr">
+      <c r="C39" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00222/2025</t>
         </is>
       </c>
-      <c r="D39" s="62" t="inlineStr">
+      <c r="D39" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E39" s="62" t="n">
+      <c r="E39" s="57" t="n">
         <v>211</v>
       </c>
-      <c r="G39" s="62" t="inlineStr">
+      <c r="G39" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H39" s="63" t="inlineStr">
+      <c r="H39" s="58" t="inlineStr">
         <is>
           <t>Parana</t>
         </is>
       </c>
-      <c r="I39" s="63" t="inlineStr">
+      <c r="I39" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3653,40 +3644,40 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="62" t="inlineStr">
+      <c r="A40" s="57" t="inlineStr">
         <is>
           <t>5862236091</t>
         </is>
       </c>
-      <c r="B40" s="62" t="inlineStr">
+      <c r="B40" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C40" s="63" t="inlineStr">
+      <c r="C40" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00223/2025</t>
         </is>
       </c>
-      <c r="D40" s="62" t="inlineStr">
+      <c r="D40" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="62" t="n">
+      <c r="E40" s="57" t="n">
         <v>211</v>
       </c>
-      <c r="G40" s="62" t="inlineStr">
+      <c r="G40" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H40" s="63" t="inlineStr">
+      <c r="H40" s="58" t="inlineStr">
         <is>
           <t>Almas</t>
         </is>
       </c>
-      <c r="I40" s="63" t="inlineStr">
+      <c r="I40" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3698,40 +3689,40 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="62" t="inlineStr">
+      <c r="A41" s="57" t="inlineStr">
         <is>
           <t>7933585074</t>
         </is>
       </c>
-      <c r="B41" s="62" t="inlineStr">
+      <c r="B41" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C41" s="63" t="inlineStr">
+      <c r="C41" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00024/2026</t>
         </is>
       </c>
-      <c r="D41" s="62" t="inlineStr">
+      <c r="D41" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E41" s="62" t="n">
+      <c r="E41" s="57" t="n">
         <v>161</v>
       </c>
-      <c r="G41" s="62" t="inlineStr">
+      <c r="G41" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H41" s="63" t="inlineStr">
+      <c r="H41" s="58" t="inlineStr">
         <is>
           <t>Dianopolis</t>
         </is>
       </c>
-      <c r="I41" s="63" t="inlineStr">
+      <c r="I41" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3743,40 +3734,40 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="62" t="inlineStr">
+      <c r="A42" s="57" t="inlineStr">
         <is>
           <t>7927646026</t>
         </is>
       </c>
-      <c r="B42" s="62" t="inlineStr">
+      <c r="B42" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C42" s="63" t="inlineStr">
+      <c r="C42" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00029/2026</t>
         </is>
       </c>
-      <c r="D42" s="62" t="inlineStr">
+      <c r="D42" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E42" s="62" t="n">
+      <c r="E42" s="57" t="n">
         <v>154</v>
       </c>
-      <c r="G42" s="62" t="inlineStr">
+      <c r="G42" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H42" s="63" t="inlineStr">
+      <c r="H42" s="58" t="inlineStr">
         <is>
           <t>Ponte Alta Tocantins</t>
         </is>
       </c>
-      <c r="I42" s="63" t="inlineStr">
+      <c r="I42" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3788,40 +3779,40 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="62" t="inlineStr">
+      <c r="A43" s="57" t="inlineStr">
         <is>
           <t>7931608059</t>
         </is>
       </c>
-      <c r="B43" s="62" t="inlineStr">
+      <c r="B43" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C43" s="63" t="inlineStr">
+      <c r="C43" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00040/2026</t>
         </is>
       </c>
-      <c r="D43" s="62" t="inlineStr">
+      <c r="D43" s="57" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E43" s="62" t="n">
+      <c r="E43" s="57" t="n">
         <v>133</v>
       </c>
-      <c r="G43" s="62" t="inlineStr">
+      <c r="G43" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H43" s="63" t="inlineStr">
+      <c r="H43" s="58" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I43" s="63" t="inlineStr">
+      <c r="I43" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3833,40 +3824,40 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="62" t="inlineStr">
+      <c r="A44" s="57" t="inlineStr">
         <is>
           <t>7908249152</t>
         </is>
       </c>
-      <c r="B44" s="62" t="inlineStr">
+      <c r="B44" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C44" s="63" t="inlineStr">
+      <c r="C44" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00038/2026</t>
         </is>
       </c>
-      <c r="D44" s="62" t="inlineStr">
+      <c r="D44" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E44" s="62" t="n">
+      <c r="E44" s="57" t="n">
         <v>133</v>
       </c>
-      <c r="G44" s="62" t="inlineStr">
+      <c r="G44" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H44" s="63" t="inlineStr">
+      <c r="H44" s="58" t="inlineStr">
         <is>
           <t>Santa Rosa Do Tocantins</t>
         </is>
       </c>
-      <c r="I44" s="63" t="inlineStr">
+      <c r="I44" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3878,40 +3869,40 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="62" t="inlineStr">
+      <c r="A45" s="57" t="inlineStr">
         <is>
           <t>7927396052</t>
         </is>
       </c>
-      <c r="B45" s="62" t="inlineStr">
+      <c r="B45" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C45" s="63" t="inlineStr">
+      <c r="C45" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00045/2026</t>
         </is>
       </c>
-      <c r="D45" s="62" t="inlineStr">
+      <c r="D45" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E45" s="62" t="n">
+      <c r="E45" s="57" t="n">
         <v>127</v>
       </c>
-      <c r="G45" s="62" t="inlineStr">
+      <c r="G45" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H45" s="63" t="inlineStr">
+      <c r="H45" s="58" t="inlineStr">
         <is>
           <t>Formoso Do Araguaia</t>
         </is>
       </c>
-      <c r="I45" s="63" t="inlineStr">
+      <c r="I45" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3923,40 +3914,40 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="62" t="inlineStr">
+      <c r="A46" s="57" t="inlineStr">
         <is>
           <t>7925871077</t>
         </is>
       </c>
-      <c r="B46" s="62" t="inlineStr">
+      <c r="B46" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C46" s="63" t="inlineStr">
+      <c r="C46" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00048/2026</t>
         </is>
       </c>
-      <c r="D46" s="62" t="inlineStr">
+      <c r="D46" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E46" s="62" t="n">
+      <c r="E46" s="57" t="n">
         <v>113</v>
       </c>
-      <c r="G46" s="62" t="inlineStr">
+      <c r="G46" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H46" s="63" t="inlineStr">
+      <c r="H46" s="58" t="inlineStr">
         <is>
           <t>Goiatins</t>
         </is>
       </c>
-      <c r="I46" s="63" t="inlineStr">
+      <c r="I46" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -3968,40 +3959,40 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="62" t="inlineStr">
+      <c r="A47" s="57" t="inlineStr">
         <is>
           <t>7953610256</t>
         </is>
       </c>
-      <c r="B47" s="62" t="inlineStr">
+      <c r="B47" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C47" s="63" t="inlineStr">
+      <c r="C47" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00050/2026</t>
         </is>
       </c>
-      <c r="D47" s="62" t="inlineStr">
+      <c r="D47" s="57" t="inlineStr">
         <is>
           <t>Muito Alto</t>
         </is>
       </c>
-      <c r="E47" s="62" t="n">
+      <c r="E47" s="57" t="n">
         <v>111</v>
       </c>
-      <c r="G47" s="62" t="inlineStr">
+      <c r="G47" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H47" s="63" t="inlineStr">
+      <c r="H47" s="58" t="inlineStr">
         <is>
           <t>Mateiros</t>
         </is>
       </c>
-      <c r="I47" s="63" t="inlineStr">
+      <c r="I47" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4013,40 +4004,40 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="62" t="inlineStr">
+      <c r="A48" s="57" t="inlineStr">
         <is>
           <t>7926442035</t>
         </is>
       </c>
-      <c r="B48" s="62" t="inlineStr">
+      <c r="B48" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C48" s="63" t="inlineStr">
+      <c r="C48" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00051/2026</t>
         </is>
       </c>
-      <c r="D48" s="62" t="inlineStr">
+      <c r="D48" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E48" s="62" t="n">
+      <c r="E48" s="57" t="n">
         <v>111</v>
       </c>
-      <c r="G48" s="62" t="inlineStr">
+      <c r="G48" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H48" s="63" t="inlineStr">
+      <c r="H48" s="58" t="inlineStr">
         <is>
           <t>Monte Do Carmo</t>
         </is>
       </c>
-      <c r="I48" s="63" t="inlineStr">
+      <c r="I48" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4058,40 +4049,40 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="62" t="inlineStr">
+      <c r="A49" s="57" t="inlineStr">
         <is>
           <t>7925744087</t>
         </is>
       </c>
-      <c r="B49" s="62" t="inlineStr">
+      <c r="B49" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C49" s="63" t="inlineStr">
+      <c r="C49" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00059/2026</t>
         </is>
       </c>
-      <c r="D49" s="62" t="inlineStr">
+      <c r="D49" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E49" s="62" t="n">
+      <c r="E49" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G49" s="62" t="inlineStr">
+      <c r="G49" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H49" s="63" t="inlineStr">
+      <c r="H49" s="58" t="inlineStr">
         <is>
           <t>Goianorte</t>
         </is>
       </c>
-      <c r="I49" s="63" t="inlineStr">
+      <c r="I49" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4103,40 +4094,40 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="62" t="inlineStr">
+      <c r="A50" s="57" t="inlineStr">
         <is>
           <t>7925733015</t>
         </is>
       </c>
-      <c r="B50" s="62" t="inlineStr">
+      <c r="B50" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C50" s="63" t="inlineStr">
+      <c r="C50" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00058/2026</t>
         </is>
       </c>
-      <c r="D50" s="62" t="inlineStr">
+      <c r="D50" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E50" s="62" t="n">
+      <c r="E50" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G50" s="62" t="inlineStr">
+      <c r="G50" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H50" s="63" t="inlineStr">
+      <c r="H50" s="58" t="inlineStr">
         <is>
           <t>Pedro Afonso</t>
         </is>
       </c>
-      <c r="I50" s="63" t="inlineStr">
+      <c r="I50" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4148,40 +4139,40 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="62" t="inlineStr">
+      <c r="A51" s="57" t="inlineStr">
         <is>
           <t>7901110084</t>
         </is>
       </c>
-      <c r="B51" s="62" t="inlineStr">
+      <c r="B51" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C51" s="63" t="inlineStr">
+      <c r="C51" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00061/2026</t>
         </is>
       </c>
-      <c r="D51" s="62" t="inlineStr">
+      <c r="D51" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E51" s="62" t="n">
+      <c r="E51" s="57" t="n">
         <v>98</v>
       </c>
-      <c r="G51" s="62" t="inlineStr">
+      <c r="G51" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H51" s="63" t="inlineStr">
+      <c r="H51" s="58" t="inlineStr">
         <is>
           <t>Divinopolis</t>
         </is>
       </c>
-      <c r="I51" s="63" t="inlineStr">
+      <c r="I51" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4193,40 +4184,40 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="62" t="inlineStr">
+      <c r="A52" s="57" t="inlineStr">
         <is>
           <t>7944559149</t>
         </is>
       </c>
-      <c r="B52" s="62" t="inlineStr">
+      <c r="B52" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C52" s="63" t="inlineStr">
+      <c r="C52" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00063/2026</t>
         </is>
       </c>
-      <c r="D52" s="62" t="inlineStr">
+      <c r="D52" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E52" s="62" t="n">
+      <c r="E52" s="57" t="n">
         <v>98</v>
       </c>
-      <c r="G52" s="62" t="inlineStr">
+      <c r="G52" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H52" s="63" t="inlineStr">
+      <c r="H52" s="58" t="inlineStr">
         <is>
           <t>Caseara</t>
         </is>
       </c>
-      <c r="I52" s="63" t="inlineStr">
+      <c r="I52" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4238,40 +4229,40 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="62" t="inlineStr">
+      <c r="A53" s="57" t="inlineStr">
         <is>
           <t>5800291035</t>
         </is>
       </c>
-      <c r="B53" s="62" t="inlineStr">
+      <c r="B53" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C53" s="63" t="inlineStr">
+      <c r="C53" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-PO 00097/2026</t>
         </is>
       </c>
-      <c r="D53" s="62" t="inlineStr">
+      <c r="D53" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E53" s="62" t="n">
+      <c r="E53" s="57" t="n">
         <v>98</v>
       </c>
-      <c r="G53" s="62" t="inlineStr">
+      <c r="G53" s="57" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H53" s="63" t="inlineStr">
+      <c r="H53" s="58" t="inlineStr">
         <is>
           <t>Monte Do Carmo</t>
         </is>
       </c>
-      <c r="I53" s="64" t="inlineStr">
+      <c r="I53" s="59" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -4283,40 +4274,40 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="62" t="inlineStr">
+      <c r="A54" s="57" t="inlineStr">
         <is>
           <t>7919270014</t>
         </is>
       </c>
-      <c r="B54" s="62" t="inlineStr">
+      <c r="B54" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C54" s="63" t="inlineStr">
+      <c r="C54" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00074/2026</t>
         </is>
       </c>
-      <c r="D54" s="62" t="inlineStr">
+      <c r="D54" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E54" s="62" t="n">
+      <c r="E54" s="57" t="n">
         <v>82</v>
       </c>
-      <c r="G54" s="62" t="inlineStr">
+      <c r="G54" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H54" s="63" t="inlineStr">
+      <c r="H54" s="58" t="inlineStr">
         <is>
           <t>Pium</t>
         </is>
       </c>
-      <c r="I54" s="63" t="inlineStr">
+      <c r="I54" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4328,40 +4319,40 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="62" t="inlineStr">
+      <c r="A55" s="57" t="inlineStr">
         <is>
           <t>5801866013</t>
         </is>
       </c>
-      <c r="B55" s="62" t="inlineStr">
+      <c r="B55" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C55" s="63" t="inlineStr">
+      <c r="C55" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00077/2026</t>
         </is>
       </c>
-      <c r="D55" s="62" t="inlineStr">
+      <c r="D55" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E55" s="62" t="n">
+      <c r="E55" s="57" t="n">
         <v>79</v>
       </c>
-      <c r="G55" s="62" t="inlineStr">
+      <c r="G55" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H55" s="63" t="inlineStr">
+      <c r="H55" s="58" t="inlineStr">
         <is>
           <t>Paraiso Do Tocantins</t>
         </is>
       </c>
-      <c r="I55" s="63" t="inlineStr">
+      <c r="I55" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4373,40 +4364,40 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="62" t="inlineStr">
+      <c r="A56" s="57" t="inlineStr">
         <is>
           <t>7926089013</t>
         </is>
       </c>
-      <c r="B56" s="62" t="inlineStr">
+      <c r="B56" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C56" s="63" t="inlineStr">
+      <c r="C56" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00078/2026</t>
         </is>
       </c>
-      <c r="D56" s="62" t="inlineStr">
+      <c r="D56" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E56" s="62" t="n">
+      <c r="E56" s="57" t="n">
         <v>76</v>
       </c>
-      <c r="G56" s="62" t="inlineStr">
+      <c r="G56" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H56" s="63" t="inlineStr">
+      <c r="H56" s="58" t="inlineStr">
         <is>
           <t>Paraiso Do Tocantins</t>
         </is>
       </c>
-      <c r="I56" s="63" t="inlineStr">
+      <c r="I56" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4418,40 +4409,40 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="62" t="inlineStr">
+      <c r="A57" s="57" t="inlineStr">
         <is>
           <t>7900573047</t>
         </is>
       </c>
-      <c r="B57" s="62" t="inlineStr">
+      <c r="B57" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C57" s="63" t="inlineStr">
+      <c r="C57" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00080/2026</t>
         </is>
       </c>
-      <c r="D57" s="62" t="inlineStr">
+      <c r="D57" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E57" s="62" t="n">
+      <c r="E57" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="G57" s="62" t="inlineStr">
+      <c r="G57" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H57" s="63" t="inlineStr">
+      <c r="H57" s="58" t="inlineStr">
         <is>
           <t>Figueiropolis</t>
         </is>
       </c>
-      <c r="I57" s="63" t="inlineStr">
+      <c r="I57" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4463,40 +4454,40 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="62" t="inlineStr">
+      <c r="A58" s="57" t="inlineStr">
         <is>
           <t>7927413001</t>
         </is>
       </c>
-      <c r="B58" s="62" t="inlineStr">
+      <c r="B58" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C58" s="63" t="inlineStr">
+      <c r="C58" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-PO 00118/2026</t>
         </is>
       </c>
-      <c r="D58" s="62" t="inlineStr">
+      <c r="D58" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E58" s="62" t="n">
+      <c r="E58" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="G58" s="62" t="inlineStr">
+      <c r="G58" s="57" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H58" s="63" t="inlineStr">
+      <c r="H58" s="58" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I58" s="64" t="inlineStr">
+      <c r="I58" s="59" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -4508,40 +4499,40 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="62" t="inlineStr">
+      <c r="A59" s="57" t="inlineStr">
         <is>
           <t>7908686014</t>
         </is>
       </c>
-      <c r="B59" s="62" t="inlineStr">
+      <c r="B59" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C59" s="63" t="inlineStr">
+      <c r="C59" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00086/2026</t>
         </is>
       </c>
-      <c r="D59" s="62" t="inlineStr">
+      <c r="D59" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E59" s="62" t="n">
+      <c r="E59" s="57" t="n">
         <v>74</v>
       </c>
-      <c r="G59" s="62" t="inlineStr">
+      <c r="G59" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H59" s="63" t="inlineStr">
+      <c r="H59" s="58" t="inlineStr">
         <is>
           <t>Pium</t>
         </is>
       </c>
-      <c r="I59" s="63" t="inlineStr">
+      <c r="I59" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4553,40 +4544,40 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="62" t="inlineStr">
+      <c r="A60" s="57" t="inlineStr">
         <is>
           <t>7900117013</t>
         </is>
       </c>
-      <c r="B60" s="62" t="inlineStr">
+      <c r="B60" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C60" s="63" t="inlineStr">
+      <c r="C60" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00084/2026</t>
         </is>
       </c>
-      <c r="D60" s="62" t="inlineStr">
+      <c r="D60" s="57" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E60" s="62" t="n">
+      <c r="E60" s="57" t="n">
         <v>74</v>
       </c>
-      <c r="G60" s="62" t="inlineStr">
+      <c r="G60" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H60" s="63" t="inlineStr">
+      <c r="H60" s="58" t="inlineStr">
         <is>
           <t>Paraiso Do Tocantins</t>
         </is>
       </c>
-      <c r="I60" s="63" t="inlineStr">
+      <c r="I60" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4598,40 +4589,40 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="62" t="inlineStr">
+      <c r="A61" s="57" t="inlineStr">
         <is>
           <t>7900453110</t>
         </is>
       </c>
-      <c r="B61" s="62" t="inlineStr">
+      <c r="B61" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C61" s="63" t="inlineStr">
+      <c r="C61" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00087/2026</t>
         </is>
       </c>
-      <c r="D61" s="62" t="inlineStr">
+      <c r="D61" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E61" s="62" t="n">
+      <c r="E61" s="57" t="n">
         <v>71</v>
       </c>
-      <c r="G61" s="62" t="inlineStr">
+      <c r="G61" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H61" s="63" t="inlineStr">
+      <c r="H61" s="58" t="inlineStr">
         <is>
           <t>Santa Rita Do Tocantins</t>
         </is>
       </c>
-      <c r="I61" s="63" t="inlineStr">
+      <c r="I61" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4643,40 +4634,40 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="62" t="inlineStr">
+      <c r="A62" s="57" t="inlineStr">
         <is>
           <t>5865120195</t>
         </is>
       </c>
-      <c r="B62" s="62" t="inlineStr">
+      <c r="B62" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C62" s="63" t="inlineStr">
+      <c r="C62" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-GR 00538/2026</t>
         </is>
       </c>
-      <c r="D62" s="62" t="inlineStr">
+      <c r="D62" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E62" s="62" t="n">
+      <c r="E62" s="57" t="n">
         <v>51</v>
       </c>
-      <c r="G62" s="62" t="inlineStr">
+      <c r="G62" s="57" t="inlineStr">
         <is>
           <t>COCM-N</t>
         </is>
       </c>
-      <c r="H62" s="63" t="inlineStr">
+      <c r="H62" s="58" t="inlineStr">
         <is>
           <t>Centenario</t>
         </is>
       </c>
-      <c r="I62" s="64" t="inlineStr">
+      <c r="I62" s="59" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -4688,40 +4679,40 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="62" t="inlineStr">
+      <c r="A63" s="57" t="inlineStr">
         <is>
           <t>5836786094</t>
         </is>
       </c>
-      <c r="B63" s="62" t="inlineStr">
+      <c r="B63" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C63" s="63" t="inlineStr">
+      <c r="C63" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00095/2026</t>
         </is>
       </c>
-      <c r="D63" s="62" t="inlineStr">
+      <c r="D63" s="57" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E63" s="62" t="n">
+      <c r="E63" s="57" t="n">
         <v>50</v>
       </c>
-      <c r="G63" s="62" t="inlineStr">
+      <c r="G63" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H63" s="63" t="inlineStr">
+      <c r="H63" s="58" t="inlineStr">
         <is>
           <t>Peixe</t>
         </is>
       </c>
-      <c r="I63" s="63" t="inlineStr">
+      <c r="I63" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4733,40 +4724,40 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="62" t="inlineStr">
+      <c r="A64" s="57" t="inlineStr">
         <is>
           <t>7900594026</t>
         </is>
       </c>
-      <c r="B64" s="62" t="inlineStr">
+      <c r="B64" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C64" s="63" t="inlineStr">
+      <c r="C64" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00113/2026</t>
         </is>
       </c>
-      <c r="D64" s="62" t="inlineStr">
+      <c r="D64" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E64" s="62" t="n">
+      <c r="E64" s="57" t="n">
         <v>27</v>
       </c>
-      <c r="G64" s="62" t="inlineStr">
+      <c r="G64" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H64" s="63" t="inlineStr">
+      <c r="H64" s="58" t="inlineStr">
         <is>
           <t>Ponte Alta Tocantins</t>
         </is>
       </c>
-      <c r="I64" s="63" t="inlineStr">
+      <c r="I64" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4778,40 +4769,40 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="62" t="inlineStr">
+      <c r="A65" s="57" t="inlineStr">
         <is>
           <t>7913662076</t>
         </is>
       </c>
-      <c r="B65" s="62" t="inlineStr">
+      <c r="B65" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C65" s="63" t="inlineStr">
+      <c r="C65" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00114/2026</t>
         </is>
       </c>
-      <c r="D65" s="62" t="inlineStr">
+      <c r="D65" s="57" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E65" s="62" t="n">
+      <c r="E65" s="57" t="n">
         <v>27</v>
       </c>
-      <c r="G65" s="62" t="inlineStr">
+      <c r="G65" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H65" s="63" t="inlineStr">
+      <c r="H65" s="58" t="inlineStr">
         <is>
           <t>Duere</t>
         </is>
       </c>
-      <c r="I65" s="63" t="inlineStr">
+      <c r="I65" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4823,40 +4814,40 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="62" t="inlineStr">
+      <c r="A66" s="57" t="inlineStr">
         <is>
           <t>5800859011</t>
         </is>
       </c>
-      <c r="B66" s="62" t="inlineStr">
+      <c r="B66" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C66" s="63" t="inlineStr">
+      <c r="C66" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00115/2026</t>
         </is>
       </c>
-      <c r="D66" s="62" t="inlineStr">
+      <c r="D66" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E66" s="62" t="n">
+      <c r="E66" s="57" t="n">
         <v>25</v>
       </c>
-      <c r="G66" s="62" t="inlineStr">
+      <c r="G66" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H66" s="63" t="inlineStr">
+      <c r="H66" s="58" t="inlineStr">
         <is>
           <t>Tupirama</t>
         </is>
       </c>
-      <c r="I66" s="63" t="inlineStr">
+      <c r="I66" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4868,40 +4859,40 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="62" t="inlineStr">
+      <c r="A67" s="57" t="inlineStr">
         <is>
           <t>5800090147</t>
         </is>
       </c>
-      <c r="B67" s="62" t="inlineStr">
+      <c r="B67" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C67" s="63" t="inlineStr">
+      <c r="C67" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00117/2026</t>
         </is>
       </c>
-      <c r="D67" s="62" t="inlineStr">
+      <c r="D67" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E67" s="62" t="n">
+      <c r="E67" s="57" t="n">
         <v>22</v>
       </c>
-      <c r="G67" s="62" t="inlineStr">
+      <c r="G67" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H67" s="63" t="inlineStr">
+      <c r="H67" s="58" t="inlineStr">
         <is>
           <t>Taipas Do Tocantins</t>
         </is>
       </c>
-      <c r="I67" s="63" t="inlineStr">
+      <c r="I67" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -4913,40 +4904,40 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="62" t="inlineStr">
+      <c r="A68" s="57" t="inlineStr">
         <is>
           <t>5856156091</t>
         </is>
       </c>
-      <c r="B68" s="62" t="inlineStr">
+      <c r="B68" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C68" s="63" t="inlineStr">
+      <c r="C68" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-DP 00403/2026</t>
         </is>
       </c>
-      <c r="D68" s="62" t="inlineStr">
+      <c r="D68" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E68" s="62" t="n">
+      <c r="E68" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="G68" s="62" t="inlineStr">
+      <c r="G68" s="57" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H68" s="63" t="inlineStr">
+      <c r="H68" s="58" t="inlineStr">
         <is>
           <t>Almas</t>
         </is>
       </c>
-      <c r="I68" s="64" t="inlineStr">
+      <c r="I68" s="59" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -4958,40 +4949,40 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="62" t="inlineStr">
+      <c r="A69" s="57" t="inlineStr">
         <is>
           <t>5827102054</t>
         </is>
       </c>
-      <c r="B69" s="62" t="inlineStr">
+      <c r="B69" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C69" s="63" t="inlineStr">
+      <c r="C69" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-PS 00289/2026</t>
         </is>
       </c>
-      <c r="D69" s="62" t="inlineStr">
+      <c r="D69" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E69" s="62" t="n">
+      <c r="E69" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="G69" s="62" t="inlineStr">
+      <c r="G69" s="57" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H69" s="63" t="inlineStr">
+      <c r="H69" s="58" t="inlineStr">
         <is>
           <t>Pugmil</t>
         </is>
       </c>
-      <c r="I69" s="63" t="inlineStr">
+      <c r="I69" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5003,40 +4994,40 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="62" t="inlineStr">
+      <c r="A70" s="57" t="inlineStr">
         <is>
           <t>5846328094</t>
         </is>
       </c>
-      <c r="B70" s="62" t="inlineStr">
+      <c r="B70" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C70" s="63" t="inlineStr">
+      <c r="C70" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-GU 00687/2026</t>
         </is>
       </c>
-      <c r="D70" s="62" t="inlineStr">
+      <c r="D70" s="57" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E70" s="62" t="n">
+      <c r="E70" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="G70" s="62" t="inlineStr">
+      <c r="G70" s="57" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H70" s="63" t="inlineStr">
+      <c r="H70" s="58" t="inlineStr">
         <is>
           <t>Peixe</t>
         </is>
       </c>
-      <c r="I70" s="64" t="inlineStr">
+      <c r="I70" s="59" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -5048,40 +5039,40 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="62" t="inlineStr">
+      <c r="A71" s="57" t="inlineStr">
         <is>
           <t>7942572059</t>
         </is>
       </c>
-      <c r="B71" s="62" t="inlineStr">
+      <c r="B71" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C71" s="63" t="inlineStr">
+      <c r="C71" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00427/2026</t>
         </is>
       </c>
-      <c r="D71" s="62" t="inlineStr">
+      <c r="D71" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E71" s="62" t="n">
+      <c r="E71" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="G71" s="62" t="inlineStr">
+      <c r="G71" s="57" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H71" s="63" t="inlineStr">
+      <c r="H71" s="58" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I71" s="64" t="inlineStr">
+      <c r="I71" s="59" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -5093,40 +5084,40 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="62" t="inlineStr">
+      <c r="A72" s="57" t="inlineStr">
         <is>
           <t>7929376022</t>
         </is>
       </c>
-      <c r="B72" s="62" t="inlineStr">
+      <c r="B72" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C72" s="63" t="inlineStr">
+      <c r="C72" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00120/2026</t>
         </is>
       </c>
-      <c r="D72" s="62" t="inlineStr">
+      <c r="D72" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E72" s="62" t="n">
+      <c r="E72" s="57" t="n">
         <v>7</v>
       </c>
-      <c r="G72" s="62" t="inlineStr">
+      <c r="G72" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H72" s="63" t="inlineStr">
+      <c r="H72" s="58" t="inlineStr">
         <is>
           <t>Babaculandia</t>
         </is>
       </c>
-      <c r="I72" s="63" t="inlineStr">
+      <c r="I72" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5138,40 +5129,40 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="62" t="inlineStr">
+      <c r="A73" s="57" t="inlineStr">
         <is>
           <t>5800438116</t>
         </is>
       </c>
-      <c r="B73" s="62" t="inlineStr">
+      <c r="B73" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C73" s="63" t="inlineStr">
+      <c r="C73" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-DP 00404/2026</t>
         </is>
       </c>
-      <c r="D73" s="62" t="inlineStr">
+      <c r="D73" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E73" s="62" t="n">
+      <c r="E73" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="G73" s="62" t="inlineStr">
+      <c r="G73" s="57" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H73" s="63" t="inlineStr">
+      <c r="H73" s="58" t="inlineStr">
         <is>
           <t>Chapada Da Natividade</t>
         </is>
       </c>
-      <c r="I73" s="63" t="inlineStr">
+      <c r="I73" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5183,40 +5174,40 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="62" t="inlineStr">
+      <c r="A74" s="57" t="inlineStr">
         <is>
           <t>5803327001</t>
         </is>
       </c>
-      <c r="B74" s="62" t="inlineStr">
+      <c r="B74" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C74" s="63" t="inlineStr">
+      <c r="C74" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00434/2026</t>
         </is>
       </c>
-      <c r="D74" s="62" t="inlineStr">
+      <c r="D74" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E74" s="62" t="n">
+      <c r="E74" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="G74" s="62" t="inlineStr">
+      <c r="G74" s="57" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H74" s="63" t="inlineStr">
+      <c r="H74" s="58" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I74" s="64" t="inlineStr">
+      <c r="I74" s="59" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -5228,40 +5219,40 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="62" t="inlineStr">
+      <c r="A75" s="57" t="inlineStr">
         <is>
           <t>7933766059</t>
         </is>
       </c>
-      <c r="B75" s="62" t="inlineStr">
+      <c r="B75" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C75" s="63" t="inlineStr">
+      <c r="C75" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00431/2026</t>
         </is>
       </c>
-      <c r="D75" s="62" t="inlineStr">
+      <c r="D75" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E75" s="62" t="n">
+      <c r="E75" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="G75" s="62" t="inlineStr">
+      <c r="G75" s="57" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H75" s="63" t="inlineStr">
+      <c r="H75" s="58" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I75" s="63" t="inlineStr">
+      <c r="I75" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5273,40 +5264,40 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="62" t="inlineStr">
+      <c r="A76" s="57" t="inlineStr">
         <is>
           <t>7931610122</t>
         </is>
       </c>
-      <c r="B76" s="62" t="inlineStr">
+      <c r="B76" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C76" s="63" t="inlineStr">
+      <c r="C76" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00433/2026</t>
         </is>
       </c>
-      <c r="D76" s="62" t="inlineStr">
+      <c r="D76" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E76" s="62" t="n">
+      <c r="E76" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="G76" s="62" t="inlineStr">
+      <c r="G76" s="57" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H76" s="63" t="inlineStr">
+      <c r="H76" s="58" t="inlineStr">
         <is>
           <t>Palmas</t>
         </is>
       </c>
-      <c r="I76" s="63" t="inlineStr">
+      <c r="I76" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5318,40 +5309,40 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="62" t="inlineStr">
+      <c r="A77" s="57" t="inlineStr">
         <is>
           <t>7927169001</t>
         </is>
       </c>
-      <c r="B77" s="62" t="inlineStr">
+      <c r="B77" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C77" s="63" t="inlineStr">
+      <c r="C77" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-PA 00432/2026</t>
         </is>
       </c>
-      <c r="D77" s="62" t="inlineStr">
+      <c r="D77" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E77" s="62" t="n">
+      <c r="E77" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="G77" s="62" t="inlineStr">
+      <c r="G77" s="57" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H77" s="63" t="inlineStr">
+      <c r="H77" s="58" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="I77" s="63" t="inlineStr">
+      <c r="I77" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5363,40 +5354,40 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="62" t="inlineStr">
+      <c r="A78" s="57" t="inlineStr">
         <is>
           <t>7933726256</t>
         </is>
       </c>
-      <c r="B78" s="62" t="inlineStr">
+      <c r="B78" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C78" s="63" t="inlineStr">
+      <c r="C78" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-PO 00181/2026</t>
         </is>
       </c>
-      <c r="D78" s="62" t="inlineStr">
+      <c r="D78" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E78" s="62" t="n">
+      <c r="E78" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="G78" s="62" t="inlineStr">
+      <c r="G78" s="57" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H78" s="63" t="inlineStr">
+      <c r="H78" s="58" t="inlineStr">
         <is>
           <t>Mateiros</t>
         </is>
       </c>
-      <c r="I78" s="63" t="inlineStr">
+      <c r="I78" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5408,40 +5399,40 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="62" t="inlineStr">
+      <c r="A79" s="57" t="inlineStr">
         <is>
           <t>7911120026</t>
         </is>
       </c>
-      <c r="B79" s="62" t="inlineStr">
+      <c r="B79" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C79" s="63" t="inlineStr">
+      <c r="C79" s="58" t="inlineStr">
         <is>
           <t>DG-RD-PO 00444/2026</t>
         </is>
       </c>
-      <c r="D79" s="62" t="inlineStr">
+      <c r="D79" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E79" s="62" t="n">
+      <c r="E79" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="G79" s="62" t="inlineStr">
+      <c r="G79" s="57" t="inlineStr">
         <is>
           <t>COCM-C</t>
         </is>
       </c>
-      <c r="H79" s="63" t="inlineStr">
+      <c r="H79" s="58" t="inlineStr">
         <is>
           <t>Ponte Alta Tocantins</t>
         </is>
       </c>
-      <c r="I79" s="64" t="inlineStr">
+      <c r="I79" s="59" t="inlineStr">
         <is>
           <t>Só no Mapeamento Criticidades</t>
         </is>
@@ -5453,40 +5444,40 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="62" t="inlineStr">
+      <c r="A80" s="57" t="inlineStr">
         <is>
           <t>7908705049</t>
         </is>
       </c>
-      <c r="B80" s="62" t="inlineStr">
+      <c r="B80" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C80" s="63" t="inlineStr">
+      <c r="C80" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-DP 00409/2026</t>
         </is>
       </c>
-      <c r="D80" s="62" t="inlineStr">
+      <c r="D80" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E80" s="62" t="n">
+      <c r="E80" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="G80" s="62" t="inlineStr">
+      <c r="G80" s="57" t="inlineStr">
         <is>
           <t>COCM-S</t>
         </is>
       </c>
-      <c r="H80" s="63" t="inlineStr">
+      <c r="H80" s="58" t="inlineStr">
         <is>
           <t>Aurora Do Tocantins</t>
         </is>
       </c>
-      <c r="I80" s="63" t="inlineStr">
+      <c r="I80" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5498,40 +5489,40 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="62" t="inlineStr">
+      <c r="A81" s="57" t="inlineStr">
         <is>
           <t>7900230155</t>
         </is>
       </c>
-      <c r="B81" s="62" t="inlineStr">
+      <c r="B81" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C81" s="63" t="inlineStr">
+      <c r="C81" s="58" t="inlineStr">
         <is>
           <t>ETO-RD-GR 00685/2026</t>
         </is>
       </c>
-      <c r="D81" s="62" t="inlineStr">
+      <c r="D81" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E81" s="62" t="n">
+      <c r="E81" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G81" s="62" t="inlineStr">
+      <c r="G81" s="57" t="inlineStr">
         <is>
           <t>COCM-N</t>
         </is>
       </c>
-      <c r="H81" s="63" t="inlineStr">
+      <c r="H81" s="58" t="inlineStr">
         <is>
           <t>Palmeirante</t>
         </is>
       </c>
-      <c r="I81" s="63" t="inlineStr">
+      <c r="I81" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5543,40 +5534,40 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="62" t="inlineStr">
+      <c r="A82" s="57" t="inlineStr">
         <is>
           <t>7928564039</t>
         </is>
       </c>
-      <c r="B82" s="62" t="inlineStr">
+      <c r="B82" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C82" s="63" t="inlineStr">
+      <c r="C82" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00123/2026</t>
         </is>
       </c>
-      <c r="D82" s="62" t="inlineStr">
+      <c r="D82" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E82" s="62" t="n">
+      <c r="E82" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="62" t="inlineStr">
+      <c r="G82" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H82" s="63" t="inlineStr">
+      <c r="H82" s="58" t="inlineStr">
         <is>
           <t>Araguatins</t>
         </is>
       </c>
-      <c r="I82" s="63" t="inlineStr">
+      <c r="I82" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5588,40 +5579,40 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="62" t="inlineStr">
+      <c r="A83" s="57" t="inlineStr">
         <is>
           <t>7928241200</t>
         </is>
       </c>
-      <c r="B83" s="62" t="inlineStr">
+      <c r="B83" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C83" s="63" t="inlineStr">
+      <c r="C83" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00128/2026</t>
         </is>
       </c>
-      <c r="D83" s="62" t="inlineStr">
+      <c r="D83" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E83" s="62" t="n">
+      <c r="E83" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G83" s="62" t="inlineStr">
+      <c r="G83" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H83" s="63" t="inlineStr">
+      <c r="H83" s="58" t="inlineStr">
         <is>
           <t>Sao Salvador Do Tocantins</t>
         </is>
       </c>
-      <c r="I83" s="63" t="inlineStr">
+      <c r="I83" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5633,40 +5624,40 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="62" t="inlineStr">
+      <c r="A84" s="57" t="inlineStr">
         <is>
           <t>5856070091</t>
         </is>
       </c>
-      <c r="B84" s="62" t="inlineStr">
+      <c r="B84" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C84" s="63" t="inlineStr">
+      <c r="C84" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00130/2026</t>
         </is>
       </c>
-      <c r="D84" s="62" t="inlineStr">
+      <c r="D84" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E84" s="62" t="n">
+      <c r="E84" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G84" s="62" t="inlineStr">
+      <c r="G84" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H84" s="63" t="inlineStr">
+      <c r="H84" s="58" t="inlineStr">
         <is>
           <t>Almas</t>
         </is>
       </c>
-      <c r="I84" s="63" t="inlineStr">
+      <c r="I84" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5678,40 +5669,40 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="62" t="inlineStr">
+      <c r="A85" s="57" t="inlineStr">
         <is>
           <t>5850308009</t>
         </is>
       </c>
-      <c r="B85" s="62" t="inlineStr">
+      <c r="B85" s="57" t="inlineStr">
         <is>
           <t>RT (58)</t>
         </is>
       </c>
-      <c r="C85" s="63" t="inlineStr">
+      <c r="C85" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00127/2026</t>
         </is>
       </c>
-      <c r="D85" s="62" t="inlineStr">
+      <c r="D85" s="57" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="E85" s="62" t="n">
+      <c r="E85" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G85" s="62" t="inlineStr">
+      <c r="G85" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H85" s="63" t="inlineStr">
+      <c r="H85" s="58" t="inlineStr">
         <is>
           <t>Guarai</t>
         </is>
       </c>
-      <c r="I85" s="63" t="inlineStr">
+      <c r="I85" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5723,40 +5714,40 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="62" t="inlineStr">
+      <c r="A86" s="57" t="inlineStr">
         <is>
           <t>7937102148</t>
         </is>
       </c>
-      <c r="B86" s="62" t="inlineStr">
+      <c r="B86" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C86" s="63" t="inlineStr">
+      <c r="C86" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00129/2026</t>
         </is>
       </c>
-      <c r="D86" s="62" t="inlineStr">
+      <c r="D86" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E86" s="62" t="n">
+      <c r="E86" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="62" t="inlineStr">
+      <c r="G86" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H86" s="63" t="inlineStr">
+      <c r="H86" s="58" t="inlineStr">
         <is>
           <t>Sao Valerio Da Natividade</t>
         </is>
       </c>
-      <c r="I86" s="63" t="inlineStr">
+      <c r="I86" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5768,40 +5759,40 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="62" t="inlineStr">
+      <c r="A87" s="57" t="inlineStr">
         <is>
           <t>7923673004</t>
         </is>
       </c>
-      <c r="B87" s="62" t="inlineStr">
+      <c r="B87" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C87" s="63" t="inlineStr">
+      <c r="C87" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00124/2026</t>
         </is>
       </c>
-      <c r="D87" s="62" t="inlineStr">
+      <c r="D87" s="57" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="E87" s="62" t="n">
+      <c r="E87" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G87" s="62" t="inlineStr">
+      <c r="G87" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H87" s="63" t="inlineStr">
+      <c r="H87" s="58" t="inlineStr">
         <is>
           <t>Araguaina</t>
         </is>
       </c>
-      <c r="I87" s="63" t="inlineStr">
+      <c r="I87" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -5813,40 +5804,40 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="62" t="inlineStr">
+      <c r="A88" s="57" t="inlineStr">
         <is>
           <t>7900525015</t>
         </is>
       </c>
-      <c r="B88" s="62" t="inlineStr">
+      <c r="B88" s="57" t="inlineStr">
         <is>
           <t>RL (79)</t>
         </is>
       </c>
-      <c r="C88" s="63" t="inlineStr">
+      <c r="C88" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00125/2026</t>
         </is>
       </c>
-      <c r="D88" s="62" t="inlineStr">
+      <c r="D88" s="57" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="E88" s="62" t="n">
+      <c r="E88" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="62" t="inlineStr">
+      <c r="G88" s="57" t="inlineStr">
         <is>
           <t>COEP</t>
         </is>
       </c>
-      <c r="H88" s="63" t="inlineStr">
+      <c r="H88" s="58" t="inlineStr">
         <is>
           <t>Pedro Afonso</t>
         </is>
       </c>
-      <c r="I88" s="63" t="inlineStr">
+      <c r="I88" s="58" t="inlineStr">
         <is>
           <t>SIM (detalhamento)</t>
         </is>
@@ -14994,7 +14985,7 @@
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t>COEP: não há compra de equipamento especial</t>
+          <t>CONFIRMADO NO SGM (print 08/07): cadeia ETO-TELE 00694/2025 &gt; ETO-COEP 00163/2025 (encerrada 29/06/2026, motivo NÃO É RESPONSABILIDADE DA ÁREA) &gt; repassada ETO-RD-PO 00180/2026 (COCM, pendente) e ETO-TELE 00975/2026 — sem compra COEP</t>
         </is>
       </c>
       <c r="K11" s="25" t="n">

--- a/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
+++ b/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
@@ -3099,7 +3099,7 @@
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="J55" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="J57" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="J59" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="J60" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="J61" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="J64" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="J66" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="J69" s="23" t="inlineStr">
         <is>
-          <t>Pendente (fora do posto)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="J71" s="23" t="inlineStr">
         <is>
-          <t>EXECUTADO</t>
+          <t>Em execução (ETO-RD-PA)</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="J72" s="23" t="inlineStr">
         <is>
-          <t>No posto do COEP (pendente)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="J73" s="23" t="inlineStr">
         <is>
-          <t>Pendente (fora do posto)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="J75" s="23" t="inlineStr">
         <is>
-          <t>Pendente (fora do posto)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="J76" s="23" t="inlineStr">
         <is>
-          <t>Pendente (fora do posto)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="J77" s="23" t="inlineStr">
         <is>
-          <t>Pendente (fora do posto)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="J78" s="23" t="inlineStr">
         <is>
-          <t>Pendente (fora do posto)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="J80" s="23" t="inlineStr">
         <is>
-          <t>Pendente (fora do posto)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="J81" s="23" t="inlineStr">
         <is>
-          <t>Pendente (fora do posto)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="J85" s="23" t="inlineStr">
         <is>
-          <t>CONCLUÍDA MAS AINDA NO POSTO (VERIFICAR)</t>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
     </row>
@@ -7263,20 +7263,25 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
+          <t>Em execução (logística)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
           <t>Em execução (COCM)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>No posto COEP</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Pendente fora do posto</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -7295,15 +7300,18 @@
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>12</v>
-      </c>
       <c r="F6" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="19" t="n">
         <v>30</v>
       </c>
     </row>
@@ -7320,15 +7328,18 @@
         <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>9</v>
-      </c>
       <c r="F7" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="19" t="n">
         <v>21</v>
       </c>
     </row>
@@ -7345,15 +7356,18 @@
         <v>0</v>
       </c>
       <c r="D8" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>13</v>
-      </c>
       <c r="F8" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="19" t="n">
         <v>25</v>
       </c>
     </row>
@@ -7370,15 +7384,18 @@
         <v>1</v>
       </c>
       <c r="D9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="11" t="n">
-        <v>13</v>
-      </c>
       <c r="F9" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="19" t="n">
         <v>26</v>
       </c>
     </row>
@@ -7401,9 +7418,12 @@
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="H10" s="19" t="n">
         <v>13</v>
       </c>
     </row>
@@ -7423,12 +7443,15 @@
         <v>0</v>
       </c>
       <c r="E11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="G11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="H11" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7445,15 +7468,18 @@
         <v>1</v>
       </c>
       <c r="D12" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="19" t="n">
-        <v>48</v>
-      </c>
       <c r="F12" s="19" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G12" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="19" t="n">
         <v>116</v>
       </c>
     </row>
@@ -9140,67 +9166,65 @@
     <row r="42">
       <c r="A42" s="57" t="inlineStr">
         <is>
-          <t>7942572059</t>
+          <t>5800859011</t>
         </is>
       </c>
       <c r="B42" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C42" s="58" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Tupirama</t>
         </is>
       </c>
       <c r="D42" s="58" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Guarai</t>
         </is>
       </c>
       <c r="E42" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F42" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-PA 00427/2026</t>
+          <t>ETO-COEP 00115/2026</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>Comunicação/rádio + Aterramento (da descrição da SS)</t>
+          <t xml:space="preserve">Controle </t>
         </is>
       </c>
       <c r="H42" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Muito Alta</t>
         </is>
       </c>
       <c r="I42" s="57" t="n">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="J42" s="52" t="inlineStr">
         <is>
-          <t>Em execução (ETO-RD-PA)</t>
-        </is>
-      </c>
-      <c r="K42" s="31" t="inlineStr">
-        <is>
-          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
-        </is>
+          <t>Em execução (obra/logística)</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="n">
+        <v>29445.39</v>
       </c>
       <c r="L42" s="23" t="inlineStr">
         <is>
-          <t>Atendimento do Ramal do Marasca e GAs (108 UCs) | Definição do gestor 08/07: melhoria de aterramento SEM CUSTO; SS ETO-RD-PA 00427/2026 ainda aberta (8 dias aguardando DCMD) =&gt; em execução</t>
+          <t>Atendimento de parte da RDU Guaraí por fonte alternativa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="57" t="inlineStr">
         <is>
-          <t>5800859011</t>
+          <t>5854566043</t>
         </is>
       </c>
       <c r="B43" s="57" t="inlineStr">
@@ -9210,27 +9234,27 @@
       </c>
       <c r="C43" s="58" t="inlineStr">
         <is>
-          <t>Tupirama</t>
+          <t>Silvanopolis</t>
         </is>
       </c>
       <c r="D43" s="58" t="inlineStr">
         <is>
-          <t>Guarai</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="E43" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F43" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00115/2026</t>
+          <t>ETO-COEP 00160/2025</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Controle </t>
+          <t>1 célula</t>
         </is>
       </c>
       <c r="H43" s="57" t="inlineStr">
@@ -9241,39 +9265,39 @@
       <c r="I43" s="57" t="n">
         <v>110</v>
       </c>
-      <c r="J43" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+      <c r="J43" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K43" s="24" t="n">
-        <v>29445.39</v>
+        <v>207212.3</v>
       </c>
       <c r="L43" s="23" t="inlineStr">
         <is>
-          <t>Atendimento de parte da RDU Guaraí por fonte alternativa</t>
+          <t>Aumento de reclamações no atendimento de Silvanópolis por Porto Nacional no período seco (Outra fonte com defeito também)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="57" t="inlineStr">
         <is>
-          <t>5854566043</t>
+          <t>7900117013</t>
         </is>
       </c>
       <c r="B44" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C44" s="58" t="inlineStr">
         <is>
-          <t>Silvanopolis</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="D44" s="58" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E44" s="58" t="inlineStr">
@@ -9283,12 +9307,12 @@
       </c>
       <c r="F44" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00160/2025</t>
+          <t>ETO-COEP 00084/2026</t>
         </is>
       </c>
       <c r="G44" s="23" t="inlineStr">
         <is>
-          <t>1 célula</t>
+          <t>Relé Cooper</t>
         </is>
       </c>
       <c r="H44" s="57" t="inlineStr">
@@ -9297,56 +9321,56 @@
         </is>
       </c>
       <c r="I44" s="57" t="n">
-        <v>110</v>
-      </c>
-      <c r="J44" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>95</v>
+      </c>
+      <c r="J44" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K44" s="24" t="n">
-        <v>207212.3</v>
+        <v>66619.48</v>
       </c>
       <c r="L44" s="23" t="inlineStr">
         <is>
-          <t>Aumento de reclamações no atendimento de Silvanópolis por Porto Nacional no período seco (Outra fonte com defeito também)</t>
+          <t>Transferência do 214R de Paraíso I, Centro Comercial de Paraíso</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="57" t="inlineStr">
         <is>
-          <t>5856070091</t>
+          <t>7900230155</t>
         </is>
       </c>
       <c r="B45" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C45" s="58" t="inlineStr">
         <is>
-          <t>Almas</t>
+          <t>Palmeirante</t>
         </is>
       </c>
       <c r="D45" s="58" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Colinas Do Tocantins</t>
         </is>
       </c>
       <c r="E45" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F45" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00955/2026</t>
+          <t>ETO-COEP 00106/2026</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>Conexão invertida</t>
+          <t>Tanque e PR do trafo e chave</t>
         </is>
       </c>
       <c r="H45" s="57" t="inlineStr">
@@ -9355,26 +9379,26 @@
         </is>
       </c>
       <c r="I45" s="57" t="n">
-        <v>100</v>
-      </c>
-      <c r="J45" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>80</v>
+      </c>
+      <c r="J45" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K45" s="24" t="n">
-        <v>460999.9</v>
+        <v>89455.53999999999</v>
       </c>
       <c r="L45" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da região da Engegold, Nativa, cidade Natividade e Chapada da Natividade</t>
+          <t>Fonte principal de Palmeirante, RL de transferência operando</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="57" t="inlineStr">
         <is>
-          <t>7900117013</t>
+          <t>7900453110</t>
         </is>
       </c>
       <c r="B46" s="57" t="inlineStr">
@@ -9384,12 +9408,12 @@
       </c>
       <c r="C46" s="58" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Santa Rita Do Tocantins</t>
         </is>
       </c>
       <c r="D46" s="58" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="E46" s="58" t="inlineStr">
@@ -9399,12 +9423,12 @@
       </c>
       <c r="F46" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00084/2026</t>
+          <t>ETO-COEP 00087/2026</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
-          <t>Relé Cooper</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H46" s="57" t="inlineStr">
@@ -9413,26 +9437,26 @@
         </is>
       </c>
       <c r="I46" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="J46" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>85</v>
+      </c>
+      <c r="J46" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K46" s="24" t="n">
-        <v>66619.48</v>
+        <v>89455.53999999999</v>
       </c>
       <c r="L46" s="23" t="inlineStr">
         <is>
-          <t>Transferência do 214R de Paraíso I, Centro Comercial de Paraíso</t>
+          <t>Transferência de Santa Rita, fonte principal operando</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="57" t="inlineStr">
         <is>
-          <t>7900453110</t>
+          <t>7900594026</t>
         </is>
       </c>
       <c r="B47" s="57" t="inlineStr">
@@ -9442,12 +9466,12 @@
       </c>
       <c r="C47" s="58" t="inlineStr">
         <is>
-          <t>Santa Rita Do Tocantins</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="D47" s="58" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="E47" s="58" t="inlineStr">
@@ -9457,12 +9481,12 @@
       </c>
       <c r="F47" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00087/2026</t>
+          <t>ETO-COEP 00113/2026</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Comunicação/rádio (da descrição da SS)</t>
         </is>
       </c>
       <c r="H47" s="57" t="inlineStr">
@@ -9471,11 +9495,11 @@
         </is>
       </c>
       <c r="I47" s="57" t="n">
-        <v>85</v>
-      </c>
-      <c r="J47" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>95</v>
+      </c>
+      <c r="J47" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K47" s="24" t="n">
@@ -9483,14 +9507,14 @@
       </c>
       <c r="L47" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Santa Rita, fonte principal operando</t>
+          <t>Religador responsável pela proteção da barra da SE Ponte Alta (2381 UCs)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="57" t="inlineStr">
         <is>
-          <t>7900594026</t>
+          <t>7908686014</t>
         </is>
       </c>
       <c r="B48" s="57" t="inlineStr">
@@ -9500,12 +9524,12 @@
       </c>
       <c r="C48" s="58" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Pium</t>
         </is>
       </c>
       <c r="D48" s="58" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E48" s="58" t="inlineStr">
@@ -9515,12 +9539,12 @@
       </c>
       <c r="F48" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00113/2026</t>
+          <t>ETO-COEP 00086/2026</t>
         </is>
       </c>
       <c r="G48" s="23" t="inlineStr">
         <is>
-          <t>Comunicação/rádio (da descrição da SS)</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H48" s="57" t="inlineStr">
@@ -9529,26 +9553,26 @@
         </is>
       </c>
       <c r="I48" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="J48" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>90</v>
+      </c>
+      <c r="J48" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K48" s="24" t="n">
-        <v>89455.53999999999</v>
+        <v>51360.82000000001</v>
       </c>
       <c r="L48" s="23" t="inlineStr">
         <is>
-          <t>Religador responsável pela proteção da barra da SE Ponte Alta (2381 UCs)</t>
+          <t>Fonte principal de Pium, RL de transferência operando</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="57" t="inlineStr">
         <is>
-          <t>7908686014</t>
+          <t>7908705049</t>
         </is>
       </c>
       <c r="B49" s="57" t="inlineStr">
@@ -9558,27 +9582,27 @@
       </c>
       <c r="C49" s="58" t="inlineStr">
         <is>
-          <t>Pium</t>
+          <t>Aurora Do Tocantins</t>
         </is>
       </c>
       <c r="D49" s="58" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E49" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F49" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00086/2026</t>
+          <t>ETO-COEP 00089/2026</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Tanque e relé</t>
         </is>
       </c>
       <c r="H49" s="57" t="inlineStr">
@@ -9587,26 +9611,26 @@
         </is>
       </c>
       <c r="I49" s="57" t="n">
-        <v>90</v>
-      </c>
-      <c r="J49" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>95</v>
+      </c>
+      <c r="J49" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K49" s="24" t="n">
-        <v>51360.82000000001</v>
+        <v>66619.48</v>
       </c>
       <c r="L49" s="23" t="inlineStr">
         <is>
-          <t>Fonte principal de Pium, RL de transferência operando</t>
+          <t>Proteção da baixa do TF de força da SE Aurora</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="57" t="inlineStr">
         <is>
-          <t>7923673004</t>
+          <t>7929376022</t>
         </is>
       </c>
       <c r="B50" s="57" t="inlineStr">
@@ -9616,14 +9640,14 @@
       </c>
       <c r="C50" s="58" t="inlineStr">
         <is>
+          <t>Babaculandia</t>
+        </is>
+      </c>
+      <c r="D50" s="58" t="inlineStr">
+        <is>
           <t>Araguaina</t>
         </is>
       </c>
-      <c r="D50" s="58" t="inlineStr">
-        <is>
-          <t>Araguaina</t>
-        </is>
-      </c>
       <c r="E50" s="58" t="inlineStr">
         <is>
           <t>Norte</t>
@@ -9631,12 +9655,12 @@
       </c>
       <c r="F50" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00967/2026</t>
+          <t>ETO-COEP 00120/2026</t>
         </is>
       </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
-          <t>Relé (da descrição da SS)</t>
+          <t>Controle + Relé + Bateria (da descrição da SS)</t>
         </is>
       </c>
       <c r="H50" s="57" t="inlineStr">
@@ -9645,26 +9669,26 @@
         </is>
       </c>
       <c r="I50" s="57" t="n">
-        <v>105</v>
-      </c>
-      <c r="J50" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>95</v>
+      </c>
+      <c r="J50" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K50" s="24" t="n">
-        <v>21470.95</v>
+        <v>51304.06</v>
       </c>
       <c r="L50" s="23" t="inlineStr">
         <is>
-          <t>Transferência de cargas na RDU de Araguaína (2797 UCs)</t>
+          <t>Transferência de Babaçulândia, fonte principal operando</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="57" t="inlineStr">
         <is>
-          <t>7925744087</t>
+          <t>7931610122</t>
         </is>
       </c>
       <c r="B51" s="57" t="inlineStr">
@@ -9674,27 +9698,27 @@
       </c>
       <c r="C51" s="58" t="inlineStr">
         <is>
-          <t>Goianorte</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D51" s="58" t="inlineStr">
         <is>
-          <t>Guarai</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="E51" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F51" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00059/2026</t>
+          <t>ETO-RD-PA 00433/2026</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa + Comunicação/rádio + Bateria (da descrição da SS)</t>
+          <t>Tanque e antena</t>
         </is>
       </c>
       <c r="H51" s="57" t="inlineStr">
@@ -9703,26 +9727,26 @@
         </is>
       </c>
       <c r="I51" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="J51" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>105</v>
+      </c>
+      <c r="J51" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K51" s="24" t="n">
-        <v>51360.82000000001</v>
+        <v>32802.66</v>
       </c>
       <c r="L51" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Goianorte, fonte principal operando</t>
+          <t>Transferência entre 284R SE Palmas IV e 2294R SE Palmas II</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="57" t="inlineStr">
         <is>
-          <t>7925871077</t>
+          <t>7933726256</t>
         </is>
       </c>
       <c r="B52" s="57" t="inlineStr">
@@ -9732,27 +9756,27 @@
       </c>
       <c r="C52" s="58" t="inlineStr">
         <is>
-          <t>Goiatins</t>
+          <t>Mateiros</t>
         </is>
       </c>
       <c r="D52" s="58" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="E52" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F52" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00048/2026</t>
+          <t>ETO-RD-PO 00181/2026</t>
         </is>
       </c>
       <c r="G52" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa (da descrição da SS)</t>
+          <t>Tanque/parte ativa + Comunicação/rádio + Bateria (da descrição da SS)</t>
         </is>
       </c>
       <c r="H52" s="57" t="inlineStr">
@@ -9761,26 +9785,26 @@
         </is>
       </c>
       <c r="I52" s="57" t="n">
-        <v>80</v>
-      </c>
-      <c r="J52" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>95</v>
+      </c>
+      <c r="J52" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K52" s="24" t="n">
-        <v>51360.82000000001</v>
+        <v>13209.34</v>
       </c>
       <c r="L52" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Goiatins e GAs (2492 UCs)</t>
+          <t>Transferência da cidade de Mateiros (733 UCs) para o gerador</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="57" t="inlineStr">
         <is>
-          <t>7929376022</t>
+          <t>7933766059</t>
         </is>
       </c>
       <c r="B53" s="57" t="inlineStr">
@@ -9790,27 +9814,27 @@
       </c>
       <c r="C53" s="58" t="inlineStr">
         <is>
-          <t>Babaculandia</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="D53" s="58" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="E53" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F53" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00120/2026</t>
+          <t>ETO-RD-PA 00431/2026</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>Controle + Relé + Bateria (da descrição da SS)</t>
+          <t xml:space="preserve">Tanque </t>
         </is>
       </c>
       <c r="H53" s="57" t="inlineStr">
@@ -9821,39 +9845,39 @@
       <c r="I53" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="J53" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+      <c r="J53" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K53" s="24" t="n">
-        <v>51304.06</v>
+        <v>32802.66</v>
       </c>
       <c r="L53" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Babaçulândia, fonte principal operando</t>
+          <t>Seccionamento de trecho do Setor Taquari</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="57" t="inlineStr">
         <is>
-          <t>7931608059</t>
+          <t>5801866013</t>
         </is>
       </c>
       <c r="B54" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C54" s="58" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="D54" s="58" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E54" s="58" t="inlineStr">
@@ -9863,70 +9887,70 @@
       </c>
       <c r="F54" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00040/2026</t>
+          <t>ETO-COEP 00077/2026</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
         <is>
-          <t>Tanque e rádio</t>
+          <t>1 célula</t>
         </is>
       </c>
       <c r="H54" s="57" t="inlineStr">
         <is>
-          <t>Muito Alta</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I54" s="57" t="n">
-        <v>105</v>
-      </c>
-      <c r="J54" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>70</v>
+      </c>
+      <c r="J54" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K54" s="24" t="n">
-        <v>47414.74000000001</v>
+        <v>79018.75999999999</v>
       </c>
       <c r="L54" s="23" t="inlineStr">
         <is>
-          <t>Transferência dos bairros Morada do Sol, Vale do Sol, Morada do Sol II, Nova Esperança, Sõa João, Araras I e II e Jardim Laila em Taquaralto (6033 UCs)</t>
+          <t>Atendimento da RDU Luzimangues Industrial por fonte alternativa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="57" t="inlineStr">
         <is>
-          <t>5800371025</t>
+          <t>7900573047</t>
         </is>
       </c>
       <c r="B55" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C55" s="58" t="inlineStr">
         <is>
-          <t>Arapoema</t>
+          <t>Figueiropolis</t>
         </is>
       </c>
       <c r="D55" s="58" t="inlineStr">
         <is>
-          <t>Colinas Do Tocantins</t>
+          <t>Alvorada</t>
         </is>
       </c>
       <c r="E55" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F55" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00187/2025</t>
+          <t>ETO-COEP 00080/2026</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
         <is>
-          <t>Relé e fiquei em duvida sobre kit</t>
+          <t>Tanque e relé</t>
         </is>
       </c>
       <c r="H55" s="57" t="inlineStr">
@@ -9935,56 +9959,56 @@
         </is>
       </c>
       <c r="I55" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="J55" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>65</v>
+      </c>
+      <c r="J55" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K55" s="24" t="n">
-        <v>282925.12</v>
+        <v>66619.48</v>
       </c>
       <c r="L55" s="23" t="inlineStr">
         <is>
-          <t>Aumento de reclamações no atendimento de Arapoema no período seco</t>
+          <t>Transferência da Bunge, Saneatins e secadora</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="57" t="inlineStr">
         <is>
-          <t>5801866013</t>
+          <t>7903112004</t>
         </is>
       </c>
       <c r="B56" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C56" s="58" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="D56" s="58" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="E56" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F56" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00077/2026</t>
+          <t>ETO-COEP 00184/2025</t>
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr">
         <is>
-          <t>1 célula</t>
+          <t>Tanque cooper</t>
         </is>
       </c>
       <c r="H56" s="57" t="inlineStr">
@@ -9993,26 +10017,26 @@
         </is>
       </c>
       <c r="I56" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="J56" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>55</v>
+      </c>
+      <c r="J56" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K56" s="24" t="n">
-        <v>79018.75999999999</v>
+        <v>51304.06</v>
       </c>
       <c r="L56" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da RDU Luzimangues Industrial por fonte alternativa</t>
+          <t>Transferência de Babaçulândia, 4 RLs sendo 2 operando</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="57" t="inlineStr">
         <is>
-          <t>7900573047</t>
+          <t>7925087021</t>
         </is>
       </c>
       <c r="B57" s="57" t="inlineStr">
@@ -10022,12 +10046,12 @@
       </c>
       <c r="C57" s="58" t="inlineStr">
         <is>
-          <t>Figueiropolis</t>
+          <t>Parana</t>
         </is>
       </c>
       <c r="D57" s="58" t="inlineStr">
         <is>
-          <t>Alvorada</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="E57" s="58" t="inlineStr">
@@ -10037,12 +10061,12 @@
       </c>
       <c r="F57" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00080/2026</t>
+          <t>ETO-COEP 00222/2025</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
         <is>
-          <t>Tanque e relé</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H57" s="57" t="inlineStr">
@@ -10051,26 +10075,26 @@
         </is>
       </c>
       <c r="I57" s="57" t="n">
-        <v>65</v>
-      </c>
-      <c r="J57" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>70</v>
+      </c>
+      <c r="J57" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K57" s="24" t="n">
-        <v>66619.48</v>
+        <v>51360.82000000001</v>
       </c>
       <c r="L57" s="23" t="inlineStr">
         <is>
-          <t>Transferência da Bunge, Saneatins e secadora</t>
+          <t>Primeiro RL do 414R de Paranã, RL a jusante na LD também está bay-passado (630 UCs)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="57" t="inlineStr">
         <is>
-          <t>7903112004</t>
+          <t>7927169001</t>
         </is>
       </c>
       <c r="B58" s="57" t="inlineStr">
@@ -10080,27 +10104,27 @@
       </c>
       <c r="C58" s="58" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="D58" s="58" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="E58" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F58" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00184/2025</t>
+          <t>ETO-RD-PA 00432/2026</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
-          <t>Tanque cooper</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H58" s="57" t="inlineStr">
@@ -10111,24 +10135,24 @@
       <c r="I58" s="57" t="n">
         <v>55</v>
       </c>
-      <c r="J58" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+      <c r="J58" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K58" s="24" t="n">
-        <v>51304.06</v>
+        <v>66619.48</v>
       </c>
       <c r="L58" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Babaçulândia, 4 RLs sendo 2 operando</t>
+          <t>Transferência dos Grupos A -  VLI e Frisia</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="57" t="inlineStr">
         <is>
-          <t>7920024127</t>
+          <t>7953610256</t>
         </is>
       </c>
       <c r="B59" s="57" t="inlineStr">
@@ -10138,27 +10162,27 @@
       </c>
       <c r="C59" s="58" t="inlineStr">
         <is>
-          <t>Palmeiras Do Tocantins</t>
+          <t>Mateiros</t>
         </is>
       </c>
       <c r="D59" s="58" t="inlineStr">
         <is>
-          <t>Tocantinopolis</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="E59" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F59" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00120/2025</t>
+          <t>ETO-COEP 00050/2026</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr">
         <is>
-          <t>Tanque, relé e chave</t>
+          <t>Tanque/parte ativa + Relé + Curto interno (da descrição da SS)</t>
         </is>
       </c>
       <c r="H59" s="57" t="inlineStr">
@@ -10167,26 +10191,26 @@
         </is>
       </c>
       <c r="I59" s="57" t="n">
-        <v>55</v>
-      </c>
-      <c r="J59" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>65</v>
+      </c>
+      <c r="J59" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K59" s="24" t="n">
-        <v>90191.96999999999</v>
+        <v>51360.82000000001</v>
       </c>
       <c r="L59" s="23" t="inlineStr">
         <is>
-          <t>Transferência de Palmeiras, 3 fontes operando</t>
+          <t>Atenidmento da COELBA (Alto potencial de compensação)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="57" t="inlineStr">
         <is>
-          <t>7925087021</t>
+          <t>7955520116</t>
         </is>
       </c>
       <c r="B60" s="57" t="inlineStr">
@@ -10196,12 +10220,12 @@
       </c>
       <c r="C60" s="58" t="inlineStr">
         <is>
-          <t>Parana</t>
+          <t>Chapada Da Natividade</t>
         </is>
       </c>
       <c r="D60" s="58" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E60" s="58" t="inlineStr">
@@ -10211,7 +10235,7 @@
       </c>
       <c r="F60" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00222/2025</t>
+          <t>ETO-TELE 00961/2026</t>
         </is>
       </c>
       <c r="G60" s="23" t="inlineStr">
@@ -10225,11 +10249,11 @@
         </is>
       </c>
       <c r="I60" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="J60" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>50</v>
+      </c>
+      <c r="J60" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K60" s="24" t="n">
@@ -10237,87 +10261,87 @@
       </c>
       <c r="L60" s="23" t="inlineStr">
         <is>
-          <t>Primeiro RL do 414R de Paranã, RL a jusante na LD também está bay-passado (630 UCs)</t>
+          <t>Transferência do Grupo A - Engegold (TF 7500 kVA)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="57" t="inlineStr">
         <is>
-          <t>7926089013</t>
+          <t>5800438116</t>
         </is>
       </c>
       <c r="B61" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C61" s="58" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Chapada Da Natividade</t>
         </is>
       </c>
       <c r="D61" s="58" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E61" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F61" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00078/2026</t>
+          <t>ETO-RD-DP 00404/2026</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>2 Celula</t>
         </is>
       </c>
       <c r="H61" s="57" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I61" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="J61" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>60</v>
+      </c>
+      <c r="J61" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K61" s="24" t="n">
-        <v>51360.82000000001</v>
+        <v>80318.5</v>
       </c>
       <c r="L61" s="23" t="inlineStr">
         <is>
-          <t>Transferência da RDU de Chapada de Areia (937 UCs) para fonte alternativa</t>
+          <t>Atendimento da região da Engegold, Nativa, cidade Natividade e Chapada da Natividade (Fonte alternativa)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="57" t="inlineStr">
         <is>
-          <t>7927646026</t>
+          <t>5827102054</t>
         </is>
       </c>
       <c r="B62" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C62" s="58" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Pugmil</t>
         </is>
       </c>
       <c r="D62" s="58" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E62" s="58" t="inlineStr">
@@ -10327,128 +10351,130 @@
       </c>
       <c r="F62" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00029/2026</t>
+          <t>ETO-RD-PS 00289/2026</t>
         </is>
       </c>
       <c r="G62" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Controle e melhoria de aterramento</t>
         </is>
       </c>
       <c r="H62" s="57" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I62" s="57" t="n">
-        <v>55</v>
-      </c>
-      <c r="J62" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
-        </is>
-      </c>
-      <c r="K62" s="24" t="n">
-        <v>51360.82000000001</v>
+        <v>50</v>
+      </c>
+      <c r="J62" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
+        </is>
+      </c>
+      <c r="K62" s="31" t="inlineStr">
+        <is>
+          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
+        </is>
       </c>
       <c r="L62" s="23" t="inlineStr">
         <is>
-          <t>Opção de isolação de São Félix e Mateiros para alimentação por gerador</t>
+          <t>Misto: aterramento desconsiderado; controle a avaliar | Aumento de reclamações no atendimento de Pugmil no período seco</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="57" t="inlineStr">
         <is>
-          <t>7953610256</t>
+          <t>5850308009</t>
         </is>
       </c>
       <c r="B63" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C63" s="58" t="inlineStr">
         <is>
-          <t>Mateiros</t>
+          <t>Guarai</t>
         </is>
       </c>
       <c r="D63" s="58" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Guarai</t>
         </is>
       </c>
       <c r="E63" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F63" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00050/2026</t>
+          <t>ETO-TELE 00958/2026</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa + Relé + Curto interno (da descrição da SS)</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="H63" s="57" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I63" s="57" t="n">
-        <v>65</v>
-      </c>
-      <c r="J63" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>50</v>
+      </c>
+      <c r="J63" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K63" s="24" t="n">
-        <v>51360.82000000001</v>
+        <v>29445.39</v>
       </c>
       <c r="L63" s="23" t="inlineStr">
         <is>
-          <t>Atenidmento da COELBA (Alto potencial de compensação)</t>
+          <t>Atendimento de parte da RDU de Guaraí e ramal da PRF/Repetidora | Definição do gestor 08/07: NÃO concluído; print SGM (SS 00127/2026) confirma EQUIPAMENTO EM PROCESSO DE LOGÍSTICA e só controle =&gt; em execução</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="57" t="inlineStr">
         <is>
-          <t>5800090147</t>
+          <t>7957126085</t>
         </is>
       </c>
       <c r="B64" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C64" s="58" t="inlineStr">
         <is>
-          <t>Taipas Do Tocantins</t>
+          <t>Monte Santo Do Tocantins</t>
         </is>
       </c>
       <c r="D64" s="58" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E64" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F64" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00117/2026</t>
+          <t>ETO-COEP 00156/2025</t>
         </is>
       </c>
       <c r="G64" s="23" t="inlineStr">
         <is>
-          <t>Célula + Comunicação/rádio (da descrição da SS)</t>
+          <t>Relé, controle e ajuste</t>
         </is>
       </c>
       <c r="H64" s="57" t="inlineStr">
@@ -10457,26 +10483,26 @@
         </is>
       </c>
       <c r="I64" s="57" t="n">
-        <v>60</v>
-      </c>
-      <c r="J64" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>30</v>
+      </c>
+      <c r="J64" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K64" s="24" t="n">
-        <v>138038.91</v>
+        <v>51304.06</v>
       </c>
       <c r="L64" s="23" t="inlineStr">
         <is>
-          <t>Atendimento de Taipas</t>
+          <t>444R de Paraíso I, atendimento de Monte Santo, devido defeito a RDU está manobrada para o 454R</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="57" t="inlineStr">
         <is>
-          <t>5800961074</t>
+          <t>5844630060</t>
         </is>
       </c>
       <c r="B65" s="57" t="inlineStr">
@@ -10486,55 +10512,55 @@
       </c>
       <c r="C65" s="58" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Nova Olinda</t>
         </is>
       </c>
       <c r="D65" s="58" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Colinas Do Tocantins</t>
         </is>
       </c>
       <c r="E65" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F65" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00221/2025</t>
+          <t>ETO-COEP 00167/2025</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
         <is>
-          <t>3 células e conectores</t>
+          <t>1 celula</t>
         </is>
       </c>
       <c r="H65" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I65" s="57" t="n">
-        <v>40</v>
-      </c>
-      <c r="J65" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>30</v>
+      </c>
+      <c r="J65" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K65" s="24" t="n">
-        <v>253479.73</v>
+        <v>112500.43</v>
       </c>
       <c r="L65" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da COELBA e GA Alessandro Maurício (1600 kVA)</t>
+          <t>Atendimento dos ramais PA Remansão e Água Branca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="57" t="inlineStr">
         <is>
-          <t>5850308009</t>
+          <t>5855411017</t>
         </is>
       </c>
       <c r="B66" s="57" t="inlineStr">
@@ -10544,22 +10570,22 @@
       </c>
       <c r="C66" s="58" t="inlineStr">
         <is>
-          <t>Guarai</t>
+          <t>Barrolandia</t>
         </is>
       </c>
       <c r="D66" s="58" t="inlineStr">
         <is>
-          <t>Guarai</t>
+          <t>Miracema Do Tocantins</t>
         </is>
       </c>
       <c r="E66" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F66" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00958/2026</t>
+          <t>ETO-COEP 00199/2025</t>
         </is>
       </c>
       <c r="G66" s="23" t="inlineStr">
@@ -10569,15 +10595,15 @@
       </c>
       <c r="H66" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I66" s="57" t="n">
-        <v>50</v>
-      </c>
-      <c r="J66" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>30</v>
+      </c>
+      <c r="J66" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K66" s="24" t="n">
@@ -10585,29 +10611,29 @@
       </c>
       <c r="L66" s="23" t="inlineStr">
         <is>
-          <t>Atendimento de parte da RDU de Guaraí e ramal da PRF/Repetidora | Definição do gestor 08/07: NÃO concluído — oficial ETO 36 mostra 0 dias aguardando DCMD</t>
+          <t>Atendimento do Assentamento Irmã Adelaide</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="57" t="inlineStr">
         <is>
-          <t>7900525015</t>
+          <t>5858783119</t>
         </is>
       </c>
       <c r="B67" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C67" s="58" t="inlineStr">
         <is>
-          <t>Pedro Afonso</t>
+          <t>Sao Bento Do Tocantins</t>
         </is>
       </c>
       <c r="D67" s="58" t="inlineStr">
         <is>
-          <t>Guarai</t>
+          <t>Tocantinopolis</t>
         </is>
       </c>
       <c r="E67" s="58" t="inlineStr">
@@ -10617,98 +10643,98 @@
       </c>
       <c r="F67" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00971/2026</t>
+          <t>ETO-COEP 00123/2025</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
         <is>
-          <t>Buchas (da descrição da SS)</t>
+          <t>3 celula</t>
         </is>
       </c>
       <c r="H67" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I67" s="57" t="n">
-        <v>35</v>
-      </c>
-      <c r="J67" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K67" s="24" t="n">
-        <v>0</v>
+        <v>460999.9</v>
       </c>
       <c r="L67" s="23" t="inlineStr">
         <is>
-          <t>Tranferência do Ramal do Chaparral (251 UCs)</t>
+          <t>Equipamento novo furtado antes de ser colocado em operação, não inserido no SCADA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="57" t="inlineStr">
         <is>
-          <t>7900535058</t>
+          <t>5862236091</t>
         </is>
       </c>
       <c r="B68" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C68" s="58" t="inlineStr">
         <is>
-          <t>Santa Fe Do Araguaia</t>
+          <t>Almas</t>
         </is>
       </c>
       <c r="D68" s="58" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E68" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F68" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00173/2025</t>
+          <t>ETO-COEP 00223/2025</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr">
         <is>
-          <t>Relé Cooper</t>
+          <t>1 celula</t>
         </is>
       </c>
       <c r="H68" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I68" s="57" t="n">
-        <v>45</v>
-      </c>
-      <c r="J68" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>20</v>
+      </c>
+      <c r="J68" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K68" s="24" t="n">
-        <v>89455.53999999999</v>
+        <v>207212.3</v>
       </c>
       <c r="L68" s="23" t="inlineStr">
         <is>
-          <t>Atendimento 3 povoados, na perca 4 ficam fora (900 UCs)</t>
+          <t>Atendimento da LD Vale Rio Doce (Nova Aura Mineradora)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="57" t="inlineStr">
         <is>
-          <t>7908249152</t>
+          <t>7938137007</t>
         </is>
       </c>
       <c r="B69" s="57" t="inlineStr">
@@ -10718,12 +10744,12 @@
       </c>
       <c r="C69" s="58" t="inlineStr">
         <is>
-          <t>Santa Rosa Do Tocantins</t>
+          <t>Miracema Do Tocantins</t>
         </is>
       </c>
       <c r="D69" s="58" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Miracema Do Tocantins</t>
         </is>
       </c>
       <c r="E69" s="58" t="inlineStr">
@@ -10733,40 +10759,40 @@
       </c>
       <c r="F69" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00038/2026</t>
+          <t>ETO-TELE 00888/2026</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
         <is>
-          <t>Tanque e controle</t>
+          <t>bateria, rádio, trafo (entender sobre bucha da fase A)</t>
         </is>
       </c>
       <c r="H69" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I69" s="57" t="n">
-        <v>35</v>
-      </c>
-      <c r="J69" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
+        <v>15</v>
+      </c>
+      <c r="J69" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (obra/logística)</t>
         </is>
       </c>
       <c r="K69" s="24" t="n">
-        <v>89455.53999999999</v>
+        <v>25629.02</v>
       </c>
       <c r="L69" s="23" t="inlineStr">
         <is>
-          <t>Atendimento de zona rural em Santa Rosa (160 UCs)</t>
+          <t>Transferência do Irmã Adelaide (470 UCs)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="57" t="inlineStr">
         <is>
-          <t>7925733015</t>
+          <t>7942572059</t>
         </is>
       </c>
       <c r="B70" s="57" t="inlineStr">
@@ -10776,27 +10802,27 @@
       </c>
       <c r="C70" s="58" t="inlineStr">
         <is>
-          <t>Pedro Afonso</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="D70" s="58" t="inlineStr">
         <is>
-          <t>Guarai</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="E70" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F70" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00058/2026</t>
+          <t>ETO-RD-PA 00427/2026</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa + Comunicação/rádio + Chave (da descrição da SS)</t>
+          <t>Comunicação/rádio + Aterramento (da descrição da SS)</t>
         </is>
       </c>
       <c r="H70" s="57" t="inlineStr">
@@ -10807,39 +10833,41 @@
       <c r="I70" s="57" t="n">
         <v>35</v>
       </c>
-      <c r="J70" s="53" t="inlineStr">
-        <is>
-          <t>No posto do COEP (pendente)</t>
-        </is>
-      </c>
-      <c r="K70" s="24" t="n">
-        <v>51360.82000000001</v>
+      <c r="J70" s="52" t="inlineStr">
+        <is>
+          <t>Em execução (ETO-RD-PA)</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
+        </is>
       </c>
       <c r="L70" s="23" t="inlineStr">
         <is>
-          <t>Transferência do Ramal Agrovila (73 UCs)</t>
+          <t>Atendimento do Ramal do Marasca e GAs (108 UCs) | Definição do gestor 08/07: melhoria de aterramento SEM CUSTO; SS ETO-RD-PA 00427/2026 ainda aberta (8 dias aguardando DCMD) =&gt; em execução</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="57" t="inlineStr">
         <is>
-          <t>7927396052</t>
+          <t>5856070091</t>
         </is>
       </c>
       <c r="B71" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C71" s="58" t="inlineStr">
         <is>
-          <t>Formoso Do Araguaia</t>
+          <t>Almas</t>
         </is>
       </c>
       <c r="D71" s="58" t="inlineStr">
         <is>
-          <t>Formoso Do Araguaia</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E71" s="58" t="inlineStr">
@@ -10849,21 +10877,21 @@
       </c>
       <c r="F71" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00045/2026</t>
+          <t>ETO-TELE 00955/2026</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Conexão invertida</t>
         </is>
       </c>
       <c r="H71" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Muito Alta</t>
         </is>
       </c>
       <c r="I71" s="57" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="J71" s="53" t="inlineStr">
         <is>
@@ -10871,18 +10899,18 @@
         </is>
       </c>
       <c r="K71" s="24" t="n">
-        <v>51360.82000000001</v>
+        <v>460999.9</v>
       </c>
       <c r="L71" s="23" t="inlineStr">
         <is>
-          <t>Equipamento localizado Fonte principal de atendimento a SE Cobrape</t>
+          <t>Atendimento da região da Engegold, Nativa, cidade Natividade e Chapada da Natividade</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="57" t="inlineStr">
         <is>
-          <t>7928564039</t>
+          <t>7923673004</t>
         </is>
       </c>
       <c r="B72" s="57" t="inlineStr">
@@ -10892,12 +10920,12 @@
       </c>
       <c r="C72" s="58" t="inlineStr">
         <is>
-          <t>Araguatins</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="D72" s="58" t="inlineStr">
         <is>
-          <t>Augustinopolis</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="E72" s="58" t="inlineStr">
@@ -10907,21 +10935,21 @@
       </c>
       <c r="F72" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00976/2026</t>
+          <t>ETO-TELE 00967/2026</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
         <is>
-          <t>Tanque, relé e modulo</t>
+          <t>Relé (da descrição da SS)</t>
         </is>
       </c>
       <c r="H72" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Muito Alta</t>
         </is>
       </c>
       <c r="I72" s="57" t="n">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="J72" s="53" t="inlineStr">
         <is>
@@ -10929,18 +10957,18 @@
         </is>
       </c>
       <c r="K72" s="24" t="n">
-        <v>89455.53999999999</v>
+        <v>21470.95</v>
       </c>
       <c r="L72" s="23" t="inlineStr">
         <is>
-          <t>Transferência entre 424R Araguatins e 434R Augustinópolis</t>
+          <t>Transferência de cargas na RDU de Araguaína (2797 UCs)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="57" t="inlineStr">
         <is>
-          <t>7933585074</t>
+          <t>7925744087</t>
         </is>
       </c>
       <c r="B73" s="57" t="inlineStr">
@@ -10950,36 +10978,36 @@
       </c>
       <c r="C73" s="58" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Goianorte</t>
         </is>
       </c>
       <c r="D73" s="58" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Guarai</t>
         </is>
       </c>
       <c r="E73" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F73" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00024/2026</t>
+          <t>ETO-COEP 00059/2026</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Tanque/parte ativa + Comunicação/rádio + Bateria (da descrição da SS)</t>
         </is>
       </c>
       <c r="H73" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Muito Alta</t>
         </is>
       </c>
       <c r="I73" s="57" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="J73" s="53" t="inlineStr">
         <is>
@@ -10991,14 +11019,14 @@
       </c>
       <c r="L73" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da COELBA</t>
+          <t>Transferência de Goianorte, fonte principal operando</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="57" t="inlineStr">
         <is>
-          <t>7937102148</t>
+          <t>7925871077</t>
         </is>
       </c>
       <c r="B74" s="57" t="inlineStr">
@@ -11008,36 +11036,36 @@
       </c>
       <c r="C74" s="58" t="inlineStr">
         <is>
-          <t>Sao Valerio Da Natividade</t>
+          <t>Goiatins</t>
         </is>
       </c>
       <c r="D74" s="58" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="E74" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F74" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00977/2026</t>
+          <t>ETO-COEP 00048/2026</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Tanque/parte ativa (da descrição da SS)</t>
         </is>
       </c>
       <c r="H74" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Muito Alta</t>
         </is>
       </c>
       <c r="I74" s="57" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J74" s="53" t="inlineStr">
         <is>
@@ -11049,14 +11077,14 @@
       </c>
       <c r="L74" s="23" t="inlineStr">
         <is>
-          <t>Fonte principal do Ramal Serranópolis (181 UCs), RL de transferência operando</t>
+          <t>Transferência de Goiatins e GAs (2492 UCs)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="57" t="inlineStr">
         <is>
-          <t>7944559149</t>
+          <t>7931608059</t>
         </is>
       </c>
       <c r="B75" s="57" t="inlineStr">
@@ -11066,12 +11094,12 @@
       </c>
       <c r="C75" s="58" t="inlineStr">
         <is>
-          <t>Caseara</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="D75" s="58" t="inlineStr">
         <is>
-          <t>Divinopolis</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="E75" s="58" t="inlineStr">
@@ -11081,21 +11109,21 @@
       </c>
       <c r="F75" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00063/2026</t>
+          <t>ETO-COEP 00040/2026</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
         <is>
-          <t>Placa + Bateria + Curto interno (da descrição da SS)</t>
+          <t>Tanque e rádio</t>
         </is>
       </c>
       <c r="H75" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Muito Alta</t>
         </is>
       </c>
       <c r="I75" s="57" t="n">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="J75" s="53" t="inlineStr">
         <is>
@@ -11103,57 +11131,57 @@
         </is>
       </c>
       <c r="K75" s="24" t="n">
-        <v>51304.06</v>
+        <v>47414.74000000001</v>
       </c>
       <c r="L75" s="23" t="inlineStr">
         <is>
-          <t>Atendimento de cargas rurais entre Caseaarra e Araguacema (221 UCs)</t>
+          <t>Transferência dos bairros Morada do Sol, Vale do Sol, Morada do Sol II, Nova Esperança, Sõa João, Araras I e II e Jardim Laila em Taquaralto (6033 UCs)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="57" t="inlineStr">
         <is>
-          <t>7957126085</t>
+          <t>5800371025</t>
         </is>
       </c>
       <c r="B76" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C76" s="58" t="inlineStr">
         <is>
-          <t>Monte Santo Do Tocantins</t>
+          <t>Arapoema</t>
         </is>
       </c>
       <c r="D76" s="58" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Colinas Do Tocantins</t>
         </is>
       </c>
       <c r="E76" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F76" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00156/2025</t>
+          <t>ETO-COEP 00187/2025</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
         <is>
-          <t>Relé, controle e ajuste</t>
+          <t>Relé e fiquei em duvida sobre kit</t>
         </is>
       </c>
       <c r="H76" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I76" s="57" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="J76" s="53" t="inlineStr">
         <is>
@@ -11161,57 +11189,57 @@
         </is>
       </c>
       <c r="K76" s="24" t="n">
-        <v>51304.06</v>
+        <v>282925.12</v>
       </c>
       <c r="L76" s="23" t="inlineStr">
         <is>
-          <t>444R de Paraíso I, atendimento de Monte Santo, devido defeito a RDU está manobrada para o 454R</t>
+          <t>Aumento de reclamações no atendimento de Arapoema no período seco</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="57" t="inlineStr">
         <is>
-          <t>5836786094</t>
+          <t>7920024127</t>
         </is>
       </c>
       <c r="B77" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C77" s="58" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Palmeiras Do Tocantins</t>
         </is>
       </c>
       <c r="D77" s="58" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Tocantinopolis</t>
         </is>
       </c>
       <c r="E77" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F77" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00095/2026</t>
+          <t>ETO-COEP 00120/2025</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
         <is>
-          <t>Furto (da descrição da SS)</t>
+          <t>Tanque, relé e chave</t>
         </is>
       </c>
       <c r="H77" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I77" s="57" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="J77" s="53" t="inlineStr">
         <is>
@@ -11219,57 +11247,57 @@
         </is>
       </c>
       <c r="K77" s="24" t="n">
-        <v>253479.73</v>
+        <v>90191.96999999999</v>
       </c>
       <c r="L77" s="23" t="inlineStr">
         <is>
-          <t>Atendimento de clientes rurais na LD Peixe Angical - Peixe</t>
+          <t>Transferência de Palmeiras, 3 fontes operando</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="57" t="inlineStr">
         <is>
-          <t>5844630060</t>
+          <t>7926089013</t>
         </is>
       </c>
       <c r="B78" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C78" s="58" t="inlineStr">
         <is>
-          <t>Nova Olinda</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="D78" s="58" t="inlineStr">
         <is>
-          <t>Colinas Do Tocantins</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E78" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F78" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00167/2025</t>
+          <t>ETO-COEP 00078/2026</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
         <is>
-          <t>1 celula</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H78" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I78" s="57" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="J78" s="53" t="inlineStr">
         <is>
@@ -11277,33 +11305,33 @@
         </is>
       </c>
       <c r="K78" s="24" t="n">
-        <v>112500.43</v>
+        <v>51360.82000000001</v>
       </c>
       <c r="L78" s="23" t="inlineStr">
         <is>
-          <t>Atendimento dos ramais PA Remansão e Água Branca</t>
+          <t>Transferência da RDU de Chapada de Areia (937 UCs) para fonte alternativa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="57" t="inlineStr">
         <is>
-          <t>5855411017</t>
+          <t>7927646026</t>
         </is>
       </c>
       <c r="B79" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C79" s="58" t="inlineStr">
         <is>
-          <t>Barrolandia</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="D79" s="58" t="inlineStr">
         <is>
-          <t>Miracema Do Tocantins</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="E79" s="58" t="inlineStr">
@@ -11313,21 +11341,21 @@
       </c>
       <c r="F79" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00199/2025</t>
+          <t>ETO-COEP 00029/2026</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
         <is>
-          <t>Controle</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H79" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I79" s="57" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="J79" s="53" t="inlineStr">
         <is>
@@ -11335,18 +11363,18 @@
         </is>
       </c>
       <c r="K79" s="24" t="n">
-        <v>29445.39</v>
+        <v>51360.82000000001</v>
       </c>
       <c r="L79" s="23" t="inlineStr">
         <is>
-          <t>Atendimento do Assentamento Irmã Adelaide</t>
+          <t>Opção de isolação de São Félix e Mateiros para alimentação por gerador</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="57" t="inlineStr">
         <is>
-          <t>5858783119</t>
+          <t>5800090147</t>
         </is>
       </c>
       <c r="B80" s="57" t="inlineStr">
@@ -11356,36 +11384,36 @@
       </c>
       <c r="C80" s="58" t="inlineStr">
         <is>
-          <t>Sao Bento Do Tocantins</t>
+          <t>Taipas Do Tocantins</t>
         </is>
       </c>
       <c r="D80" s="58" t="inlineStr">
         <is>
-          <t>Tocantinopolis</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E80" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F80" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00123/2025</t>
+          <t>ETO-COEP 00117/2026</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
         <is>
-          <t>3 celula</t>
+          <t>Célula + Comunicação/rádio (da descrição da SS)</t>
         </is>
       </c>
       <c r="H80" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I80" s="57" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J80" s="53" t="inlineStr">
         <is>
@@ -11393,18 +11421,18 @@
         </is>
       </c>
       <c r="K80" s="24" t="n">
-        <v>460999.9</v>
+        <v>138038.91</v>
       </c>
       <c r="L80" s="23" t="inlineStr">
         <is>
-          <t>Equipamento novo furtado antes de ser colocado em operação, não inserido no SCADA</t>
+          <t>Atendimento de Taipas</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="57" t="inlineStr">
         <is>
-          <t>5862236091</t>
+          <t>5800961074</t>
         </is>
       </c>
       <c r="B81" s="57" t="inlineStr">
@@ -11414,7 +11442,7 @@
       </c>
       <c r="C81" s="58" t="inlineStr">
         <is>
-          <t>Almas</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="D81" s="58" t="inlineStr">
@@ -11429,21 +11457,21 @@
       </c>
       <c r="F81" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00223/2025</t>
+          <t>ETO-COEP 00221/2025</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
         <is>
-          <t>1 celula</t>
+          <t>3 células e conectores</t>
         </is>
       </c>
       <c r="H81" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I81" s="57" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J81" s="53" t="inlineStr">
         <is>
@@ -11451,18 +11479,18 @@
         </is>
       </c>
       <c r="K81" s="24" t="n">
-        <v>207212.3</v>
+        <v>253479.73</v>
       </c>
       <c r="L81" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da LD Vale Rio Doce (Nova Aura Mineradora)</t>
+          <t>Atendimento da COELBA e GA Alessandro Maurício (1600 kVA)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="57" t="inlineStr">
         <is>
-          <t>7901110084</t>
+          <t>7900525015</t>
         </is>
       </c>
       <c r="B82" s="57" t="inlineStr">
@@ -11472,36 +11500,36 @@
       </c>
       <c r="C82" s="58" t="inlineStr">
         <is>
-          <t>Divinopolis</t>
+          <t>Pedro Afonso</t>
         </is>
       </c>
       <c r="D82" s="58" t="inlineStr">
         <is>
-          <t>Divinopolis</t>
+          <t>Guarai</t>
         </is>
       </c>
       <c r="E82" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F82" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00061/2026</t>
+          <t>ETO-TELE 00971/2026</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa (da descrição da SS)</t>
+          <t>Buchas (da descrição da SS)</t>
         </is>
       </c>
       <c r="H82" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I82" s="57" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J82" s="53" t="inlineStr">
         <is>
@@ -11509,18 +11537,18 @@
         </is>
       </c>
       <c r="K82" s="24" t="n">
-        <v>51360.82000000001</v>
+        <v>0</v>
       </c>
       <c r="L82" s="23" t="inlineStr">
         <is>
-          <t>Localizado na fonte principal de atendimento de Divinópolis e Abreulândia</t>
+          <t>Tranferência do Ramal do Chaparral (251 UCs)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="57" t="inlineStr">
         <is>
-          <t>7913662076</t>
+          <t>7900535058</t>
         </is>
       </c>
       <c r="B83" s="57" t="inlineStr">
@@ -11530,36 +11558,36 @@
       </c>
       <c r="C83" s="58" t="inlineStr">
         <is>
-          <t>Duere</t>
+          <t>Santa Fe Do Araguaia</t>
         </is>
       </c>
       <c r="D83" s="58" t="inlineStr">
         <is>
-          <t>Gurupi</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="E83" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F83" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00114/2026</t>
+          <t>ETO-COEP 00173/2025</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa + Chave (da descrição da SS)</t>
+          <t>Relé Cooper</t>
         </is>
       </c>
       <c r="H83" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I83" s="57" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="J83" s="53" t="inlineStr">
         <is>
@@ -11567,18 +11595,18 @@
         </is>
       </c>
       <c r="K83" s="24" t="n">
-        <v>33539.09</v>
+        <v>89455.53999999999</v>
       </c>
       <c r="L83" s="23" t="inlineStr">
         <is>
-          <t>Atendimento do Ramal do Bacuri (168 UCs)</t>
+          <t>Atendimento 3 povoados, na perca 4 ficam fora (900 UCs)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="57" t="inlineStr">
         <is>
-          <t>7919270014</t>
+          <t>7908249152</t>
         </is>
       </c>
       <c r="B84" s="57" t="inlineStr">
@@ -11588,12 +11616,12 @@
       </c>
       <c r="C84" s="58" t="inlineStr">
         <is>
-          <t>Pium</t>
+          <t>Santa Rosa Do Tocantins</t>
         </is>
       </c>
       <c r="D84" s="58" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="E84" s="58" t="inlineStr">
@@ -11603,21 +11631,21 @@
       </c>
       <c r="F84" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00074/2026</t>
+          <t>ETO-COEP 00038/2026</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa + Controle + Placa (da descrição da SS)</t>
+          <t>Tanque e controle</t>
         </is>
       </c>
       <c r="H84" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I84" s="57" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J84" s="53" t="inlineStr">
         <is>
@@ -11629,14 +11657,14 @@
       </c>
       <c r="L84" s="23" t="inlineStr">
         <is>
-          <t>Atendimento de Clientes rurais (48 UCs)</t>
+          <t>Atendimento de zona rural em Santa Rosa (160 UCs)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="57" t="inlineStr">
         <is>
-          <t>7923927122</t>
+          <t>7925733015</t>
         </is>
       </c>
       <c r="B85" s="57" t="inlineStr">
@@ -11646,36 +11674,36 @@
       </c>
       <c r="C85" s="58" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Pedro Afonso</t>
         </is>
       </c>
       <c r="D85" s="58" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Guarai</t>
         </is>
       </c>
       <c r="E85" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F85" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00079/2025</t>
+          <t>ETO-COEP 00058/2026</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
         <is>
-          <t>tanque</t>
+          <t>Tanque/parte ativa + Comunicação/rádio + Chave (da descrição da SS)</t>
         </is>
       </c>
       <c r="H85" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I85" s="57" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J85" s="53" t="inlineStr">
         <is>
@@ -11687,14 +11715,14 @@
       </c>
       <c r="L85" s="23" t="inlineStr">
         <is>
-          <t>Transferência entre 414R e 424R SE Palmas II</t>
+          <t>Transferência do Ramal Agrovila (73 UCs)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="57" t="inlineStr">
         <is>
-          <t>7926442035</t>
+          <t>7927396052</t>
         </is>
       </c>
       <c r="B86" s="57" t="inlineStr">
@@ -11704,36 +11732,36 @@
       </c>
       <c r="C86" s="58" t="inlineStr">
         <is>
-          <t>Monte Do Carmo</t>
+          <t>Formoso Do Araguaia</t>
         </is>
       </c>
       <c r="D86" s="58" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Formoso Do Araguaia</t>
         </is>
       </c>
       <c r="E86" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F86" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00051/2026</t>
+          <t>ETO-COEP 00045/2026</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa + Comunicação/rádio + Buchas (da descrição da SS)</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H86" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I86" s="57" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J86" s="53" t="inlineStr">
         <is>
@@ -11745,14 +11773,14 @@
       </c>
       <c r="L86" s="23" t="inlineStr">
         <is>
-          <t>Atenidmento do PA Principado (200 UCs)</t>
+          <t>Equipamento localizado Fonte principal de atendimento a SE Cobrape</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="57" t="inlineStr">
         <is>
-          <t>7927446001</t>
+          <t>7928564039</t>
         </is>
       </c>
       <c r="B87" s="57" t="inlineStr">
@@ -11762,36 +11790,36 @@
       </c>
       <c r="C87" s="58" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Araguatins</t>
         </is>
       </c>
       <c r="D87" s="58" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Augustinopolis</t>
         </is>
       </c>
       <c r="E87" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F87" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00143/2025</t>
+          <t>ETO-TELE 00976/2026</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
         <is>
-          <t>Parte ativa danificada</t>
+          <t>Tanque, relé e modulo</t>
         </is>
       </c>
       <c r="H87" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I87" s="57" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J87" s="53" t="inlineStr">
         <is>
@@ -11803,14 +11831,14 @@
       </c>
       <c r="L87" s="23" t="inlineStr">
         <is>
-          <t>Alimentação de Monte do Carmo por Porto Nacional</t>
+          <t>Transferência entre 424R Araguatins e 434R Augustinópolis</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="57" t="inlineStr">
         <is>
-          <t>7928241200</t>
+          <t>7933585074</t>
         </is>
       </c>
       <c r="B88" s="57" t="inlineStr">
@@ -11820,12 +11848,12 @@
       </c>
       <c r="C88" s="58" t="inlineStr">
         <is>
-          <t>Sao Salvador Do Tocantins</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="D88" s="58" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E88" s="58" t="inlineStr">
@@ -11835,21 +11863,21 @@
       </c>
       <c r="F88" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00974/2026</t>
+          <t>ETO-COEP 00024/2026</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
         <is>
-          <t>tanque</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H88" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I88" s="57" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J88" s="53" t="inlineStr">
         <is>
@@ -11861,14 +11889,14 @@
       </c>
       <c r="L88" s="23" t="inlineStr">
         <is>
-          <t>Fonte principal do Ramal do Retiro (246UCs), RL transferência by-passado</t>
+          <t>Atendimento da COELBA</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="57" t="inlineStr">
         <is>
-          <t>7942485096</t>
+          <t>7937102148</t>
         </is>
       </c>
       <c r="B89" s="57" t="inlineStr">
@@ -11878,36 +11906,36 @@
       </c>
       <c r="C89" s="58" t="inlineStr">
         <is>
-          <t>Pindorama Do Tocantins</t>
+          <t>Sao Valerio Da Natividade</t>
         </is>
       </c>
       <c r="D89" s="58" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="E89" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F89" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00158/2025</t>
+          <t>ETO-TELE 00977/2026</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
         <is>
-          <t>Parte ativa danificada (tanque)</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H89" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I89" s="57" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J89" s="53" t="inlineStr">
         <is>
@@ -11919,14 +11947,14 @@
       </c>
       <c r="L89" s="23" t="inlineStr">
         <is>
-          <t>Transferência da PCH Bagagem</t>
+          <t>Fonte principal do Ramal Serranópolis (181 UCs), RL de transferência operando</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="57" t="inlineStr">
         <is>
-          <t>7900532053</t>
+          <t>7944559149</t>
         </is>
       </c>
       <c r="B90" s="57" t="inlineStr">
@@ -11936,36 +11964,36 @@
       </c>
       <c r="C90" s="58" t="inlineStr">
         <is>
-          <t>Piraque</t>
+          <t>Caseara</t>
         </is>
       </c>
       <c r="D90" s="58" t="inlineStr">
         <is>
-          <t>Tocantinopolis</t>
+          <t>Divinopolis</t>
         </is>
       </c>
       <c r="E90" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F90" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00102/2025</t>
+          <t>ETO-COEP 00063/2026</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Placa + Bateria + Curto interno (da descrição da SS)</t>
         </is>
       </c>
       <c r="H90" s="57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I90" s="57" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J90" s="53" t="inlineStr">
         <is>
@@ -11973,76 +12001,76 @@
         </is>
       </c>
       <c r="K90" s="24" t="n">
-        <v>104067.62</v>
+        <v>51304.06</v>
       </c>
       <c r="L90" s="23" t="inlineStr">
         <is>
-          <t>Equipamento não identificado no SCADA e Mapa TS</t>
+          <t>Atendimento de cargas rurais entre Caseaarra e Araguacema (221 UCs)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="57" t="inlineStr">
         <is>
-          <t>7900230155</t>
+          <t>5836786094</t>
         </is>
       </c>
       <c r="B91" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C91" s="58" t="inlineStr">
         <is>
-          <t>Palmeirante</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="D91" s="58" t="inlineStr">
         <is>
-          <t>Colinas Do Tocantins</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="E91" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F91" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00106/2026</t>
+          <t>ETO-COEP 00095/2026</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
         <is>
-          <t>Tanque e PR do trafo e chave</t>
+          <t>Furto (da descrição da SS)</t>
         </is>
       </c>
       <c r="H91" s="57" t="inlineStr">
         <is>
-          <t>Muito Alta</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I91" s="57" t="n">
-        <v>80</v>
-      </c>
-      <c r="J91" s="54" t="inlineStr">
-        <is>
-          <t>Pendente (fora do posto)</t>
+        <v>20</v>
+      </c>
+      <c r="J91" s="53" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K91" s="24" t="n">
-        <v>89455.53999999999</v>
+        <v>253479.73</v>
       </c>
       <c r="L91" s="23" t="inlineStr">
         <is>
-          <t>Fonte principal de Palmeirante, RL de transferência operando</t>
+          <t>Atendimento de clientes rurais na LD Peixe Angical - Peixe</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="57" t="inlineStr">
         <is>
-          <t>7903569004</t>
+          <t>7901110084</t>
         </is>
       </c>
       <c r="B92" s="57" t="inlineStr">
@@ -12052,57 +12080,55 @@
       </c>
       <c r="C92" s="58" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Divinopolis</t>
         </is>
       </c>
       <c r="D92" s="58" t="inlineStr">
         <is>
-          <t>Araguaina</t>
+          <t>Divinopolis</t>
         </is>
       </c>
       <c r="E92" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F92" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00963/2026</t>
+          <t>ETO-COEP 00061/2026</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa + Comunicação/rádio (da descrição da SS)</t>
+          <t>Tanque/parte ativa (da descrição da SS)</t>
         </is>
       </c>
       <c r="H92" s="57" t="inlineStr">
         <is>
-          <t>Muito Alta</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I92" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="J92" s="54" t="inlineStr">
-        <is>
-          <t>Pendente (fora do posto)</t>
-        </is>
-      </c>
-      <c r="K92" s="23" t="inlineStr">
-        <is>
-          <t>(sem orçamento nesta base)</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="J92" s="53" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+      <c r="K92" s="24" t="n">
+        <v>51360.82000000001</v>
       </c>
       <c r="L92" s="23" t="inlineStr">
         <is>
-          <t>Transferência dos bairros JD Santa Helena, Jd Filadelfiae Setor Caraja em Araguaína (2053 UCs), AL 254R de AR I e AL 214R de AR III</t>
+          <t>Localizado na fonte principal de atendimento de Divinópolis e Abreulândia</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="57" t="inlineStr">
         <is>
-          <t>7908705049</t>
+          <t>7913662076</t>
         </is>
       </c>
       <c r="B93" s="57" t="inlineStr">
@@ -12112,12 +12138,12 @@
       </c>
       <c r="C93" s="58" t="inlineStr">
         <is>
-          <t>Aurora Do Tocantins</t>
+          <t>Duere</t>
         </is>
       </c>
       <c r="D93" s="58" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Gurupi</t>
         </is>
       </c>
       <c r="E93" s="58" t="inlineStr">
@@ -12127,40 +12153,40 @@
       </c>
       <c r="F93" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00089/2026</t>
+          <t>ETO-COEP 00114/2026</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
         <is>
-          <t>Tanque e relé</t>
+          <t>Tanque/parte ativa + Chave (da descrição da SS)</t>
         </is>
       </c>
       <c r="H93" s="57" t="inlineStr">
         <is>
-          <t>Muito Alta</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I93" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="J93" s="54" t="inlineStr">
-        <is>
-          <t>Pendente (fora do posto)</t>
+        <v>20</v>
+      </c>
+      <c r="J93" s="53" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K93" s="24" t="n">
-        <v>66619.48</v>
+        <v>33539.09</v>
       </c>
       <c r="L93" s="23" t="inlineStr">
         <is>
-          <t>Proteção da baixa do TF de força da SE Aurora</t>
+          <t>Atendimento do Ramal do Bacuri (168 UCs)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="57" t="inlineStr">
         <is>
-          <t>7927413001</t>
+          <t>7919270014</t>
         </is>
       </c>
       <c r="B94" s="57" t="inlineStr">
@@ -12170,12 +12196,12 @@
       </c>
       <c r="C94" s="58" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Pium</t>
         </is>
       </c>
       <c r="D94" s="58" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E94" s="58" t="inlineStr">
@@ -12185,42 +12211,40 @@
       </c>
       <c r="F94" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-PO 00118/2026</t>
+          <t>ETO-COEP 00074/2026</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
         <is>
-          <t>Placa + Relé + Comunicação/rádio (da descrição da SS)</t>
+          <t>Tanque/parte ativa + Controle + Placa (da descrição da SS)</t>
         </is>
       </c>
       <c r="H94" s="57" t="inlineStr">
         <is>
-          <t>Muito Alta</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I94" s="57" t="n">
-        <v>90</v>
-      </c>
-      <c r="J94" s="54" t="inlineStr">
-        <is>
-          <t>Pendente (fora do posto)</t>
-        </is>
-      </c>
-      <c r="K94" s="23" t="inlineStr">
-        <is>
-          <t>(sem orçamento nesta base)</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="J94" s="53" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+      <c r="K94" s="24" t="n">
+        <v>89455.53999999999</v>
       </c>
       <c r="L94" s="23" t="inlineStr">
         <is>
-          <t>Transferência do Distrito Ind de Porto Nacional e GAs</t>
+          <t>Atendimento de Clientes rurais (48 UCs)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="57" t="inlineStr">
         <is>
-          <t>7931610122</t>
+          <t>7923927122</t>
         </is>
       </c>
       <c r="B95" s="57" t="inlineStr">
@@ -12245,40 +12269,40 @@
       </c>
       <c r="F95" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-PA 00433/2026</t>
+          <t>ETO-COEP 00079/2025</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
         <is>
-          <t>Tanque e antena</t>
+          <t>tanque</t>
         </is>
       </c>
       <c r="H95" s="57" t="inlineStr">
         <is>
-          <t>Muito Alta</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I95" s="57" t="n">
-        <v>105</v>
-      </c>
-      <c r="J95" s="54" t="inlineStr">
-        <is>
-          <t>Pendente (fora do posto)</t>
+        <v>25</v>
+      </c>
+      <c r="J95" s="53" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K95" s="24" t="n">
-        <v>32802.66</v>
+        <v>51360.82000000001</v>
       </c>
       <c r="L95" s="23" t="inlineStr">
         <is>
-          <t>Transferência entre 284R SE Palmas IV e 2294R SE Palmas II</t>
+          <t>Transferência entre 414R e 424R SE Palmas II</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="57" t="inlineStr">
         <is>
-          <t>7933726256</t>
+          <t>7926442035</t>
         </is>
       </c>
       <c r="B96" s="57" t="inlineStr">
@@ -12288,7 +12312,7 @@
       </c>
       <c r="C96" s="58" t="inlineStr">
         <is>
-          <t>Mateiros</t>
+          <t>Monte Do Carmo</t>
         </is>
       </c>
       <c r="D96" s="58" t="inlineStr">
@@ -12303,40 +12327,40 @@
       </c>
       <c r="F96" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-PO 00181/2026</t>
+          <t>ETO-COEP 00051/2026</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa + Comunicação/rádio + Bateria (da descrição da SS)</t>
+          <t>Tanque/parte ativa + Comunicação/rádio + Buchas (da descrição da SS)</t>
         </is>
       </c>
       <c r="H96" s="57" t="inlineStr">
         <is>
-          <t>Muito Alta</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I96" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="J96" s="54" t="inlineStr">
-        <is>
-          <t>Pendente (fora do posto)</t>
+        <v>20</v>
+      </c>
+      <c r="J96" s="53" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>13209.34</v>
+        <v>51360.82000000001</v>
       </c>
       <c r="L96" s="23" t="inlineStr">
         <is>
-          <t>Transferência da cidade de Mateiros (733 UCs) para o gerador</t>
+          <t>Atenidmento do PA Principado (200 UCs)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="57" t="inlineStr">
         <is>
-          <t>7933766059</t>
+          <t>7927446001</t>
         </is>
       </c>
       <c r="B97" s="57" t="inlineStr">
@@ -12346,12 +12370,12 @@
       </c>
       <c r="C97" s="58" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="D97" s="58" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="E97" s="58" t="inlineStr">
@@ -12361,40 +12385,40 @@
       </c>
       <c r="F97" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-PA 00431/2026</t>
+          <t>ETO-COEP 00143/2025</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tanque </t>
+          <t>Parte ativa danificada</t>
         </is>
       </c>
       <c r="H97" s="57" t="inlineStr">
         <is>
-          <t>Muito Alta</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I97" s="57" t="n">
-        <v>95</v>
-      </c>
-      <c r="J97" s="54" t="inlineStr">
-        <is>
-          <t>Pendente (fora do posto)</t>
+        <v>25</v>
+      </c>
+      <c r="J97" s="53" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
         </is>
       </c>
       <c r="K97" s="24" t="n">
-        <v>32802.66</v>
+        <v>89455.53999999999</v>
       </c>
       <c r="L97" s="23" t="inlineStr">
         <is>
-          <t>Seccionamento de trecho do Setor Taquari</t>
+          <t>Alimentação de Monte do Carmo por Porto Nacional</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="57" t="inlineStr">
         <is>
-          <t>7947203070</t>
+          <t>7928241200</t>
         </is>
       </c>
       <c r="B98" s="57" t="inlineStr">
@@ -12404,72 +12428,70 @@
       </c>
       <c r="C98" s="58" t="inlineStr">
         <is>
-          <t>Rio Sono</t>
+          <t>Sao Salvador Do Tocantins</t>
         </is>
       </c>
       <c r="D98" s="58" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="E98" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F98" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00966/2026</t>
+          <t>ETO-TELE 00974/2026</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
         <is>
-          <t>Placa + Comunicação/rádio + Bateria (da descrição da SS)</t>
+          <t>tanque</t>
         </is>
       </c>
       <c r="H98" s="57" t="inlineStr">
         <is>
-          <t>Muito Alta</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I98" s="57" t="n">
-        <v>100</v>
-      </c>
-      <c r="J98" s="54" t="inlineStr">
-        <is>
-          <t>Pendente (fora do posto)</t>
-        </is>
-      </c>
-      <c r="K98" s="23" t="inlineStr">
-        <is>
-          <t>(sem orçamento nesta base)</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="J98" s="53" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+      <c r="K98" s="24" t="n">
+        <v>51360.82000000001</v>
       </c>
       <c r="L98" s="23" t="inlineStr">
         <is>
-          <t>Transferência da RDU de Lizarda (1650 UCs) para fonte alternativa</t>
+          <t>Fonte principal do Ramal do Retiro (246UCs), RL transferência by-passado</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="57" t="inlineStr">
         <is>
-          <t>5803327001</t>
+          <t>7942485096</t>
         </is>
       </c>
       <c r="B99" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C99" s="58" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Pindorama Do Tocantins</t>
         </is>
       </c>
       <c r="D99" s="58" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="E99" s="58" t="inlineStr">
@@ -12479,117 +12501,113 @@
       </c>
       <c r="F99" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-PA 00434/2026</t>
+          <t>ETO-COEP 00158/2025</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
         <is>
-          <t>Controle e aterramento</t>
+          <t>Parte ativa danificada (tanque)</t>
         </is>
       </c>
       <c r="H99" s="57" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baixa</t>
         </is>
       </c>
       <c r="I99" s="57" t="n">
-        <v>80</v>
-      </c>
-      <c r="J99" s="54" t="inlineStr">
-        <is>
-          <t>Pendente (fora do posto)</t>
-        </is>
-      </c>
-      <c r="K99" s="31" t="inlineStr">
-        <is>
-          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="J99" s="53" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+      <c r="K99" s="24" t="n">
+        <v>51360.82000000001</v>
       </c>
       <c r="L99" s="23" t="inlineStr">
         <is>
-          <t>Misto: aterramento desconsiderado; controle a avaliar | Em caso de perca da fonte principal é necessário esse RT para alimentação da Frísia</t>
+          <t>Transferência da PCH Bagagem</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="57" t="inlineStr">
         <is>
-          <t>5853360007</t>
+          <t>7900532053</t>
         </is>
       </c>
       <c r="B100" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C100" s="58" t="inlineStr">
         <is>
-          <t>Miracema Do Tocantins</t>
+          <t>Piraque</t>
         </is>
       </c>
       <c r="D100" s="58" t="inlineStr">
         <is>
-          <t>Miracema Do Tocantins</t>
+          <t>Tocantinopolis</t>
         </is>
       </c>
       <c r="E100" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F100" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-PS 00323/2025</t>
+          <t>ETO-COEP 00102/2025</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
         <is>
-          <t>Melhoria de aterramento</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="H100" s="57" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="J100" s="54" t="inlineStr">
-        <is>
-          <t>Pendente (fora do posto)</t>
-        </is>
-      </c>
-      <c r="K100" s="31" t="inlineStr">
-        <is>
-          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J100" s="53" t="inlineStr">
+        <is>
+          <t>No posto do COEP (pendente)</t>
+        </is>
+      </c>
+      <c r="K100" s="24" t="n">
+        <v>104067.62</v>
       </c>
       <c r="L100" s="23" t="inlineStr">
         <is>
-          <t>Aumento de reclamações no atendimento de Miracema no período seco</t>
+          <t>Equipamento não identificado no SCADA e Mapa TS</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="57" t="inlineStr">
         <is>
-          <t>5865120195</t>
+          <t>7903569004</t>
         </is>
       </c>
       <c r="B101" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C101" s="58" t="inlineStr">
         <is>
-          <t>Centenario</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="D101" s="58" t="inlineStr">
         <is>
-          <t>Guarai</t>
+          <t>Araguaina</t>
         </is>
       </c>
       <c r="E101" s="58" t="inlineStr">
@@ -12599,42 +12617,42 @@
       </c>
       <c r="F101" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-GR 00538/2026</t>
+          <t>ETO-TELE 00963/2026</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
         <is>
-          <t>Melhoria de aterramento</t>
+          <t>Tanque/parte ativa + Comunicação/rádio (da descrição da SS)</t>
         </is>
       </c>
       <c r="H101" s="57" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muito Alta</t>
         </is>
       </c>
       <c r="I101" s="57" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="J101" s="54" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
-      <c r="K101" s="31" t="inlineStr">
-        <is>
-          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
+      <c r="K101" s="23" t="inlineStr">
+        <is>
+          <t>(sem orçamento nesta base)</t>
         </is>
       </c>
       <c r="L101" s="23" t="inlineStr">
         <is>
-          <t>Atendimento das RDUs de Centenário, Recursolândia e clientes rurais</t>
+          <t>Transferência dos bairros JD Santa Helena, Jd Filadelfiae Setor Caraja em Araguaína (2053 UCs), AL 254R de AR I e AL 214R de AR III</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="57" t="inlineStr">
         <is>
-          <t>7927169001</t>
+          <t>7927413001</t>
         </is>
       </c>
       <c r="B102" s="57" t="inlineStr">
@@ -12659,40 +12677,42 @@
       </c>
       <c r="F102" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-PA 00432/2026</t>
+          <t>ETO-RD-PO 00118/2026</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Placa + Relé + Comunicação/rádio (da descrição da SS)</t>
         </is>
       </c>
       <c r="H102" s="57" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muito Alta</t>
         </is>
       </c>
       <c r="I102" s="57" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="J102" s="54" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
-      <c r="K102" s="24" t="n">
-        <v>66619.48</v>
+      <c r="K102" s="23" t="inlineStr">
+        <is>
+          <t>(sem orçamento nesta base)</t>
+        </is>
       </c>
       <c r="L102" s="23" t="inlineStr">
         <is>
-          <t>Transferência dos Grupos A -  VLI e Frisia</t>
+          <t>Transferência do Distrito Ind de Porto Nacional e GAs</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="57" t="inlineStr">
         <is>
-          <t>7930428001</t>
+          <t>7947203070</t>
         </is>
       </c>
       <c r="B103" s="57" t="inlineStr">
@@ -12702,12 +12722,12 @@
       </c>
       <c r="C103" s="58" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Rio Sono</t>
         </is>
       </c>
       <c r="D103" s="58" t="inlineStr">
         <is>
-          <t>Porto Nacional</t>
+          <t>Taquaralto</t>
         </is>
       </c>
       <c r="E103" s="58" t="inlineStr">
@@ -12717,21 +12737,21 @@
       </c>
       <c r="F103" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00965/2026</t>
+          <t>ETO-TELE 00966/2026</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Placa + Comunicação/rádio + Bateria (da descrição da SS)</t>
         </is>
       </c>
       <c r="H103" s="57" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muito Alta</t>
         </is>
       </c>
       <c r="I103" s="57" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J103" s="54" t="inlineStr">
         <is>
@@ -12745,44 +12765,44 @@
       </c>
       <c r="L103" s="23" t="inlineStr">
         <is>
-          <t>Transferência dos Grupos A -  Ramal do Rossato (TF 225kVA e TF 750kVA)</t>
+          <t>Transferência da RDU de Lizarda (1650 UCs) para fonte alternativa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="57" t="inlineStr">
         <is>
-          <t>7936038076</t>
+          <t>5803327001</t>
         </is>
       </c>
       <c r="B104" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C104" s="58" t="inlineStr">
         <is>
-          <t>Duere</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="D104" s="58" t="inlineStr">
         <is>
-          <t>Gurupi</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="E104" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F104" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00962/2026</t>
+          <t>ETO-RD-PA 00434/2026</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Controle e aterramento</t>
         </is>
       </c>
       <c r="H104" s="57" t="inlineStr">
@@ -12791,58 +12811,58 @@
         </is>
       </c>
       <c r="I104" s="57" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J104" s="54" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
-      <c r="K104" s="23" t="inlineStr">
-        <is>
-          <t>(sem orçamento nesta base)</t>
+      <c r="K104" s="31" t="inlineStr">
+        <is>
+          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
         </is>
       </c>
       <c r="L104" s="23" t="inlineStr">
         <is>
-          <t>Transferência do Grupo A - Xavante (TF 1087,5 kVA) e outros GA menores</t>
+          <t>Misto: aterramento desconsiderado; controle a avaliar | Em caso de perca da fonte principal é necessário esse RT para alimentação da Frísia</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="57" t="inlineStr">
         <is>
-          <t>7955520116</t>
+          <t>5853360007</t>
         </is>
       </c>
       <c r="B105" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C105" s="58" t="inlineStr">
         <is>
-          <t>Chapada Da Natividade</t>
+          <t>Miracema Do Tocantins</t>
         </is>
       </c>
       <c r="D105" s="58" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Miracema Do Tocantins</t>
         </is>
       </c>
       <c r="E105" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F105" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00961/2026</t>
+          <t>ETO-RD-PS 00323/2025</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Melhoria de aterramento</t>
         </is>
       </c>
       <c r="H105" s="57" t="inlineStr">
@@ -12851,26 +12871,28 @@
         </is>
       </c>
       <c r="I105" s="57" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J105" s="54" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
-      <c r="K105" s="24" t="n">
-        <v>51360.82000000001</v>
+      <c r="K105" s="31" t="inlineStr">
+        <is>
+          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
+        </is>
       </c>
       <c r="L105" s="23" t="inlineStr">
         <is>
-          <t>Transferência do Grupo A - Engegold (TF 7500 kVA)</t>
+          <t>Aumento de reclamações no atendimento de Miracema no período seco</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="57" t="inlineStr">
         <is>
-          <t>5800291035</t>
+          <t>5865120195</t>
         </is>
       </c>
       <c r="B106" s="57" t="inlineStr">
@@ -12880,22 +12902,22 @@
       </c>
       <c r="C106" s="58" t="inlineStr">
         <is>
-          <t>Monte Do Carmo</t>
+          <t>Centenario</t>
         </is>
       </c>
       <c r="D106" s="58" t="inlineStr">
         <is>
-          <t>Ponte Alta Tocantins</t>
+          <t>Guarai</t>
         </is>
       </c>
       <c r="E106" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F106" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-PO 00097/2026</t>
+          <t>ETO-RD-GR 00538/2026</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -12905,11 +12927,11 @@
       </c>
       <c r="H106" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I106" s="57" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J106" s="54" t="inlineStr">
         <is>
@@ -12923,107 +12945,109 @@
       </c>
       <c r="L106" s="23" t="inlineStr">
         <is>
-          <t>Aumento de reclamações no atendimento de Silvanópolis por Monte do Carmo no período seco</t>
+          <t>Atendimento das RDUs de Centenário, Recursolândia e clientes rurais</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="57" t="inlineStr">
         <is>
-          <t>5800438116</t>
+          <t>7930428001</t>
         </is>
       </c>
       <c r="B107" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C107" s="58" t="inlineStr">
         <is>
-          <t>Chapada Da Natividade</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="D107" s="58" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Porto Nacional</t>
         </is>
       </c>
       <c r="E107" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F107" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00404/2026</t>
+          <t>ETO-TELE 00965/2026</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
         <is>
-          <t>2 Celula</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H107" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I107" s="57" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J107" s="54" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
-      <c r="K107" s="24" t="n">
-        <v>80318.5</v>
+      <c r="K107" s="23" t="inlineStr">
+        <is>
+          <t>(sem orçamento nesta base)</t>
+        </is>
       </c>
       <c r="L107" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da região da Engegold, Nativa, cidade Natividade e Chapada da Natividade (Fonte alternativa)</t>
+          <t>Transferência dos Grupos A -  Ramal do Rossato (TF 225kVA e TF 750kVA)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="57" t="inlineStr">
         <is>
-          <t>5827102054</t>
+          <t>7936038076</t>
         </is>
       </c>
       <c r="B108" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C108" s="58" t="inlineStr">
         <is>
-          <t>Pugmil</t>
+          <t>Duere</t>
         </is>
       </c>
       <c r="D108" s="58" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Gurupi</t>
         </is>
       </c>
       <c r="E108" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F108" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-PS 00289/2026</t>
+          <t>ETO-TELE 00962/2026</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
         <is>
-          <t>Controle e melhoria de aterramento</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H108" s="57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I108" s="57" t="n">
@@ -13034,21 +13058,21 @@
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
-      <c r="K108" s="31" t="inlineStr">
-        <is>
-          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
+      <c r="K108" s="23" t="inlineStr">
+        <is>
+          <t>(sem orçamento nesta base)</t>
         </is>
       </c>
       <c r="L108" s="23" t="inlineStr">
         <is>
-          <t>Misto: aterramento desconsiderado; controle a avaliar | Aumento de reclamações no atendimento de Pugmil no período seco</t>
+          <t>Transferência do Grupo A - Xavante (TF 1087,5 kVA) e outros GA menores</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="57" t="inlineStr">
         <is>
-          <t>5840227063</t>
+          <t>5800291035</t>
         </is>
       </c>
       <c r="B109" s="57" t="inlineStr">
@@ -13058,27 +13082,27 @@
       </c>
       <c r="C109" s="58" t="inlineStr">
         <is>
-          <t>Bandeirantes Do Tocantins</t>
+          <t>Monte Do Carmo</t>
         </is>
       </c>
       <c r="D109" s="58" t="inlineStr">
         <is>
-          <t>Colinas Do Tocantins</t>
+          <t>Ponte Alta Tocantins</t>
         </is>
       </c>
       <c r="E109" s="58" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F109" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00942/2026</t>
+          <t>ETO-RD-PO 00097/2026</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
         <is>
-          <t>Curto interno (da descrição da SS)</t>
+          <t>Melhoria de aterramento</t>
         </is>
       </c>
       <c r="H109" s="57" t="inlineStr">
@@ -13087,28 +13111,28 @@
         </is>
       </c>
       <c r="I109" s="57" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J109" s="54" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
-      <c r="K109" s="23" t="inlineStr">
-        <is>
-          <t>(sem orçamento nesta base)</t>
+      <c r="K109" s="31" t="inlineStr">
+        <is>
+          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
         </is>
       </c>
       <c r="L109" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da RDU Bandeirantes e clientes rurais</t>
+          <t>Aumento de reclamações no atendimento de Silvanópolis por Monte do Carmo no período seco</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="57" t="inlineStr">
         <is>
-          <t>5846328094</t>
+          <t>5840227063</t>
         </is>
       </c>
       <c r="B110" s="57" t="inlineStr">
@@ -13118,27 +13142,27 @@
       </c>
       <c r="C110" s="58" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Bandeirantes Do Tocantins</t>
         </is>
       </c>
       <c r="D110" s="58" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Colinas Do Tocantins</t>
         </is>
       </c>
       <c r="E110" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F110" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-GU 00687/2026</t>
+          <t>ETO-TELE 00942/2026</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
         <is>
-          <t>Aterramento + Buchas (da descrição da SS)</t>
+          <t>Curto interno (da descrição da SS)</t>
         </is>
       </c>
       <c r="H110" s="57" t="inlineStr">
@@ -13154,21 +13178,21 @@
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
-      <c r="K110" s="31" t="inlineStr">
-        <is>
-          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
+      <c r="K110" s="23" t="inlineStr">
+        <is>
+          <t>(sem orçamento nesta base)</t>
         </is>
       </c>
       <c r="L110" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da RDU Sucupira e clientes rurais</t>
+          <t>Atendimento da RDU Bandeirantes e clientes rurais</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="57" t="inlineStr">
         <is>
-          <t>5851753086</t>
+          <t>5846328094</t>
         </is>
       </c>
       <c r="B111" s="57" t="inlineStr">
@@ -13178,27 +13202,27 @@
       </c>
       <c r="C111" s="58" t="inlineStr">
         <is>
-          <t>Marianopolis</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="D111" s="58" t="inlineStr">
         <is>
-          <t>Divinopolis</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="E111" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F111" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00881/2026</t>
+          <t>ETO-RD-GU 00687/2026</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
         <is>
-          <t>Relé + Comunicação/rádio + Aterramento (da descrição da SS)</t>
+          <t>Aterramento + Buchas (da descrição da SS)</t>
         </is>
       </c>
       <c r="H111" s="57" t="inlineStr">
@@ -13214,51 +13238,51 @@
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
-      <c r="K111" s="23" t="inlineStr">
-        <is>
-          <t>(sem orçamento nesta base)</t>
+      <c r="K111" s="31" t="inlineStr">
+        <is>
+          <t>R$ 0 — DESCONSIDERADO (melhoria de aterramento)</t>
         </is>
       </c>
       <c r="L111" s="23" t="inlineStr">
         <is>
-          <t>Atendimento da RDU Marianópolis e clientes rurais</t>
+          <t>Atendimento da RDU Sucupira e clientes rurais</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="57" t="inlineStr">
         <is>
-          <t>7927713200</t>
+          <t>5851753086</t>
         </is>
       </c>
       <c r="B112" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C112" s="58" t="inlineStr">
         <is>
-          <t>Sao Salvador Do Tocantins</t>
+          <t>Marianopolis</t>
         </is>
       </c>
       <c r="D112" s="58" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Divinopolis</t>
         </is>
       </c>
       <c r="E112" s="58" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="F112" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00960/2026</t>
+          <t>ETO-TELE 00881/2026</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
         <is>
-          <t>Tanque</t>
+          <t>Relé + Comunicação/rádio + Aterramento (da descrição da SS)</t>
         </is>
       </c>
       <c r="H112" s="57" t="inlineStr">
@@ -13267,7 +13291,7 @@
         </is>
       </c>
       <c r="I112" s="57" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J112" s="54" t="inlineStr">
         <is>
@@ -13281,29 +13305,29 @@
       </c>
       <c r="L112" s="23" t="inlineStr">
         <is>
-          <t>Transferência do Ramal do Retiro (246UCs), fonte principal by-passado</t>
+          <t>Atendimento da RDU Marianópolis e clientes rurais</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="57" t="inlineStr">
         <is>
-          <t>5856156091</t>
+          <t>7927713200</t>
         </is>
       </c>
       <c r="B113" s="57" t="inlineStr">
         <is>
-          <t>RT (58)</t>
+          <t>RL (79)</t>
         </is>
       </c>
       <c r="C113" s="58" t="inlineStr">
         <is>
-          <t>Almas</t>
+          <t>Sao Salvador Do Tocantins</t>
         </is>
       </c>
       <c r="D113" s="58" t="inlineStr">
         <is>
-          <t>Dianopolis</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="E113" s="58" t="inlineStr">
@@ -13313,21 +13337,21 @@
       </c>
       <c r="F113" s="58" t="inlineStr">
         <is>
-          <t>ETO-RD-DP 00403/2026</t>
+          <t>ETO-TELE 00960/2026</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
         <is>
-          <t>Comissionar</t>
+          <t>Tanque</t>
         </is>
       </c>
       <c r="H113" s="57" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I113" s="57" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J113" s="54" t="inlineStr">
         <is>
@@ -13341,24 +13365,24 @@
       </c>
       <c r="L113" s="23" t="inlineStr">
         <is>
-          <t>Equipamento novo furtado antes de ser colocado em operação</t>
+          <t>Transferência do Ramal do Retiro (246UCs), fonte principal by-passado</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="57" t="inlineStr">
         <is>
-          <t>7908708116</t>
+          <t>5856156091</t>
         </is>
       </c>
       <c r="B114" s="57" t="inlineStr">
         <is>
-          <t>RL (79)</t>
+          <t>RT (58)</t>
         </is>
       </c>
       <c r="C114" s="58" t="inlineStr">
         <is>
-          <t>Chapada Da Natividade</t>
+          <t>Almas</t>
         </is>
       </c>
       <c r="D114" s="58" t="inlineStr">
@@ -13373,12 +13397,12 @@
       </c>
       <c r="F114" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00959/2026</t>
+          <t>ETO-RD-DP 00403/2026</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
         <is>
-          <t>Tanque e controle</t>
+          <t>Comissionar</t>
         </is>
       </c>
       <c r="H114" s="57" t="inlineStr">
@@ -13387,7 +13411,7 @@
         </is>
       </c>
       <c r="I114" s="57" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J114" s="54" t="inlineStr">
         <is>
@@ -13401,14 +13425,14 @@
       </c>
       <c r="L114" s="23" t="inlineStr">
         <is>
-          <t>Atendimento do PA Xobo (194 UCs)</t>
+          <t>Equipamento novo furtado antes de ser colocado em operação</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="57" t="inlineStr">
         <is>
-          <t>7921202014</t>
+          <t>7908708116</t>
         </is>
       </c>
       <c r="B115" s="57" t="inlineStr">
@@ -13418,27 +13442,27 @@
       </c>
       <c r="C115" s="58" t="inlineStr">
         <is>
-          <t>Pium</t>
+          <t>Chapada Da Natividade</t>
         </is>
       </c>
       <c r="D115" s="58" t="inlineStr">
         <is>
-          <t>Paraiso Do Tocantins</t>
+          <t>Dianopolis</t>
         </is>
       </c>
       <c r="E115" s="58" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sul</t>
         </is>
       </c>
       <c r="F115" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00972/2026</t>
+          <t>ETO-TELE 00959/2026</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
         <is>
-          <t>Tanque/parte ativa + Relé + Aterramento (da descrição da SS)</t>
+          <t>Tanque e controle</t>
         </is>
       </c>
       <c r="H115" s="57" t="inlineStr">
@@ -13447,7 +13471,7 @@
         </is>
       </c>
       <c r="I115" s="57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J115" s="54" t="inlineStr">
         <is>
@@ -13461,14 +13485,14 @@
       </c>
       <c r="L115" s="23" t="inlineStr">
         <is>
-          <t>Atendimento de Clientes rurais (483 UCs)</t>
+          <t>Atendimento do PA Xobo (194 UCs)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="57" t="inlineStr">
         <is>
-          <t>7938137007</t>
+          <t>7921202014</t>
         </is>
       </c>
       <c r="B116" s="57" t="inlineStr">
@@ -13478,12 +13502,12 @@
       </c>
       <c r="C116" s="58" t="inlineStr">
         <is>
-          <t>Miracema Do Tocantins</t>
+          <t>Pium</t>
         </is>
       </c>
       <c r="D116" s="58" t="inlineStr">
         <is>
-          <t>Miracema Do Tocantins</t>
+          <t>Paraiso Do Tocantins</t>
         </is>
       </c>
       <c r="E116" s="58" t="inlineStr">
@@ -13493,12 +13517,12 @@
       </c>
       <c r="F116" s="58" t="inlineStr">
         <is>
-          <t>ETO-TELE 00888/2026</t>
+          <t>ETO-TELE 00972/2026</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
         <is>
-          <t>bateria, rádio, trafo (entender sobre bucha da fase A)</t>
+          <t>Tanque/parte ativa + Relé + Aterramento (da descrição da SS)</t>
         </is>
       </c>
       <c r="H116" s="57" t="inlineStr">
@@ -13507,19 +13531,21 @@
         </is>
       </c>
       <c r="I116" s="57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J116" s="54" t="inlineStr">
         <is>
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
-      <c r="K116" s="24" t="n">
-        <v>25629.02</v>
+      <c r="K116" s="23" t="inlineStr">
+        <is>
+          <t>(sem orçamento nesta base)</t>
+        </is>
       </c>
       <c r="L116" s="23" t="inlineStr">
         <is>
-          <t>Transferência do Irmã Adelaide (470 UCs)</t>
+          <t>Atendimento de Clientes rurais (483 UCs)</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18317,7 @@
       </c>
       <c r="M9" s="23" t="inlineStr">
         <is>
-          <t>Obras cita SS 00180/2025 — adotada a mais recente (00127/2026); EMD 514635</t>
+          <t>PRINT SGM 08/07 (SS 00127/2026): PARECER COEP = EQUIPAMENTO EM PROCESSO DE LOGÍSTICA — confirmado SÓ CONTROLE; obras citavam SS 00180/2025 (adotada a mais recente); EMD 514635</t>
         </is>
       </c>
       <c r="N9" s="25" t="n">

--- a/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
+++ b/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
@@ -712,7 +712,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>⚠ DADOS CONGELADOS EM 07/07/2026 (D-1) — bases: SS pendentes posto COEP, OBRAS_EQ_ESPECIAL e ETO ATUALIZADA v10.</t>
+          <t>⚠ DADOS CONGELADOS EM 07/07/2026 (D-1) — bases: SS pendentes posto COEP, OBRAS_EQ_ESPECIAL e ETO ATUALIZADA v10. Exceção: SS 00131/2026 (7947203070), aberta em 08/07, incluída por instrução do gestor.</t>
         </is>
       </c>
     </row>
@@ -786,16 +786,16 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>2188151.77</v>
+        <v>2264397.97</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>592337.78</v>
+        <v>605547.12</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>2780489.55</v>
+        <v>2869945.09</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>4477002.739999999</v>
+        <v>4553248.939999999</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>1418008.56</v>
+        <v>1431217.9</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>5895011.3</v>
+        <v>5984466.84</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="H13" s="11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>18</v>
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1208112.37</v>
+        <v>1284358.57</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>321463.9000000001</v>
+        <v>334673.2400000001</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1529576.27</v>
+        <v>1619031.81</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="B18" s="19" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2188151.77</v>
+        <v>2264397.97</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>592337.7800000001</v>
+        <v>605547.1200000001</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>2780489.55</v>
+        <v>2869945.09</v>
       </c>
     </row>
     <row r="20">
@@ -1187,16 +1187,16 @@
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1187671.95</v>
+        <v>1263918.15</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>211404.38</v>
+        <v>224613.72</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1399076.33</v>
+        <v>1488531.87</v>
       </c>
     </row>
     <row r="26">
@@ -1244,16 +1244,16 @@
         </is>
       </c>
       <c r="B28" s="19" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C28" s="8" t="n">
-        <v>2188151.77</v>
+        <v>2264397.97</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>592337.7799999999</v>
+        <v>605547.1199999999</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>2780489.549999999</v>
+        <v>2869945.09</v>
       </c>
     </row>
     <row r="30">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -5926,16 +5926,16 @@
         </is>
       </c>
       <c r="B6" s="55" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" s="55" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>2780489.550000001</v>
+        <v>2869945.090000001</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>59159.35212765959</v>
+        <v>59790.52270833335</v>
       </c>
     </row>
     <row r="7">
@@ -5983,13 +5983,13 @@
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>5895011.300000001</v>
+        <v>5984466.840000001</v>
       </c>
       <c r="E9" s="17" t="n"/>
     </row>
@@ -12758,10 +12758,8 @@
           <t>Pendente (fora do posto)</t>
         </is>
       </c>
-      <c r="K103" s="23" t="inlineStr">
-        <is>
-          <t>(sem orçamento nesta base)</t>
-        </is>
+      <c r="K103" s="24" t="n">
+        <v>89455.53999999999</v>
       </c>
       <c r="L103" s="23" t="inlineStr">
         <is>
@@ -14400,7 +14398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -16950,27 +16948,27 @@
     <row r="41">
       <c r="A41" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00177/2025</t>
+          <t>ETO-COEP 00131/2026</t>
         </is>
       </c>
       <c r="B41" s="57" t="inlineStr">
         <is>
-          <t>7908705049</t>
+          <t>7947203070</t>
         </is>
       </c>
       <c r="C41" s="58" t="inlineStr">
         <is>
-          <t>Aurora do Tocantins</t>
+          <t>Rio Sono</t>
         </is>
       </c>
       <c r="D41" s="57" t="inlineStr">
         <is>
-          <t>COOPER F6</t>
+          <t>TAVRIDA</t>
         </is>
       </c>
       <c r="E41" s="57" t="inlineStr">
         <is>
-          <t>13,8</t>
+          <t>34,5</t>
         </is>
       </c>
       <c r="F41" s="58" t="inlineStr">
@@ -16980,58 +16978,58 @@
       </c>
       <c r="G41" s="23" t="inlineStr">
         <is>
-          <t>Religador completo</t>
+          <t>Religador completo (parte ativa + tanque) — decisão COEP 08/07</t>
         </is>
       </c>
       <c r="H41" s="24" t="n">
-        <v>55602.54</v>
+        <v>76246.2</v>
       </c>
       <c r="I41" s="24" t="n">
-        <v>11016.94</v>
+        <v>13209.34</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>Fora da base de pendentes; EMD 511536, prev. 15/07</t>
+          <t>SS ABERTA EM 08/07 (após o congelamento de 07/07) — incluída por instrução do gestor. DMSL sem atualização de modelo/placa =&gt; compra do completo; COEP pergunta modelo da placa/código do material; TAVRIDA (Ajustes) sem sobressalente; ocorrência de 23/11/2025</t>
         </is>
       </c>
       <c r="K41" s="25" t="n">
-        <v>66619.48</v>
-      </c>
-      <c r="L41" s="26" t="inlineStr">
-        <is>
-          <t>Em execução (obra)</t>
+        <v>89455.53999999999</v>
+      </c>
+      <c r="L41" s="57" t="inlineStr">
+        <is>
+          <t>Só selecionado para Compra</t>
         </is>
       </c>
       <c r="M41" s="57" t="inlineStr">
         <is>
-          <t>0512600135</t>
-        </is>
-      </c>
-      <c r="N41" s="27" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="28" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00082/2026</t>
+          <t>ETO-COEP 00177/2025</t>
         </is>
       </c>
       <c r="B42" s="57" t="inlineStr">
         <is>
-          <t>7933766059</t>
+          <t>7908705049</t>
         </is>
       </c>
       <c r="C42" s="58" t="inlineStr">
         <is>
-          <t>Taquaralto</t>
+          <t>Aurora do Tocantins</t>
         </is>
       </c>
       <c r="D42" s="57" t="inlineStr">
         <is>
-          <t>NOJA RC10</t>
+          <t>COOPER F6</t>
         </is>
       </c>
       <c r="E42" s="57" t="inlineStr">
@@ -17041,168 +17039,168 @@
       </c>
       <c r="F42" s="58" t="inlineStr">
         <is>
-          <t>Parte ativa (Tanque)</t>
+          <t>Equipamento completo</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>Tanque (parte ativa)</t>
+          <t>Religador completo</t>
         </is>
       </c>
       <c r="H42" s="24" t="n">
-        <v>21785.72</v>
+        <v>55602.54</v>
       </c>
       <c r="I42" s="24" t="n">
         <v>11016.94</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
+          <t>Fora da base de pendentes; EMD 511536, prev. 15/07</t>
+        </is>
+      </c>
+      <c r="K42" s="25" t="n">
+        <v>66619.48</v>
+      </c>
+      <c r="L42" s="26" t="inlineStr">
+        <is>
+          <t>Em execução (obra)</t>
+        </is>
+      </c>
+      <c r="M42" s="57" t="inlineStr">
+        <is>
+          <t>0512600135</t>
+        </is>
+      </c>
+      <c r="N42" s="27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="58" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00082/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="57" t="inlineStr">
+        <is>
+          <t>7933766059</t>
+        </is>
+      </c>
+      <c r="C43" s="58" t="inlineStr">
+        <is>
+          <t>Taquaralto</t>
+        </is>
+      </c>
+      <c r="D43" s="57" t="inlineStr">
+        <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E43" s="57" t="inlineStr">
+        <is>
+          <t>13,8</t>
+        </is>
+      </c>
+      <c r="F43" s="58" t="inlineStr">
+        <is>
+          <t>Parte ativa (Tanque)</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>Tanque (parte ativa)</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>21785.72</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>11016.94</v>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
           <t>Obras cita SS 00211/2025 — adotada a mais recente (00082/2026); entrega concluída, substituição pendente</t>
         </is>
       </c>
-      <c r="K42" s="25" t="n">
+      <c r="K43" s="25" t="n">
         <v>32802.66</v>
       </c>
-      <c r="L42" s="26" t="inlineStr">
+      <c r="L43" s="26" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M42" s="57" t="inlineStr">
+      <c r="M43" s="57" t="inlineStr">
         <is>
           <t>0112600424</t>
         </is>
       </c>
-      <c r="N42" s="27" t="inlineStr">
+      <c r="N43" s="27" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="46" t="inlineStr">
         <is>
           <t>ETO-COEP 00036/2026</t>
         </is>
       </c>
-      <c r="B43" s="45" t="inlineStr">
+      <c r="B44" s="45" t="inlineStr">
         <is>
           <t>7927169001</t>
         </is>
       </c>
-      <c r="C43" s="46" t="inlineStr">
+      <c r="C44" s="46" t="inlineStr">
         <is>
           <t>Porto Nacional</t>
         </is>
       </c>
-      <c r="D43" s="45" t="inlineStr">
+      <c r="D44" s="45" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E43" s="45" t="inlineStr">
+      <c r="E44" s="45" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F43" s="46" t="inlineStr">
+      <c r="F44" s="46" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G43" s="31" t="inlineStr">
+      <c r="G44" s="31" t="inlineStr">
         <is>
           <t>Religador completo — EM DÚVIDA (obras=completo x v1.5=tanque)</t>
         </is>
       </c>
-      <c r="H43" s="32" t="n">
+      <c r="H44" s="32" t="n">
         <v>55602.54</v>
       </c>
-      <c r="I43" s="32" t="n">
+      <c r="I44" s="32" t="n">
         <v>11016.94</v>
       </c>
-      <c r="J43" s="31" t="inlineStr">
+      <c r="J44" s="31" t="inlineStr">
         <is>
           <t>EM DÚVIDA =&gt; assumido EQUIPAMENTO COMPLETO (padrão do gestor). Modelo NOJA RC10 nos Ajustes (há peças) — AVALIAR na aba VERIFICAR</t>
         </is>
       </c>
-      <c r="K43" s="33" t="n">
+      <c r="K44" s="33" t="n">
         <v>66619.48</v>
       </c>
-      <c r="L43" s="45" t="inlineStr">
+      <c r="L44" s="45" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M43" s="45" t="inlineStr">
+      <c r="M44" s="45" t="inlineStr">
         <is>
           <t>0112600425</t>
-        </is>
-      </c>
-      <c r="N43" s="28" t="inlineStr">
-        <is>
-          <t>VERIFICAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="58" t="inlineStr">
-        <is>
-          <t>ETO-COEP 00085/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="57" t="inlineStr">
-        <is>
-          <t>7938137007</t>
-        </is>
-      </c>
-      <c r="C44" s="58" t="inlineStr">
-        <is>
-          <t>Miracema do Tocantins</t>
-        </is>
-      </c>
-      <c r="D44" s="57" t="inlineStr">
-        <is>
-          <t>SCHNEIDER ADVC</t>
-        </is>
-      </c>
-      <c r="E44" s="57" t="inlineStr">
-        <is>
-          <t>13,8</t>
-        </is>
-      </c>
-      <c r="F44" s="58" t="inlineStr">
-        <is>
-          <t>Componentes/Acessórios</t>
-        </is>
-      </c>
-      <c r="G44" s="23" t="inlineStr">
-        <is>
-          <t>Bateria + rádio + trafo/bucha fase A</t>
-        </is>
-      </c>
-      <c r="H44" s="24" t="n">
-        <v>14612.08</v>
-      </c>
-      <c r="I44" s="24" t="n">
-        <v>11016.94</v>
-      </c>
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>Obras cita SS 00034/2026 — adotada a mais detalhada (00085/2026); rádio será testado/reaproveitado; 'entender sobre bucha da fase A'</t>
-        </is>
-      </c>
-      <c r="K44" s="25" t="n">
-        <v>25629.02</v>
-      </c>
-      <c r="L44" s="26" t="inlineStr">
-        <is>
-          <t>Em execução (obra)</t>
-        </is>
-      </c>
-      <c r="M44" s="57" t="inlineStr">
-        <is>
-          <t>0212600423</t>
         </is>
       </c>
       <c r="N44" s="28" t="inlineStr">
@@ -17214,52 +17212,52 @@
     <row r="45">
       <c r="A45" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00106/2025</t>
+          <t>ETO-COEP 00085/2026</t>
         </is>
       </c>
       <c r="B45" s="57" t="inlineStr">
         <is>
-          <t>7900230155</t>
+          <t>7938137007</t>
         </is>
       </c>
       <c r="C45" s="58" t="inlineStr">
         <is>
-          <t>Palmeirante</t>
+          <t>Miracema do Tocantins</t>
         </is>
       </c>
       <c r="D45" s="57" t="inlineStr">
         <is>
-          <t>COOPER F6</t>
+          <t>SCHNEIDER ADVC</t>
         </is>
       </c>
       <c r="E45" s="57" t="inlineStr">
         <is>
-          <t>34,5</t>
+          <t>13,8</t>
         </is>
       </c>
       <c r="F45" s="58" t="inlineStr">
         <is>
-          <t>Equipamento completo</t>
+          <t>Componentes/Acessórios</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>Tanque + controle NOJA enviado 07/07</t>
+          <t>Bateria + rádio + trafo/bucha fase A</t>
         </is>
       </c>
       <c r="H45" s="24" t="n">
-        <v>76246.2</v>
+        <v>14612.08</v>
       </c>
       <c r="I45" s="24" t="n">
-        <v>13209.34</v>
+        <v>11016.94</v>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>v1.5 (SS 00056/2025 — mesmo ano, adotada a mais recente 00106/2025) considerava só tanque; controle NOJA também enviado — custo de completo. Concluída parcialmente</t>
+          <t>Obras cita SS 00034/2026 — adotada a mais detalhada (00085/2026); rádio será testado/reaproveitado; 'entender sobre bucha da fase A'</t>
         </is>
       </c>
       <c r="K45" s="25" t="n">
-        <v>89455.53999999999</v>
+        <v>25629.02</v>
       </c>
       <c r="L45" s="26" t="inlineStr">
         <is>
@@ -17268,7 +17266,7 @@
       </c>
       <c r="M45" s="57" t="inlineStr">
         <is>
-          <t>0712600318</t>
+          <t>0212600423</t>
         </is>
       </c>
       <c r="N45" s="28" t="inlineStr">
@@ -17280,22 +17278,22 @@
     <row r="46">
       <c r="A46" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00181/2025</t>
+          <t>ETO-COEP 00106/2025</t>
         </is>
       </c>
       <c r="B46" s="57" t="inlineStr">
         <is>
-          <t>7943790134</t>
+          <t>7900230155</t>
         </is>
       </c>
       <c r="C46" s="58" t="inlineStr">
         <is>
-          <t>Esperantina</t>
+          <t>Palmeirante</t>
         </is>
       </c>
       <c r="D46" s="57" t="inlineStr">
         <is>
-          <t>NOJA RC10</t>
+          <t>COOPER F6</t>
         </is>
       </c>
       <c r="E46" s="57" t="inlineStr">
@@ -17305,58 +17303,58 @@
       </c>
       <c r="F46" s="58" t="inlineStr">
         <is>
-          <t>Parte ativa (Tanque)</t>
+          <t>Equipamento completo</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
-          <t>Tanque (parte ativa)</t>
+          <t>Tanque + controle NOJA enviado 07/07</t>
         </is>
       </c>
       <c r="H46" s="24" t="n">
-        <v>38151.48</v>
+        <v>76246.2</v>
       </c>
       <c r="I46" s="24" t="n">
         <v>13209.34</v>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>CONCLUÍDA 06/06; obras: posto COEP 'Verificar' — confirmar baixa</t>
+          <t>v1.5 (SS 00056/2025 — mesmo ano, adotada a mais recente 00106/2025) considerava só tanque; controle NOJA também enviado — custo de completo. Concluída parcialmente</t>
         </is>
       </c>
       <c r="K46" s="25" t="n">
-        <v>51360.82000000001</v>
-      </c>
-      <c r="L46" s="57" t="inlineStr">
-        <is>
-          <t>Concluído</t>
+        <v>89455.53999999999</v>
+      </c>
+      <c r="L46" s="26" t="inlineStr">
+        <is>
+          <t>Em execução (obra)</t>
         </is>
       </c>
       <c r="M46" s="57" t="inlineStr">
         <is>
-          <t>0662600266</t>
-        </is>
-      </c>
-      <c r="N46" s="27" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>0712600318</t>
+        </is>
+      </c>
+      <c r="N46" s="28" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00178/2025</t>
+          <t>ETO-COEP 00181/2025</t>
         </is>
       </c>
       <c r="B47" s="57" t="inlineStr">
         <is>
-          <t>7900018004</t>
+          <t>7943790134</t>
         </is>
       </c>
       <c r="C47" s="58" t="inlineStr">
         <is>
-          <t>Araguaína</t>
+          <t>Esperantina</t>
         </is>
       </c>
       <c r="D47" s="57" t="inlineStr">
@@ -17371,27 +17369,27 @@
       </c>
       <c r="F47" s="58" t="inlineStr">
         <is>
-          <t>Equipamento completo</t>
+          <t>Parte ativa (Tanque)</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>Religador completo (Cooper→NOJA)</t>
+          <t>Tanque (parte ativa)</t>
         </is>
       </c>
       <c r="H47" s="24" t="n">
-        <v>76246.2</v>
+        <v>38151.48</v>
       </c>
       <c r="I47" s="24" t="n">
         <v>13209.34</v>
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>CONCLUÍDA 27/05; tanque cooper retirado será usado no 7903112004</t>
+          <t>CONCLUÍDA 06/06; obras: posto COEP 'Verificar' — confirmar baixa</t>
         </is>
       </c>
       <c r="K47" s="25" t="n">
-        <v>89455.53999999999</v>
+        <v>51360.82000000001</v>
       </c>
       <c r="L47" s="57" t="inlineStr">
         <is>
@@ -17400,7 +17398,7 @@
       </c>
       <c r="M47" s="57" t="inlineStr">
         <is>
-          <t>0612600439</t>
+          <t>0662600266</t>
         </is>
       </c>
       <c r="N47" s="27" t="inlineStr">
@@ -17412,17 +17410,17 @@
     <row r="48">
       <c r="A48" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00083/2026</t>
+          <t>ETO-COEP 00178/2025</t>
         </is>
       </c>
       <c r="B48" s="57" t="inlineStr">
         <is>
-          <t>7931610122</t>
+          <t>7900018004</t>
         </is>
       </c>
       <c r="C48" s="58" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Araguaína</t>
         </is>
       </c>
       <c r="D48" s="57" t="inlineStr">
@@ -17432,41 +17430,41 @@
       </c>
       <c r="E48" s="57" t="inlineStr">
         <is>
-          <t>13,8</t>
+          <t>34,5</t>
         </is>
       </c>
       <c r="F48" s="58" t="inlineStr">
         <is>
-          <t>Parte ativa (Tanque)</t>
+          <t>Equipamento completo</t>
         </is>
       </c>
       <c r="G48" s="23" t="inlineStr">
         <is>
-          <t>Tanque + antena</t>
+          <t>Religador completo (Cooper→NOJA)</t>
         </is>
       </c>
       <c r="H48" s="24" t="n">
-        <v>21785.72</v>
+        <v>76246.2</v>
       </c>
       <c r="I48" s="24" t="n">
-        <v>11016.94</v>
+        <v>13209.34</v>
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>Obras cita SS 00206/2025 — adotada a mais recente (00083/2026); substituição prev. 09/07</t>
+          <t>CONCLUÍDA 27/05; tanque cooper retirado será usado no 7903112004</t>
         </is>
       </c>
       <c r="K48" s="25" t="n">
-        <v>32802.66</v>
-      </c>
-      <c r="L48" s="26" t="inlineStr">
-        <is>
-          <t>Em execução (obra)</t>
+        <v>89455.53999999999</v>
+      </c>
+      <c r="L48" s="57" t="inlineStr">
+        <is>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="M48" s="57" t="inlineStr">
         <is>
-          <t>0112600383</t>
+          <t>0612600439</t>
         </is>
       </c>
       <c r="N48" s="27" t="inlineStr">
@@ -17478,17 +17476,17 @@
     <row r="49">
       <c r="A49" s="58" t="inlineStr">
         <is>
-          <t>ETO-COEP 00081/2026</t>
+          <t>ETO-COEP 00083/2026</t>
         </is>
       </c>
       <c r="B49" s="57" t="inlineStr">
         <is>
-          <t>7957620015</t>
+          <t>7931610122</t>
         </is>
       </c>
       <c r="C49" s="58" t="inlineStr">
         <is>
-          <t>Pedro Afonso</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D49" s="57" t="inlineStr">
@@ -17503,256 +17501,322 @@
       </c>
       <c r="F49" s="58" t="inlineStr">
         <is>
-          <t>Controle completo</t>
+          <t>Parte ativa (Tanque)</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
         <is>
-          <t>Rádio + antena + controle</t>
+          <t>Tanque + antena</t>
         </is>
       </c>
       <c r="H49" s="24" t="n">
-        <v>33816.82</v>
+        <v>21785.72</v>
       </c>
       <c r="I49" s="24" t="n">
         <v>11016.94</v>
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
+          <t>Obras cita SS 00206/2025 — adotada a mais recente (00083/2026); substituição prev. 09/07</t>
+        </is>
+      </c>
+      <c r="K49" s="25" t="n">
+        <v>32802.66</v>
+      </c>
+      <c r="L49" s="26" t="inlineStr">
+        <is>
+          <t>Em execução (obra)</t>
+        </is>
+      </c>
+      <c r="M49" s="57" t="inlineStr">
+        <is>
+          <t>0112600383</t>
+        </is>
+      </c>
+      <c r="N49" s="27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="58" t="inlineStr">
+        <is>
+          <t>ETO-COEP 00081/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="57" t="inlineStr">
+        <is>
+          <t>7957620015</t>
+        </is>
+      </c>
+      <c r="C50" s="58" t="inlineStr">
+        <is>
+          <t>Pedro Afonso</t>
+        </is>
+      </c>
+      <c r="D50" s="57" t="inlineStr">
+        <is>
+          <t>NOJA RC10</t>
+        </is>
+      </c>
+      <c r="E50" s="57" t="inlineStr">
+        <is>
+          <t>13,8</t>
+        </is>
+      </c>
+      <c r="F50" s="58" t="inlineStr">
+        <is>
+          <t>Controle completo</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>Rádio + antena + controle</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="n">
+        <v>33816.82</v>
+      </c>
+      <c r="I50" s="24" t="n">
+        <v>11016.94</v>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
           <t>Obras cita SS 00104/2025 — adotada a mais recente (00081/2026); CONCLUÍDA (22/05)</t>
         </is>
       </c>
-      <c r="K49" s="25" t="n">
+      <c r="K50" s="25" t="n">
         <v>44833.76</v>
       </c>
-      <c r="L49" s="57" t="inlineStr">
+      <c r="L50" s="57" t="inlineStr">
         <is>
           <t>Concluído</t>
         </is>
       </c>
-      <c r="M49" s="57" t="inlineStr">
+      <c r="M50" s="57" t="inlineStr">
         <is>
           <t>0712600316</t>
         </is>
       </c>
-      <c r="N49" s="27" t="inlineStr">
+      <c r="N50" s="27" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="46" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="46" t="inlineStr">
         <is>
           <t>ETO-COEP 00094/2025</t>
         </is>
       </c>
-      <c r="B50" s="45" t="inlineStr">
+      <c r="B51" s="45" t="inlineStr">
         <is>
           <t>7934698002</t>
         </is>
       </c>
-      <c r="C50" s="46" t="inlineStr">
+      <c r="C51" s="46" t="inlineStr">
         <is>
           <t>Tocantinópolis</t>
         </is>
       </c>
-      <c r="D50" s="45" t="inlineStr">
+      <c r="D51" s="45" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E50" s="45" t="inlineStr">
+      <c r="E51" s="45" t="inlineStr">
         <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="F50" s="46" t="inlineStr">
+      <c r="F51" s="46" t="inlineStr">
         <is>
           <t>Equipamento completo</t>
         </is>
       </c>
-      <c r="G50" s="31" t="inlineStr">
+      <c r="G51" s="31" t="inlineStr">
         <is>
           <t>Religador completo — EM DÚVIDA (obras=completo x v1.5=controle)</t>
         </is>
       </c>
-      <c r="H50" s="32" t="n">
+      <c r="H51" s="32" t="n">
         <v>55602.54</v>
       </c>
-      <c r="I50" s="32" t="n">
+      <c r="I51" s="32" t="n">
         <v>11016.94</v>
       </c>
-      <c r="J50" s="31" t="inlineStr">
+      <c r="J51" s="31" t="inlineStr">
         <is>
           <t>EM DÚVIDA =&gt; assumido EQUIPAMENTO COMPLETO (padrão do gestor). CONCLUÍDA 30/05 — confirmar o que foi aplicado; posto COEP 'Verificar'</t>
         </is>
       </c>
-      <c r="K50" s="33" t="n">
+      <c r="K51" s="33" t="n">
         <v>66619.48</v>
       </c>
-      <c r="L50" s="45" t="inlineStr">
+      <c r="L51" s="45" t="inlineStr">
         <is>
           <t>Concluído</t>
         </is>
       </c>
-      <c r="M50" s="45" t="inlineStr">
+      <c r="M51" s="45" t="inlineStr">
         <is>
           <t>0662600265</t>
         </is>
       </c>
-      <c r="N50" s="28" t="inlineStr">
+      <c r="N51" s="28" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="58" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="58" t="inlineStr">
         <is>
           <t>ETO-COEP 00151/2026</t>
         </is>
       </c>
-      <c r="B51" s="57" t="inlineStr">
+      <c r="B52" s="57" t="inlineStr">
         <is>
           <t>7955520116</t>
         </is>
       </c>
-      <c r="C51" s="58" t="inlineStr">
+      <c r="C52" s="58" t="inlineStr">
         <is>
           <t>Chapada da Natividade</t>
         </is>
       </c>
-      <c r="D51" s="57" t="inlineStr">
+      <c r="D52" s="57" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E51" s="57" t="inlineStr">
+      <c r="E52" s="57" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F51" s="58" t="inlineStr">
+      <c r="F52" s="58" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G51" s="23" t="inlineStr">
+      <c r="G52" s="23" t="inlineStr">
         <is>
           <t>Tanque (parte ativa)</t>
         </is>
       </c>
-      <c r="H51" s="24" t="n">
+      <c r="H52" s="24" t="n">
         <v>38151.48</v>
       </c>
-      <c r="I51" s="24" t="n">
+      <c r="I52" s="24" t="n">
         <v>13209.34</v>
       </c>
-      <c r="J51" s="23" t="inlineStr">
+      <c r="J52" s="23" t="inlineStr">
         <is>
           <t>v1.5 cita SS 00149/2025 — adotada a mais recente (00151/2026); Requisitar=Não; EMD/entrega 'João verificar'</t>
         </is>
       </c>
-      <c r="K51" s="25" t="n">
+      <c r="K52" s="25" t="n">
         <v>51360.82000000001</v>
       </c>
-      <c r="L51" s="26" t="inlineStr">
+      <c r="L52" s="26" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M51" s="57" t="inlineStr">
+      <c r="M52" s="57" t="inlineStr">
         <is>
           <t>0512600178</t>
         </is>
       </c>
-      <c r="N51" s="28" t="inlineStr">
+      <c r="N52" s="28" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="34" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="34" t="inlineStr">
         <is>
           <t>ETO-COEP 00108/2026</t>
         </is>
       </c>
-      <c r="B52" s="35" t="inlineStr">
+      <c r="B53" s="35" t="inlineStr">
         <is>
           <t>7933726256</t>
         </is>
       </c>
-      <c r="C52" s="34" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
         <is>
           <t>Mateiros</t>
         </is>
       </c>
-      <c r="D52" s="35" t="inlineStr">
+      <c r="D53" s="35" t="inlineStr">
         <is>
           <t>NOJA RC10</t>
         </is>
       </c>
-      <c r="E52" s="35" t="inlineStr">
+      <c r="E53" s="35" t="inlineStr">
         <is>
           <t>34,5</t>
         </is>
       </c>
-      <c r="F52" s="34" t="inlineStr">
+      <c r="F53" s="34" t="inlineStr">
         <is>
           <t>Parte ativa (Tanque)</t>
         </is>
       </c>
-      <c r="G52" s="36" t="inlineStr">
+      <c r="G53" s="36" t="inlineStr">
         <is>
           <t>Tanque REAPROVEITADO (redirecionado de Santa Rita/7900453110)</t>
         </is>
       </c>
-      <c r="H52" s="37" t="n">
+      <c r="H53" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="37" t="n">
+      <c r="I53" s="37" t="n">
         <v>13209.34</v>
       </c>
-      <c r="J52" s="36" t="inlineStr">
+      <c r="J53" s="36" t="inlineStr">
         <is>
           <t>DISCUSSÃO COM MATHEUS ALVES — material R$ 0 (reaproveitamento); obras pede cancelar obra COCM</t>
         </is>
       </c>
-      <c r="K52" s="38" t="n">
+      <c r="K53" s="38" t="n">
         <v>13209.34</v>
       </c>
-      <c r="L52" s="35" t="inlineStr">
+      <c r="L53" s="35" t="inlineStr">
         <is>
           <t>Em execução (obra)</t>
         </is>
       </c>
-      <c r="M52" s="35" t="inlineStr">
+      <c r="M53" s="35" t="inlineStr">
         <is>
           <t>0312600351</t>
         </is>
       </c>
-      <c r="N52" s="28" t="inlineStr">
+      <c r="N53" s="28" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="G53" s="4" t="inlineStr">
+    <row r="54">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="H53" s="39" t="n">
-        <v>2188151.77</v>
-      </c>
-      <c r="I53" s="39" t="n">
-        <v>592337.78</v>
-      </c>
-      <c r="K53" s="39" t="n">
-        <v>2780489.55</v>
+      <c r="H54" s="39" t="n">
+        <v>2264397.97</v>
+      </c>
+      <c r="I54" s="39" t="n">
+        <v>605547.12</v>
+      </c>
+      <c r="K54" s="39" t="n">
+        <v>2869945.09</v>
       </c>
     </row>
   </sheetData>

--- a/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
+++ b/ORCAMENTO_EQ_ESPECIAIS_V2.xlsx
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="G25" s="23" t="inlineStr">
         <is>
-          <t>Relé prot. 50/51</t>
+          <t>Relé prot. 50/51 — MANDAR O RELÉ (decisão gestor 08/07)</t>
         </is>
       </c>
       <c r="H25" s="24" t="n">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>Modelo em campo ARTECHE P500 — confirmar compatibilidade; SS 00057/2026 (v1.5) é duplicata — adotada a mais recente</t>
+          <t>DECISÃO DO GESTOR 08/07 (print SGM, mesma SS 00124/2026): mandar o relé (cód 625510). Modelo em campo ARTECHE P500; SS 00057/2026 (v1.5) é duplicata — adotada a mais recente</t>
         </is>
       </c>
       <c r="K25" s="25" t="n">
@@ -15949,9 +15949,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N25" s="28" t="inlineStr">
-        <is>
-          <t>VERIFICAR</t>
+      <c r="N25" s="27" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
